--- a/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
+++ b/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-045-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="940" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32192243-D392-4995-9EDE-DE2C940EDF32}"/>
+  <xr:revisionPtr revIDLastSave="955" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{590C11B0-C3D5-4F79-948E-AEE74246ED14}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -1828,44 +1828,102 @@
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
+      <c r="J3" s="6">
+        <v>12.8</v>
+      </c>
+      <c r="K3" s="6">
+        <v>12.6</v>
+      </c>
+      <c r="L3" s="6">
+        <v>99.2</v>
+      </c>
+      <c r="M3" s="6">
+        <v>17.2</v>
+      </c>
+      <c r="N3" s="6">
+        <v>320</v>
+      </c>
+      <c r="O3" s="6">
+        <v>0.67</v>
+      </c>
+      <c r="P3" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>6.03</v>
+      </c>
       <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="6"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6"/>
-      <c r="AD3" s="16"/>
-      <c r="AE3" s="6"/>
-      <c r="AF3" s="6"/>
-      <c r="AG3" s="6"/>
+      <c r="S3" s="6">
+        <v>0.72</v>
+      </c>
+      <c r="T3" s="6">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="U3" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="V3" s="6">
+        <v>7.2160000000000002</v>
+      </c>
+      <c r="W3" s="6">
+        <v>64</v>
+      </c>
+      <c r="X3" s="6">
+        <v>34.4</v>
+      </c>
+      <c r="Y3" s="6">
+        <v>6.93</v>
+      </c>
+      <c r="Z3" s="6">
+        <v>112.2</v>
+      </c>
+      <c r="AA3" s="6">
+        <v>25.2</v>
+      </c>
+      <c r="AB3" s="6">
+        <v>56.1</v>
+      </c>
+      <c r="AC3" s="6">
+        <v>27.8</v>
+      </c>
+      <c r="AD3" s="16">
+        <v>7.2560000000000002</v>
+      </c>
+      <c r="AE3" s="6">
+        <v>299</v>
+      </c>
+      <c r="AF3" s="6">
+        <v>50.4</v>
+      </c>
+      <c r="AG3" s="6">
+        <v>7.09</v>
+      </c>
       <c r="AH3" s="40">
         <f>AF3/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI3" s="6"/>
-      <c r="AJ3" s="6"/>
-      <c r="AK3" s="44"/>
-      <c r="AL3" s="6"/>
+        <v>0.504</v>
+      </c>
+      <c r="AI3" s="6">
+        <v>34</v>
+      </c>
+      <c r="AJ3" s="6">
+        <v>2.88</v>
+      </c>
+      <c r="AK3" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="6">
+        <v>0</v>
+      </c>
       <c r="AM3" s="42">
         <f>BO3</f>
-        <v>4.6805555555555507E-3</v>
-      </c>
-      <c r="AN3" s="6"/>
-      <c r="AO3" s="6"/>
+        <v>4.6885555555555508E-3</v>
+      </c>
+      <c r="AN3" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="6">
+        <v>0</v>
+      </c>
       <c r="AP3" s="6"/>
       <c r="AQ3" s="40">
         <v>0</v>
@@ -1903,27 +1961,27 @@
       </c>
       <c r="BC3" s="8">
         <f>AY3*K3*BE3/1000</f>
-        <v>0</v>
+        <v>6.3801863999999996E-3</v>
       </c>
       <c r="BD3" s="9">
         <f t="shared" ref="BD3:BD66" si="0">BC3*24*60</f>
-        <v>0</v>
+        <v>9.187468415999998</v>
       </c>
       <c r="BE3" s="9">
         <f t="shared" ref="BE3:BE10" si="1">AU3+SUM(AJ3:AL3,AN3:AO3)-(AT3*(D3+1))</f>
-        <v>1685</v>
-      </c>
-      <c r="BF3" s="10" t="str">
+        <v>1687.88</v>
+      </c>
+      <c r="BF3" s="10">
         <f>IF(ISBLANK(AN3),"",IFERROR(AN3/BE3,0))</f>
-        <v/>
-      </c>
-      <c r="BG3" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="BG3" s="10">
         <f>IF(ISBLANK(AN3),"",AN3/AU3)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BH3" s="10">
         <f>AM3*24*60</f>
-        <v>6.7399999999999931</v>
+        <v>6.751519999999994</v>
       </c>
       <c r="BI3" s="10" t="str">
         <f>IF(B3="Python",AZ3*BE3/24/60,"")</f>
@@ -1931,7 +1989,7 @@
       </c>
       <c r="BJ3" s="10">
         <f>IF(B3="Julia",BA3*BE3/24/60,"")</f>
-        <v>4.6805555555555507E-3</v>
+        <v>4.6885555555555508E-3</v>
       </c>
       <c r="BK3" s="35" t="str">
         <f>IF(B3="No MPC", AY3*K3*BE3/1000,"")</f>
@@ -1943,19 +2001,19 @@
       </c>
       <c r="BM3" s="50">
         <f t="shared" ref="BM3" si="2">IF(B3="Julia",BB3*BE3,"")</f>
-        <v>1.685E-4</v>
+        <v>1.6878800000000001E-4</v>
       </c>
       <c r="BN3" s="27">
         <f>IF(BI3&lt;&gt;"",BI3/0.000385,IF(BJ3&lt;&gt;"",BJ3/0.000385,BK3/0.000385))</f>
-        <v>12.157287157287145</v>
+        <v>12.178066378066367</v>
       </c>
       <c r="BO3" s="37">
         <f>IF(BI3&lt;&gt;"",BI3,IF(BJ3&lt;&gt;"",BJ3,BK3))</f>
-        <v>4.6805555555555507E-3</v>
+        <v>4.6885555555555508E-3</v>
       </c>
       <c r="BP3" s="32">
         <f>IF(BL3&lt;&gt;"",BL3,BM3)</f>
-        <v>1.685E-4</v>
+        <v>1.6878800000000001E-4</v>
       </c>
     </row>
     <row r="4" spans="1:68" x14ac:dyDescent="0.3">
@@ -1977,44 +2035,102 @@
       </c>
       <c r="H4" s="44"/>
       <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
+      <c r="J4" s="44">
+        <v>12.1</v>
+      </c>
+      <c r="K4" s="44">
+        <v>11.9</v>
+      </c>
+      <c r="L4" s="44">
+        <v>97.9</v>
+      </c>
+      <c r="M4" s="44">
+        <v>16.7</v>
+      </c>
+      <c r="N4" s="44">
+        <v>323</v>
+      </c>
+      <c r="O4" s="44">
+        <v>0.64</v>
+      </c>
+      <c r="P4" s="44">
+        <v>0.61</v>
+      </c>
+      <c r="Q4" s="44">
+        <v>5.86</v>
+      </c>
       <c r="R4" s="44"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="44"/>
-      <c r="V4" s="44"/>
-      <c r="W4" s="44"/>
-      <c r="X4" s="44"/>
-      <c r="Y4" s="44"/>
-      <c r="Z4" s="44"/>
-      <c r="AA4" s="44"/>
-      <c r="AB4" s="44"/>
-      <c r="AC4" s="44"/>
-      <c r="AD4" s="17"/>
-      <c r="AE4" s="44"/>
-      <c r="AF4" s="44"/>
-      <c r="AG4" s="44"/>
+      <c r="S4" s="44">
+        <v>0.97</v>
+      </c>
+      <c r="T4" s="44">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="U4" s="44">
+        <v>1.02</v>
+      </c>
+      <c r="V4" s="44">
+        <v>7.2439999999999998</v>
+      </c>
+      <c r="W4" s="44">
+        <v>72.8</v>
+      </c>
+      <c r="X4" s="44">
+        <v>68.5</v>
+      </c>
+      <c r="Y4" s="44">
+        <v>6.59</v>
+      </c>
+      <c r="Z4" s="44">
+        <v>109.1</v>
+      </c>
+      <c r="AA4" s="44">
+        <v>30.7</v>
+      </c>
+      <c r="AB4" s="44">
+        <v>63.9</v>
+      </c>
+      <c r="AC4" s="44">
+        <v>55.9</v>
+      </c>
+      <c r="AD4" s="17">
+        <v>7.2850000000000001</v>
+      </c>
+      <c r="AE4" s="44">
+        <v>299</v>
+      </c>
+      <c r="AF4" s="44">
+        <v>49.6</v>
+      </c>
+      <c r="AG4" s="44">
+        <v>7.09</v>
+      </c>
       <c r="AH4" s="45">
         <f t="shared" ref="AH4" si="3">AF4/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI4" s="44"/>
-      <c r="AJ4" s="44"/>
-      <c r="AK4" s="44"/>
-      <c r="AL4" s="44"/>
+        <v>0.496</v>
+      </c>
+      <c r="AI4" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ4" s="44">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="AK4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="44">
+        <v>0</v>
+      </c>
       <c r="AM4" s="45">
         <f t="shared" ref="AM4" si="4">BO4</f>
-        <v>4.6805555555555507E-3</v>
-      </c>
-      <c r="AN4" s="44"/>
-      <c r="AO4" s="44"/>
+        <v>4.6923055555555511E-3</v>
+      </c>
+      <c r="AN4" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="44">
+        <v>0</v>
+      </c>
       <c r="AP4" s="44"/>
       <c r="AQ4" s="45">
         <v>0</v>
@@ -2052,27 +2168,27 @@
       </c>
       <c r="BC4" s="11">
         <f t="shared" ref="BC4" si="5">AY4*K4*BE4/1000</f>
-        <v>0</v>
+        <v>6.030551099999999E-3</v>
       </c>
       <c r="BD4" s="46">
         <f t="shared" ref="BD4" si="6">BC4*24*60</f>
-        <v>0</v>
+        <v>8.6839935839999978</v>
       </c>
       <c r="BE4" s="46">
         <f t="shared" si="1"/>
-        <v>1685</v>
-      </c>
-      <c r="BF4" s="47" t="str">
+        <v>1689.23</v>
+      </c>
+      <c r="BF4" s="47">
         <f t="shared" ref="BF4:BF67" si="7">IF(ISBLANK(AN4),"",IFERROR(AN4/BE4,0))</f>
-        <v/>
-      </c>
-      <c r="BG4" s="47" t="str">
+        <v>0</v>
+      </c>
+      <c r="BG4" s="47">
         <f t="shared" ref="BG4:BG67" si="8">IF(ISBLANK(AN4),"",AN4/AU4)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BH4" s="47">
         <f t="shared" ref="BH4" si="9">AM4*24*60</f>
-        <v>6.7399999999999931</v>
+        <v>6.7569199999999938</v>
       </c>
       <c r="BI4" s="47" t="str">
         <f t="shared" ref="BI4:BI67" si="10">IF(B4="Python",AZ4*BE4/24/60,"")</f>
@@ -2080,7 +2196,7 @@
       </c>
       <c r="BJ4" s="47">
         <f t="shared" ref="BJ4:BJ5" si="11">IF(B4="Julia",BA4*BE4/24/60,"")</f>
-        <v>4.6805555555555507E-3</v>
+        <v>4.6923055555555511E-3</v>
       </c>
       <c r="BK4" s="48" t="str">
         <f>IF(B4="No MPC", AY4*K4*BE4/1000,"")</f>
@@ -2092,19 +2208,19 @@
       </c>
       <c r="BM4" s="51">
         <f>IF(B4="Julia",BB4*BE4,"")</f>
-        <v>1.685E-4</v>
+        <v>1.68923E-4</v>
       </c>
       <c r="BN4" s="28">
         <f t="shared" ref="BN4" si="12">IF(BI4&lt;&gt;"",BI4/0.000385,IF(BJ4&lt;&gt;"",BJ4/0.000385,BK4/0.000385))</f>
-        <v>12.157287157287145</v>
+        <v>12.187806637806627</v>
       </c>
       <c r="BO4" s="49">
         <f t="shared" ref="BO4" si="13">IF(BI4&lt;&gt;"",BI4,IF(BJ4&lt;&gt;"",BJ4,BK4))</f>
-        <v>4.6805555555555507E-3</v>
+        <v>4.6923055555555511E-3</v>
       </c>
       <c r="BP4" s="30">
         <f t="shared" ref="BP4" si="14">IF(BL4&lt;&gt;"",BL4,BM4)</f>
-        <v>1.685E-4</v>
+        <v>1.68923E-4</v>
       </c>
     </row>
     <row r="5" spans="1:68" x14ac:dyDescent="0.3">
@@ -2126,44 +2242,102 @@
       </c>
       <c r="H5" s="44"/>
       <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
+      <c r="J5" s="44">
+        <v>12.6</v>
+      </c>
+      <c r="K5" s="44">
+        <v>12.4</v>
+      </c>
+      <c r="L5" s="44">
+        <v>97.9</v>
+      </c>
+      <c r="M5" s="44">
+        <v>16.7</v>
+      </c>
+      <c r="N5" s="44">
+        <v>322</v>
+      </c>
+      <c r="O5" s="44">
+        <v>0.66</v>
+      </c>
+      <c r="P5" s="44">
+        <v>0.61</v>
+      </c>
+      <c r="Q5" s="44">
+        <v>5.81</v>
+      </c>
       <c r="R5" s="44"/>
-      <c r="S5" s="44"/>
-      <c r="T5" s="44"/>
-      <c r="U5" s="44"/>
-      <c r="V5" s="44"/>
-      <c r="W5" s="44"/>
-      <c r="X5" s="44"/>
-      <c r="Y5" s="44"/>
-      <c r="Z5" s="44"/>
-      <c r="AA5" s="44"/>
-      <c r="AB5" s="44"/>
-      <c r="AC5" s="44"/>
-      <c r="AD5" s="17"/>
-      <c r="AE5" s="44"/>
-      <c r="AF5" s="44"/>
-      <c r="AG5" s="44"/>
+      <c r="S5" s="44">
+        <v>0.99</v>
+      </c>
+      <c r="T5" s="44">
+        <v>2.44</v>
+      </c>
+      <c r="U5" s="44">
+        <v>1.03</v>
+      </c>
+      <c r="V5" s="44">
+        <v>7.3230000000000004</v>
+      </c>
+      <c r="W5" s="44">
+        <v>54</v>
+      </c>
+      <c r="X5" s="44">
+        <v>77.099999999999994</v>
+      </c>
+      <c r="Y5" s="44">
+        <v>6.62</v>
+      </c>
+      <c r="Z5" s="44">
+        <v>108.8</v>
+      </c>
+      <c r="AA5" s="44">
+        <v>27.3</v>
+      </c>
+      <c r="AB5" s="44">
+        <v>47.3</v>
+      </c>
+      <c r="AC5" s="44">
+        <v>63.2</v>
+      </c>
+      <c r="AD5" s="17">
+        <v>7.3659999999999997</v>
+      </c>
+      <c r="AE5" s="44">
+        <v>301</v>
+      </c>
+      <c r="AF5" s="44">
+        <v>49.9</v>
+      </c>
+      <c r="AG5" s="44">
+        <v>7.09</v>
+      </c>
       <c r="AH5" s="45">
         <f t="shared" ref="AH5:AH8" si="15">AF5/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI5" s="44"/>
-      <c r="AJ5" s="44"/>
-      <c r="AK5" s="44"/>
-      <c r="AL5" s="44"/>
+        <v>0.499</v>
+      </c>
+      <c r="AI5" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ5" s="44">
+        <v>4.3</v>
+      </c>
+      <c r="AK5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="44">
+        <v>0</v>
+      </c>
       <c r="AM5" s="45">
         <f t="shared" ref="AM5:AM8" si="16">BO5</f>
-        <v>4.6805555555555507E-3</v>
-      </c>
-      <c r="AN5" s="44"/>
-      <c r="AO5" s="44"/>
+        <v>4.6924999999999944E-3</v>
+      </c>
+      <c r="AN5" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="44">
+        <v>0</v>
+      </c>
       <c r="AP5" s="44"/>
       <c r="AQ5" s="45">
         <v>0</v>
@@ -2201,27 +2375,27 @@
       </c>
       <c r="BC5" s="11">
         <f t="shared" ref="BC5:BC66" si="17">AY5*K5*BE5/1000</f>
-        <v>0</v>
+        <v>6.2841959999999997E-3</v>
       </c>
       <c r="BD5" s="46">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.0492422399999999</v>
       </c>
       <c r="BE5" s="46">
         <f t="shared" si="1"/>
-        <v>1685</v>
-      </c>
-      <c r="BF5" s="47" t="str">
+        <v>1689.3</v>
+      </c>
+      <c r="BF5" s="47">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="BG5" s="47" t="str">
+        <v>0</v>
+      </c>
+      <c r="BG5" s="47">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BH5" s="47">
         <f t="shared" ref="BH5:BH66" si="18">AM5*24*60</f>
-        <v>6.7399999999999931</v>
+        <v>6.7571999999999912</v>
       </c>
       <c r="BI5" s="47" t="str">
         <f t="shared" si="10"/>
@@ -2229,7 +2403,7 @@
       </c>
       <c r="BJ5" s="47">
         <f t="shared" si="11"/>
-        <v>4.6805555555555507E-3</v>
+        <v>4.6924999999999944E-3</v>
       </c>
       <c r="BK5" s="48" t="str">
         <f>IF(B5="No MPC", AY5*K5*BE5/1000,"")</f>
@@ -2245,11 +2419,11 @@
       </c>
       <c r="BN5" s="28">
         <f t="shared" ref="BN5:BN8" si="19">IF(BI5&lt;&gt;"",BI5/0.000385,IF(BJ5&lt;&gt;"",BJ5/0.000385,BK5/0.000385))</f>
-        <v>12.157287157287145</v>
+        <v>12.188311688311675</v>
       </c>
       <c r="BO5" s="49">
         <f t="shared" ref="BO5:BO8" si="20">IF(BI5&lt;&gt;"",BI5,IF(BJ5&lt;&gt;"",BJ5,BK5))</f>
-        <v>4.6805555555555507E-3</v>
+        <v>4.6924999999999944E-3</v>
       </c>
       <c r="BP5" s="30">
         <f t="shared" ref="BP5:BP66" si="21">IF(BL5&lt;&gt;"",BL5,BM5)</f>
@@ -2275,44 +2449,102 @@
       </c>
       <c r="H6" s="44"/>
       <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
+      <c r="J6" s="44">
+        <v>13.5</v>
+      </c>
+      <c r="K6" s="44">
+        <v>13.3</v>
+      </c>
+      <c r="L6" s="44">
+        <v>98.3</v>
+      </c>
+      <c r="M6" s="44">
+        <v>17</v>
+      </c>
+      <c r="N6" s="44">
+        <v>324</v>
+      </c>
+      <c r="O6" s="44">
+        <v>0.74</v>
+      </c>
+      <c r="P6" s="44">
+        <v>0.69</v>
+      </c>
+      <c r="Q6" s="44">
+        <v>5.67</v>
+      </c>
       <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="44"/>
-      <c r="U6" s="44"/>
-      <c r="V6" s="44"/>
-      <c r="W6" s="44"/>
-      <c r="X6" s="44"/>
-      <c r="Y6" s="44"/>
-      <c r="Z6" s="44"/>
-      <c r="AA6" s="44"/>
-      <c r="AB6" s="44"/>
-      <c r="AC6" s="44"/>
-      <c r="AD6" s="17"/>
-      <c r="AE6" s="44"/>
-      <c r="AF6" s="44"/>
-      <c r="AG6" s="44"/>
+      <c r="S6" s="44">
+        <v>0.72</v>
+      </c>
+      <c r="T6" s="44">
+        <v>2.42</v>
+      </c>
+      <c r="U6" s="44">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="V6" s="44">
+        <v>7.2439999999999998</v>
+      </c>
+      <c r="W6" s="44">
+        <v>70.099999999999994</v>
+      </c>
+      <c r="X6" s="44">
+        <v>52.8</v>
+      </c>
+      <c r="Y6" s="44">
+        <v>6.79</v>
+      </c>
+      <c r="Z6" s="44">
+        <v>115.2</v>
+      </c>
+      <c r="AA6" s="44">
+        <v>29.5</v>
+      </c>
+      <c r="AB6" s="44">
+        <v>61.5</v>
+      </c>
+      <c r="AC6" s="44">
+        <v>42.8</v>
+      </c>
+      <c r="AD6" s="17">
+        <v>7.2850000000000001</v>
+      </c>
+      <c r="AE6" s="44">
+        <v>299</v>
+      </c>
+      <c r="AF6" s="44">
+        <v>50.2</v>
+      </c>
+      <c r="AG6" s="44">
+        <v>7.09</v>
+      </c>
       <c r="AH6" s="45">
         <f t="shared" ref="AH6" si="22">AF6/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI6" s="44"/>
-      <c r="AJ6" s="44"/>
-      <c r="AK6" s="44"/>
-      <c r="AL6" s="44"/>
+        <v>0.502</v>
+      </c>
+      <c r="AI6" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ6" s="44">
+        <v>5.58</v>
+      </c>
+      <c r="AK6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="44">
+        <v>0</v>
+      </c>
       <c r="AM6" s="45">
         <f t="shared" ref="AM6" si="23">BO6</f>
-        <v>6.9716747687283455E-3</v>
-      </c>
-      <c r="AN6" s="44"/>
-      <c r="AO6" s="44"/>
+        <v>6.9947619765678131E-3</v>
+      </c>
+      <c r="AN6" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="44">
+        <v>0</v>
+      </c>
       <c r="AP6" s="44"/>
       <c r="AQ6" s="45">
         <v>0</v>
@@ -2347,31 +2579,31 @@
       <c r="BB6" s="22"/>
       <c r="BC6" s="11">
         <f t="shared" ref="BC6" si="24">AY6*K6*BE6/1000</f>
-        <v>0</v>
+        <v>6.7454141999999991E-3</v>
       </c>
       <c r="BD6" s="46">
         <f t="shared" ref="BD6" si="25">BC6*24*60</f>
-        <v>0</v>
+        <v>9.7133964479999975</v>
       </c>
       <c r="BE6" s="46">
         <f t="shared" si="1"/>
-        <v>1685</v>
-      </c>
-      <c r="BF6" s="47" t="str">
+        <v>1690.58</v>
+      </c>
+      <c r="BF6" s="47">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="BG6" s="47" t="str">
+        <v>0</v>
+      </c>
+      <c r="BG6" s="47">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BH6" s="47">
         <f t="shared" ref="BH6" si="26">AM6*24*60</f>
-        <v>10.039211666968818</v>
+        <v>10.072457246257651</v>
       </c>
       <c r="BI6" s="47">
         <f>IF(B6="Python",AZ6*BE6/24/60,"")</f>
-        <v>6.9716747687283455E-3</v>
+        <v>6.9947619765678131E-3</v>
       </c>
       <c r="BJ6" s="48" t="str">
         <f>IF(B6="Julia",BA6*BE6/24/60,"")</f>
@@ -2390,11 +2622,11 @@
       </c>
       <c r="BN6" s="28">
         <f t="shared" ref="BN6" si="29">IF(BI6&lt;&gt;"",BI6/0.000385,IF(BJ6&lt;&gt;"",BJ6/0.000385,BK6/0.000385))</f>
-        <v>18.10824615254116</v>
+        <v>18.168212926150165</v>
       </c>
       <c r="BO6" s="49">
         <f t="shared" ref="BO6" si="30">IF(BI6&lt;&gt;"",BI6,IF(BJ6&lt;&gt;"",BJ6,BK6))</f>
-        <v>6.9716747687283455E-3</v>
+        <v>6.9947619765678131E-3</v>
       </c>
       <c r="BP6" s="30">
         <f>IF(BL6&lt;&gt;"",BL6,BM6)</f>
@@ -2420,44 +2652,102 @@
       </c>
       <c r="H7" s="44"/>
       <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
+      <c r="J7" s="44">
+        <v>12.7</v>
+      </c>
+      <c r="K7" s="44">
+        <v>12.5</v>
+      </c>
+      <c r="L7" s="44">
+        <v>98.1</v>
+      </c>
+      <c r="M7" s="44">
+        <v>17</v>
+      </c>
+      <c r="N7" s="44">
+        <v>324</v>
+      </c>
+      <c r="O7" s="44">
+        <v>0.75</v>
+      </c>
+      <c r="P7" s="44">
+        <v>0.65</v>
+      </c>
+      <c r="Q7" s="44">
+        <v>5.71</v>
+      </c>
       <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="44"/>
-      <c r="U7" s="44"/>
-      <c r="V7" s="44"/>
-      <c r="W7" s="44"/>
-      <c r="X7" s="44"/>
-      <c r="Y7" s="44"/>
-      <c r="Z7" s="44"/>
-      <c r="AA7" s="44"/>
-      <c r="AB7" s="44"/>
-      <c r="AC7" s="44"/>
-      <c r="AD7" s="17"/>
-      <c r="AE7" s="44"/>
-      <c r="AF7" s="44"/>
-      <c r="AG7" s="44"/>
+      <c r="S7" s="44">
+        <v>0.71</v>
+      </c>
+      <c r="T7" s="44">
+        <v>2.41</v>
+      </c>
+      <c r="U7" s="44">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="V7" s="44">
+        <v>7.2309999999999999</v>
+      </c>
+      <c r="W7" s="44">
+        <v>71.5</v>
+      </c>
+      <c r="X7" s="44">
+        <v>49.5</v>
+      </c>
+      <c r="Y7" s="44">
+        <v>6.69</v>
+      </c>
+      <c r="Z7" s="44">
+        <v>111.9</v>
+      </c>
+      <c r="AA7" s="44">
+        <v>29.2</v>
+      </c>
+      <c r="AB7" s="44">
+        <v>62.7</v>
+      </c>
+      <c r="AC7" s="44">
+        <v>40.1</v>
+      </c>
+      <c r="AD7" s="17">
+        <v>7.2720000000000002</v>
+      </c>
+      <c r="AE7" s="44">
+        <v>302</v>
+      </c>
+      <c r="AF7" s="44">
+        <v>50.2</v>
+      </c>
+      <c r="AG7" s="44">
+        <v>7.09</v>
+      </c>
       <c r="AH7" s="45">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AI7" s="44"/>
-      <c r="AJ7" s="44"/>
-      <c r="AK7" s="44"/>
-      <c r="AL7" s="44"/>
+        <v>0.502</v>
+      </c>
+      <c r="AI7" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ7" s="44">
+        <v>5.44</v>
+      </c>
+      <c r="AK7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="44">
+        <v>0</v>
+      </c>
       <c r="AM7" s="45">
         <f t="shared" si="16"/>
-        <v>6.9716747687283455E-3</v>
-      </c>
-      <c r="AN7" s="44"/>
-      <c r="AO7" s="44"/>
+        <v>6.9941827276256046E-3</v>
+      </c>
+      <c r="AN7" s="44">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="44">
+        <v>0</v>
+      </c>
       <c r="AP7" s="44"/>
       <c r="AQ7" s="45">
         <v>0</v>
@@ -2492,31 +2782,31 @@
       <c r="BB7" s="22"/>
       <c r="BC7" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>6.33915E-3</v>
       </c>
       <c r="BD7" s="46">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.1283759999999994</v>
       </c>
       <c r="BE7" s="46">
         <f t="shared" si="1"/>
-        <v>1685</v>
-      </c>
-      <c r="BF7" s="47" t="str">
+        <v>1690.44</v>
+      </c>
+      <c r="BF7" s="47">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="BG7" s="47" t="str">
+        <v>0</v>
+      </c>
+      <c r="BG7" s="47">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BH7" s="47">
         <f t="shared" si="18"/>
-        <v>10.039211666968818</v>
+        <v>10.071623127780871</v>
       </c>
       <c r="BI7" s="47">
         <f t="shared" si="10"/>
-        <v>6.9716747687283455E-3</v>
+        <v>6.9941827276256046E-3</v>
       </c>
       <c r="BJ7" s="48" t="str">
         <f t="shared" ref="BJ7:BJ70" si="31">IF(B7="Julia",BA7*BE7/24/60,"")</f>
@@ -2535,11 +2825,11 @@
       </c>
       <c r="BN7" s="28">
         <f t="shared" si="19"/>
-        <v>18.10824615254116</v>
+        <v>18.16670838344313</v>
       </c>
       <c r="BO7" s="49">
         <f t="shared" si="20"/>
-        <v>6.9716747687283455E-3</v>
+        <v>6.9941827276256046E-3</v>
       </c>
       <c r="BP7" s="30">
         <f t="shared" si="21"/>
@@ -2566,44 +2856,102 @@
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
+      <c r="J8" s="7">
+        <v>12.2</v>
+      </c>
+      <c r="K8" s="7">
+        <v>12</v>
+      </c>
+      <c r="L8" s="7">
+        <v>98.2</v>
+      </c>
+      <c r="M8" s="7">
+        <v>17</v>
+      </c>
+      <c r="N8" s="7">
+        <v>325</v>
+      </c>
+      <c r="O8" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0.66</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>5.66</v>
+      </c>
       <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="7"/>
-      <c r="AA8" s="7"/>
-      <c r="AB8" s="7"/>
-      <c r="AC8" s="7"/>
-      <c r="AD8" s="18"/>
-      <c r="AE8" s="7"/>
-      <c r="AF8" s="7"/>
-      <c r="AG8" s="7"/>
+      <c r="S8" s="7">
+        <v>0.63</v>
+      </c>
+      <c r="T8" s="7">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="U8" s="7">
+        <v>1.18</v>
+      </c>
+      <c r="V8" s="7">
+        <v>7.266</v>
+      </c>
+      <c r="W8" s="7">
+        <v>67.8</v>
+      </c>
+      <c r="X8" s="7">
+        <v>61.7</v>
+      </c>
+      <c r="Y8" s="7">
+        <v>6.66</v>
+      </c>
+      <c r="Z8" s="7">
+        <v>112.3</v>
+      </c>
+      <c r="AA8" s="7">
+        <v>30</v>
+      </c>
+      <c r="AB8" s="7">
+        <v>59.5</v>
+      </c>
+      <c r="AC8" s="7">
+        <v>50.2</v>
+      </c>
+      <c r="AD8" s="18">
+        <v>7.3070000000000004</v>
+      </c>
+      <c r="AE8" s="7">
+        <v>300</v>
+      </c>
+      <c r="AF8" s="7">
+        <v>49.6</v>
+      </c>
+      <c r="AG8" s="7">
+        <v>7.08</v>
+      </c>
       <c r="AH8" s="41">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AI8" s="7"/>
-      <c r="AJ8" s="7"/>
-      <c r="AK8" s="7"/>
-      <c r="AL8" s="7"/>
+        <v>0.496</v>
+      </c>
+      <c r="AI8" s="7">
+        <v>34</v>
+      </c>
+      <c r="AJ8" s="7">
+        <v>6.34</v>
+      </c>
+      <c r="AK8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="7">
+        <v>0</v>
+      </c>
       <c r="AM8" s="41">
         <f t="shared" si="16"/>
-        <v>8.4868529347877988E-3</v>
-      </c>
-      <c r="AN8" s="7"/>
-      <c r="AO8" s="7"/>
+        <v>8.5187856633376826E-3</v>
+      </c>
+      <c r="AN8" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="7">
+        <v>0</v>
+      </c>
       <c r="AP8" s="7"/>
       <c r="AQ8" s="41">
         <v>0</v>
@@ -2639,31 +2987,31 @@
       <c r="BB8" s="23"/>
       <c r="BC8" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>6.0888239999999996E-3</v>
       </c>
       <c r="BD8" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.7679065600000001</v>
       </c>
       <c r="BE8" s="13">
         <f t="shared" si="1"/>
-        <v>1685</v>
-      </c>
-      <c r="BF8" s="14" t="str">
+        <v>1691.34</v>
+      </c>
+      <c r="BF8" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="BG8" s="14" t="str">
+        <v>0</v>
+      </c>
+      <c r="BG8" s="14">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="BH8" s="14">
         <f t="shared" si="18"/>
-        <v>12.221068226094431</v>
+        <v>12.267051355206263</v>
       </c>
       <c r="BI8" s="14">
         <f t="shared" si="10"/>
-        <v>8.4868529347877988E-3</v>
+        <v>8.5187856633376826E-3</v>
       </c>
       <c r="BJ8" s="48" t="str">
         <f t="shared" si="31"/>
@@ -2682,11 +3030,11 @@
       </c>
       <c r="BN8" s="29">
         <f t="shared" si="19"/>
-        <v>22.043773856591688</v>
+        <v>22.126716008669305</v>
       </c>
       <c r="BO8" s="38">
         <f t="shared" si="20"/>
-        <v>8.4868529347877988E-3</v>
+        <v>8.5187856633376826E-3</v>
       </c>
       <c r="BP8" s="31">
         <f t="shared" si="21"/>
@@ -13631,6 +13979,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -13853,48 +14228,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13917,9 +14254,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
+++ b/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-045-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1166" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B804E2ED-1439-49D1-AEA7-556819472ACF}"/>
+  <xr:revisionPtr revIDLastSave="1220" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D98ABA2-FC69-4F1E-9F9C-A520E5F311D8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="4224" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="88">
   <si>
     <t>Batch Data</t>
   </si>
@@ -300,6 +300,9 @@
   </si>
   <si>
     <t>Glucose Strategy: feed up to 3g/L if under 1.5 g/L, CSFR was used since model predicted low feed</t>
+  </si>
+  <si>
+    <t>pH, pCO2, pO2, bicarb, pCO2 at temp, pO2 at temp, and pH at temp were not measured in BR05's first sample</t>
   </si>
 </sst>
 </file>
@@ -5990,7 +5993,7 @@
       </c>
       <c r="AM21" s="42">
         <f>BR21</f>
-        <v>0</v>
+        <v>9.7818429790420998E-3</v>
       </c>
       <c r="AN21" s="6">
         <v>39.340000000000003</v>
@@ -6042,8 +6045,14 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC21" s="8"/>
-      <c r="BD21" s="9"/>
-      <c r="BE21" s="21"/>
+      <c r="BD21" s="46">
+        <f>BM21*24*60/BH21</f>
+        <v>8.1160529770802521E-3</v>
+      </c>
+      <c r="BE21" s="22">
+        <f>BP21/BH21</f>
+        <v>7.907325656743288E-3</v>
+      </c>
       <c r="BF21" s="8">
         <f t="shared" si="17"/>
         <v>1.0933994609999997E-2</v>
@@ -6066,15 +6075,14 @@
       </c>
       <c r="BK21" s="10">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>14.085853889820624</v>
       </c>
       <c r="BL21" s="10" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM21" s="10">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>9.7818429790420998E-3</v>
       </c>
       <c r="BN21" s="35" t="str">
         <f t="shared" si="32"/>
@@ -6085,20 +6093,19 @@
         <v/>
       </c>
       <c r="BP21" s="50">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>13.723596207991401</v>
       </c>
       <c r="BQ21" s="27">
         <f>IF(BL21&lt;&gt;"",BL21/0.000385,IF(BM21&lt;&gt;"",BM21/0.000385,BN21/0.000385))</f>
-        <v>0</v>
+        <v>25.407384361148313</v>
       </c>
       <c r="BR21" s="37">
         <f>IF(BL21&lt;&gt;"",BL21,IF(BM21&lt;&gt;"",BM21,BN21))</f>
-        <v>0</v>
+        <v>9.7818429790420998E-3</v>
       </c>
       <c r="BS21" s="32">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>13.723596207991401</v>
       </c>
     </row>
     <row r="22" spans="1:71" x14ac:dyDescent="0.25">
@@ -6212,7 +6219,7 @@
       </c>
       <c r="AM22" s="45">
         <f t="shared" ref="AM22:AM26" si="49">BR22</f>
-        <v>0</v>
+        <v>1.09245133137067E-2</v>
       </c>
       <c r="AN22" s="44">
         <v>39.74</v>
@@ -6264,8 +6271,14 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC22" s="11"/>
-      <c r="BD22" s="46"/>
-      <c r="BE22" s="22"/>
+      <c r="BD22" s="46">
+        <f>BM22*24*60/BH22</f>
+        <v>9.0475349583796875E-3</v>
+      </c>
+      <c r="BE22" s="22">
+        <f>BP22/BH22</f>
+        <v>7.6771012137581696E-3</v>
+      </c>
       <c r="BF22" s="11">
         <f t="shared" si="17"/>
         <v>1.2884053766999998E-2</v>
@@ -6288,15 +6301,14 @@
       </c>
       <c r="BK22" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>15.73129917173765</v>
       </c>
       <c r="BL22" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM22" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.09245133137067E-2</v>
       </c>
       <c r="BN22" s="48" t="str">
         <f t="shared" si="32"/>
@@ -6307,20 +6319,19 @@
         <v/>
       </c>
       <c r="BP22" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>13.348472984178301</v>
       </c>
       <c r="BQ22" s="28">
         <f t="shared" ref="BQ22:BQ26" si="50">IF(BL22&lt;&gt;"",BL22/0.000385,IF(BM22&lt;&gt;"",BM22/0.000385,BN22/0.000385))</f>
-        <v>0</v>
+        <v>28.375359256381039</v>
       </c>
       <c r="BR22" s="49">
         <f t="shared" ref="BR22:BR26" si="51">IF(BL22&lt;&gt;"",BL22,IF(BM22&lt;&gt;"",BM22,BN22))</f>
-        <v>0</v>
+        <v>1.09245133137067E-2</v>
       </c>
       <c r="BS22" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>13.348472984178301</v>
       </c>
     </row>
     <row r="23" spans="1:71" x14ac:dyDescent="0.25">
@@ -6434,7 +6445,7 @@
       </c>
       <c r="AM23" s="45">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1.7280784666155399E-2</v>
       </c>
       <c r="AN23" s="44">
         <v>30.62</v>
@@ -6486,8 +6497,14 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC23" s="11"/>
-      <c r="BD23" s="46"/>
-      <c r="BE23" s="22"/>
+      <c r="BD23" s="46">
+        <f>BM23*24*60/BH23</f>
+        <v>1.4412449076821883E-2</v>
+      </c>
+      <c r="BE23" s="22">
+        <f>BP23/BH23</f>
+        <v>7.1167129289496063E-3</v>
+      </c>
       <c r="BF23" s="11">
         <f t="shared" si="17"/>
         <v>1.3622761962000001E-2</v>
@@ -6510,15 +6527,14 @@
       </c>
       <c r="BK23" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>24.884329919263774</v>
       </c>
       <c r="BL23" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM23" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.7280784666155399E-2</v>
       </c>
       <c r="BN23" s="48" t="str">
         <f t="shared" si="32"/>
@@ -6529,20 +6545,19 @@
         <v/>
       </c>
       <c r="BP23" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>12.287615485800799</v>
       </c>
       <c r="BQ23" s="28">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>44.885154977027014</v>
       </c>
       <c r="BR23" s="49">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1.7280784666155399E-2</v>
       </c>
       <c r="BS23" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>12.287615485800799</v>
       </c>
     </row>
     <row r="24" spans="1:71" x14ac:dyDescent="0.25">
@@ -6656,7 +6671,7 @@
       </c>
       <c r="AM24" s="45">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>9.5190912847222236E-3</v>
       </c>
       <c r="AN24" s="44">
         <v>32.28</v>
@@ -6707,7 +6722,9 @@
       <c r="BB24" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC24" s="11"/>
+      <c r="BC24" s="11">
+        <v>7.9000000000000008E-3</v>
+      </c>
       <c r="BE24" s="22"/>
       <c r="BF24" s="11">
         <f t="shared" si="17"/>
@@ -6731,11 +6748,11 @@
       </c>
       <c r="BK24" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>13.707491450000001</v>
       </c>
       <c r="BL24" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9.5190912847222236E-3</v>
       </c>
       <c r="BM24" s="48" t="str">
         <f t="shared" si="31"/>
@@ -6755,11 +6772,11 @@
       </c>
       <c r="BQ24" s="28">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>24.724912427849933</v>
       </c>
       <c r="BR24" s="49">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>9.5190912847222236E-3</v>
       </c>
       <c r="BS24" s="30">
         <f t="shared" si="21"/>
@@ -6877,7 +6894,7 @@
       </c>
       <c r="AM25" s="45">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1.2907771124999998E-2</v>
       </c>
       <c r="AN25" s="44">
         <v>38.58</v>
@@ -6928,7 +6945,9 @@
       <c r="BB25" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC25" s="11"/>
+      <c r="BC25" s="11">
+        <v>1.0699999999999999E-2</v>
+      </c>
       <c r="BE25" s="22"/>
       <c r="BF25" s="11">
         <f t="shared" si="17"/>
@@ -6952,11 +6971,11 @@
       </c>
       <c r="BK25" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>18.587190419999999</v>
       </c>
       <c r="BL25" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.2907771124999998E-2</v>
       </c>
       <c r="BM25" s="48" t="str">
         <f t="shared" si="31"/>
@@ -6976,11 +6995,11 @@
       </c>
       <c r="BQ25" s="28">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>33.526678246753242</v>
       </c>
       <c r="BR25" s="49">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1.2907771124999998E-2</v>
       </c>
       <c r="BS25" s="30">
         <f t="shared" si="21"/>
@@ -7099,7 +7118,7 @@
       </c>
       <c r="AM26" s="41">
         <f t="shared" si="49"/>
-        <v>0</v>
+        <v>1.1483651458333331E-2</v>
       </c>
       <c r="AN26" s="7">
         <v>38.42</v>
@@ -7150,7 +7169,9 @@
       <c r="BB26" s="23">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC26" s="12"/>
+      <c r="BC26" s="12">
+        <v>9.4999999999999998E-3</v>
+      </c>
       <c r="BD26" s="5"/>
       <c r="BE26" s="23"/>
       <c r="BF26" s="12">
@@ -7175,11 +7196,11 @@
       </c>
       <c r="BK26" s="14">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>16.536458099999997</v>
       </c>
       <c r="BL26" s="14">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.1483651458333331E-2</v>
       </c>
       <c r="BM26" s="48" t="str">
         <f t="shared" si="31"/>
@@ -7199,11 +7220,11 @@
       </c>
       <c r="BQ26" s="29">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>29.827666125541121</v>
       </c>
       <c r="BR26" s="38">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>1.1483651458333331E-2</v>
       </c>
       <c r="BS26" s="31">
         <f t="shared" si="21"/>
@@ -7224,70 +7245,136 @@
         <v>4</v>
       </c>
       <c r="E27" s="3"/>
-      <c r="F27" s="60"/>
+      <c r="F27" s="60">
+        <v>45537.435821759304</v>
+      </c>
       <c r="G27" s="3">
         <v>2119.61</v>
       </c>
       <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
+      <c r="I27" s="6">
+        <v>1925.0550000000001</v>
+      </c>
+      <c r="J27" s="6">
+        <v>24.3</v>
+      </c>
+      <c r="K27" s="6">
+        <v>23.1</v>
+      </c>
+      <c r="L27" s="6">
+        <v>95.3</v>
+      </c>
+      <c r="M27" s="6">
+        <v>16.5</v>
+      </c>
+      <c r="N27" s="6">
+        <v>335</v>
+      </c>
+      <c r="O27" s="6">
+        <v>1.32</v>
+      </c>
+      <c r="P27" s="6">
+        <v>0.36</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>2.97</v>
+      </c>
       <c r="R27" s="6"/>
-      <c r="S27" s="6"/>
-      <c r="T27" s="6"/>
-      <c r="U27" s="6"/>
-      <c r="V27" s="6"/>
-      <c r="W27" s="6"/>
-      <c r="X27" s="6"/>
-      <c r="Y27" s="6"/>
-      <c r="Z27" s="6"/>
-      <c r="AA27" s="6"/>
-      <c r="AB27" s="6"/>
-      <c r="AC27" s="6"/>
-      <c r="AD27" s="16"/>
-      <c r="AE27" s="6"/>
-      <c r="AF27" s="6"/>
-      <c r="AG27" s="6"/>
+      <c r="S27" s="6">
+        <v>0.13</v>
+      </c>
+      <c r="T27" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="U27" s="6">
+        <v>2.34</v>
+      </c>
+      <c r="V27" s="6">
+        <v>7.24</v>
+      </c>
+      <c r="W27" s="6">
+        <v>112</v>
+      </c>
+      <c r="X27" s="6">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="Y27" s="6">
+        <v>2.97</v>
+      </c>
+      <c r="Z27" s="6">
+        <v>142.9</v>
+      </c>
+      <c r="AA27" s="6">
+        <v>46.7</v>
+      </c>
+      <c r="AB27" s="6">
+        <v>98.2</v>
+      </c>
+      <c r="AC27" s="6">
+        <v>13.2</v>
+      </c>
+      <c r="AD27" s="16">
+        <v>7.2809999999999997</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>301</v>
+      </c>
+      <c r="AF27" s="6">
+        <v>50.3</v>
+      </c>
+      <c r="AG27" s="6">
+        <v>7.27</v>
+      </c>
       <c r="AH27" s="40">
         <f>AF27/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI27" s="6"/>
-      <c r="AJ27" s="6"/>
-      <c r="AK27" s="44"/>
-      <c r="AL27" s="6"/>
+        <v>0.503</v>
+      </c>
+      <c r="AI27" s="6">
+        <v>34</v>
+      </c>
+      <c r="AJ27" s="6">
+        <v>22.065000000000001</v>
+      </c>
+      <c r="AK27" s="44">
+        <v>4.6547999999999998</v>
+      </c>
+      <c r="AL27" s="6">
+        <v>2.27</v>
+      </c>
       <c r="AM27" s="42">
         <f>BR27</f>
         <v>0</v>
       </c>
-      <c r="AN27" s="6"/>
-      <c r="AO27" s="6"/>
-      <c r="AP27" s="6"/>
-      <c r="AQ27" s="6"/>
+      <c r="AN27" s="6">
+        <v>51.88</v>
+      </c>
+      <c r="AO27" s="6">
+        <v>46.32</v>
+      </c>
+      <c r="AP27" s="6">
+        <v>629.08000000000004</v>
+      </c>
+      <c r="AQ27" s="6">
+        <v>1822</v>
+      </c>
       <c r="AR27" s="40">
         <v>137.11999999999989</v>
       </c>
       <c r="AS27" s="40">
         <f t="shared" si="0"/>
-        <v>-137.11999999999989</v>
+        <v>1684.88</v>
       </c>
       <c r="AT27" s="40">
         <f t="shared" si="35"/>
-        <v>-39.340000000000003</v>
+        <v>12.54</v>
       </c>
       <c r="AU27" s="40">
         <f t="shared" si="36"/>
-        <v>-31.99</v>
+        <v>14.330000000000002</v>
       </c>
       <c r="AV27" s="40">
         <f t="shared" si="37"/>
-        <v>-642</v>
+        <v>-12.919999999999959</v>
       </c>
       <c r="AW27" s="24">
         <v>15</v>
@@ -7312,23 +7399,23 @@
       <c r="BE27" s="21"/>
       <c r="BF27" s="8">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.2142675314E-2</v>
       </c>
       <c r="BG27" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.485452452160001</v>
       </c>
       <c r="BH27" s="9">
         <f t="shared" si="41"/>
-        <v>1625</v>
-      </c>
-      <c r="BI27" s="10" t="str">
+        <v>1752.1898000000001</v>
+      </c>
+      <c r="BI27" s="10">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ27" s="10" t="str">
+        <v>2.9608664540793469E-2</v>
+      </c>
+      <c r="BJ27" s="10">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3.0517647058823531E-2</v>
       </c>
       <c r="BK27" s="10">
         <f t="shared" si="18"/>
@@ -7380,70 +7467,136 @@
       <c r="D28">
         <v>4</v>
       </c>
-      <c r="F28" s="61"/>
+      <c r="F28" s="61">
+        <v>45537.4385763889</v>
+      </c>
       <c r="G28">
         <v>2119.61</v>
       </c>
       <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="44"/>
-      <c r="L28" s="44"/>
-      <c r="M28" s="44"/>
-      <c r="N28" s="44"/>
-      <c r="O28" s="44"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="44"/>
+      <c r="I28" s="44">
+        <v>1966.86</v>
+      </c>
+      <c r="J28" s="44">
+        <v>25.1</v>
+      </c>
+      <c r="K28" s="44">
+        <v>24</v>
+      </c>
+      <c r="L28" s="44">
+        <v>95.6</v>
+      </c>
+      <c r="M28" s="44">
+        <v>16.7</v>
+      </c>
+      <c r="N28" s="44">
+        <v>338</v>
+      </c>
+      <c r="O28" s="44">
+        <v>1.28</v>
+      </c>
+      <c r="P28" s="44">
+        <v>0.34</v>
+      </c>
+      <c r="Q28" s="44">
+        <v>2.62</v>
+      </c>
       <c r="R28" s="44"/>
-      <c r="S28" s="44"/>
-      <c r="T28" s="44"/>
-      <c r="U28" s="44"/>
-      <c r="V28" s="44"/>
-      <c r="W28" s="44"/>
-      <c r="X28" s="44"/>
-      <c r="Y28" s="44"/>
-      <c r="Z28" s="44"/>
-      <c r="AA28" s="44"/>
-      <c r="AB28" s="44"/>
-      <c r="AC28" s="44"/>
-      <c r="AD28" s="17"/>
-      <c r="AE28" s="44"/>
-      <c r="AF28" s="44"/>
-      <c r="AG28" s="44"/>
+      <c r="S28" s="44">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="T28" s="44">
+        <v>0.04</v>
+      </c>
+      <c r="U28" s="44">
+        <v>2.15</v>
+      </c>
+      <c r="V28" s="44">
+        <v>7.2809999999999997</v>
+      </c>
+      <c r="W28" s="44">
+        <v>121.3</v>
+      </c>
+      <c r="X28" s="44">
+        <v>31.7</v>
+      </c>
+      <c r="Y28" s="44">
+        <v>2.82</v>
+      </c>
+      <c r="Z28" s="44">
+        <v>145.5</v>
+      </c>
+      <c r="AA28" s="44">
+        <v>55.7</v>
+      </c>
+      <c r="AB28" s="44">
+        <v>106.4</v>
+      </c>
+      <c r="AC28" s="44">
+        <v>25.6</v>
+      </c>
+      <c r="AD28" s="17">
+        <v>7.3230000000000004</v>
+      </c>
+      <c r="AE28" s="44">
+        <v>301</v>
+      </c>
+      <c r="AF28" s="44">
+        <v>52.8</v>
+      </c>
+      <c r="AG28" s="44">
+        <v>7.29</v>
+      </c>
       <c r="AH28" s="45">
         <f t="shared" ref="AH28:AH32" si="52">AF28/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI28" s="44"/>
-      <c r="AJ28" s="44"/>
-      <c r="AK28" s="44"/>
-      <c r="AL28" s="44"/>
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="AI28" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ28" s="44">
+        <v>24.568000000000001</v>
+      </c>
+      <c r="AK28" s="44">
+        <v>3.2469000000000001</v>
+      </c>
+      <c r="AL28" s="44">
+        <v>1.38</v>
+      </c>
       <c r="AM28" s="45">
         <f t="shared" ref="AM28:AM32" si="53">BR28</f>
         <v>0</v>
       </c>
-      <c r="AN28" s="44"/>
-      <c r="AO28" s="44"/>
-      <c r="AP28" s="44"/>
-      <c r="AQ28" s="44"/>
+      <c r="AN28" s="44">
+        <v>53.59</v>
+      </c>
+      <c r="AO28" s="44">
+        <v>46.45</v>
+      </c>
+      <c r="AP28" s="44">
+        <v>632.23</v>
+      </c>
+      <c r="AQ28" s="44">
+        <v>1763</v>
+      </c>
       <c r="AR28" s="45">
         <v>45.769999999999982</v>
       </c>
       <c r="AS28" s="45">
         <f t="shared" si="0"/>
-        <v>-45.769999999999982</v>
+        <v>1717.23</v>
       </c>
       <c r="AT28" s="45">
         <f t="shared" si="35"/>
-        <v>-39.74</v>
+        <v>13.850000000000001</v>
       </c>
       <c r="AU28" s="45">
         <f t="shared" si="36"/>
-        <v>-32.46</v>
+        <v>13.990000000000002</v>
       </c>
       <c r="AV28" s="45">
         <f t="shared" si="37"/>
-        <v>-647</v>
+        <v>-14.769999999999982</v>
       </c>
       <c r="AW28" s="25">
         <v>15</v>
@@ -7468,23 +7621,23 @@
       <c r="BE28" s="22"/>
       <c r="BF28" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.263049128E-2</v>
       </c>
       <c r="BG28" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18.187907443199997</v>
       </c>
       <c r="BH28" s="46">
         <f t="shared" si="41"/>
-        <v>1625</v>
-      </c>
-      <c r="BI28" s="47" t="str">
+        <v>1754.2348999999999</v>
+      </c>
+      <c r="BI28" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ28" s="47" t="str">
+        <v>3.0548930476756567E-2</v>
+      </c>
+      <c r="BJ28" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3.1523529411764707E-2</v>
       </c>
       <c r="BK28" s="47">
         <f t="shared" si="18"/>
@@ -7536,70 +7689,136 @@
       <c r="D29">
         <v>4</v>
       </c>
-      <c r="F29" s="61"/>
+      <c r="F29" s="61">
+        <v>45537.441435185203</v>
+      </c>
       <c r="G29">
         <v>2119.61</v>
       </c>
       <c r="H29" s="44"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="44"/>
-      <c r="K29" s="44"/>
-      <c r="L29" s="44"/>
-      <c r="M29" s="44"/>
-      <c r="N29" s="44"/>
-      <c r="O29" s="44"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="44"/>
+      <c r="I29" s="44">
+        <v>1661.28</v>
+      </c>
+      <c r="J29" s="44">
+        <v>28.4</v>
+      </c>
+      <c r="K29" s="44">
+        <v>26.2</v>
+      </c>
+      <c r="L29" s="44">
+        <v>92.5</v>
+      </c>
+      <c r="M29" s="44">
+        <v>15.6</v>
+      </c>
+      <c r="N29" s="44">
+        <v>373</v>
+      </c>
+      <c r="O29" s="44">
+        <v>1.94</v>
+      </c>
+      <c r="P29" s="44">
+        <v>0.37</v>
+      </c>
+      <c r="Q29" s="44">
+        <v>0.03</v>
+      </c>
       <c r="R29" s="44"/>
-      <c r="S29" s="44"/>
-      <c r="T29" s="44"/>
-      <c r="U29" s="44"/>
-      <c r="V29" s="44"/>
-      <c r="W29" s="44"/>
-      <c r="X29" s="44"/>
-      <c r="Y29" s="44"/>
-      <c r="Z29" s="44"/>
-      <c r="AA29" s="44"/>
-      <c r="AB29" s="44"/>
-      <c r="AC29" s="44"/>
-      <c r="AD29" s="17"/>
-      <c r="AE29" s="44"/>
-      <c r="AF29" s="44"/>
-      <c r="AG29" s="44"/>
+      <c r="S29" s="44">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="T29" s="44">
+        <v>0.98</v>
+      </c>
+      <c r="U29" s="44">
+        <v>6.46</v>
+      </c>
+      <c r="V29" s="44">
+        <v>7.1040000000000001</v>
+      </c>
+      <c r="W29" s="44">
+        <v>52.1</v>
+      </c>
+      <c r="X29" s="44">
+        <v>25.9</v>
+      </c>
+      <c r="Y29" s="44">
+        <v>5.14</v>
+      </c>
+      <c r="Z29" s="44">
+        <v>157.1</v>
+      </c>
+      <c r="AA29" s="44">
+        <v>15.8</v>
+      </c>
+      <c r="AB29" s="44">
+        <v>45.7</v>
+      </c>
+      <c r="AC29" s="44">
+        <v>20.9</v>
+      </c>
+      <c r="AD29" s="17">
+        <v>7.1420000000000003</v>
+      </c>
+      <c r="AE29" s="44">
+        <v>298</v>
+      </c>
+      <c r="AF29" s="44">
+        <v>64.3</v>
+      </c>
+      <c r="AG29" s="44">
+        <v>7.17</v>
+      </c>
       <c r="AH29" s="45">
         <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AI29" s="44"/>
-      <c r="AJ29" s="44"/>
-      <c r="AK29" s="44"/>
-      <c r="AL29" s="44"/>
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="AI29" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ29" s="44">
+        <v>34.698999999999998</v>
+      </c>
+      <c r="AK29" s="44">
+        <v>1.2355</v>
+      </c>
+      <c r="AL29" s="44">
+        <v>2.92</v>
+      </c>
       <c r="AM29" s="45">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="AN29" s="44"/>
-      <c r="AO29" s="44"/>
-      <c r="AP29" s="44"/>
-      <c r="AQ29" s="44"/>
+      <c r="AN29" s="44">
+        <v>51.12</v>
+      </c>
+      <c r="AO29" s="44">
+        <v>45.63</v>
+      </c>
+      <c r="AP29" s="44">
+        <v>621.55999999999995</v>
+      </c>
+      <c r="AQ29" s="44">
+        <v>1791</v>
+      </c>
       <c r="AR29" s="45">
         <v>84.700000000000045</v>
       </c>
       <c r="AS29" s="45">
         <f t="shared" si="0"/>
-        <v>-84.700000000000045</v>
+        <v>1706.3</v>
       </c>
       <c r="AT29" s="45">
         <f t="shared" si="35"/>
-        <v>-30.62</v>
+        <v>20.499999999999996</v>
       </c>
       <c r="AU29" s="45">
         <f t="shared" si="36"/>
-        <v>-32.630000000000003</v>
+        <v>13</v>
       </c>
       <c r="AV29" s="45">
         <f t="shared" si="37"/>
-        <v>-646</v>
+        <v>-24.440000000000055</v>
       </c>
       <c r="AW29" s="25">
         <v>15</v>
@@ -7624,23 +7843,23 @@
       <c r="BE29" s="22"/>
       <c r="BF29" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.3838351369999998E-2</v>
       </c>
       <c r="BG29" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>19.927225972799995</v>
       </c>
       <c r="BH29" s="46">
         <f t="shared" si="41"/>
-        <v>1625</v>
-      </c>
-      <c r="BI29" s="47" t="str">
+        <v>1760.6044999999999</v>
+      </c>
+      <c r="BI29" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ29" s="47" t="str">
+        <v>2.9035481847285976E-2</v>
+      </c>
+      <c r="BJ29" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3.0070588235294116E-2</v>
       </c>
       <c r="BK29" s="47">
         <f t="shared" si="18"/>
@@ -7692,70 +7911,136 @@
       <c r="D30">
         <v>4</v>
       </c>
-      <c r="F30" s="61"/>
+      <c r="F30" s="61">
+        <v>45537.446064814802</v>
+      </c>
       <c r="G30">
         <v>2119.61</v>
       </c>
       <c r="H30" s="44"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44"/>
-      <c r="K30" s="44"/>
-      <c r="L30" s="44"/>
-      <c r="M30" s="44"/>
-      <c r="N30" s="44"/>
-      <c r="O30" s="44"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="44"/>
+      <c r="I30" s="44">
+        <v>1852.2</v>
+      </c>
+      <c r="J30" s="44">
+        <v>23.4</v>
+      </c>
+      <c r="K30" s="44">
+        <v>21.7</v>
+      </c>
+      <c r="L30" s="44">
+        <v>92.8</v>
+      </c>
+      <c r="M30" s="44">
+        <v>17</v>
+      </c>
+      <c r="N30" s="44">
+        <v>338</v>
+      </c>
+      <c r="O30" s="44">
+        <v>1.47</v>
+      </c>
+      <c r="P30" s="44">
+        <v>0.37</v>
+      </c>
+      <c r="Q30" s="44">
+        <v>1.04</v>
+      </c>
       <c r="R30" s="44"/>
-      <c r="S30" s="44"/>
-      <c r="T30" s="44"/>
-      <c r="U30" s="44"/>
-      <c r="V30" s="44"/>
-      <c r="W30" s="44"/>
-      <c r="X30" s="44"/>
-      <c r="Y30" s="44"/>
-      <c r="Z30" s="44"/>
-      <c r="AA30" s="44"/>
-      <c r="AB30" s="44"/>
-      <c r="AC30" s="44"/>
-      <c r="AD30" s="17"/>
-      <c r="AE30" s="44"/>
-      <c r="AF30" s="44"/>
-      <c r="AG30" s="44"/>
+      <c r="S30" s="44">
+        <v>0.15</v>
+      </c>
+      <c r="T30" s="44">
+        <v>0.04</v>
+      </c>
+      <c r="U30" s="44">
+        <v>4.01</v>
+      </c>
+      <c r="V30" s="44">
+        <v>7.1879999999999997</v>
+      </c>
+      <c r="W30" s="44">
+        <v>104.1</v>
+      </c>
+      <c r="X30" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="44">
+        <v>3.22</v>
+      </c>
+      <c r="Z30" s="44">
+        <v>149.1</v>
+      </c>
+      <c r="AA30" s="44">
+        <v>38.4</v>
+      </c>
+      <c r="AB30" s="44">
+        <v>91.3</v>
+      </c>
+      <c r="AC30" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="17">
+        <v>7.2279999999999998</v>
+      </c>
+      <c r="AE30" s="44">
+        <v>302</v>
+      </c>
+      <c r="AF30" s="44">
+        <v>46.6</v>
+      </c>
+      <c r="AG30" s="44">
+        <v>7.22</v>
+      </c>
       <c r="AH30" s="45">
         <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AI30" s="44"/>
-      <c r="AJ30" s="44"/>
-      <c r="AK30" s="44"/>
-      <c r="AL30" s="44"/>
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="AI30" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ30" s="44">
+        <v>28.350999999999999</v>
+      </c>
+      <c r="AK30" s="44">
+        <v>6.8529</v>
+      </c>
+      <c r="AL30" s="44">
+        <v>2.95</v>
+      </c>
       <c r="AM30" s="45">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="AN30" s="44"/>
-      <c r="AO30" s="44"/>
-      <c r="AP30" s="44"/>
-      <c r="AQ30" s="44"/>
+      <c r="AN30" s="44">
+        <v>44.08</v>
+      </c>
+      <c r="AO30" s="44">
+        <v>43.02</v>
+      </c>
+      <c r="AP30" s="44">
+        <v>629.41999999999996</v>
+      </c>
+      <c r="AQ30" s="44">
+        <v>1763</v>
+      </c>
       <c r="AR30" s="45">
         <v>47.420000000000073</v>
       </c>
       <c r="AS30" s="45">
         <f t="shared" si="0"/>
-        <v>-47.420000000000073</v>
+        <v>1715.58</v>
       </c>
       <c r="AT30" s="45">
         <f t="shared" si="35"/>
-        <v>-32.28</v>
+        <v>11.799999999999997</v>
       </c>
       <c r="AU30" s="45">
         <f t="shared" si="36"/>
-        <v>-29.18</v>
+        <v>13.840000000000003</v>
       </c>
       <c r="AV30" s="45">
         <f t="shared" si="37"/>
-        <v>-644</v>
+        <v>-14.580000000000041</v>
       </c>
       <c r="AW30" s="25">
         <v>15</v>
@@ -7779,23 +8064,23 @@
       <c r="BE30" s="22"/>
       <c r="BF30" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.1394152889E-2</v>
       </c>
       <c r="BG30" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.407580160159998</v>
       </c>
       <c r="BH30" s="46">
         <f t="shared" si="41"/>
-        <v>1625</v>
-      </c>
-      <c r="BI30" s="47" t="str">
+        <v>1750.2538999999999</v>
+      </c>
+      <c r="BI30" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ30" s="47" t="str">
+        <v>2.5184917456832979E-2</v>
+      </c>
+      <c r="BJ30" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>2.5929411764705881E-2</v>
       </c>
       <c r="BK30" s="47">
         <f t="shared" si="18"/>
@@ -7815,7 +8100,7 @@
       </c>
       <c r="BO30" s="47">
         <f t="shared" si="47"/>
-        <v>12.1875</v>
+        <v>8.5762441099999993</v>
       </c>
       <c r="BP30" s="51" t="str">
         <f t="shared" si="28"/>
@@ -7831,7 +8116,7 @@
       </c>
       <c r="BS30" s="30">
         <f t="shared" si="21"/>
-        <v>12.1875</v>
+        <v>8.5762441099999993</v>
       </c>
     </row>
     <row r="31" spans="1:71" x14ac:dyDescent="0.25">
@@ -7847,70 +8132,139 @@
       <c r="D31">
         <v>4</v>
       </c>
-      <c r="F31" s="61"/>
+      <c r="E31" t="s">
+        <v>87</v>
+      </c>
+      <c r="F31" s="61">
+        <v>45537.449282407397</v>
+      </c>
       <c r="G31">
         <v>2119.61</v>
       </c>
       <c r="H31" s="44"/>
-      <c r="I31" s="44"/>
-      <c r="J31" s="44"/>
-      <c r="K31" s="44"/>
-      <c r="L31" s="44"/>
-      <c r="M31" s="44"/>
-      <c r="N31" s="44"/>
-      <c r="O31" s="44"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="44"/>
+      <c r="I31" s="44">
+        <v>1875.4649999999999</v>
+      </c>
+      <c r="J31" s="44">
+        <v>23</v>
+      </c>
+      <c r="K31" s="44">
+        <v>21.6</v>
+      </c>
+      <c r="L31" s="44">
+        <v>93.8</v>
+      </c>
+      <c r="M31" s="44">
+        <v>17</v>
+      </c>
+      <c r="N31" s="44">
+        <v>351</v>
+      </c>
+      <c r="O31" s="44">
+        <v>1.47</v>
+      </c>
+      <c r="P31" s="44">
+        <v>0.36</v>
+      </c>
+      <c r="Q31" s="44">
+        <v>1.58</v>
+      </c>
       <c r="R31" s="44"/>
-      <c r="S31" s="44"/>
-      <c r="T31" s="44"/>
-      <c r="U31" s="44"/>
-      <c r="V31" s="44"/>
-      <c r="W31" s="44"/>
-      <c r="X31" s="44"/>
-      <c r="Y31" s="44"/>
-      <c r="Z31" s="44"/>
-      <c r="AA31" s="44"/>
-      <c r="AB31" s="44"/>
-      <c r="AC31" s="44"/>
-      <c r="AD31" s="17"/>
-      <c r="AE31" s="44"/>
-      <c r="AF31" s="44"/>
-      <c r="AG31" s="44"/>
+      <c r="S31" s="44">
+        <v>0.17</v>
+      </c>
+      <c r="T31" s="44">
+        <v>0.03</v>
+      </c>
+      <c r="U31" s="44">
+        <v>2.94</v>
+      </c>
+      <c r="V31" s="44">
+        <v>7.2830000000000004</v>
+      </c>
+      <c r="W31" s="44">
+        <v>116.1</v>
+      </c>
+      <c r="X31" s="44">
+        <v>17.7</v>
+      </c>
+      <c r="Y31" s="44">
+        <v>2.74</v>
+      </c>
+      <c r="Z31" s="44">
+        <v>154.6</v>
+      </c>
+      <c r="AA31" s="44">
+        <v>53.6</v>
+      </c>
+      <c r="AB31" s="44">
+        <v>101.8</v>
+      </c>
+      <c r="AC31" s="44">
+        <v>14.3</v>
+      </c>
+      <c r="AD31" s="17">
+        <v>7.3250000000000002</v>
+      </c>
+      <c r="AE31" s="44">
+        <v>299</v>
+      </c>
+      <c r="AF31" s="44">
+        <v>50.1</v>
+      </c>
+      <c r="AG31" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH31" s="45">
         <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AI31" s="44"/>
-      <c r="AJ31" s="44"/>
-      <c r="AK31" s="44"/>
-      <c r="AL31" s="44"/>
+        <v>0.501</v>
+      </c>
+      <c r="AI31" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ31" s="44">
+        <v>27.696000000000002</v>
+      </c>
+      <c r="AK31" s="44">
+        <v>5.5312000000000001</v>
+      </c>
+      <c r="AL31" s="44">
+        <v>2.77</v>
+      </c>
       <c r="AM31" s="45">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="AN31" s="44"/>
-      <c r="AO31" s="44"/>
-      <c r="AP31" s="44"/>
-      <c r="AQ31" s="44"/>
+      <c r="AN31" s="44">
+        <v>54.19</v>
+      </c>
+      <c r="AO31" s="44">
+        <v>40.74</v>
+      </c>
+      <c r="AP31" s="44">
+        <v>597.16</v>
+      </c>
+      <c r="AQ31" s="44">
+        <v>1790</v>
+      </c>
       <c r="AR31" s="45">
         <v>133.55999999999995</v>
       </c>
       <c r="AS31" s="45">
         <f t="shared" si="0"/>
-        <v>-133.55999999999995</v>
+        <v>1656.44</v>
       </c>
       <c r="AT31" s="45">
         <f t="shared" si="35"/>
-        <v>-38.58</v>
+        <v>15.61</v>
       </c>
       <c r="AU31" s="45">
         <f t="shared" si="36"/>
-        <v>-26.94</v>
+        <v>13.8</v>
       </c>
       <c r="AV31" s="45">
         <f t="shared" si="37"/>
-        <v>-618</v>
+        <v>-20.840000000000032</v>
       </c>
       <c r="AW31" s="25">
         <v>15</v>
@@ -7934,23 +8288,23 @@
       <c r="BE31" s="22"/>
       <c r="BF31" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.1378408256E-2</v>
       </c>
       <c r="BG31" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.384907888640001</v>
       </c>
       <c r="BH31" s="46">
         <f t="shared" si="41"/>
-        <v>1625</v>
-      </c>
-      <c r="BI31" s="47" t="str">
+        <v>1755.9272000000001</v>
+      </c>
+      <c r="BI31" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ31" s="47" t="str">
+        <v>3.0861188322613829E-2</v>
+      </c>
+      <c r="BJ31" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3.1876470588235291E-2</v>
       </c>
       <c r="BK31" s="47">
         <f t="shared" si="18"/>
@@ -7970,7 +8324,7 @@
       </c>
       <c r="BO31" s="47">
         <f t="shared" si="47"/>
-        <v>12.1875</v>
+        <v>0</v>
       </c>
       <c r="BP31" s="51" t="str">
         <f t="shared" si="28"/>
@@ -7986,7 +8340,7 @@
       </c>
       <c r="BS31" s="30">
         <f t="shared" si="21"/>
-        <v>12.1875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -8003,70 +8357,136 @@
         <v>4</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="62"/>
+      <c r="F32" s="62">
+        <v>45537.452534722201</v>
+      </c>
       <c r="G32" s="5">
         <v>2119.61</v>
       </c>
       <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="7"/>
+      <c r="I32" s="7">
+        <v>1929.885</v>
+      </c>
+      <c r="J32" s="7">
+        <v>24.6</v>
+      </c>
+      <c r="K32" s="7">
+        <v>23</v>
+      </c>
+      <c r="L32" s="7">
+        <v>93.2</v>
+      </c>
+      <c r="M32" s="7">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="N32" s="7">
+        <v>345</v>
+      </c>
+      <c r="O32" s="7">
+        <v>1.31</v>
+      </c>
+      <c r="P32" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="Q32" s="7">
+        <v>1.59</v>
+      </c>
       <c r="R32" s="7"/>
-      <c r="S32" s="7"/>
-      <c r="T32" s="7"/>
-      <c r="U32" s="7"/>
-      <c r="V32" s="7"/>
-      <c r="W32" s="7"/>
-      <c r="X32" s="7"/>
-      <c r="Y32" s="7"/>
-      <c r="Z32" s="7"/>
-      <c r="AA32" s="7"/>
-      <c r="AB32" s="7"/>
-      <c r="AC32" s="7"/>
-      <c r="AD32" s="18"/>
-      <c r="AE32" s="7"/>
-      <c r="AF32" s="7"/>
-      <c r="AG32" s="7"/>
+      <c r="S32" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="T32" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="U32" s="7">
+        <v>3.07</v>
+      </c>
+      <c r="V32" s="7">
+        <v>7.3159999999999998</v>
+      </c>
+      <c r="W32" s="7">
+        <v>98.5</v>
+      </c>
+      <c r="X32" s="7">
+        <v>51</v>
+      </c>
+      <c r="Y32" s="7">
+        <v>2.91</v>
+      </c>
+      <c r="Z32" s="7">
+        <v>149.6</v>
+      </c>
+      <c r="AA32" s="7">
+        <v>49.1</v>
+      </c>
+      <c r="AB32" s="7">
+        <v>86.4</v>
+      </c>
+      <c r="AC32" s="7">
+        <v>41.4</v>
+      </c>
+      <c r="AD32" s="18">
+        <v>7.359</v>
+      </c>
+      <c r="AE32" s="7">
+        <v>301</v>
+      </c>
+      <c r="AF32" s="7">
+        <v>49.1</v>
+      </c>
+      <c r="AG32" s="7">
+        <v>7.3</v>
+      </c>
       <c r="AH32" s="41">
         <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AI32" s="7"/>
-      <c r="AJ32" s="7"/>
-      <c r="AK32" s="7"/>
-      <c r="AL32" s="7"/>
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="AI32" s="7">
+        <v>34</v>
+      </c>
+      <c r="AJ32" s="7">
+        <v>28.271000000000001</v>
+      </c>
+      <c r="AK32" s="7">
+        <v>7.8441999999999998</v>
+      </c>
+      <c r="AL32" s="7">
+        <v>2.8</v>
+      </c>
       <c r="AM32" s="41">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="AN32" s="7"/>
-      <c r="AO32" s="7"/>
-      <c r="AP32" s="7"/>
-      <c r="AQ32" s="7"/>
+      <c r="AN32" s="7">
+        <v>52.46</v>
+      </c>
+      <c r="AO32" s="7">
+        <v>42.45</v>
+      </c>
+      <c r="AP32" s="7">
+        <v>633.13</v>
+      </c>
+      <c r="AQ32" s="7">
+        <v>1784</v>
+      </c>
       <c r="AR32" s="41">
         <v>51.660000000000082</v>
       </c>
       <c r="AS32" s="41">
         <f t="shared" si="0"/>
-        <v>-51.660000000000082</v>
+        <v>1732.34</v>
       </c>
       <c r="AT32" s="41">
         <f t="shared" si="35"/>
-        <v>-38.42</v>
+        <v>14.04</v>
       </c>
       <c r="AU32" s="41">
         <f t="shared" si="36"/>
-        <v>-28.8</v>
+        <v>13.650000000000002</v>
       </c>
       <c r="AV32" s="41">
         <f t="shared" si="37"/>
-        <v>-648</v>
+        <v>-14.870000000000005</v>
       </c>
       <c r="AW32" s="26">
         <v>15</v>
@@ -8091,23 +8511,23 @@
       <c r="BE32" s="23"/>
       <c r="BF32" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.2135893879999998E-2</v>
       </c>
       <c r="BG32" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.475687187199998</v>
       </c>
       <c r="BH32" s="13">
         <f t="shared" si="41"/>
-        <v>1625</v>
-      </c>
-      <c r="BI32" s="14" t="str">
+        <v>1758.8252</v>
+      </c>
+      <c r="BI32" s="14">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ32" s="14" t="str">
+        <v>2.9826727522439412E-2</v>
+      </c>
+      <c r="BJ32" s="14">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3.0858823529411765E-2</v>
       </c>
       <c r="BK32" s="14">
         <f t="shared" si="18"/>
@@ -8127,7 +8547,7 @@
       </c>
       <c r="BO32" s="14">
         <f t="shared" si="47"/>
-        <v>12.1875</v>
+        <v>0</v>
       </c>
       <c r="BP32" s="52" t="str">
         <f t="shared" si="28"/>
@@ -8143,7 +8563,7 @@
       </c>
       <c r="BS32" s="31">
         <f t="shared" si="21"/>
-        <v>12.1875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:71" x14ac:dyDescent="0.25">
@@ -8215,15 +8635,15 @@
       </c>
       <c r="AT33" s="40">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>-51.88</v>
       </c>
       <c r="AU33" s="40">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-46.32</v>
       </c>
       <c r="AV33" s="40">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-629.08000000000004</v>
       </c>
       <c r="AW33" s="24">
         <v>15</v>
@@ -8371,15 +8791,15 @@
       </c>
       <c r="AT34" s="45">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>-53.59</v>
       </c>
       <c r="AU34" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-46.45</v>
       </c>
       <c r="AV34" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-632.23</v>
       </c>
       <c r="AW34" s="25">
         <v>15</v>
@@ -8527,15 +8947,15 @@
       </c>
       <c r="AT35" s="45">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>-51.12</v>
       </c>
       <c r="AU35" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-45.63</v>
       </c>
       <c r="AV35" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-621.55999999999995</v>
       </c>
       <c r="AW35" s="25">
         <v>15</v>
@@ -8683,15 +9103,15 @@
       </c>
       <c r="AT36" s="45">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>-44.08</v>
       </c>
       <c r="AU36" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-43.02</v>
       </c>
       <c r="AV36" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-629.41999999999996</v>
       </c>
       <c r="AW36" s="25">
         <v>15</v>
@@ -8838,15 +9258,15 @@
       </c>
       <c r="AT37" s="45">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>-54.19</v>
       </c>
       <c r="AU37" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-40.74</v>
       </c>
       <c r="AV37" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-597.16</v>
       </c>
       <c r="AW37" s="25">
         <v>15</v>
@@ -8994,15 +9414,15 @@
       </c>
       <c r="AT38" s="41">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>-52.46</v>
       </c>
       <c r="AU38" s="41">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-42.45</v>
       </c>
       <c r="AV38" s="41">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-633.13</v>
       </c>
       <c r="AW38" s="26">
         <v>15</v>
@@ -15684,15 +16104,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -15915,7 +16326,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
@@ -15933,15 +16344,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15960,7 +16372,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -15975,4 +16387,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
+++ b/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-045-MPC-3L/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yl604392\Git\state-space-model\data\mr24-045-experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1220" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D98ABA2-FC69-4F1E-9F9C-A520E5F311D8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B0633D-1023-4835-949F-5D6C595C648E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="4224" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="AM27" s="42">
         <f>BR27</f>
-        <v>0</v>
+        <v>2.03306636472439E-2</v>
       </c>
       <c r="AN27" s="6">
         <v>51.88</v>
@@ -7395,8 +7395,14 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC27" s="8"/>
-      <c r="BD27" s="9"/>
-      <c r="BE27" s="21"/>
+      <c r="BD27" s="46">
+        <f>BM27*24*60/BH27</f>
+        <v>1.6708324436103449E-2</v>
+      </c>
+      <c r="BE27" s="22">
+        <f>BP27/BH27</f>
+        <v>3.1248605606522366E-3</v>
+      </c>
       <c r="BF27" s="8">
         <f t="shared" si="17"/>
         <v>1.2142675314E-2</v>
@@ -7419,15 +7425,14 @@
       </c>
       <c r="BK27" s="10">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>29.276155652031218</v>
       </c>
       <c r="BL27" s="10" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM27" s="10">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>2.03306636472439E-2</v>
       </c>
       <c r="BN27" s="35" t="str">
         <f t="shared" si="32"/>
@@ -7438,20 +7443,19 @@
         <v/>
       </c>
       <c r="BP27" s="50">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>5.4753488007971303</v>
       </c>
       <c r="BQ27" s="27">
         <f>IF(BL27&lt;&gt;"",BL27/0.000385,IF(BM27&lt;&gt;"",BM27/0.000385,BN27/0.000385))</f>
-        <v>0</v>
+        <v>52.806918564269871</v>
       </c>
       <c r="BR27" s="37">
         <f>IF(BL27&lt;&gt;"",BL27,IF(BM27&lt;&gt;"",BM27,BN27))</f>
-        <v>0</v>
+        <v>2.03306636472439E-2</v>
       </c>
       <c r="BS27" s="32">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>5.4753488007971303</v>
       </c>
     </row>
     <row r="28" spans="1:71" x14ac:dyDescent="0.25">
@@ -7565,7 +7569,7 @@
       </c>
       <c r="AM28" s="45">
         <f t="shared" ref="AM28:AM32" si="53">BR28</f>
-        <v>0</v>
+        <v>1.81470467977842E-2</v>
       </c>
       <c r="AN28" s="44">
         <v>53.59</v>
@@ -7617,8 +7621,14 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC28" s="11"/>
-      <c r="BD28" s="46"/>
-      <c r="BE28" s="22"/>
+      <c r="BD28" s="46">
+        <f>BM28*24*60/BH28</f>
+        <v>1.4896378694101485E-2</v>
+      </c>
+      <c r="BE28" s="22">
+        <f>BP28/BH28</f>
+        <v>2.389137326932978E-3</v>
+      </c>
       <c r="BF28" s="11">
         <f t="shared" si="17"/>
         <v>1.263049128E-2</v>
@@ -7641,15 +7651,14 @@
       </c>
       <c r="BK28" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>26.131747388809249</v>
       </c>
       <c r="BL28" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM28" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.81470467977842E-2</v>
       </c>
       <c r="BN28" s="48" t="str">
         <f t="shared" si="32"/>
@@ -7660,20 +7669,19 @@
         <v/>
       </c>
       <c r="BP28" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>4.1911080797985401</v>
       </c>
       <c r="BQ28" s="28">
         <f t="shared" ref="BQ28:BQ32" si="54">IF(BL28&lt;&gt;"",BL28/0.000385,IF(BM28&lt;&gt;"",BM28/0.000385,BN28/0.000385))</f>
-        <v>0</v>
+        <v>47.13518648775117</v>
       </c>
       <c r="BR28" s="49">
         <f t="shared" ref="BR28:BR32" si="55">IF(BL28&lt;&gt;"",BL28,IF(BM28&lt;&gt;"",BM28,BN28))</f>
-        <v>0</v>
+        <v>1.81470467977842E-2</v>
       </c>
       <c r="BS28" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>4.1911080797985401</v>
       </c>
     </row>
     <row r="29" spans="1:71" x14ac:dyDescent="0.25">
@@ -7787,7 +7795,7 @@
       </c>
       <c r="AM29" s="45">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>2.93434083333333E-2</v>
       </c>
       <c r="AN29" s="44">
         <v>51.12</v>
@@ -7839,8 +7847,14 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC29" s="11"/>
-      <c r="BD29" s="46"/>
-      <c r="BE29" s="22"/>
+      <c r="BD29" s="46">
+        <f>BM29*24*60/BH29</f>
+        <v>2.3999999999999976E-2</v>
+      </c>
+      <c r="BE29" s="22">
+        <f>BP29/BH29</f>
+        <v>8.502714696423018E-3</v>
+      </c>
       <c r="BF29" s="11">
         <f t="shared" si="17"/>
         <v>1.3838351369999998E-2</v>
@@ -7863,15 +7877,14 @@
       </c>
       <c r="BK29" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>42.254507999999959</v>
       </c>
       <c r="BL29" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM29" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>2.93434083333333E-2</v>
       </c>
       <c r="BN29" s="48" t="str">
         <f t="shared" si="32"/>
@@ -7882,20 +7895,19 @@
         <v/>
       </c>
       <c r="BP29" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>14.9699177567385</v>
       </c>
       <c r="BQ29" s="28">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>76.216645021644936</v>
       </c>
       <c r="BR29" s="49">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>2.93434083333333E-2</v>
       </c>
       <c r="BS29" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>14.9699177567385</v>
       </c>
     </row>
     <row r="30" spans="1:71" x14ac:dyDescent="0.25">
@@ -8009,7 +8021,7 @@
       </c>
       <c r="AM30" s="45">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>8.9943603194444447E-3</v>
       </c>
       <c r="AN30" s="44">
         <v>44.08</v>
@@ -8060,7 +8072,9 @@
       <c r="BB30" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC30" s="11"/>
+      <c r="BC30" s="11">
+        <v>7.4000000000000003E-3</v>
+      </c>
       <c r="BE30" s="22"/>
       <c r="BF30" s="11">
         <f t="shared" si="17"/>
@@ -8084,11 +8098,11 @@
       </c>
       <c r="BK30" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>12.951878860000001</v>
       </c>
       <c r="BL30" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>8.9943603194444447E-3</v>
       </c>
       <c r="BM30" s="48" t="str">
         <f t="shared" si="31"/>
@@ -8108,11 +8122,11 @@
       </c>
       <c r="BQ30" s="28">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>23.361974855699856</v>
       </c>
       <c r="BR30" s="49">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>8.9943603194444447E-3</v>
       </c>
       <c r="BS30" s="30">
         <f t="shared" si="21"/>
@@ -8233,7 +8247,7 @@
       </c>
       <c r="AM31" s="45">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>2.4387877777777778E-2</v>
       </c>
       <c r="AN31" s="44">
         <v>54.19</v>
@@ -8284,7 +8298,9 @@
       <c r="BB31" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC31" s="11"/>
+      <c r="BC31" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BE31" s="22"/>
       <c r="BF31" s="11">
         <f t="shared" si="17"/>
@@ -8308,11 +8324,11 @@
       </c>
       <c r="BK31" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>35.118544</v>
       </c>
       <c r="BL31" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.4387877777777778E-2</v>
       </c>
       <c r="BM31" s="48" t="str">
         <f t="shared" si="31"/>
@@ -8332,11 +8348,11 @@
       </c>
       <c r="BQ31" s="28">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>63.34513708513709</v>
       </c>
       <c r="BR31" s="49">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>2.4387877777777778E-2</v>
       </c>
       <c r="BS31" s="30">
         <f t="shared" si="21"/>
@@ -8455,7 +8471,7 @@
       </c>
       <c r="AM32" s="41">
         <f t="shared" si="53"/>
-        <v>0</v>
+        <v>2.2596018194444442E-2</v>
       </c>
       <c r="AN32" s="7">
         <v>52.46</v>
@@ -8506,7 +8522,9 @@
       <c r="BB32" s="23">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC32" s="12"/>
+      <c r="BC32" s="12">
+        <v>1.8499999999999999E-2</v>
+      </c>
       <c r="BD32" s="5"/>
       <c r="BE32" s="23"/>
       <c r="BF32" s="12">
@@ -8531,11 +8549,11 @@
       </c>
       <c r="BK32" s="14">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>32.538266199999995</v>
       </c>
       <c r="BL32" s="14">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.2596018194444442E-2</v>
       </c>
       <c r="BM32" s="48" t="str">
         <f t="shared" si="31"/>
@@ -8555,11 +8573,11 @@
       </c>
       <c r="BQ32" s="29">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>58.690956349206346</v>
       </c>
       <c r="BR32" s="38">
         <f t="shared" si="55"/>
-        <v>0</v>
+        <v>2.2596018194444442E-2</v>
       </c>
       <c r="BS32" s="31">
         <f t="shared" si="21"/>
@@ -8580,70 +8598,136 @@
         <v>5</v>
       </c>
       <c r="E33" s="3"/>
-      <c r="F33" s="60"/>
+      <c r="F33" s="60">
+        <v>45538.412222222199</v>
+      </c>
       <c r="G33" s="3">
         <v>2716.05</v>
       </c>
       <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
+      <c r="I33" s="6">
+        <v>2667.585</v>
+      </c>
+      <c r="J33" s="6">
+        <v>24</v>
+      </c>
+      <c r="K33" s="6">
+        <v>22.9</v>
+      </c>
+      <c r="L33" s="6">
+        <v>95.6</v>
+      </c>
+      <c r="M33" s="6">
+        <v>16.8</v>
+      </c>
+      <c r="N33" s="6">
+        <v>340</v>
+      </c>
+      <c r="O33" s="6">
+        <v>1.19</v>
+      </c>
+      <c r="P33" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>4.21</v>
+      </c>
       <c r="R33" s="6"/>
-      <c r="S33" s="6"/>
-      <c r="T33" s="6"/>
-      <c r="U33" s="6"/>
-      <c r="V33" s="6"/>
-      <c r="W33" s="6"/>
-      <c r="X33" s="6"/>
-      <c r="Y33" s="6"/>
-      <c r="Z33" s="6"/>
-      <c r="AA33" s="6"/>
-      <c r="AB33" s="6"/>
-      <c r="AC33" s="6"/>
-      <c r="AD33" s="16"/>
-      <c r="AE33" s="6"/>
-      <c r="AF33" s="6"/>
-      <c r="AG33" s="6"/>
+      <c r="S33" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="T33" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="U33" s="6">
+        <v>1.35</v>
+      </c>
+      <c r="V33" s="6">
+        <v>7.3150000000000004</v>
+      </c>
+      <c r="W33" s="6">
+        <v>116.6</v>
+      </c>
+      <c r="X33" s="6">
+        <v>11.2</v>
+      </c>
+      <c r="Y33" s="6">
+        <v>2.67</v>
+      </c>
+      <c r="Z33" s="6">
+        <v>142.4</v>
+      </c>
+      <c r="AA33" s="6">
+        <v>57.9</v>
+      </c>
+      <c r="AB33" s="6">
+        <v>102.2</v>
+      </c>
+      <c r="AC33" s="6">
+        <v>9</v>
+      </c>
+      <c r="AD33" s="16">
+        <v>7.3570000000000002</v>
+      </c>
+      <c r="AE33" s="6">
+        <v>301</v>
+      </c>
+      <c r="AF33" s="6">
+        <v>51.5</v>
+      </c>
+      <c r="AG33" s="6">
+        <v>7.3</v>
+      </c>
       <c r="AH33" s="40">
         <f>AF33/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI33" s="6"/>
-      <c r="AJ33" s="6"/>
-      <c r="AK33" s="44"/>
-      <c r="AL33" s="6"/>
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="AI33" s="6">
+        <v>34</v>
+      </c>
+      <c r="AJ33" s="6">
+        <v>22.07</v>
+      </c>
+      <c r="AK33" s="44">
+        <v>7.36</v>
+      </c>
+      <c r="AL33" s="6">
+        <v>3.02</v>
+      </c>
       <c r="AM33" s="42">
         <f>BR33</f>
         <v>0</v>
       </c>
-      <c r="AN33" s="6"/>
-      <c r="AO33" s="6"/>
-      <c r="AP33" s="6"/>
-      <c r="AQ33" s="6"/>
+      <c r="AN33" s="6">
+        <v>77.8</v>
+      </c>
+      <c r="AO33" s="6">
+        <v>52.48</v>
+      </c>
+      <c r="AP33" s="6">
+        <v>598</v>
+      </c>
+      <c r="AQ33" s="6">
+        <v>1853</v>
+      </c>
       <c r="AR33" s="40">
         <v>137.11999999999989</v>
       </c>
       <c r="AS33" s="40">
         <f t="shared" si="0"/>
-        <v>-137.11999999999989</v>
+        <v>1715.88</v>
       </c>
       <c r="AT33" s="40">
         <f t="shared" si="35"/>
-        <v>-51.88</v>
+        <v>25.919999999999995</v>
       </c>
       <c r="AU33" s="40">
         <f t="shared" si="36"/>
-        <v>-46.32</v>
+        <v>6.1599999999999966</v>
       </c>
       <c r="AV33" s="40">
         <f t="shared" si="37"/>
-        <v>-629.08000000000004</v>
+        <v>-31.080000000000041</v>
       </c>
       <c r="AW33" s="24">
         <v>15</v>
@@ -8668,23 +8752,23 @@
       <c r="BE33" s="21"/>
       <c r="BF33" s="8">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.2178655099999998E-2</v>
       </c>
       <c r="BG33" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.537263343999996</v>
       </c>
       <c r="BH33" s="9">
         <f t="shared" si="41"/>
-        <v>1610</v>
-      </c>
-      <c r="BI33" s="10" t="str">
+        <v>1772.73</v>
+      </c>
+      <c r="BI33" s="10">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ33" s="10" t="str">
+        <v>4.3887111968545688E-2</v>
+      </c>
+      <c r="BJ33" s="10">
         <f t="shared" si="9"/>
-        <v/>
+        <v>4.5764705882352937E-2</v>
       </c>
       <c r="BK33" s="10">
         <f t="shared" si="18"/>
@@ -8736,70 +8820,136 @@
       <c r="D34">
         <v>5</v>
       </c>
-      <c r="F34" s="61"/>
+      <c r="F34" s="61">
+        <v>45538.419768518499</v>
+      </c>
       <c r="G34">
         <v>2716.05</v>
       </c>
       <c r="H34" s="44"/>
-      <c r="I34" s="44"/>
-      <c r="J34" s="44"/>
-      <c r="K34" s="44"/>
-      <c r="L34" s="44"/>
-      <c r="M34" s="44"/>
-      <c r="N34" s="44"/>
-      <c r="O34" s="44"/>
-      <c r="P34" s="44"/>
-      <c r="Q34" s="44"/>
+      <c r="I34" s="44">
+        <v>2629.92</v>
+      </c>
+      <c r="J34" s="44">
+        <v>26.2</v>
+      </c>
+      <c r="K34" s="44">
+        <v>25</v>
+      </c>
+      <c r="L34" s="44">
+        <v>95.3</v>
+      </c>
+      <c r="M34" s="44">
+        <v>17</v>
+      </c>
+      <c r="N34" s="44">
+        <v>344</v>
+      </c>
+      <c r="O34" s="44">
+        <v>1.19</v>
+      </c>
+      <c r="P34" s="44">
+        <v>0.3</v>
+      </c>
+      <c r="Q34" s="44">
+        <v>3.43</v>
+      </c>
       <c r="R34" s="44"/>
-      <c r="S34" s="44"/>
-      <c r="T34" s="44"/>
-      <c r="U34" s="44"/>
-      <c r="V34" s="44"/>
-      <c r="W34" s="44"/>
-      <c r="X34" s="44"/>
-      <c r="Y34" s="44"/>
-      <c r="Z34" s="44"/>
-      <c r="AA34" s="44"/>
-      <c r="AB34" s="44"/>
-      <c r="AC34" s="44"/>
-      <c r="AD34" s="17"/>
-      <c r="AE34" s="44"/>
-      <c r="AF34" s="44"/>
-      <c r="AG34" s="44"/>
+      <c r="S34" s="44">
+        <v>0.16</v>
+      </c>
+      <c r="T34" s="44">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="U34" s="44">
+        <v>1.42</v>
+      </c>
+      <c r="V34" s="44">
+        <v>7.298</v>
+      </c>
+      <c r="W34" s="44">
+        <v>126.9</v>
+      </c>
+      <c r="X34" s="44">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="Y34" s="44">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="Z34" s="44">
+        <v>147.5</v>
+      </c>
+      <c r="AA34" s="44">
+        <v>60.6</v>
+      </c>
+      <c r="AB34" s="44">
+        <v>111.3</v>
+      </c>
+      <c r="AC34" s="44">
+        <v>29.8</v>
+      </c>
+      <c r="AD34" s="17">
+        <v>7.34</v>
+      </c>
+      <c r="AE34" s="44">
+        <v>300</v>
+      </c>
+      <c r="AF34" s="44">
+        <v>49.2</v>
+      </c>
+      <c r="AG34" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH34" s="45">
         <f t="shared" ref="AH34:AH38" si="56">AF34/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI34" s="44"/>
-      <c r="AJ34" s="44"/>
-      <c r="AK34" s="44"/>
-      <c r="AL34" s="44"/>
+        <v>0.49200000000000005</v>
+      </c>
+      <c r="AI34" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ34" s="44">
+        <v>24.57</v>
+      </c>
+      <c r="AK34" s="44">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="AL34" s="44">
+        <v>1.79</v>
+      </c>
       <c r="AM34" s="45">
         <f t="shared" ref="AM34:AM38" si="57">BR34</f>
         <v>0</v>
       </c>
-      <c r="AN34" s="44"/>
-      <c r="AO34" s="44"/>
-      <c r="AP34" s="44"/>
-      <c r="AQ34" s="44"/>
+      <c r="AN34" s="44">
+        <v>77.14</v>
+      </c>
+      <c r="AO34" s="44">
+        <v>51.28</v>
+      </c>
+      <c r="AP34" s="44">
+        <v>604</v>
+      </c>
+      <c r="AQ34" s="44">
+        <v>1776</v>
+      </c>
       <c r="AR34" s="45">
         <v>45.769999999999982</v>
       </c>
       <c r="AS34" s="45">
         <f t="shared" si="0"/>
-        <v>-45.769999999999982</v>
+        <v>1730.23</v>
       </c>
       <c r="AT34" s="45">
         <f t="shared" si="35"/>
-        <v>-53.59</v>
+        <v>23.549999999999997</v>
       </c>
       <c r="AU34" s="45">
         <f t="shared" si="36"/>
-        <v>-46.45</v>
+        <v>4.8299999999999983</v>
       </c>
       <c r="AV34" s="45">
         <f t="shared" si="37"/>
-        <v>-632.23</v>
+        <v>-28.230000000000018</v>
       </c>
       <c r="AW34" s="25">
         <v>15</v>
@@ -8824,23 +8974,23 @@
       <c r="BE34" s="22"/>
       <c r="BF34" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.3304924999999999E-2</v>
       </c>
       <c r="BG34" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>19.159092000000001</v>
       </c>
       <c r="BH34" s="46">
         <f t="shared" si="41"/>
-        <v>1610</v>
-      </c>
-      <c r="BI34" s="47" t="str">
+        <v>1773.99</v>
+      </c>
+      <c r="BI34" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ34" s="47" t="str">
+        <v>4.3483897879920408E-2</v>
+      </c>
+      <c r="BJ34" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>4.5376470588235296E-2</v>
       </c>
       <c r="BK34" s="47">
         <f t="shared" si="18"/>
@@ -8892,70 +9042,134 @@
       <c r="D35">
         <v>5</v>
       </c>
-      <c r="F35" s="61"/>
+      <c r="F35" s="61">
+        <v>45538.424803240698</v>
+      </c>
       <c r="G35">
         <v>2716.05</v>
       </c>
       <c r="H35" s="44"/>
-      <c r="I35" s="44"/>
-      <c r="J35" s="44"/>
-      <c r="K35" s="44"/>
-      <c r="L35" s="44"/>
-      <c r="M35" s="44"/>
+      <c r="I35" s="44">
+        <v>2112.0749999999998</v>
+      </c>
+      <c r="J35" s="44">
+        <v>23.7</v>
+      </c>
+      <c r="K35" s="44">
+        <v>19.2</v>
+      </c>
+      <c r="L35" s="44">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="M35" s="44">
+        <v>16.899999999999999</v>
+      </c>
       <c r="N35" s="44"/>
-      <c r="O35" s="44"/>
-      <c r="P35" s="44"/>
-      <c r="Q35" s="44"/>
+      <c r="O35" s="44">
+        <v>1.33</v>
+      </c>
+      <c r="P35" s="44">
+        <v>0.34</v>
+      </c>
+      <c r="Q35" s="44">
+        <v>5.19</v>
+      </c>
       <c r="R35" s="44"/>
-      <c r="S35" s="44"/>
-      <c r="T35" s="44"/>
-      <c r="U35" s="44"/>
-      <c r="V35" s="44"/>
-      <c r="W35" s="44"/>
-      <c r="X35" s="44"/>
-      <c r="Y35" s="44"/>
-      <c r="Z35" s="44"/>
-      <c r="AA35" s="44"/>
-      <c r="AB35" s="44"/>
-      <c r="AC35" s="44"/>
-      <c r="AD35" s="17"/>
-      <c r="AE35" s="44"/>
-      <c r="AF35" s="44"/>
-      <c r="AG35" s="44"/>
+      <c r="S35" s="44">
+        <v>0.41</v>
+      </c>
+      <c r="T35" s="44">
+        <v>0.77</v>
+      </c>
+      <c r="U35" s="44">
+        <v>5.15</v>
+      </c>
+      <c r="V35" s="44">
+        <v>7.181</v>
+      </c>
+      <c r="W35" s="44">
+        <v>94</v>
+      </c>
+      <c r="X35" s="44">
+        <v>60.6</v>
+      </c>
+      <c r="Y35" s="44">
+        <v>2.7</v>
+      </c>
+      <c r="Z35" s="44">
+        <v>167.4</v>
+      </c>
+      <c r="AA35" s="44">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="AB35" s="44">
+        <v>82.5</v>
+      </c>
+      <c r="AC35" s="44">
+        <v>49.2</v>
+      </c>
+      <c r="AD35" s="17">
+        <v>7.2210000000000001</v>
+      </c>
+      <c r="AE35" s="44">
+        <v>299</v>
+      </c>
+      <c r="AF35" s="44">
+        <v>49.5</v>
+      </c>
+      <c r="AG35" s="44">
+        <v>7.17</v>
+      </c>
       <c r="AH35" s="45">
         <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="AI35" s="44"/>
-      <c r="AJ35" s="44"/>
-      <c r="AK35" s="44"/>
-      <c r="AL35" s="44"/>
+        <v>0.495</v>
+      </c>
+      <c r="AI35" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ35" s="44">
+        <v>38.049999999999997</v>
+      </c>
+      <c r="AK35" s="44">
+        <v>1.26</v>
+      </c>
+      <c r="AL35" s="44">
+        <v>3.86</v>
+      </c>
       <c r="AM35" s="45">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AN35" s="44"/>
-      <c r="AO35" s="44"/>
-      <c r="AP35" s="44"/>
-      <c r="AQ35" s="44"/>
+      <c r="AN35" s="44">
+        <v>89.1</v>
+      </c>
+      <c r="AO35" s="44">
+        <v>61.29</v>
+      </c>
+      <c r="AP35" s="44">
+        <v>574</v>
+      </c>
+      <c r="AQ35" s="44">
+        <v>1840</v>
+      </c>
       <c r="AR35" s="45">
         <v>84.700000000000045</v>
       </c>
       <c r="AS35" s="45">
         <f t="shared" ref="AS35:AS66" si="60">AQ35-AR35</f>
-        <v>-84.700000000000045</v>
+        <v>1755.3</v>
       </c>
       <c r="AT35" s="45">
         <f t="shared" si="35"/>
-        <v>-51.12</v>
+        <v>37.979999999999997</v>
       </c>
       <c r="AU35" s="45">
         <f t="shared" si="36"/>
-        <v>-45.63</v>
+        <v>15.659999999999997</v>
       </c>
       <c r="AV35" s="45">
         <f t="shared" si="37"/>
-        <v>-621.55999999999995</v>
+        <v>-47.559999999999945</v>
       </c>
       <c r="AW35" s="25">
         <v>15</v>
@@ -8980,23 +9194,23 @@
       <c r="BE35" s="22"/>
       <c r="BF35" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.0388505599999999E-2</v>
       </c>
       <c r="BG35" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.959448063999996</v>
       </c>
       <c r="BH35" s="46">
         <f t="shared" si="41"/>
-        <v>1610</v>
-      </c>
-      <c r="BI35" s="47" t="str">
+        <v>1803.56</v>
+      </c>
+      <c r="BI35" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ35" s="47" t="str">
+        <v>4.940229324225421E-2</v>
+      </c>
+      <c r="BJ35" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>5.2411764705882352E-2</v>
       </c>
       <c r="BK35" s="47">
         <f t="shared" si="18"/>
@@ -9048,70 +9262,134 @@
       <c r="D36">
         <v>5</v>
       </c>
-      <c r="F36" s="61"/>
+      <c r="F36" s="61">
+        <v>45538.430219907401</v>
+      </c>
       <c r="G36">
         <v>2716.05</v>
       </c>
       <c r="H36" s="44"/>
-      <c r="I36" s="44"/>
-      <c r="J36" s="44"/>
-      <c r="K36" s="44"/>
-      <c r="L36" s="44"/>
-      <c r="M36" s="44"/>
-      <c r="N36" s="44"/>
-      <c r="O36" s="44"/>
-      <c r="P36" s="44"/>
-      <c r="Q36" s="44"/>
+      <c r="I36" s="44">
+        <v>2211.7800000000002</v>
+      </c>
+      <c r="J36" s="44">
+        <v>23.6</v>
+      </c>
+      <c r="K36" s="44">
+        <v>21.3</v>
+      </c>
+      <c r="L36" s="44">
+        <v>90.2</v>
+      </c>
+      <c r="M36" s="44">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="N36" s="44">
+        <v>382</v>
+      </c>
+      <c r="O36" s="44">
+        <v>1.48</v>
+      </c>
+      <c r="P36" s="44">
+        <v>0.34</v>
+      </c>
+      <c r="Q36" s="44">
+        <v>0.04</v>
+      </c>
       <c r="R36" s="44"/>
-      <c r="S36" s="44"/>
-      <c r="T36" s="44"/>
+      <c r="S36" s="44">
+        <v>0.24</v>
+      </c>
+      <c r="T36" s="44">
+        <v>0.12</v>
+      </c>
       <c r="U36" s="44"/>
-      <c r="V36" s="44"/>
-      <c r="W36" s="44"/>
-      <c r="X36" s="44"/>
-      <c r="Y36" s="44"/>
-      <c r="Z36" s="44"/>
-      <c r="AA36" s="44"/>
-      <c r="AB36" s="44"/>
-      <c r="AC36" s="44"/>
-      <c r="AD36" s="17"/>
-      <c r="AE36" s="44"/>
-      <c r="AF36" s="44"/>
-      <c r="AG36" s="44"/>
+      <c r="V36" s="44">
+        <v>7.2439999999999998</v>
+      </c>
+      <c r="W36" s="44">
+        <v>52.9</v>
+      </c>
+      <c r="X36" s="44">
+        <v>43.9</v>
+      </c>
+      <c r="Y36" s="44">
+        <v>3.32</v>
+      </c>
+      <c r="Z36" s="44">
+        <v>172.1</v>
+      </c>
+      <c r="AA36" s="44">
+        <v>22.3</v>
+      </c>
+      <c r="AB36" s="44">
+        <v>46.4</v>
+      </c>
+      <c r="AC36" s="44">
+        <v>35.5</v>
+      </c>
+      <c r="AD36" s="17">
+        <v>7.2850000000000001</v>
+      </c>
+      <c r="AE36" s="44">
+        <v>299</v>
+      </c>
+      <c r="AF36" s="44">
+        <v>54.9</v>
+      </c>
+      <c r="AG36" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH36" s="45">
         <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="AI36" s="44"/>
-      <c r="AJ36" s="44"/>
-      <c r="AK36" s="44"/>
-      <c r="AL36" s="44"/>
+        <v>0.54899999999999993</v>
+      </c>
+      <c r="AI36" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ36" s="44">
+        <v>43.09</v>
+      </c>
+      <c r="AK36" s="44">
+        <v>7.28</v>
+      </c>
+      <c r="AL36" s="44">
+        <v>3.9</v>
+      </c>
       <c r="AM36" s="45">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AN36" s="44"/>
-      <c r="AO36" s="44"/>
-      <c r="AP36" s="44"/>
-      <c r="AQ36" s="44"/>
+      <c r="AN36" s="44">
+        <v>56.53</v>
+      </c>
+      <c r="AO36" s="44">
+        <v>57.03</v>
+      </c>
+      <c r="AP36" s="44">
+        <v>615</v>
+      </c>
+      <c r="AQ36" s="44">
+        <v>1788</v>
+      </c>
       <c r="AR36" s="45">
         <v>47.420000000000073</v>
       </c>
       <c r="AS36" s="45">
         <f t="shared" si="60"/>
-        <v>-47.420000000000073</v>
+        <v>1740.58</v>
       </c>
       <c r="AT36" s="45">
         <f t="shared" si="35"/>
-        <v>-44.08</v>
+        <v>12.450000000000003</v>
       </c>
       <c r="AU36" s="45">
         <f t="shared" si="36"/>
-        <v>-43.02</v>
+        <v>14.009999999999998</v>
       </c>
       <c r="AV36" s="45">
         <f t="shared" si="37"/>
-        <v>-629.41999999999996</v>
+        <v>-14.419999999999959</v>
       </c>
       <c r="AW36" s="25">
         <v>15</v>
@@ -9135,23 +9413,23 @@
       <c r="BE36" s="22"/>
       <c r="BF36" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.1360333699999999E-2</v>
       </c>
       <c r="BG36" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.358880527999997</v>
       </c>
       <c r="BH36" s="46">
         <f t="shared" si="41"/>
-        <v>1610</v>
-      </c>
-      <c r="BI36" s="47" t="str">
+        <v>1777.83</v>
+      </c>
+      <c r="BI36" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ36" s="47" t="str">
+        <v>3.1797190957515625E-2</v>
+      </c>
+      <c r="BJ36" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3.3252941176470589E-2</v>
       </c>
       <c r="BK36" s="47">
         <f t="shared" si="18"/>
@@ -9171,7 +9449,7 @@
       </c>
       <c r="BO36" s="47">
         <f t="shared" si="47"/>
-        <v>12.074999999999999</v>
+        <v>13.155942</v>
       </c>
       <c r="BP36" s="51" t="str">
         <f t="shared" si="28"/>
@@ -9187,7 +9465,7 @@
       </c>
       <c r="BS36" s="30">
         <f t="shared" si="21"/>
-        <v>12.074999999999999</v>
+        <v>13.155942</v>
       </c>
     </row>
     <row r="37" spans="1:71" x14ac:dyDescent="0.25">
@@ -9203,70 +9481,136 @@
       <c r="D37">
         <v>5</v>
       </c>
-      <c r="F37" s="61"/>
+      <c r="F37" s="61">
+        <v>45538.436261574097</v>
+      </c>
       <c r="G37">
         <v>2716.05</v>
       </c>
       <c r="H37" s="44"/>
-      <c r="I37" s="44"/>
-      <c r="J37" s="44"/>
-      <c r="K37" s="44"/>
-      <c r="L37" s="44"/>
-      <c r="M37" s="44"/>
-      <c r="N37" s="44"/>
-      <c r="O37" s="44"/>
-      <c r="P37" s="44"/>
-      <c r="Q37" s="44"/>
+      <c r="I37" s="44">
+        <v>2474.67</v>
+      </c>
+      <c r="J37" s="44">
+        <v>22.5</v>
+      </c>
+      <c r="K37" s="44">
+        <v>21.4</v>
+      </c>
+      <c r="L37" s="44">
+        <v>95.1</v>
+      </c>
+      <c r="M37" s="44">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="N37" s="44">
+        <v>371</v>
+      </c>
+      <c r="O37" s="44">
+        <v>1.42</v>
+      </c>
+      <c r="P37" s="44">
+        <v>0.32</v>
+      </c>
+      <c r="Q37" s="44">
+        <v>3.13</v>
+      </c>
       <c r="R37" s="44"/>
-      <c r="S37" s="44"/>
-      <c r="T37" s="44"/>
-      <c r="U37" s="44"/>
-      <c r="V37" s="44"/>
-      <c r="W37" s="44"/>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="44"/>
-      <c r="Z37" s="44"/>
-      <c r="AA37" s="44"/>
-      <c r="AB37" s="44"/>
-      <c r="AC37" s="44"/>
-      <c r="AD37" s="17"/>
-      <c r="AE37" s="44"/>
-      <c r="AF37" s="44"/>
-      <c r="AG37" s="44"/>
+      <c r="S37" s="44">
+        <v>0.37</v>
+      </c>
+      <c r="T37" s="44">
+        <v>0.08</v>
+      </c>
+      <c r="U37" s="44">
+        <v>4.29</v>
+      </c>
+      <c r="V37" s="44">
+        <v>7.032</v>
+      </c>
+      <c r="W37" s="44">
+        <v>120.8</v>
+      </c>
+      <c r="X37" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="44">
+        <v>2.17</v>
+      </c>
+      <c r="Z37" s="44">
+        <v>158.4</v>
+      </c>
+      <c r="AA37" s="44">
+        <v>30.9</v>
+      </c>
+      <c r="AB37" s="44">
+        <v>105.9</v>
+      </c>
+      <c r="AC37" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="17">
+        <v>7.069</v>
+      </c>
+      <c r="AE37" s="44">
+        <v>298</v>
+      </c>
+      <c r="AF37" s="44">
+        <v>47.9</v>
+      </c>
+      <c r="AG37" s="44">
+        <v>7.1</v>
+      </c>
       <c r="AH37" s="45">
         <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="AI37" s="44"/>
-      <c r="AJ37" s="44"/>
-      <c r="AK37" s="44"/>
-      <c r="AL37" s="44"/>
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="AI37" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ37" s="44">
+        <v>30.4</v>
+      </c>
+      <c r="AK37" s="44">
+        <v>7.31</v>
+      </c>
+      <c r="AL37" s="44">
+        <v>3.7</v>
+      </c>
       <c r="AM37" s="45">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AN37" s="44"/>
-      <c r="AO37" s="44"/>
-      <c r="AP37" s="44"/>
-      <c r="AQ37" s="44"/>
+      <c r="AN37" s="44">
+        <v>85.27</v>
+      </c>
+      <c r="AO37" s="44">
+        <v>54.88</v>
+      </c>
+      <c r="AP37" s="44">
+        <v>560</v>
+      </c>
+      <c r="AQ37" s="44">
+        <v>1834</v>
+      </c>
       <c r="AR37" s="45">
         <v>133.55999999999995</v>
       </c>
       <c r="AS37" s="45">
         <f t="shared" si="60"/>
-        <v>-133.55999999999995</v>
+        <v>1700.44</v>
       </c>
       <c r="AT37" s="45">
         <f t="shared" si="35"/>
-        <v>-54.19</v>
+        <v>31.08</v>
       </c>
       <c r="AU37" s="45">
         <f t="shared" si="36"/>
-        <v>-40.74</v>
+        <v>14.14</v>
       </c>
       <c r="AV37" s="45">
         <f t="shared" si="37"/>
-        <v>-597.16</v>
+        <v>-37.159999999999968</v>
       </c>
       <c r="AW37" s="25">
         <v>15</v>
@@ -9290,23 +9634,23 @@
       <c r="BE37" s="22"/>
       <c r="BF37" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.1501815199999998E-2</v>
       </c>
       <c r="BG37" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.562613887999994</v>
       </c>
       <c r="BH37" s="46">
         <f t="shared" si="41"/>
-        <v>1610</v>
-      </c>
-      <c r="BI37" s="47" t="str">
+        <v>1791.56</v>
+      </c>
+      <c r="BI37" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ37" s="47" t="str">
+        <v>4.7595391725646918E-2</v>
+      </c>
+      <c r="BJ37" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>5.0158823529411763E-2</v>
       </c>
       <c r="BK37" s="47">
         <f t="shared" si="18"/>
@@ -9326,7 +9670,7 @@
       </c>
       <c r="BO37" s="47">
         <f t="shared" si="47"/>
-        <v>12.074999999999999</v>
+        <v>0</v>
       </c>
       <c r="BP37" s="51" t="str">
         <f t="shared" si="28"/>
@@ -9342,7 +9686,7 @@
       </c>
       <c r="BS37" s="30">
         <f t="shared" si="21"/>
-        <v>12.074999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9359,70 +9703,136 @@
         <v>5</v>
       </c>
       <c r="E38" s="5"/>
-      <c r="F38" s="62"/>
+      <c r="F38" s="62">
+        <v>45538.440740740698</v>
+      </c>
       <c r="G38" s="5">
         <v>2716.05</v>
       </c>
       <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
-      <c r="P38" s="7"/>
-      <c r="Q38" s="7"/>
+      <c r="I38" s="7">
+        <v>2568.7950000000001</v>
+      </c>
+      <c r="J38" s="7">
+        <v>23.6</v>
+      </c>
+      <c r="K38" s="7">
+        <v>22.1</v>
+      </c>
+      <c r="L38" s="7">
+        <v>93.6</v>
+      </c>
+      <c r="M38" s="7">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="N38" s="7">
+        <v>362</v>
+      </c>
+      <c r="O38" s="7">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="P38" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="Q38" s="7">
+        <v>4.75</v>
+      </c>
       <c r="R38" s="7"/>
-      <c r="S38" s="7"/>
-      <c r="T38" s="7"/>
-      <c r="U38" s="7"/>
-      <c r="V38" s="7"/>
-      <c r="W38" s="7"/>
-      <c r="X38" s="7"/>
-      <c r="Y38" s="7"/>
-      <c r="Z38" s="7"/>
-      <c r="AA38" s="7"/>
-      <c r="AB38" s="7"/>
-      <c r="AC38" s="7"/>
-      <c r="AD38" s="18"/>
-      <c r="AE38" s="7"/>
-      <c r="AF38" s="7"/>
-      <c r="AG38" s="7"/>
+      <c r="S38" s="7">
+        <v>0.16</v>
+      </c>
+      <c r="T38" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="U38" s="7">
+        <v>2.42</v>
+      </c>
+      <c r="V38" s="7">
+        <v>7.2969999999999997</v>
+      </c>
+      <c r="W38" s="7">
+        <v>115.7</v>
+      </c>
+      <c r="X38" s="7">
+        <v>35.4</v>
+      </c>
+      <c r="Y38" s="7">
+        <v>2.38</v>
+      </c>
+      <c r="Z38" s="7">
+        <v>153</v>
+      </c>
+      <c r="AA38" s="7">
+        <v>55.1</v>
+      </c>
+      <c r="AB38" s="7">
+        <v>101.5</v>
+      </c>
+      <c r="AC38" s="7">
+        <v>28.6</v>
+      </c>
+      <c r="AD38" s="18">
+        <v>7.3390000000000004</v>
+      </c>
+      <c r="AE38" s="7">
+        <v>298</v>
+      </c>
+      <c r="AF38" s="7">
+        <v>47.6</v>
+      </c>
+      <c r="AG38" s="7">
+        <v>7.3</v>
+      </c>
       <c r="AH38" s="41">
         <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="AI38" s="7"/>
-      <c r="AJ38" s="7"/>
-      <c r="AK38" s="7"/>
-      <c r="AL38" s="7"/>
+        <v>0.47600000000000003</v>
+      </c>
+      <c r="AI38" s="7">
+        <v>34</v>
+      </c>
+      <c r="AJ38" s="7">
+        <v>28.27</v>
+      </c>
+      <c r="AK38" s="7">
+        <v>12.15</v>
+      </c>
+      <c r="AL38" s="7">
+        <v>3.73</v>
+      </c>
       <c r="AM38" s="41">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="AN38" s="7"/>
-      <c r="AO38" s="7"/>
-      <c r="AP38" s="7"/>
-      <c r="AQ38" s="7"/>
+      <c r="AN38" s="7">
+        <v>81.16</v>
+      </c>
+      <c r="AO38" s="7">
+        <v>56.59</v>
+      </c>
+      <c r="AP38" s="7">
+        <v>598</v>
+      </c>
+      <c r="AQ38" s="7">
+        <v>1805</v>
+      </c>
       <c r="AR38" s="41">
         <v>51.660000000000082</v>
       </c>
       <c r="AS38" s="41">
         <f t="shared" si="60"/>
-        <v>-51.660000000000082</v>
+        <v>1753.34</v>
       </c>
       <c r="AT38" s="41">
         <f t="shared" si="35"/>
-        <v>-52.46</v>
+        <v>28.699999999999996</v>
       </c>
       <c r="AU38" s="41">
         <f t="shared" si="36"/>
-        <v>-42.45</v>
+        <v>14.14</v>
       </c>
       <c r="AV38" s="41">
         <f t="shared" si="37"/>
-        <v>-633.13</v>
+        <v>-35.129999999999995</v>
       </c>
       <c r="AW38" s="26">
         <v>15</v>
@@ -9447,23 +9857,23 @@
       <c r="BE38" s="23"/>
       <c r="BF38" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.1880297E-2</v>
       </c>
       <c r="BG38" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.10762768</v>
       </c>
       <c r="BH38" s="13">
         <f t="shared" si="41"/>
-        <v>1610</v>
-      </c>
-      <c r="BI38" s="14" t="str">
+        <v>1791.9</v>
+      </c>
+      <c r="BI38" s="14">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ38" s="14" t="str">
+        <v>4.5292706066186725E-2</v>
+      </c>
+      <c r="BJ38" s="14">
         <f t="shared" si="9"/>
-        <v/>
+        <v>4.7741176470588231E-2</v>
       </c>
       <c r="BK38" s="14">
         <f t="shared" si="18"/>
@@ -9483,7 +9893,7 @@
       </c>
       <c r="BO38" s="14">
         <f t="shared" si="47"/>
-        <v>12.074999999999999</v>
+        <v>0</v>
       </c>
       <c r="BP38" s="52" t="str">
         <f t="shared" si="28"/>
@@ -9499,7 +9909,7 @@
       </c>
       <c r="BS38" s="31">
         <f t="shared" si="21"/>
-        <v>12.074999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:71" x14ac:dyDescent="0.25">
@@ -9571,15 +9981,15 @@
       </c>
       <c r="AT39" s="40">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>-77.8</v>
       </c>
       <c r="AU39" s="40">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-52.48</v>
       </c>
       <c r="AV39" s="40">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-598</v>
       </c>
       <c r="AW39" s="24">
         <v>15</v>
@@ -9727,15 +10137,15 @@
       </c>
       <c r="AT40" s="45">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>-77.14</v>
       </c>
       <c r="AU40" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-51.28</v>
       </c>
       <c r="AV40" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-604</v>
       </c>
       <c r="AW40" s="25">
         <v>15</v>
@@ -9883,15 +10293,15 @@
       </c>
       <c r="AT41" s="45">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>-89.1</v>
       </c>
       <c r="AU41" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-61.29</v>
       </c>
       <c r="AV41" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-574</v>
       </c>
       <c r="AW41" s="25">
         <v>15</v>
@@ -10039,15 +10449,15 @@
       </c>
       <c r="AT42" s="45">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>-56.53</v>
       </c>
       <c r="AU42" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-57.03</v>
       </c>
       <c r="AV42" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-615</v>
       </c>
       <c r="AW42" s="25">
         <v>15</v>
@@ -10194,15 +10604,15 @@
       </c>
       <c r="AT43" s="45">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>-85.27</v>
       </c>
       <c r="AU43" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-54.88</v>
       </c>
       <c r="AV43" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-560</v>
       </c>
       <c r="AW43" s="25">
         <v>15</v>
@@ -10350,15 +10760,15 @@
       </c>
       <c r="AT44" s="41">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>-81.16</v>
       </c>
       <c r="AU44" s="41">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-56.59</v>
       </c>
       <c r="AV44" s="41">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-598</v>
       </c>
       <c r="AW44" s="26">
         <v>15</v>
@@ -16327,6 +16737,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
@@ -16342,15 +16761,6 @@
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16373,6 +16783,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -16387,12 +16805,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
+++ b/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yl604392\Git\state-space-model\data\mr24-045-experiment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-045-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B0633D-1023-4835-949F-5D6C595C648E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1329" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7BD7647-660D-48B3-A1D1-318A1E7650F5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="89">
   <si>
     <t>Batch Data</t>
   </si>
@@ -263,28 +263,10 @@
     <t>Glucose to Copy to System</t>
   </si>
   <si>
-    <t>MR24-038-801</t>
-  </si>
-  <si>
     <t>Julia</t>
   </si>
   <si>
-    <t>MR24-038-802</t>
-  </si>
-  <si>
-    <t>MR24-038-803</t>
-  </si>
-  <si>
-    <t>MR24-038-804</t>
-  </si>
-  <si>
     <t>Python</t>
-  </si>
-  <si>
-    <t>MR24-038-805</t>
-  </si>
-  <si>
-    <t>MR24-038-806</t>
   </si>
   <si>
     <t>Glucose Strategy: feed up to 5g/L</t>
@@ -303,6 +285,27 @@
   </si>
   <si>
     <t>pH, pCO2, pO2, bicarb, pCO2 at temp, pO2 at temp, and pH at temp were not measured in BR05's first sample</t>
+  </si>
+  <si>
+    <t>Switched to optical DO probe</t>
+  </si>
+  <si>
+    <t>MR24-045-801</t>
+  </si>
+  <si>
+    <t>MR24-045-802</t>
+  </si>
+  <si>
+    <t>MR24-045-803</t>
+  </si>
+  <si>
+    <t>MR24-045-804</t>
+  </si>
+  <si>
+    <t>MR24-045-805</t>
+  </si>
+  <si>
+    <t>MR24-045-806</t>
   </si>
 </sst>
 </file>
@@ -1527,22 +1530,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:BS87"/>
-  <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
-    <col min="7" max="18" width="12.7109375" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" customWidth="1"/>
-    <col min="20" max="20" width="16.140625" customWidth="1"/>
-    <col min="21" max="43" width="12.7109375" customWidth="1"/>
-    <col min="44" max="44" width="12.7109375" hidden="1" customWidth="1"/>
-    <col min="45" max="68" width="12.7109375" customWidth="1"/>
-    <col min="69" max="69" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="70" max="71" width="16.28515625" customWidth="1"/>
+    <col min="2" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" customWidth="1"/>
+    <col min="7" max="18" width="12.6640625" customWidth="1"/>
+    <col min="19" max="19" width="15.109375" customWidth="1"/>
+    <col min="20" max="20" width="16.109375" customWidth="1"/>
+    <col min="21" max="43" width="12.6640625" customWidth="1"/>
+    <col min="44" max="44" width="12.6640625" hidden="1" customWidth="1"/>
+    <col min="45" max="68" width="12.6640625" customWidth="1"/>
+    <col min="69" max="69" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="70" max="71" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:71" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
@@ -1629,7 +1632,7 @@
       <c r="BR1" s="73"/>
       <c r="BS1" s="74"/>
     </row>
-    <row r="2" spans="1:71" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:71" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>7</v>
       </c>
@@ -1757,13 +1760,13 @@
         <v>48</v>
       </c>
       <c r="AQ2" s="19" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AR2" s="19" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AS2" s="19" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AT2" s="19" t="s">
         <v>49</v>
@@ -1844,12 +1847,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C3" s="3">
         <v>12</v>
@@ -2068,12 +2071,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4">
         <v>12</v>
@@ -2291,12 +2294,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5">
         <v>12</v>
@@ -2514,12 +2517,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C6">
         <v>12</v>
@@ -2733,12 +2736,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C7">
         <v>12</v>
@@ -2952,12 +2955,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C8" s="5">
         <v>12</v>
@@ -3173,12 +3176,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C9" s="3">
         <v>12</v>
@@ -3315,8 +3318,8 @@
         <v>0</v>
       </c>
       <c r="AV9" s="40">
-        <f>AP9-AP3</f>
-        <v>-5</v>
+        <f t="shared" ref="AV9:AV40" si="33">AP3-AP9</f>
+        <v>5</v>
       </c>
       <c r="AW9" s="24">
         <v>15</v>
@@ -3400,12 +3403,12 @@
         <v>17.2171504761906</v>
       </c>
     </row>
-    <row r="10" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10">
         <v>12</v>
@@ -3494,7 +3497,7 @@
         <v>7.1</v>
       </c>
       <c r="AH10" s="45">
-        <f t="shared" ref="AH10:AH14" si="33">AF10/100</f>
+        <f t="shared" ref="AH10:AH14" si="34">AF10/100</f>
         <v>0.5</v>
       </c>
       <c r="AI10" s="44">
@@ -3510,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="AM10" s="45">
-        <f t="shared" ref="AM10:AM14" si="34">BR10</f>
+        <f t="shared" ref="AM10:AM14" si="35">BR10</f>
         <v>7.4155433071382898E-3</v>
       </c>
       <c r="AN10" s="44">
@@ -3533,16 +3536,16 @@
         <v>1687.23</v>
       </c>
       <c r="AT10" s="45">
-        <f t="shared" ref="AT10:AT73" si="35">AN10-AN4</f>
+        <f t="shared" ref="AT10:AT73" si="36">AN10-AN4</f>
         <v>5</v>
       </c>
       <c r="AU10" s="45">
-        <f t="shared" ref="AU10:AU73" si="36">AO10-AO4</f>
+        <f t="shared" ref="AU10:AU73" si="37">AO10-AO4</f>
         <v>0</v>
       </c>
       <c r="AV10" s="45">
-        <f t="shared" ref="AV10:AV73" si="37">AP10-AP4</f>
-        <v>-5</v>
+        <f t="shared" si="33"/>
+        <v>5</v>
       </c>
       <c r="AW10" s="25">
         <v>15</v>
@@ -3626,12 +3629,12 @@
         <v>16.819329499794499</v>
       </c>
     </row>
-    <row r="11" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C11">
         <v>12</v>
@@ -3720,7 +3723,7 @@
         <v>7.1</v>
       </c>
       <c r="AH11" s="45">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.47399999999999998</v>
       </c>
       <c r="AI11" s="44">
@@ -3736,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="AM11" s="45">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>6.7023138508712403E-3</v>
       </c>
       <c r="AN11" s="44">
@@ -3759,16 +3762,16 @@
         <v>1685.3</v>
       </c>
       <c r="AT11" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>5</v>
       </c>
       <c r="AU11" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV11" s="45">
-        <f t="shared" si="37"/>
-        <v>-7</v>
+        <f t="shared" si="33"/>
+        <v>7</v>
       </c>
       <c r="AW11" s="25">
         <v>15</v>
@@ -3852,12 +3855,12 @@
         <v>14.550506861694201</v>
       </c>
     </row>
-    <row r="12" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C12">
         <v>12</v>
@@ -3866,7 +3869,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F12" s="61">
         <v>45534.389444444401</v>
@@ -3949,7 +3952,7 @@
         <v>7.1</v>
       </c>
       <c r="AH12" s="45">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.53</v>
       </c>
       <c r="AI12" s="44">
@@ -3965,7 +3968,7 @@
         <v>0</v>
       </c>
       <c r="AM12" s="45">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>5.2940937500000002E-3</v>
       </c>
       <c r="AN12" s="44">
@@ -3992,12 +3995,12 @@
         <v>8</v>
       </c>
       <c r="AU12" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV12" s="45">
-        <f t="shared" si="37"/>
-        <v>-9</v>
+        <f t="shared" si="33"/>
+        <v>9</v>
       </c>
       <c r="AW12" s="25">
         <v>15</v>
@@ -4078,12 +4081,12 @@
         <v>16.305808749999997</v>
       </c>
     </row>
-    <row r="13" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -4092,7 +4095,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F13" s="61">
         <v>45534.406238425901</v>
@@ -4175,7 +4178,7 @@
         <v>7.1</v>
       </c>
       <c r="AH13" s="45">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.49700000000000005</v>
       </c>
       <c r="AI13" s="44">
@@ -4191,7 +4194,7 @@
         <v>0</v>
       </c>
       <c r="AM13" s="45">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.0780833333333329E-3</v>
       </c>
       <c r="AN13" s="44">
@@ -4214,16 +4217,16 @@
         <v>1702.44</v>
       </c>
       <c r="AT13" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11</v>
       </c>
       <c r="AU13" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV13" s="45">
-        <f t="shared" si="37"/>
-        <v>-10</v>
+        <f t="shared" si="33"/>
+        <v>10</v>
       </c>
       <c r="AW13" s="25">
         <v>15</v>
@@ -4304,12 +4307,12 @@
         <v>14.226947500000001</v>
       </c>
     </row>
-    <row r="14" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C14" s="5">
         <v>12</v>
@@ -4318,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F14" s="62">
         <v>45534.411597222199</v>
@@ -4401,7 +4404,7 @@
         <v>7.1</v>
       </c>
       <c r="AH14" s="41">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.495</v>
       </c>
       <c r="AI14" s="7">
@@ -4417,7 +4420,7 @@
         <v>0</v>
       </c>
       <c r="AM14" s="41">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.0777499999999998E-3</v>
       </c>
       <c r="AN14" s="7">
@@ -4440,16 +4443,16 @@
         <v>1700.34</v>
       </c>
       <c r="AT14" s="41">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11</v>
       </c>
       <c r="AU14" s="41">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV14" s="41">
-        <f t="shared" si="37"/>
-        <v>-9</v>
+        <f t="shared" si="33"/>
+        <v>9</v>
       </c>
       <c r="AW14" s="26">
         <v>15</v>
@@ -4531,12 +4534,12 @@
         <v>15.542739000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C15" s="3">
         <v>12</v>
@@ -4665,16 +4668,16 @@
         <v>1669.88</v>
       </c>
       <c r="AT15" s="40">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11</v>
       </c>
       <c r="AU15" s="40">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>18</v>
       </c>
       <c r="AV15" s="40">
-        <f t="shared" si="37"/>
-        <v>-11</v>
+        <f t="shared" si="33"/>
+        <v>11</v>
       </c>
       <c r="AW15" s="24">
         <v>15</v>
@@ -4758,12 +4761,12 @@
         <v>13.5648651</v>
       </c>
     </row>
-    <row r="16" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C16">
         <v>12</v>
@@ -4891,16 +4894,16 @@
         <v>1671.23</v>
       </c>
       <c r="AT16" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11</v>
       </c>
       <c r="AU16" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>17</v>
       </c>
       <c r="AV16" s="45">
-        <f t="shared" si="37"/>
-        <v>-12</v>
+        <f t="shared" si="33"/>
+        <v>12</v>
       </c>
       <c r="AW16" s="25">
         <v>15</v>
@@ -4984,12 +4987,12 @@
         <v>14.26370168</v>
       </c>
     </row>
-    <row r="17" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C17">
         <v>12</v>
@@ -5115,16 +5118,16 @@
         <v>1648.3</v>
       </c>
       <c r="AT17" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>10</v>
       </c>
       <c r="AU17" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>15</v>
       </c>
       <c r="AV17" s="45">
-        <f t="shared" si="37"/>
-        <v>-12</v>
+        <f t="shared" si="33"/>
+        <v>12</v>
       </c>
       <c r="AW17" s="25">
         <v>15</v>
@@ -5208,12 +5211,12 @@
         <v>16.831299229999999</v>
       </c>
     </row>
-    <row r="18" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C18">
         <v>12</v>
@@ -5222,7 +5225,7 @@
         <v>2</v>
       </c>
       <c r="E18" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F18" s="61">
         <v>45535.493217592601</v>
@@ -5344,16 +5347,16 @@
         <v>1679.58</v>
       </c>
       <c r="AT18" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>8</v>
       </c>
       <c r="AU18" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>17</v>
       </c>
       <c r="AV18" s="45">
-        <f t="shared" si="37"/>
-        <v>-9</v>
+        <f t="shared" si="33"/>
+        <v>9</v>
       </c>
       <c r="AW18" s="25">
         <v>15</v>
@@ -5432,12 +5435,12 @@
         <v>11.53943145</v>
       </c>
     </row>
-    <row r="19" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C19">
         <v>12</v>
@@ -5446,7 +5449,7 @@
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F19" s="61">
         <v>45535.496261574102</v>
@@ -5568,16 +5571,16 @@
         <v>1636.44</v>
       </c>
       <c r="AT19" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11</v>
       </c>
       <c r="AU19" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>15</v>
       </c>
       <c r="AV19" s="45">
-        <f t="shared" si="37"/>
-        <v>-15</v>
+        <f t="shared" si="33"/>
+        <v>15</v>
       </c>
       <c r="AW19" s="25">
         <v>15</v>
@@ -5656,12 +5659,12 @@
         <v>11.368347625000002</v>
       </c>
     </row>
-    <row r="20" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C20" s="5">
         <v>12</v>
@@ -5670,7 +5673,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F20" s="62">
         <v>45535.499872685199</v>
@@ -5792,16 +5795,16 @@
         <v>1679.34</v>
       </c>
       <c r="AT20" s="41">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>10</v>
       </c>
       <c r="AU20" s="41">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>16</v>
       </c>
       <c r="AV20" s="41">
-        <f t="shared" si="37"/>
-        <v>-12</v>
+        <f t="shared" si="33"/>
+        <v>12</v>
       </c>
       <c r="AW20" s="26">
         <v>15</v>
@@ -5881,12 +5884,12 @@
         <v>11.9207928305</v>
       </c>
     </row>
-    <row r="21" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C21" s="3">
         <v>12</v>
@@ -6015,16 +6018,16 @@
         <v>1667.88</v>
       </c>
       <c r="AT21" s="40">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>23.340000000000003</v>
       </c>
       <c r="AU21" s="40">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>13.989999999999998</v>
       </c>
       <c r="AV21" s="40">
-        <f t="shared" si="37"/>
-        <v>-27</v>
+        <f t="shared" si="33"/>
+        <v>27</v>
       </c>
       <c r="AW21" s="24">
         <v>15</v>
@@ -6108,12 +6111,12 @@
         <v>13.723596207991401</v>
       </c>
     </row>
-    <row r="22" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C22">
         <v>12</v>
@@ -6241,16 +6244,16 @@
         <v>1687.23</v>
       </c>
       <c r="AT22" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>23.740000000000002</v>
       </c>
       <c r="AU22" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>15.46</v>
       </c>
       <c r="AV22" s="45">
-        <f t="shared" si="37"/>
-        <v>-28</v>
+        <f t="shared" si="33"/>
+        <v>28</v>
       </c>
       <c r="AW22" s="25">
         <v>15</v>
@@ -6334,12 +6337,12 @@
         <v>13.348472984178301</v>
       </c>
     </row>
-    <row r="23" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C23">
         <v>12</v>
@@ -6467,16 +6470,16 @@
         <v>1671.3</v>
       </c>
       <c r="AT23" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>15.620000000000001</v>
       </c>
       <c r="AU23" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>17.630000000000003</v>
       </c>
       <c r="AV23" s="45">
-        <f t="shared" si="37"/>
-        <v>-18</v>
+        <f t="shared" si="33"/>
+        <v>18</v>
       </c>
       <c r="AW23" s="25">
         <v>15</v>
@@ -6560,12 +6563,12 @@
         <v>12.287615485800799</v>
       </c>
     </row>
-    <row r="24" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C24">
         <v>12</v>
@@ -6693,16 +6696,16 @@
         <v>1702.58</v>
       </c>
       <c r="AT24" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>16.28</v>
       </c>
       <c r="AU24" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>12.18</v>
       </c>
       <c r="AV24" s="45">
-        <f t="shared" si="37"/>
-        <v>-18</v>
+        <f t="shared" si="33"/>
+        <v>18</v>
       </c>
       <c r="AW24" s="25">
         <v>15</v>
@@ -6783,12 +6786,12 @@
         <v>12.796550562500002</v>
       </c>
     </row>
-    <row r="25" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C25">
         <v>12</v>
@@ -6916,16 +6919,16 @@
         <v>1639.44</v>
       </c>
       <c r="AT25" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>16.579999999999998</v>
       </c>
       <c r="AU25" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>11.940000000000001</v>
       </c>
       <c r="AV25" s="45">
-        <f t="shared" si="37"/>
-        <v>-18</v>
+        <f t="shared" si="33"/>
+        <v>18</v>
       </c>
       <c r="AW25" s="25">
         <v>15</v>
@@ -7006,12 +7009,12 @@
         <v>12.811264425000001</v>
       </c>
     </row>
-    <row r="26" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C26" s="5">
         <v>12</v>
@@ -7140,16 +7143,16 @@
         <v>1707.34</v>
       </c>
       <c r="AT26" s="41">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>17.420000000000002</v>
       </c>
       <c r="AU26" s="41">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>12.8</v>
       </c>
       <c r="AV26" s="41">
-        <f t="shared" si="37"/>
-        <v>-20</v>
+        <f t="shared" si="33"/>
+        <v>20</v>
       </c>
       <c r="AW26" s="26">
         <v>15</v>
@@ -7231,12 +7234,12 @@
         <v>12.663445545</v>
       </c>
     </row>
-    <row r="27" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C27" s="3">
         <v>12</v>
@@ -7365,16 +7368,16 @@
         <v>1684.88</v>
       </c>
       <c r="AT27" s="40">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.54</v>
       </c>
       <c r="AU27" s="40">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>14.330000000000002</v>
       </c>
       <c r="AV27" s="40">
-        <f t="shared" si="37"/>
-        <v>-12.919999999999959</v>
+        <f t="shared" si="33"/>
+        <v>12.919999999999959</v>
       </c>
       <c r="AW27" s="24">
         <v>15</v>
@@ -7458,12 +7461,12 @@
         <v>5.4753488007971303</v>
       </c>
     </row>
-    <row r="28" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C28">
         <v>12</v>
@@ -7591,16 +7594,16 @@
         <v>1717.23</v>
       </c>
       <c r="AT28" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>13.850000000000001</v>
       </c>
       <c r="AU28" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>13.990000000000002</v>
       </c>
       <c r="AV28" s="45">
-        <f t="shared" si="37"/>
-        <v>-14.769999999999982</v>
+        <f t="shared" si="33"/>
+        <v>14.769999999999982</v>
       </c>
       <c r="AW28" s="25">
         <v>15</v>
@@ -7684,18 +7687,21 @@
         <v>4.1911080797985401</v>
       </c>
     </row>
-    <row r="29" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C29">
         <v>12</v>
       </c>
       <c r="D29">
         <v>4</v>
+      </c>
+      <c r="E29" t="s">
+        <v>82</v>
       </c>
       <c r="F29" s="61">
         <v>45537.441435185203</v>
@@ -7817,16 +7823,16 @@
         <v>1706.3</v>
       </c>
       <c r="AT29" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>20.499999999999996</v>
       </c>
       <c r="AU29" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>13</v>
       </c>
       <c r="AV29" s="45">
-        <f t="shared" si="37"/>
-        <v>-24.440000000000055</v>
+        <f t="shared" si="33"/>
+        <v>24.440000000000055</v>
       </c>
       <c r="AW29" s="25">
         <v>15</v>
@@ -7910,12 +7916,12 @@
         <v>14.9699177567385</v>
       </c>
     </row>
-    <row r="30" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C30">
         <v>12</v>
@@ -8043,16 +8049,16 @@
         <v>1715.58</v>
       </c>
       <c r="AT30" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11.799999999999997</v>
       </c>
       <c r="AU30" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>13.840000000000003</v>
       </c>
       <c r="AV30" s="45">
-        <f t="shared" si="37"/>
-        <v>-14.580000000000041</v>
+        <f t="shared" si="33"/>
+        <v>14.580000000000041</v>
       </c>
       <c r="AW30" s="25">
         <v>15</v>
@@ -8133,12 +8139,12 @@
         <v>8.5762441099999993</v>
       </c>
     </row>
-    <row r="31" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C31">
         <v>12</v>
@@ -8147,7 +8153,7 @@
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F31" s="61">
         <v>45537.449282407397</v>
@@ -8269,16 +8275,16 @@
         <v>1656.44</v>
       </c>
       <c r="AT31" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>15.61</v>
       </c>
       <c r="AU31" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>13.8</v>
       </c>
       <c r="AV31" s="45">
-        <f t="shared" si="37"/>
-        <v>-20.840000000000032</v>
+        <f t="shared" si="33"/>
+        <v>20.840000000000032</v>
       </c>
       <c r="AW31" s="25">
         <v>15</v>
@@ -8359,12 +8365,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C32" s="5">
         <v>12</v>
@@ -8493,16 +8499,16 @@
         <v>1732.34</v>
       </c>
       <c r="AT32" s="41">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>14.04</v>
       </c>
       <c r="AU32" s="41">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>13.650000000000002</v>
       </c>
       <c r="AV32" s="41">
-        <f t="shared" si="37"/>
-        <v>-14.870000000000005</v>
+        <f t="shared" si="33"/>
+        <v>14.870000000000005</v>
       </c>
       <c r="AW32" s="26">
         <v>15</v>
@@ -8584,12 +8590,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C33" s="3">
         <v>12</v>
@@ -8597,7 +8603,9 @@
       <c r="D33" s="3">
         <v>5</v>
       </c>
-      <c r="E33" s="3"/>
+      <c r="E33" t="s">
+        <v>82</v>
+      </c>
       <c r="F33" s="60">
         <v>45538.412222222199</v>
       </c>
@@ -8696,7 +8704,7 @@
       </c>
       <c r="AM33" s="42">
         <f>BR33</f>
-        <v>0</v>
+        <v>1.5867559989560302E-2</v>
       </c>
       <c r="AN33" s="6">
         <v>77.8</v>
@@ -8718,16 +8726,16 @@
         <v>1715.88</v>
       </c>
       <c r="AT33" s="40">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>25.919999999999995</v>
       </c>
       <c r="AU33" s="40">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>6.1599999999999966</v>
       </c>
       <c r="AV33" s="40">
-        <f t="shared" si="37"/>
-        <v>-31.080000000000041</v>
+        <f t="shared" si="33"/>
+        <v>31.080000000000041</v>
       </c>
       <c r="AW33" s="24">
         <v>15</v>
@@ -8748,8 +8756,14 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC33" s="8"/>
-      <c r="BD33" s="9"/>
-      <c r="BE33" s="21"/>
+      <c r="BD33" s="46">
+        <f>BM33*24*60/BH33</f>
+        <v>1.2889321207948664E-2</v>
+      </c>
+      <c r="BE33" s="22">
+        <f>BP33/BH33</f>
+        <v>2.1914951019571392E-3</v>
+      </c>
       <c r="BF33" s="8">
         <f t="shared" si="17"/>
         <v>1.2178655099999998E-2</v>
@@ -8772,15 +8786,14 @@
       </c>
       <c r="BK33" s="10">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>22.849286384966835</v>
       </c>
       <c r="BL33" s="10" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM33" s="10">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.5867559989560302E-2</v>
       </c>
       <c r="BN33" s="35" t="str">
         <f t="shared" si="32"/>
@@ -8791,28 +8804,27 @@
         <v/>
       </c>
       <c r="BP33" s="50">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>3.8849291120924798</v>
       </c>
       <c r="BQ33" s="27">
         <f>IF(BL33&lt;&gt;"",BL33/0.000385,IF(BM33&lt;&gt;"",BM33/0.000385,BN33/0.000385))</f>
-        <v>0</v>
+        <v>41.214441531325463</v>
       </c>
       <c r="BR33" s="37">
         <f>IF(BL33&lt;&gt;"",BL33,IF(BM33&lt;&gt;"",BM33,BN33))</f>
-        <v>0</v>
+        <v>1.5867559989560302E-2</v>
       </c>
       <c r="BS33" s="32">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3.8849291120924798</v>
       </c>
     </row>
-    <row r="34" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C34">
         <v>12</v>
@@ -8918,7 +8930,7 @@
       </c>
       <c r="AM34" s="45">
         <f t="shared" ref="AM34:AM38" si="57">BR34</f>
-        <v>0</v>
+        <v>1.8262915191301601E-2</v>
       </c>
       <c r="AN34" s="44">
         <v>77.14</v>
@@ -8940,16 +8952,16 @@
         <v>1730.23</v>
       </c>
       <c r="AT34" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>23.549999999999997</v>
       </c>
       <c r="AU34" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>4.8299999999999983</v>
       </c>
       <c r="AV34" s="45">
-        <f t="shared" si="37"/>
-        <v>-28.230000000000018</v>
+        <f t="shared" si="33"/>
+        <v>28.230000000000018</v>
       </c>
       <c r="AW34" s="25">
         <v>15</v>
@@ -8970,8 +8982,14 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC34" s="11"/>
-      <c r="BD34" s="46"/>
-      <c r="BE34" s="22"/>
+      <c r="BD34" s="46">
+        <f>BM34*24*60/BH34</f>
+        <v>1.4824546855097438E-2</v>
+      </c>
+      <c r="BE34" s="22">
+        <f>BP34/BH34</f>
+        <v>3.4044862839259353E-3</v>
+      </c>
       <c r="BF34" s="11">
         <f t="shared" si="17"/>
         <v>1.3304924999999999E-2</v>
@@ -8994,15 +9012,14 @@
       </c>
       <c r="BK34" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>26.298597875474304</v>
       </c>
       <c r="BL34" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM34" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.8262915191301601E-2</v>
       </c>
       <c r="BN34" s="48" t="str">
         <f t="shared" si="32"/>
@@ -9013,28 +9030,27 @@
         <v/>
       </c>
       <c r="BP34" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>6.0395246228217703</v>
       </c>
       <c r="BQ34" s="28">
         <f t="shared" ref="BQ34:BQ38" si="58">IF(BL34&lt;&gt;"",BL34/0.000385,IF(BM34&lt;&gt;"",BM34/0.000385,BN34/0.000385))</f>
-        <v>0</v>
+        <v>47.436143354030136</v>
       </c>
       <c r="BR34" s="49">
         <f t="shared" ref="BR34:BR38" si="59">IF(BL34&lt;&gt;"",BL34,IF(BM34&lt;&gt;"",BM34,BN34))</f>
-        <v>0</v>
+        <v>1.8262915191301601E-2</v>
       </c>
       <c r="BS34" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>6.0395246228217703</v>
       </c>
     </row>
-    <row r="35" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C35">
         <v>12</v>
@@ -9138,7 +9154,7 @@
       </c>
       <c r="AM35" s="45">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1.47762479948186E-2</v>
       </c>
       <c r="AN35" s="44">
         <v>89.1</v>
@@ -9160,16 +9176,16 @@
         <v>1755.3</v>
       </c>
       <c r="AT35" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>37.979999999999997</v>
       </c>
       <c r="AU35" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>15.659999999999997</v>
       </c>
       <c r="AV35" s="45">
-        <f t="shared" si="37"/>
-        <v>-47.559999999999945</v>
+        <f t="shared" si="33"/>
+        <v>47.559999999999945</v>
       </c>
       <c r="AW35" s="25">
         <v>15</v>
@@ -9190,8 +9206,14 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC35" s="11"/>
-      <c r="BD35" s="46"/>
-      <c r="BE35" s="22"/>
+      <c r="BD35" s="46">
+        <f>BM35*24*60/BH35</f>
+        <v>1.1797665235722008E-2</v>
+      </c>
+      <c r="BE35" s="22">
+        <f>BP35/BH35</f>
+        <v>5.0807161037590871E-3</v>
+      </c>
       <c r="BF35" s="11">
         <f t="shared" si="17"/>
         <v>1.0388505599999999E-2</v>
@@ -9214,15 +9236,14 @@
       </c>
       <c r="BK35" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>21.277797112538785</v>
       </c>
       <c r="BL35" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM35" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.47762479948186E-2</v>
       </c>
       <c r="BN35" s="48" t="str">
         <f t="shared" si="32"/>
@@ -9233,34 +9254,36 @@
         <v/>
       </c>
       <c r="BP35" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>9.1633763360957392</v>
       </c>
       <c r="BQ35" s="28">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>38.379864921606753</v>
       </c>
       <c r="BR35" s="49">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>1.47762479948186E-2</v>
       </c>
       <c r="BS35" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>9.1633763360957392</v>
       </c>
     </row>
-    <row r="36" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C36">
         <v>12</v>
       </c>
       <c r="D36">
         <v>5</v>
+      </c>
+      <c r="E36" t="s">
+        <v>82</v>
       </c>
       <c r="F36" s="61">
         <v>45538.430219907401</v>
@@ -9303,7 +9326,9 @@
       <c r="T36" s="44">
         <v>0.12</v>
       </c>
-      <c r="U36" s="44"/>
+      <c r="U36" s="44">
+        <v>7.2</v>
+      </c>
       <c r="V36" s="44">
         <v>7.2439999999999998</v>
       </c>
@@ -9358,7 +9383,7 @@
       </c>
       <c r="AM36" s="45">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>2.469208333333333E-2</v>
       </c>
       <c r="AN36" s="44">
         <v>56.53</v>
@@ -9380,16 +9405,16 @@
         <v>1740.58</v>
       </c>
       <c r="AT36" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.450000000000003</v>
       </c>
       <c r="AU36" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>14.009999999999998</v>
       </c>
       <c r="AV36" s="45">
-        <f t="shared" si="37"/>
-        <v>-14.419999999999959</v>
+        <f t="shared" si="33"/>
+        <v>14.419999999999959</v>
       </c>
       <c r="AW36" s="25">
         <v>15</v>
@@ -9409,7 +9434,9 @@
       <c r="BB36" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC36" s="11"/>
+      <c r="BC36" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BE36" s="22"/>
       <c r="BF36" s="11">
         <f t="shared" si="17"/>
@@ -9433,11 +9460,11 @@
       </c>
       <c r="BK36" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>35.556599999999989</v>
       </c>
       <c r="BL36" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.469208333333333E-2</v>
       </c>
       <c r="BM36" s="48" t="str">
         <f t="shared" si="31"/>
@@ -9457,23 +9484,23 @@
       </c>
       <c r="BQ36" s="28">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>64.135281385281374</v>
       </c>
       <c r="BR36" s="49">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>2.469208333333333E-2</v>
       </c>
       <c r="BS36" s="30">
         <f t="shared" si="21"/>
         <v>13.155942</v>
       </c>
     </row>
-    <row r="37" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C37">
         <v>12</v>
@@ -9579,7 +9606,7 @@
       </c>
       <c r="AM37" s="45">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>1.6795874999999998E-2</v>
       </c>
       <c r="AN37" s="44">
         <v>85.27</v>
@@ -9601,16 +9628,16 @@
         <v>1700.44</v>
       </c>
       <c r="AT37" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>31.08</v>
       </c>
       <c r="AU37" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>14.14</v>
       </c>
       <c r="AV37" s="45">
-        <f t="shared" si="37"/>
-        <v>-37.159999999999968</v>
+        <f t="shared" si="33"/>
+        <v>37.159999999999968</v>
       </c>
       <c r="AW37" s="25">
         <v>15</v>
@@ -9630,7 +9657,9 @@
       <c r="BB37" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC37" s="11"/>
+      <c r="BC37" s="11">
+        <v>1.35E-2</v>
+      </c>
       <c r="BE37" s="22"/>
       <c r="BF37" s="11">
         <f t="shared" si="17"/>
@@ -9654,11 +9683,11 @@
       </c>
       <c r="BK37" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>24.186059999999998</v>
       </c>
       <c r="BL37" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.6795874999999998E-2</v>
       </c>
       <c r="BM37" s="48" t="str">
         <f t="shared" si="31"/>
@@ -9678,23 +9707,23 @@
       </c>
       <c r="BQ37" s="28">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>43.625649350649347</v>
       </c>
       <c r="BR37" s="49">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>1.6795874999999998E-2</v>
       </c>
       <c r="BS37" s="30">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C38" s="5">
         <v>12</v>
@@ -9801,7 +9830,7 @@
       </c>
       <c r="AM38" s="41">
         <f t="shared" si="57"/>
-        <v>0</v>
+        <v>2.48875E-2</v>
       </c>
       <c r="AN38" s="7">
         <v>81.16</v>
@@ -9823,16 +9852,16 @@
         <v>1753.34</v>
       </c>
       <c r="AT38" s="41">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>28.699999999999996</v>
       </c>
       <c r="AU38" s="41">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>14.14</v>
       </c>
       <c r="AV38" s="41">
-        <f t="shared" si="37"/>
-        <v>-35.129999999999995</v>
+        <f t="shared" si="33"/>
+        <v>35.129999999999995</v>
       </c>
       <c r="AW38" s="26">
         <v>15</v>
@@ -9852,7 +9881,9 @@
       <c r="BB38" s="23">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC38" s="12"/>
+      <c r="BC38" s="12">
+        <v>0.02</v>
+      </c>
       <c r="BD38" s="5"/>
       <c r="BE38" s="23"/>
       <c r="BF38" s="12">
@@ -9877,11 +9908,11 @@
       </c>
       <c r="BK38" s="14">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>35.837999999999994</v>
       </c>
       <c r="BL38" s="14">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.48875E-2</v>
       </c>
       <c r="BM38" s="48" t="str">
         <f t="shared" si="31"/>
@@ -9901,23 +9932,23 @@
       </c>
       <c r="BQ38" s="29">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>64.642857142857153</v>
       </c>
       <c r="BR38" s="38">
         <f t="shared" si="59"/>
-        <v>0</v>
+        <v>2.48875E-2</v>
       </c>
       <c r="BS38" s="31">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C39" s="3">
         <v>12</v>
@@ -9926,70 +9957,136 @@
         <v>6</v>
       </c>
       <c r="E39" s="3"/>
-      <c r="F39" s="60"/>
+      <c r="F39" s="60">
+        <v>45539.380868055603</v>
+      </c>
       <c r="G39" s="3">
         <v>3307.9</v>
       </c>
       <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6"/>
+      <c r="I39" s="6">
+        <v>3281.3249999999998</v>
+      </c>
+      <c r="J39" s="6">
+        <v>24.8</v>
+      </c>
+      <c r="K39" s="6">
+        <v>23.7</v>
+      </c>
+      <c r="L39" s="6">
+        <v>95.4</v>
+      </c>
+      <c r="M39" s="6">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="N39" s="6">
+        <v>349</v>
+      </c>
+      <c r="O39" s="6">
+        <v>1.21</v>
+      </c>
+      <c r="P39" s="6">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>4.84</v>
+      </c>
       <c r="R39" s="6"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="6"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="6"/>
-      <c r="AB39" s="6"/>
-      <c r="AC39" s="6"/>
-      <c r="AD39" s="16"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
+      <c r="S39" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0.09</v>
+      </c>
+      <c r="U39" s="6">
+        <v>1.31</v>
+      </c>
+      <c r="V39" s="6">
+        <v>7.2489999999999997</v>
+      </c>
+      <c r="W39" s="6">
+        <v>120.8</v>
+      </c>
+      <c r="X39" s="6">
+        <v>24.1</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>143.80000000000001</v>
+      </c>
+      <c r="AA39" s="6">
+        <v>51.4</v>
+      </c>
+      <c r="AB39" s="6">
+        <v>105.9</v>
+      </c>
+      <c r="AC39" s="6">
+        <v>19.5</v>
+      </c>
+      <c r="AD39" s="16">
+        <v>7.29</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>299</v>
+      </c>
+      <c r="AF39" s="6">
+        <v>50.9</v>
+      </c>
+      <c r="AG39" s="6">
+        <v>7.3</v>
+      </c>
       <c r="AH39" s="40">
         <f>AF39/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI39" s="6"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="44"/>
-      <c r="AL39" s="6"/>
+        <v>0.50900000000000001</v>
+      </c>
+      <c r="AI39" s="6">
+        <v>34</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>22.07</v>
+      </c>
+      <c r="AK39" s="44">
+        <v>17.079999999999998</v>
+      </c>
+      <c r="AL39" s="6">
+        <v>3.78</v>
+      </c>
       <c r="AM39" s="42">
         <f>BR39</f>
-        <v>0</v>
-      </c>
-      <c r="AN39" s="6"/>
-      <c r="AO39" s="6"/>
-      <c r="AP39" s="6"/>
-      <c r="AQ39" s="6"/>
+        <v>7.8356545194428005E-3</v>
+      </c>
+      <c r="AN39" s="6">
+        <v>101.83</v>
+      </c>
+      <c r="AO39" s="6">
+        <v>56.98</v>
+      </c>
+      <c r="AP39" s="6">
+        <v>572</v>
+      </c>
+      <c r="AQ39" s="6">
+        <v>1873</v>
+      </c>
       <c r="AR39" s="40">
         <v>137.11999999999989</v>
       </c>
       <c r="AS39" s="40">
         <f t="shared" si="60"/>
-        <v>-137.11999999999989</v>
+        <v>1735.88</v>
       </c>
       <c r="AT39" s="40">
-        <f t="shared" si="35"/>
-        <v>-77.8</v>
+        <f t="shared" si="36"/>
+        <v>24.03</v>
       </c>
       <c r="AU39" s="40">
-        <f t="shared" si="36"/>
-        <v>-52.48</v>
+        <f t="shared" si="37"/>
+        <v>4.5</v>
       </c>
       <c r="AV39" s="40">
-        <f t="shared" si="37"/>
-        <v>-598</v>
+        <f t="shared" si="33"/>
+        <v>26</v>
       </c>
       <c r="AW39" s="24">
         <v>15</v>
@@ -10010,39 +10107,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC39" s="8"/>
-      <c r="BD39" s="9"/>
-      <c r="BE39" s="21"/>
+      <c r="BD39" s="46">
+        <f>BM39*24*60/BH39</f>
+        <v>6.2798972071627691E-3</v>
+      </c>
+      <c r="BE39" s="22">
+        <f>BP39/BH39</f>
+        <v>8.5936872387829075E-4</v>
+      </c>
       <c r="BF39" s="8">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.2774821399999999E-2</v>
       </c>
       <c r="BG39" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>18.395742815999998</v>
       </c>
       <c r="BH39" s="9">
         <f t="shared" si="41"/>
-        <v>1595</v>
-      </c>
-      <c r="BI39" s="10" t="str">
+        <v>1796.74</v>
+      </c>
+      <c r="BI39" s="10">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ39" s="10" t="str">
+        <v>5.667486670302882E-2</v>
+      </c>
+      <c r="BJ39" s="10">
         <f t="shared" si="9"/>
-        <v/>
+        <v>5.9900000000000002E-2</v>
       </c>
       <c r="BK39" s="10">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>11.283342507997634</v>
       </c>
       <c r="BL39" s="10" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM39" s="10">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>7.8356545194428005E-3</v>
       </c>
       <c r="BN39" s="35" t="str">
         <f t="shared" si="32"/>
@@ -10053,28 +10155,27 @@
         <v/>
       </c>
       <c r="BP39" s="50">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1.5440621609410801</v>
       </c>
       <c r="BQ39" s="27">
         <f>IF(BL39&lt;&gt;"",BL39/0.000385,IF(BM39&lt;&gt;"",BM39/0.000385,BN39/0.000385))</f>
-        <v>0</v>
+        <v>20.352349401150132</v>
       </c>
       <c r="BR39" s="37">
         <f>IF(BL39&lt;&gt;"",BL39,IF(BM39&lt;&gt;"",BM39,BN39))</f>
-        <v>0</v>
+        <v>7.8356545194428005E-3</v>
       </c>
       <c r="BS39" s="32">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1.5440621609410801</v>
       </c>
     </row>
-    <row r="40" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C40">
         <v>12</v>
@@ -10082,70 +10183,136 @@
       <c r="D40">
         <v>6</v>
       </c>
-      <c r="F40" s="61"/>
+      <c r="F40" s="61">
+        <v>45539.3855555556</v>
+      </c>
       <c r="G40">
         <v>3307.9</v>
       </c>
       <c r="H40" s="44"/>
-      <c r="I40" s="44"/>
-      <c r="J40" s="44"/>
-      <c r="K40" s="44"/>
-      <c r="L40" s="44"/>
-      <c r="M40" s="44"/>
-      <c r="N40" s="44"/>
-      <c r="O40" s="44"/>
-      <c r="P40" s="44"/>
-      <c r="Q40" s="44"/>
+      <c r="I40" s="44">
+        <v>3228.69</v>
+      </c>
+      <c r="J40" s="44">
+        <v>22.5</v>
+      </c>
+      <c r="K40" s="44">
+        <v>21.3</v>
+      </c>
+      <c r="L40" s="44">
+        <v>94.8</v>
+      </c>
+      <c r="M40" s="44">
+        <v>17.3</v>
+      </c>
+      <c r="N40" s="44">
+        <v>352</v>
+      </c>
+      <c r="O40" s="44">
+        <v>1.24</v>
+      </c>
+      <c r="P40" s="44">
+        <v>0.27</v>
+      </c>
+      <c r="Q40" s="44">
+        <v>4.63</v>
+      </c>
       <c r="R40" s="44"/>
-      <c r="S40" s="44"/>
-      <c r="T40" s="44"/>
-      <c r="U40" s="44"/>
-      <c r="V40" s="44"/>
-      <c r="W40" s="44"/>
-      <c r="X40" s="44"/>
-      <c r="Y40" s="44"/>
-      <c r="Z40" s="44"/>
-      <c r="AA40" s="44"/>
-      <c r="AB40" s="44"/>
-      <c r="AC40" s="44"/>
-      <c r="AD40" s="17"/>
-      <c r="AE40" s="44"/>
-      <c r="AF40" s="44"/>
-      <c r="AG40" s="44"/>
+      <c r="S40" s="44">
+        <v>0.19</v>
+      </c>
+      <c r="T40" s="44">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="U40" s="44">
+        <v>1.24</v>
+      </c>
+      <c r="V40" s="44">
+        <v>7.26</v>
+      </c>
+      <c r="W40" s="44">
+        <v>131.30000000000001</v>
+      </c>
+      <c r="X40" s="44">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="Y40" s="44">
+        <v>2.16</v>
+      </c>
+      <c r="Z40" s="44">
+        <v>148.80000000000001</v>
+      </c>
+      <c r="AA40" s="44">
+        <v>57.3</v>
+      </c>
+      <c r="AB40" s="44">
+        <v>115.2</v>
+      </c>
+      <c r="AC40" s="44">
+        <v>26.5</v>
+      </c>
+      <c r="AD40" s="17">
+        <v>7.3010000000000002</v>
+      </c>
+      <c r="AE40" s="44">
+        <v>300</v>
+      </c>
+      <c r="AF40" s="44">
+        <v>49.1</v>
+      </c>
+      <c r="AG40" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH40" s="45">
         <f t="shared" ref="AH40:AH44" si="61">AF40/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI40" s="44"/>
-      <c r="AJ40" s="44"/>
-      <c r="AK40" s="44"/>
-      <c r="AL40" s="44"/>
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="AI40" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ40" s="44">
+        <v>24.57</v>
+      </c>
+      <c r="AK40" s="44">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="AL40" s="44">
+        <v>2.19</v>
+      </c>
       <c r="AM40" s="45">
         <f t="shared" ref="AM40:AM44" si="62">BR40</f>
-        <v>0</v>
-      </c>
-      <c r="AN40" s="44"/>
-      <c r="AO40" s="44"/>
-      <c r="AP40" s="44"/>
-      <c r="AQ40" s="44"/>
+        <v>1.24636201409791E-2</v>
+      </c>
+      <c r="AN40" s="44">
+        <v>103.58</v>
+      </c>
+      <c r="AO40" s="44">
+        <v>57.93</v>
+      </c>
+      <c r="AP40" s="44">
+        <v>576</v>
+      </c>
+      <c r="AQ40" s="44">
+        <v>1800</v>
+      </c>
       <c r="AR40" s="45">
         <v>45.769999999999982</v>
       </c>
       <c r="AS40" s="45">
         <f t="shared" si="60"/>
-        <v>-45.769999999999982</v>
+        <v>1754.23</v>
       </c>
       <c r="AT40" s="45">
-        <f t="shared" si="35"/>
-        <v>-77.14</v>
+        <f t="shared" si="36"/>
+        <v>26.439999999999998</v>
       </c>
       <c r="AU40" s="45">
-        <f t="shared" si="36"/>
-        <v>-51.28</v>
+        <f t="shared" si="37"/>
+        <v>6.6499999999999986</v>
       </c>
       <c r="AV40" s="45">
-        <f t="shared" si="37"/>
-        <v>-604</v>
+        <f t="shared" si="33"/>
+        <v>28</v>
       </c>
       <c r="AW40" s="25">
         <v>15</v>
@@ -10166,39 +10333,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC40" s="11"/>
-      <c r="BD40" s="46"/>
-      <c r="BE40" s="22"/>
+      <c r="BD40" s="46">
+        <f>BM40*24*60/BH40</f>
+        <v>9.9688469609079833E-3</v>
+      </c>
+      <c r="BE40" s="22">
+        <f>BP40/BH40</f>
+        <v>1.0000000000000001E-7</v>
+      </c>
       <c r="BF40" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.1504364299999998E-2</v>
       </c>
       <c r="BG40" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.566284591999995</v>
       </c>
       <c r="BH40" s="46">
         <f t="shared" si="41"/>
-        <v>1595</v>
-      </c>
-      <c r="BI40" s="47" t="str">
+        <v>1800.37</v>
+      </c>
+      <c r="BI40" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ40" s="47" t="str">
+        <v>5.7532618295128228E-2</v>
+      </c>
+      <c r="BJ40" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>6.0929411764705885E-2</v>
       </c>
       <c r="BK40" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>17.947613003009906</v>
       </c>
       <c r="BL40" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM40" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.24636201409791E-2</v>
       </c>
       <c r="BN40" s="48" t="str">
         <f t="shared" si="32"/>
@@ -10209,28 +10381,27 @@
         <v/>
       </c>
       <c r="BP40" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1.80037E-4</v>
       </c>
       <c r="BQ40" s="28">
         <f t="shared" ref="BQ40:BQ44" si="63">IF(BL40&lt;&gt;"",BL40/0.000385,IF(BM40&lt;&gt;"",BM40/0.000385,BN40/0.000385))</f>
-        <v>0</v>
+        <v>32.373039327218443</v>
       </c>
       <c r="BR40" s="49">
         <f t="shared" ref="BR40:BR44" si="64">IF(BL40&lt;&gt;"",BL40,IF(BM40&lt;&gt;"",BM40,BN40))</f>
-        <v>0</v>
+        <v>1.24636201409791E-2</v>
       </c>
       <c r="BS40" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1.80037E-4</v>
       </c>
     </row>
-    <row r="41" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C41">
         <v>12</v>
@@ -10238,70 +10409,136 @@
       <c r="D41">
         <v>6</v>
       </c>
-      <c r="F41" s="61"/>
+      <c r="F41" s="61">
+        <v>45539.395648148202</v>
+      </c>
       <c r="G41">
         <v>3307.9</v>
       </c>
       <c r="H41" s="44"/>
-      <c r="I41" s="44"/>
-      <c r="J41" s="44"/>
-      <c r="K41" s="44"/>
-      <c r="L41" s="44"/>
-      <c r="M41" s="44"/>
-      <c r="N41" s="44"/>
-      <c r="O41" s="44"/>
-      <c r="P41" s="44"/>
-      <c r="Q41" s="44"/>
+      <c r="I41" s="44">
+        <v>2691.27</v>
+      </c>
+      <c r="J41" s="44">
+        <v>23.5</v>
+      </c>
+      <c r="K41" s="44">
+        <v>18.8</v>
+      </c>
+      <c r="L41" s="44">
+        <v>80.099999999999994</v>
+      </c>
+      <c r="M41" s="44">
+        <v>17.7</v>
+      </c>
+      <c r="N41" s="44">
+        <v>415</v>
+      </c>
+      <c r="O41" s="44">
+        <v>1.75</v>
+      </c>
+      <c r="P41" s="44">
+        <v>0.3</v>
+      </c>
+      <c r="Q41" s="44">
+        <v>5.42</v>
+      </c>
       <c r="R41" s="44"/>
-      <c r="S41" s="44"/>
-      <c r="T41" s="44"/>
-      <c r="U41" s="44"/>
-      <c r="V41" s="44"/>
-      <c r="W41" s="44"/>
-      <c r="X41" s="44"/>
-      <c r="Y41" s="44"/>
-      <c r="Z41" s="44"/>
-      <c r="AA41" s="44"/>
-      <c r="AB41" s="44"/>
-      <c r="AC41" s="44"/>
-      <c r="AD41" s="17"/>
-      <c r="AE41" s="44"/>
-      <c r="AF41" s="44"/>
-      <c r="AG41" s="44"/>
+      <c r="S41" s="44">
+        <v>0.22</v>
+      </c>
+      <c r="T41" s="44">
+        <v>0.11</v>
+      </c>
+      <c r="U41" s="44">
+        <v>4.7</v>
+      </c>
+      <c r="V41" s="44">
+        <v>7.1950000000000003</v>
+      </c>
+      <c r="W41" s="44">
+        <v>105.3</v>
+      </c>
+      <c r="X41" s="44">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="Y41" s="44">
+        <v>2.12</v>
+      </c>
+      <c r="Z41" s="44">
+        <v>167</v>
+      </c>
+      <c r="AA41" s="44">
+        <v>39.4</v>
+      </c>
+      <c r="AB41" s="44">
+        <v>92.3</v>
+      </c>
+      <c r="AC41" s="44">
+        <v>30.9</v>
+      </c>
+      <c r="AD41" s="17">
+        <v>7.2350000000000003</v>
+      </c>
+      <c r="AE41" s="44">
+        <v>298</v>
+      </c>
+      <c r="AF41" s="44">
+        <v>49.2</v>
+      </c>
+      <c r="AG41" s="44">
+        <v>7.22</v>
+      </c>
       <c r="AH41" s="45">
         <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="AI41" s="44"/>
-      <c r="AJ41" s="44"/>
-      <c r="AK41" s="44"/>
-      <c r="AL41" s="44"/>
+        <v>0.49200000000000005</v>
+      </c>
+      <c r="AI41" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ41" s="44">
+        <v>38.049999999999997</v>
+      </c>
+      <c r="AK41" s="44">
+        <v>1.24</v>
+      </c>
+      <c r="AL41" s="44">
+        <v>4.79</v>
+      </c>
       <c r="AM41" s="45">
         <f t="shared" si="62"/>
-        <v>0</v>
-      </c>
-      <c r="AN41" s="44"/>
-      <c r="AO41" s="44"/>
-      <c r="AP41" s="44"/>
-      <c r="AQ41" s="44"/>
+        <v>2.7129539122498301E-2</v>
+      </c>
+      <c r="AN41" s="44">
+        <v>113.88</v>
+      </c>
+      <c r="AO41" s="44">
+        <v>71.12</v>
+      </c>
+      <c r="AP41" s="44">
+        <v>547</v>
+      </c>
+      <c r="AQ41" s="44">
+        <v>1857</v>
+      </c>
       <c r="AR41" s="45">
         <v>84.700000000000045</v>
       </c>
       <c r="AS41" s="45">
         <f t="shared" si="60"/>
-        <v>-84.700000000000045</v>
+        <v>1772.3</v>
       </c>
       <c r="AT41" s="45">
-        <f t="shared" si="35"/>
-        <v>-89.1</v>
+        <f t="shared" si="36"/>
+        <v>24.78</v>
       </c>
       <c r="AU41" s="45">
-        <f t="shared" si="36"/>
-        <v>-61.29</v>
+        <f t="shared" si="37"/>
+        <v>9.8300000000000054</v>
       </c>
       <c r="AV41" s="45">
-        <f t="shared" si="37"/>
-        <v>-574</v>
+        <f t="shared" ref="AV41:AV72" si="65">AP35-AP41</f>
+        <v>27</v>
       </c>
       <c r="AW41" s="25">
         <v>15</v>
@@ -10322,39 +10559,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC41" s="11"/>
-      <c r="BD41" s="46"/>
-      <c r="BE41" s="22"/>
+      <c r="BD41" s="46">
+        <f>BM41*24*60/BH41</f>
+        <v>2.1417117854698017E-2</v>
+      </c>
+      <c r="BE41" s="22">
+        <f>BP41/BH41</f>
+        <v>1.0000000000000001E-7</v>
+      </c>
       <c r="BF41" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.02878112E-2</v>
       </c>
       <c r="BG41" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.814448128</v>
       </c>
       <c r="BH41" s="46">
         <f t="shared" si="41"/>
-        <v>1595</v>
-      </c>
-      <c r="BI41" s="47" t="str">
+        <v>1824.08</v>
+      </c>
+      <c r="BI41" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ41" s="47" t="str">
+        <v>6.2431472303846325E-2</v>
+      </c>
+      <c r="BJ41" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>6.698823529411764E-2</v>
       </c>
       <c r="BK41" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>39.066536336397554</v>
       </c>
       <c r="BL41" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM41" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>2.7129539122498301E-2</v>
       </c>
       <c r="BN41" s="48" t="str">
         <f t="shared" si="32"/>
@@ -10365,28 +10607,27 @@
         <v/>
       </c>
       <c r="BP41" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1.8240800000000001E-4</v>
       </c>
       <c r="BQ41" s="28">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>70.466335383112479</v>
       </c>
       <c r="BR41" s="49">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>2.7129539122498301E-2</v>
       </c>
       <c r="BS41" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1.8240800000000001E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C42">
         <v>12</v>
@@ -10394,70 +10635,136 @@
       <c r="D42">
         <v>6</v>
       </c>
-      <c r="F42" s="61"/>
+      <c r="F42" s="61">
+        <v>45539.400208333303</v>
+      </c>
       <c r="G42">
         <v>3307.9</v>
       </c>
       <c r="H42" s="44"/>
-      <c r="I42" s="44"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="44"/>
-      <c r="L42" s="44"/>
-      <c r="M42" s="44"/>
-      <c r="N42" s="44"/>
-      <c r="O42" s="44"/>
-      <c r="P42" s="44"/>
-      <c r="Q42" s="44"/>
+      <c r="I42" s="44">
+        <v>2749.875</v>
+      </c>
+      <c r="J42" s="44">
+        <v>21.1</v>
+      </c>
+      <c r="K42" s="44">
+        <v>18.5</v>
+      </c>
+      <c r="L42" s="44">
+        <v>87.6</v>
+      </c>
+      <c r="M42" s="44">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="N42" s="44">
+        <v>409</v>
+      </c>
+      <c r="O42" s="44">
+        <v>1</v>
+      </c>
+      <c r="P42" s="44">
+        <v>0.3</v>
+      </c>
+      <c r="Q42" s="44">
+        <v>4.26</v>
+      </c>
       <c r="R42" s="44"/>
-      <c r="S42" s="44"/>
-      <c r="T42" s="44"/>
-      <c r="U42" s="44"/>
-      <c r="V42" s="44"/>
-      <c r="W42" s="44"/>
-      <c r="X42" s="44"/>
-      <c r="Y42" s="44"/>
-      <c r="Z42" s="44"/>
-      <c r="AA42" s="44"/>
-      <c r="AB42" s="44"/>
-      <c r="AC42" s="44"/>
-      <c r="AD42" s="17"/>
-      <c r="AE42" s="44"/>
-      <c r="AF42" s="44"/>
-      <c r="AG42" s="44"/>
+      <c r="S42" s="44">
+        <v>0.2</v>
+      </c>
+      <c r="T42" s="44">
+        <v>0.09</v>
+      </c>
+      <c r="U42" s="44">
+        <v>5.07</v>
+      </c>
+      <c r="V42" s="44">
+        <v>7.2649999999999997</v>
+      </c>
+      <c r="W42" s="44">
+        <v>104.6</v>
+      </c>
+      <c r="X42" s="44">
+        <v>22.8</v>
+      </c>
+      <c r="Y42" s="44">
+        <v>2.44</v>
+      </c>
+      <c r="Z42" s="44">
+        <v>171.4</v>
+      </c>
+      <c r="AA42" s="44">
+        <v>46.3</v>
+      </c>
+      <c r="AB42" s="44">
+        <v>91.8</v>
+      </c>
+      <c r="AC42" s="44">
+        <v>18.5</v>
+      </c>
+      <c r="AD42" s="17">
+        <v>7.306</v>
+      </c>
+      <c r="AE42" s="44">
+        <v>301</v>
+      </c>
+      <c r="AF42" s="44">
+        <v>50.3</v>
+      </c>
+      <c r="AG42" s="44">
+        <v>7.29</v>
+      </c>
       <c r="AH42" s="45">
         <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="AI42" s="44"/>
-      <c r="AJ42" s="44"/>
-      <c r="AK42" s="44"/>
-      <c r="AL42" s="44"/>
+        <v>0.503</v>
+      </c>
+      <c r="AI42" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ42" s="44">
+        <v>43.09</v>
+      </c>
+      <c r="AK42" s="44">
+        <v>7.3</v>
+      </c>
+      <c r="AL42" s="44">
+        <v>4.8600000000000003</v>
+      </c>
       <c r="AM42" s="45">
         <f t="shared" si="62"/>
         <v>0</v>
       </c>
-      <c r="AN42" s="44"/>
-      <c r="AO42" s="44"/>
-      <c r="AP42" s="44"/>
-      <c r="AQ42" s="44"/>
+      <c r="AN42" s="44">
+        <v>88.68</v>
+      </c>
+      <c r="AO42" s="44">
+        <v>80.87</v>
+      </c>
+      <c r="AP42" s="44">
+        <v>580</v>
+      </c>
+      <c r="AQ42" s="44">
+        <v>1823</v>
+      </c>
       <c r="AR42" s="45">
         <v>47.420000000000073</v>
       </c>
       <c r="AS42" s="45">
         <f t="shared" si="60"/>
-        <v>-47.420000000000073</v>
+        <v>1775.58</v>
       </c>
       <c r="AT42" s="45">
-        <f t="shared" si="35"/>
-        <v>-56.53</v>
+        <f t="shared" si="36"/>
+        <v>32.150000000000006</v>
       </c>
       <c r="AU42" s="45">
-        <f t="shared" si="36"/>
-        <v>-57.03</v>
+        <f t="shared" si="37"/>
+        <v>23.840000000000003</v>
       </c>
       <c r="AV42" s="45">
-        <f t="shared" si="37"/>
-        <v>-615</v>
+        <f t="shared" si="65"/>
+        <v>35</v>
       </c>
       <c r="AW42" s="25">
         <v>15</v>
@@ -10481,23 +10788,23 @@
       <c r="BE42" s="22"/>
       <c r="BF42" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.0099889999999999E-2</v>
       </c>
       <c r="BG42" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.543841599999997</v>
       </c>
       <c r="BH42" s="46">
         <f t="shared" si="41"/>
-        <v>1595</v>
-      </c>
-      <c r="BI42" s="47" t="str">
+        <v>1819.8</v>
+      </c>
+      <c r="BI42" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ42" s="47" t="str">
+        <v>4.8730629739531822E-2</v>
+      </c>
+      <c r="BJ42" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>5.2164705882352946E-2</v>
       </c>
       <c r="BK42" s="47">
         <f t="shared" si="18"/>
@@ -10517,7 +10824,7 @@
       </c>
       <c r="BO42" s="47">
         <f t="shared" si="47"/>
-        <v>11.9625</v>
+        <v>0</v>
       </c>
       <c r="BP42" s="51" t="str">
         <f t="shared" si="28"/>
@@ -10533,15 +10840,15 @@
       </c>
       <c r="BS42" s="30">
         <f t="shared" si="21"/>
-        <v>11.9625</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B43" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C43">
         <v>12</v>
@@ -10549,70 +10856,134 @@
       <c r="D43">
         <v>6</v>
       </c>
-      <c r="F43" s="61"/>
+      <c r="F43" s="61">
+        <v>45539.404884259297</v>
+      </c>
       <c r="G43">
         <v>3307.9</v>
       </c>
       <c r="H43" s="44"/>
-      <c r="I43" s="44"/>
-      <c r="J43" s="44"/>
-      <c r="K43" s="44"/>
-      <c r="L43" s="44"/>
-      <c r="M43" s="44"/>
-      <c r="N43" s="44"/>
-      <c r="O43" s="44"/>
-      <c r="P43" s="44"/>
-      <c r="Q43" s="44"/>
+      <c r="I43" s="44">
+        <v>2520.75</v>
+      </c>
+      <c r="J43" s="44">
+        <v>22.5</v>
+      </c>
+      <c r="K43" s="44">
+        <v>18.3</v>
+      </c>
+      <c r="L43" s="44">
+        <v>81.099999999999994</v>
+      </c>
+      <c r="M43" s="44">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="N43" s="44">
+        <v>451</v>
+      </c>
+      <c r="O43" s="44">
+        <v>2.66</v>
+      </c>
+      <c r="P43" s="44">
+        <v>0.33</v>
+      </c>
+      <c r="Q43" s="44">
+        <v>0.04</v>
+      </c>
       <c r="R43" s="44"/>
-      <c r="S43" s="44"/>
-      <c r="T43" s="44"/>
+      <c r="S43" s="44">
+        <v>0.68</v>
+      </c>
+      <c r="T43" s="44">
+        <v>1.76</v>
+      </c>
       <c r="U43" s="44"/>
-      <c r="V43" s="44"/>
-      <c r="W43" s="44"/>
-      <c r="X43" s="44"/>
-      <c r="Y43" s="44"/>
-      <c r="Z43" s="44"/>
-      <c r="AA43" s="44"/>
-      <c r="AB43" s="44"/>
-      <c r="AC43" s="44"/>
-      <c r="AD43" s="17"/>
-      <c r="AE43" s="44"/>
-      <c r="AF43" s="44"/>
-      <c r="AG43" s="44"/>
+      <c r="V43" s="44">
+        <v>6.9939999999999998</v>
+      </c>
+      <c r="W43" s="44">
+        <v>57.5</v>
+      </c>
+      <c r="X43" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="44">
+        <v>3.83</v>
+      </c>
+      <c r="Z43" s="44">
+        <v>193.9</v>
+      </c>
+      <c r="AA43" s="44">
+        <v>13.5</v>
+      </c>
+      <c r="AB43" s="44">
+        <v>50.4</v>
+      </c>
+      <c r="AC43" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="17">
+        <v>7.03</v>
+      </c>
+      <c r="AE43" s="44">
+        <v>299</v>
+      </c>
+      <c r="AF43" s="44">
+        <v>49.1</v>
+      </c>
+      <c r="AG43" s="44">
+        <v>7.1</v>
+      </c>
       <c r="AH43" s="45">
         <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="AI43" s="44"/>
-      <c r="AJ43" s="44"/>
-      <c r="AK43" s="44"/>
-      <c r="AL43" s="44"/>
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="AI43" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ43" s="44">
+        <v>53.46</v>
+      </c>
+      <c r="AK43" s="44">
+        <v>7.31</v>
+      </c>
+      <c r="AL43" s="44">
+        <v>4.6100000000000003</v>
+      </c>
       <c r="AM43" s="45">
         <f t="shared" si="62"/>
         <v>0</v>
       </c>
-      <c r="AN43" s="44"/>
-      <c r="AO43" s="44"/>
-      <c r="AP43" s="44"/>
-      <c r="AQ43" s="44"/>
+      <c r="AN43" s="44">
+        <v>111.39</v>
+      </c>
+      <c r="AO43" s="44">
+        <v>54.88</v>
+      </c>
+      <c r="AP43" s="44">
+        <v>531</v>
+      </c>
+      <c r="AQ43" s="44">
+        <v>1854</v>
+      </c>
       <c r="AR43" s="45">
         <v>133.55999999999995</v>
       </c>
       <c r="AS43" s="45">
         <f t="shared" si="60"/>
-        <v>-133.55999999999995</v>
+        <v>1720.44</v>
       </c>
       <c r="AT43" s="45">
-        <f t="shared" si="35"/>
-        <v>-85.27</v>
+        <f t="shared" si="36"/>
+        <v>26.120000000000005</v>
       </c>
       <c r="AU43" s="45">
-        <f t="shared" si="36"/>
-        <v>-54.88</v>
+        <f t="shared" si="37"/>
+        <v>0</v>
       </c>
       <c r="AV43" s="45">
-        <f t="shared" si="37"/>
-        <v>-560</v>
+        <f t="shared" si="65"/>
+        <v>29</v>
       </c>
       <c r="AW43" s="25">
         <v>15</v>
@@ -10636,23 +11007,23 @@
       <c r="BE43" s="22"/>
       <c r="BF43" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.0028308500000001E-2</v>
       </c>
       <c r="BG43" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.440764240000002</v>
       </c>
       <c r="BH43" s="46">
         <f t="shared" si="41"/>
-        <v>1595</v>
-      </c>
-      <c r="BI43" s="47" t="str">
+        <v>1826.65</v>
+      </c>
+      <c r="BI43" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ43" s="47" t="str">
+        <v>6.098048339857115E-2</v>
+      </c>
+      <c r="BJ43" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>6.5523529411764703E-2</v>
       </c>
       <c r="BK43" s="47">
         <f t="shared" si="18"/>
@@ -10672,7 +11043,7 @@
       </c>
       <c r="BO43" s="47">
         <f t="shared" si="47"/>
-        <v>11.9625</v>
+        <v>13.51721</v>
       </c>
       <c r="BP43" s="51" t="str">
         <f t="shared" si="28"/>
@@ -10688,15 +11059,15 @@
       </c>
       <c r="BS43" s="30">
         <f t="shared" si="21"/>
-        <v>11.9625</v>
+        <v>13.51721</v>
       </c>
     </row>
-    <row r="44" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C44" s="5">
         <v>12</v>
@@ -10705,70 +11076,136 @@
         <v>6</v>
       </c>
       <c r="E44" s="5"/>
-      <c r="F44" s="62"/>
+      <c r="F44" s="62">
+        <v>45539.410046296303</v>
+      </c>
       <c r="G44" s="5">
         <v>3307.9</v>
       </c>
       <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
-      <c r="N44" s="7"/>
-      <c r="O44" s="7"/>
-      <c r="P44" s="7"/>
-      <c r="Q44" s="7"/>
+      <c r="I44" s="7">
+        <v>3281.13</v>
+      </c>
+      <c r="J44" s="7">
+        <v>21.3</v>
+      </c>
+      <c r="K44" s="7">
+        <v>20</v>
+      </c>
+      <c r="L44" s="7">
+        <v>94.2</v>
+      </c>
+      <c r="M44" s="7">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="N44" s="7">
+        <v>370</v>
+      </c>
+      <c r="O44" s="7">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="P44" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="Q44" s="7">
+        <v>4.78</v>
+      </c>
       <c r="R44" s="7"/>
-      <c r="S44" s="7"/>
-      <c r="T44" s="7"/>
-      <c r="U44" s="7"/>
-      <c r="V44" s="7"/>
-      <c r="W44" s="7"/>
-      <c r="X44" s="7"/>
-      <c r="Y44" s="7"/>
-      <c r="Z44" s="7"/>
-      <c r="AA44" s="7"/>
-      <c r="AB44" s="7"/>
-      <c r="AC44" s="7"/>
-      <c r="AD44" s="18"/>
-      <c r="AE44" s="7"/>
-      <c r="AF44" s="7"/>
-      <c r="AG44" s="7"/>
+      <c r="S44" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="T44" s="7">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="U44" s="7">
+        <v>2.19</v>
+      </c>
+      <c r="V44" s="7">
+        <v>7.2569999999999997</v>
+      </c>
+      <c r="W44" s="7">
+        <v>117.5</v>
+      </c>
+      <c r="X44" s="7">
+        <v>23</v>
+      </c>
+      <c r="Y44" s="7">
+        <v>1.92</v>
+      </c>
+      <c r="Z44" s="7">
+        <v>154.9</v>
+      </c>
+      <c r="AA44" s="7">
+        <v>51</v>
+      </c>
+      <c r="AB44" s="7">
+        <v>103.1</v>
+      </c>
+      <c r="AC44" s="7">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="AD44" s="18">
+        <v>7.2990000000000004</v>
+      </c>
+      <c r="AE44" s="7">
+        <v>300</v>
+      </c>
+      <c r="AF44" s="7">
+        <v>50.1</v>
+      </c>
+      <c r="AG44" s="7">
+        <v>7.3</v>
+      </c>
       <c r="AH44" s="41">
         <f t="shared" si="61"/>
-        <v>0</v>
-      </c>
-      <c r="AI44" s="7"/>
-      <c r="AJ44" s="7"/>
-      <c r="AK44" s="7"/>
-      <c r="AL44" s="7"/>
+        <v>0.501</v>
+      </c>
+      <c r="AI44" s="7">
+        <v>34</v>
+      </c>
+      <c r="AJ44" s="7">
+        <v>28.27</v>
+      </c>
+      <c r="AK44" s="7">
+        <v>18.29</v>
+      </c>
+      <c r="AL44" s="7">
+        <v>4.66</v>
+      </c>
       <c r="AM44" s="41">
         <f t="shared" si="62"/>
         <v>0</v>
       </c>
-      <c r="AN44" s="7"/>
-      <c r="AO44" s="7"/>
-      <c r="AP44" s="7"/>
-      <c r="AQ44" s="7"/>
+      <c r="AN44" s="7">
+        <v>116.7</v>
+      </c>
+      <c r="AO44" s="7">
+        <v>56.59</v>
+      </c>
+      <c r="AP44" s="7">
+        <v>558</v>
+      </c>
+      <c r="AQ44" s="7">
+        <v>1843</v>
+      </c>
       <c r="AR44" s="41">
         <v>51.660000000000082</v>
       </c>
       <c r="AS44" s="41">
         <f t="shared" si="60"/>
-        <v>-51.660000000000082</v>
+        <v>1791.34</v>
       </c>
       <c r="AT44" s="41">
-        <f t="shared" si="35"/>
-        <v>-81.16</v>
+        <f t="shared" si="36"/>
+        <v>35.540000000000006</v>
       </c>
       <c r="AU44" s="41">
-        <f t="shared" si="36"/>
-        <v>-56.59</v>
+        <f t="shared" si="37"/>
+        <v>0</v>
       </c>
       <c r="AV44" s="41">
-        <f t="shared" si="37"/>
-        <v>-598</v>
+        <f t="shared" si="65"/>
+        <v>40</v>
       </c>
       <c r="AW44" s="26">
         <v>15</v>
@@ -10793,23 +11230,23 @@
       <c r="BE44" s="23"/>
       <c r="BF44" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.0917059999999999E-2</v>
       </c>
       <c r="BG44" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15.720566399999999</v>
       </c>
       <c r="BH44" s="13">
         <f t="shared" si="41"/>
-        <v>1595</v>
-      </c>
-      <c r="BI44" s="14" t="str">
+        <v>1819.51</v>
+      </c>
+      <c r="BI44" s="14">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ44" s="14" t="str">
+        <v>6.4138147083555461E-2</v>
+      </c>
+      <c r="BJ44" s="14">
         <f t="shared" si="9"/>
-        <v/>
+        <v>6.8647058823529408E-2</v>
       </c>
       <c r="BK44" s="14">
         <f t="shared" si="18"/>
@@ -10829,7 +11266,7 @@
       </c>
       <c r="BO44" s="14">
         <f t="shared" si="47"/>
-        <v>11.9625</v>
+        <v>0</v>
       </c>
       <c r="BP44" s="52" t="str">
         <f t="shared" si="28"/>
@@ -10845,15 +11282,15 @@
       </c>
       <c r="BS44" s="31">
         <f t="shared" si="21"/>
-        <v>11.9625</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C45" s="3">
         <v>12</v>
@@ -10916,16 +11353,16 @@
         <v>-137.11999999999989</v>
       </c>
       <c r="AT45" s="40">
-        <f t="shared" si="35"/>
-        <v>0</v>
+        <f t="shared" si="36"/>
+        <v>-101.83</v>
       </c>
       <c r="AU45" s="40">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>-56.98</v>
       </c>
       <c r="AV45" s="40">
-        <f t="shared" si="37"/>
-        <v>0</v>
+        <f t="shared" si="65"/>
+        <v>572</v>
       </c>
       <c r="AW45" s="24">
         <v>15</v>
@@ -11005,12 +11442,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C46">
         <v>12</v>
@@ -11049,7 +11486,7 @@
       <c r="AF46" s="44"/>
       <c r="AG46" s="44"/>
       <c r="AH46" s="45">
-        <f t="shared" ref="AH46:AH50" si="65">AF46/100</f>
+        <f t="shared" ref="AH46:AH50" si="66">AF46/100</f>
         <v>0</v>
       </c>
       <c r="AI46" s="44"/>
@@ -11057,7 +11494,7 @@
       <c r="AK46" s="44"/>
       <c r="AL46" s="44"/>
       <c r="AM46" s="45">
-        <f t="shared" ref="AM46:AM50" si="66">BR46</f>
+        <f t="shared" ref="AM46:AM50" si="67">BR46</f>
         <v>0</v>
       </c>
       <c r="AN46" s="44"/>
@@ -11072,16 +11509,16 @@
         <v>-45.769999999999982</v>
       </c>
       <c r="AT46" s="45">
-        <f t="shared" si="35"/>
-        <v>0</v>
+        <f t="shared" si="36"/>
+        <v>-103.58</v>
       </c>
       <c r="AU46" s="45">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>-57.93</v>
       </c>
       <c r="AV46" s="45">
-        <f t="shared" si="37"/>
-        <v>0</v>
+        <f t="shared" si="65"/>
+        <v>576</v>
       </c>
       <c r="AW46" s="25">
         <v>15</v>
@@ -11149,11 +11586,11 @@
         <v>0</v>
       </c>
       <c r="BQ46" s="28">
-        <f t="shared" ref="BQ46:BQ50" si="67">IF(BL46&lt;&gt;"",BL46/0.000385,IF(BM46&lt;&gt;"",BM46/0.000385,BN46/0.000385))</f>
+        <f t="shared" ref="BQ46:BQ50" si="68">IF(BL46&lt;&gt;"",BL46/0.000385,IF(BM46&lt;&gt;"",BM46/0.000385,BN46/0.000385))</f>
         <v>0</v>
       </c>
       <c r="BR46" s="49">
-        <f t="shared" ref="BR46:BR50" si="68">IF(BL46&lt;&gt;"",BL46,IF(BM46&lt;&gt;"",BM46,BN46))</f>
+        <f t="shared" ref="BR46:BR50" si="69">IF(BL46&lt;&gt;"",BL46,IF(BM46&lt;&gt;"",BM46,BN46))</f>
         <v>0</v>
       </c>
       <c r="BS46" s="30">
@@ -11161,12 +11598,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C47">
         <v>12</v>
@@ -11205,7 +11642,7 @@
       <c r="AF47" s="44"/>
       <c r="AG47" s="44"/>
       <c r="AH47" s="45">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AI47" s="44"/>
@@ -11213,7 +11650,7 @@
       <c r="AK47" s="44"/>
       <c r="AL47" s="44"/>
       <c r="AM47" s="45">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="AN47" s="44"/>
@@ -11228,16 +11665,16 @@
         <v>-84.700000000000045</v>
       </c>
       <c r="AT47" s="45">
-        <f t="shared" si="35"/>
-        <v>0</v>
+        <f t="shared" si="36"/>
+        <v>-113.88</v>
       </c>
       <c r="AU47" s="45">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>-71.12</v>
       </c>
       <c r="AV47" s="45">
-        <f t="shared" si="37"/>
-        <v>0</v>
+        <f t="shared" si="65"/>
+        <v>547</v>
       </c>
       <c r="AW47" s="25">
         <v>15</v>
@@ -11305,11 +11742,11 @@
         <v>0</v>
       </c>
       <c r="BQ47" s="28">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="BR47" s="49">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="BS47" s="30">
@@ -11317,12 +11754,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C48">
         <v>12</v>
@@ -11361,7 +11798,7 @@
       <c r="AF48" s="44"/>
       <c r="AG48" s="44"/>
       <c r="AH48" s="45">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AI48" s="44"/>
@@ -11369,7 +11806,7 @@
       <c r="AK48" s="44"/>
       <c r="AL48" s="44"/>
       <c r="AM48" s="45">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="AN48" s="44"/>
@@ -11384,16 +11821,16 @@
         <v>-47.420000000000073</v>
       </c>
       <c r="AT48" s="45">
-        <f t="shared" si="35"/>
-        <v>0</v>
+        <f t="shared" si="36"/>
+        <v>-88.68</v>
       </c>
       <c r="AU48" s="45">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>-80.87</v>
       </c>
       <c r="AV48" s="45">
-        <f t="shared" si="37"/>
-        <v>0</v>
+        <f t="shared" si="65"/>
+        <v>580</v>
       </c>
       <c r="AW48" s="25">
         <v>15</v>
@@ -11460,11 +11897,11 @@
         <v/>
       </c>
       <c r="BQ48" s="28">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="BR48" s="49">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="BS48" s="30">
@@ -11472,12 +11909,12 @@
         <v>11.85</v>
       </c>
     </row>
-    <row r="49" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B49" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C49">
         <v>12</v>
@@ -11516,7 +11953,7 @@
       <c r="AF49" s="44"/>
       <c r="AG49" s="44"/>
       <c r="AH49" s="45">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AI49" s="44"/>
@@ -11524,7 +11961,7 @@
       <c r="AK49" s="44"/>
       <c r="AL49" s="44"/>
       <c r="AM49" s="45">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="AN49" s="44"/>
@@ -11539,16 +11976,16 @@
         <v>-133.55999999999995</v>
       </c>
       <c r="AT49" s="45">
-        <f t="shared" si="35"/>
-        <v>0</v>
+        <f t="shared" si="36"/>
+        <v>-111.39</v>
       </c>
       <c r="AU49" s="45">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>-54.88</v>
       </c>
       <c r="AV49" s="45">
-        <f t="shared" si="37"/>
-        <v>0</v>
+        <f t="shared" si="65"/>
+        <v>531</v>
       </c>
       <c r="AW49" s="25">
         <v>15</v>
@@ -11615,11 +12052,11 @@
         <v/>
       </c>
       <c r="BQ49" s="28">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="BR49" s="49">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="BS49" s="30">
@@ -11627,12 +12064,12 @@
         <v>11.85</v>
       </c>
     </row>
-    <row r="50" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C50" s="5">
         <v>12</v>
@@ -11672,7 +12109,7 @@
       <c r="AF50" s="7"/>
       <c r="AG50" s="7"/>
       <c r="AH50" s="41">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="AI50" s="7"/>
@@ -11680,7 +12117,7 @@
       <c r="AK50" s="7"/>
       <c r="AL50" s="7"/>
       <c r="AM50" s="41">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="AN50" s="7"/>
@@ -11695,16 +12132,16 @@
         <v>-51.660000000000082</v>
       </c>
       <c r="AT50" s="41">
-        <f t="shared" si="35"/>
-        <v>0</v>
+        <f t="shared" si="36"/>
+        <v>-116.7</v>
       </c>
       <c r="AU50" s="41">
-        <f t="shared" si="36"/>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>-56.59</v>
       </c>
       <c r="AV50" s="41">
-        <f t="shared" si="37"/>
-        <v>0</v>
+        <f t="shared" si="65"/>
+        <v>558</v>
       </c>
       <c r="AW50" s="26">
         <v>15</v>
@@ -11772,11 +12209,11 @@
         <v/>
       </c>
       <c r="BQ50" s="29">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="BR50" s="38">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="BS50" s="31">
@@ -11784,12 +12221,12 @@
         <v>11.85</v>
       </c>
     </row>
-    <row r="51" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C51" s="3">
         <v>12</v>
@@ -11852,15 +12289,15 @@
         <v>-137.11999999999989</v>
       </c>
       <c r="AT51" s="40">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU51" s="40">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV51" s="40">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW51" s="24">
@@ -11941,12 +12378,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B52" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C52">
         <v>12</v>
@@ -11985,7 +12422,7 @@
       <c r="AF52" s="44"/>
       <c r="AG52" s="44"/>
       <c r="AH52" s="45">
-        <f t="shared" ref="AH52:AH56" si="69">AF52/100</f>
+        <f t="shared" ref="AH52:AH56" si="70">AF52/100</f>
         <v>0</v>
       </c>
       <c r="AI52" s="44"/>
@@ -11993,7 +12430,7 @@
       <c r="AK52" s="44"/>
       <c r="AL52" s="44"/>
       <c r="AM52" s="45">
-        <f t="shared" ref="AM52:AM56" si="70">BR52</f>
+        <f t="shared" ref="AM52:AM56" si="71">BR52</f>
         <v>0</v>
       </c>
       <c r="AN52" s="44"/>
@@ -12008,15 +12445,15 @@
         <v>-45.769999999999982</v>
       </c>
       <c r="AT52" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU52" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV52" s="45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW52" s="25">
@@ -12085,11 +12522,11 @@
         <v>0</v>
       </c>
       <c r="BQ52" s="28">
-        <f t="shared" ref="BQ52:BQ56" si="71">IF(BL52&lt;&gt;"",BL52/0.000385,IF(BM52&lt;&gt;"",BM52/0.000385,BN52/0.000385))</f>
+        <f t="shared" ref="BQ52:BQ56" si="72">IF(BL52&lt;&gt;"",BL52/0.000385,IF(BM52&lt;&gt;"",BM52/0.000385,BN52/0.000385))</f>
         <v>0</v>
       </c>
       <c r="BR52" s="49">
-        <f t="shared" ref="BR52:BR56" si="72">IF(BL52&lt;&gt;"",BL52,IF(BM52&lt;&gt;"",BM52,BN52))</f>
+        <f t="shared" ref="BR52:BR56" si="73">IF(BL52&lt;&gt;"",BL52,IF(BM52&lt;&gt;"",BM52,BN52))</f>
         <v>0</v>
       </c>
       <c r="BS52" s="30">
@@ -12097,12 +12534,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B53" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C53">
         <v>12</v>
@@ -12141,7 +12578,7 @@
       <c r="AF53" s="44"/>
       <c r="AG53" s="44"/>
       <c r="AH53" s="45">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="AI53" s="44"/>
@@ -12149,7 +12586,7 @@
       <c r="AK53" s="44"/>
       <c r="AL53" s="44"/>
       <c r="AM53" s="45">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="AN53" s="44"/>
@@ -12164,15 +12601,15 @@
         <v>-84.700000000000045</v>
       </c>
       <c r="AT53" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU53" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV53" s="45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW53" s="25">
@@ -12241,11 +12678,11 @@
         <v>0</v>
       </c>
       <c r="BQ53" s="28">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="BR53" s="49">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="BS53" s="30">
@@ -12253,12 +12690,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B54" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C54">
         <v>12</v>
@@ -12297,7 +12734,7 @@
       <c r="AF54" s="44"/>
       <c r="AG54" s="44"/>
       <c r="AH54" s="45">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="AI54" s="44"/>
@@ -12305,7 +12742,7 @@
       <c r="AK54" s="44"/>
       <c r="AL54" s="44"/>
       <c r="AM54" s="45">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="AN54" s="44"/>
@@ -12320,15 +12757,15 @@
         <v>-47.420000000000073</v>
       </c>
       <c r="AT54" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU54" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV54" s="45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW54" s="25">
@@ -12396,11 +12833,11 @@
         <v/>
       </c>
       <c r="BQ54" s="28">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="BR54" s="49">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="BS54" s="30">
@@ -12408,12 +12845,12 @@
         <v>11.737500000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B55" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C55">
         <v>12</v>
@@ -12452,7 +12889,7 @@
       <c r="AF55" s="44"/>
       <c r="AG55" s="44"/>
       <c r="AH55" s="45">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="AI55" s="44"/>
@@ -12460,7 +12897,7 @@
       <c r="AK55" s="44"/>
       <c r="AL55" s="44"/>
       <c r="AM55" s="45">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="AN55" s="44"/>
@@ -12475,15 +12912,15 @@
         <v>-133.55999999999995</v>
       </c>
       <c r="AT55" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU55" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV55" s="45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW55" s="25">
@@ -12551,11 +12988,11 @@
         <v/>
       </c>
       <c r="BQ55" s="28">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="BR55" s="49">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="BS55" s="30">
@@ -12563,12 +13000,12 @@
         <v>11.737500000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C56" s="5">
         <v>12</v>
@@ -12608,7 +13045,7 @@
       <c r="AF56" s="7"/>
       <c r="AG56" s="7"/>
       <c r="AH56" s="41">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="AI56" s="7"/>
@@ -12616,7 +13053,7 @@
       <c r="AK56" s="7"/>
       <c r="AL56" s="7"/>
       <c r="AM56" s="41">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="AN56" s="7"/>
@@ -12631,15 +13068,15 @@
         <v>-51.660000000000082</v>
       </c>
       <c r="AT56" s="41">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU56" s="41">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV56" s="41">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW56" s="26">
@@ -12708,11 +13145,11 @@
         <v/>
       </c>
       <c r="BQ56" s="29">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="BR56" s="38">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="BS56" s="31">
@@ -12720,12 +13157,12 @@
         <v>11.737500000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C57" s="3">
         <v>12</v>
@@ -12788,15 +13225,15 @@
         <v>-137.11999999999989</v>
       </c>
       <c r="AT57" s="40">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU57" s="40">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV57" s="40">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW57" s="24">
@@ -12877,12 +13314,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B58" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C58">
         <v>12</v>
@@ -12921,7 +13358,7 @@
       <c r="AF58" s="44"/>
       <c r="AG58" s="44"/>
       <c r="AH58" s="45">
-        <f t="shared" ref="AH58:AH62" si="73">AF58/100</f>
+        <f t="shared" ref="AH58:AH62" si="74">AF58/100</f>
         <v>0</v>
       </c>
       <c r="AI58" s="44"/>
@@ -12929,7 +13366,7 @@
       <c r="AK58" s="44"/>
       <c r="AL58" s="44"/>
       <c r="AM58" s="45">
-        <f t="shared" ref="AM58:AM62" si="74">BR58</f>
+        <f t="shared" ref="AM58:AM62" si="75">BR58</f>
         <v>0</v>
       </c>
       <c r="AN58" s="44"/>
@@ -12944,15 +13381,15 @@
         <v>-45.769999999999982</v>
       </c>
       <c r="AT58" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU58" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV58" s="45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW58" s="25">
@@ -13021,11 +13458,11 @@
         <v>0</v>
       </c>
       <c r="BQ58" s="28">
-        <f t="shared" ref="BQ58:BQ62" si="75">IF(BL58&lt;&gt;"",BL58/0.000385,IF(BM58&lt;&gt;"",BM58/0.000385,BN58/0.000385))</f>
+        <f t="shared" ref="BQ58:BQ62" si="76">IF(BL58&lt;&gt;"",BL58/0.000385,IF(BM58&lt;&gt;"",BM58/0.000385,BN58/0.000385))</f>
         <v>0</v>
       </c>
       <c r="BR58" s="49">
-        <f t="shared" ref="BR58:BR62" si="76">IF(BL58&lt;&gt;"",BL58,IF(BM58&lt;&gt;"",BM58,BN58))</f>
+        <f t="shared" ref="BR58:BR62" si="77">IF(BL58&lt;&gt;"",BL58,IF(BM58&lt;&gt;"",BM58,BN58))</f>
         <v>0</v>
       </c>
       <c r="BS58" s="30">
@@ -13033,12 +13470,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C59">
         <v>12</v>
@@ -13077,7 +13514,7 @@
       <c r="AF59" s="44"/>
       <c r="AG59" s="44"/>
       <c r="AH59" s="45">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AI59" s="44"/>
@@ -13085,7 +13522,7 @@
       <c r="AK59" s="44"/>
       <c r="AL59" s="44"/>
       <c r="AM59" s="45">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AN59" s="44"/>
@@ -13100,15 +13537,15 @@
         <v>-84.700000000000045</v>
       </c>
       <c r="AT59" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU59" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV59" s="45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW59" s="25">
@@ -13177,11 +13614,11 @@
         <v>0</v>
       </c>
       <c r="BQ59" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="BR59" s="49">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="BS59" s="30">
@@ -13189,12 +13626,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B60" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C60">
         <v>12</v>
@@ -13233,7 +13670,7 @@
       <c r="AF60" s="44"/>
       <c r="AG60" s="44"/>
       <c r="AH60" s="45">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AI60" s="44"/>
@@ -13241,7 +13678,7 @@
       <c r="AK60" s="44"/>
       <c r="AL60" s="44"/>
       <c r="AM60" s="45">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AN60" s="44"/>
@@ -13256,15 +13693,15 @@
         <v>-47.420000000000073</v>
       </c>
       <c r="AT60" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU60" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV60" s="45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW60" s="25">
@@ -13332,11 +13769,11 @@
         <v/>
       </c>
       <c r="BQ60" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="BR60" s="49">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="BS60" s="30">
@@ -13344,12 +13781,12 @@
         <v>11.625</v>
       </c>
     </row>
-    <row r="61" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B61" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C61">
         <v>12</v>
@@ -13388,7 +13825,7 @@
       <c r="AF61" s="44"/>
       <c r="AG61" s="44"/>
       <c r="AH61" s="45">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AI61" s="44"/>
@@ -13396,7 +13833,7 @@
       <c r="AK61" s="44"/>
       <c r="AL61" s="44"/>
       <c r="AM61" s="45">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AN61" s="44"/>
@@ -13411,15 +13848,15 @@
         <v>-133.55999999999995</v>
       </c>
       <c r="AT61" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU61" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV61" s="45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW61" s="25">
@@ -13487,11 +13924,11 @@
         <v/>
       </c>
       <c r="BQ61" s="28">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="BR61" s="49">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="BS61" s="30">
@@ -13499,12 +13936,12 @@
         <v>11.625</v>
       </c>
     </row>
-    <row r="62" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C62" s="5">
         <v>12</v>
@@ -13544,7 +13981,7 @@
       <c r="AF62" s="7"/>
       <c r="AG62" s="7"/>
       <c r="AH62" s="41">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="AI62" s="7"/>
@@ -13552,7 +13989,7 @@
       <c r="AK62" s="7"/>
       <c r="AL62" s="7"/>
       <c r="AM62" s="41">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>0</v>
       </c>
       <c r="AN62" s="7"/>
@@ -13567,15 +14004,15 @@
         <v>-51.660000000000082</v>
       </c>
       <c r="AT62" s="41">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU62" s="41">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV62" s="41">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW62" s="26">
@@ -13644,11 +14081,11 @@
         <v/>
       </c>
       <c r="BQ62" s="29">
-        <f t="shared" si="75"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="BR62" s="38">
-        <f t="shared" si="76"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="BS62" s="31">
@@ -13656,12 +14093,12 @@
         <v>11.625</v>
       </c>
     </row>
-    <row r="63" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C63" s="3">
         <v>12</v>
@@ -13724,15 +14161,15 @@
         <v>-137.11999999999989</v>
       </c>
       <c r="AT63" s="40">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU63" s="40">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV63" s="40">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW63" s="24">
@@ -13813,12 +14250,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B64" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C64">
         <v>12</v>
@@ -13857,7 +14294,7 @@
       <c r="AF64" s="44"/>
       <c r="AG64" s="44"/>
       <c r="AH64" s="45">
-        <f t="shared" ref="AH64:AH68" si="77">AF64/100</f>
+        <f t="shared" ref="AH64:AH68" si="78">AF64/100</f>
         <v>0</v>
       </c>
       <c r="AI64" s="44"/>
@@ -13865,7 +14302,7 @@
       <c r="AK64" s="44"/>
       <c r="AL64" s="44"/>
       <c r="AM64" s="45">
-        <f t="shared" ref="AM64:AM68" si="78">BR64</f>
+        <f t="shared" ref="AM64:AM68" si="79">BR64</f>
         <v>0</v>
       </c>
       <c r="AN64" s="44"/>
@@ -13880,15 +14317,15 @@
         <v>-45.769999999999982</v>
       </c>
       <c r="AT64" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU64" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV64" s="45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW64" s="25">
@@ -13957,11 +14394,11 @@
         <v>0</v>
       </c>
       <c r="BQ64" s="28">
-        <f t="shared" ref="BQ64:BQ68" si="79">IF(BL64&lt;&gt;"",BL64/0.000385,IF(BM64&lt;&gt;"",BM64/0.000385,BN64/0.000385))</f>
+        <f t="shared" ref="BQ64:BQ68" si="80">IF(BL64&lt;&gt;"",BL64/0.000385,IF(BM64&lt;&gt;"",BM64/0.000385,BN64/0.000385))</f>
         <v>0</v>
       </c>
       <c r="BR64" s="49">
-        <f t="shared" ref="BR64:BR68" si="80">IF(BL64&lt;&gt;"",BL64,IF(BM64&lt;&gt;"",BM64,BN64))</f>
+        <f t="shared" ref="BR64:BR68" si="81">IF(BL64&lt;&gt;"",BL64,IF(BM64&lt;&gt;"",BM64,BN64))</f>
         <v>0</v>
       </c>
       <c r="BS64" s="30">
@@ -13969,12 +14406,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C65">
         <v>12</v>
@@ -14013,7 +14450,7 @@
       <c r="AF65" s="44"/>
       <c r="AG65" s="44"/>
       <c r="AH65" s="45">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="AI65" s="44"/>
@@ -14021,7 +14458,7 @@
       <c r="AK65" s="44"/>
       <c r="AL65" s="44"/>
       <c r="AM65" s="45">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AN65" s="44"/>
@@ -14036,15 +14473,15 @@
         <v>-84.700000000000045</v>
       </c>
       <c r="AT65" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU65" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV65" s="45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW65" s="25">
@@ -14113,11 +14550,11 @@
         <v>0</v>
       </c>
       <c r="BQ65" s="28">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="BR65" s="49">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="BS65" s="30">
@@ -14125,12 +14562,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B66" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C66">
         <v>12</v>
@@ -14169,7 +14606,7 @@
       <c r="AF66" s="44"/>
       <c r="AG66" s="44"/>
       <c r="AH66" s="45">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="AI66" s="44"/>
@@ -14177,7 +14614,7 @@
       <c r="AK66" s="44"/>
       <c r="AL66" s="44"/>
       <c r="AM66" s="45">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AN66" s="44"/>
@@ -14192,15 +14629,15 @@
         <v>-47.420000000000073</v>
       </c>
       <c r="AT66" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU66" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV66" s="45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW66" s="25">
@@ -14268,11 +14705,11 @@
         <v/>
       </c>
       <c r="BQ66" s="28">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="BR66" s="49">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="BS66" s="30">
@@ -14280,12 +14717,12 @@
         <v>11.512499999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B67" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C67">
         <v>12</v>
@@ -14324,7 +14761,7 @@
       <c r="AF67" s="44"/>
       <c r="AG67" s="44"/>
       <c r="AH67" s="45">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="AI67" s="44"/>
@@ -14332,7 +14769,7 @@
       <c r="AK67" s="44"/>
       <c r="AL67" s="44"/>
       <c r="AM67" s="45">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AN67" s="44"/>
@@ -14343,19 +14780,19 @@
         <v>133.55999999999995</v>
       </c>
       <c r="AS67" s="45">
-        <f t="shared" ref="AS67:AS80" si="81">AQ67-AR67</f>
+        <f t="shared" ref="AS67:AS80" si="82">AQ67-AR67</f>
         <v>-133.55999999999995</v>
       </c>
       <c r="AT67" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU67" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV67" s="45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW67" s="25">
@@ -14379,11 +14816,11 @@
       <c r="BC67" s="11"/>
       <c r="BE67" s="22"/>
       <c r="BF67" s="11">
-        <f t="shared" ref="BF67:BF74" si="82">BB67*K67*BH67/1000</f>
+        <f t="shared" ref="BF67:BF74" si="83">BB67*K67*BH67/1000</f>
         <v>0</v>
       </c>
       <c r="BG67" s="46">
-        <f t="shared" ref="BG67:BG74" si="83">BF67*24*60</f>
+        <f t="shared" ref="BG67:BG74" si="84">BF67*24*60</f>
         <v>0</v>
       </c>
       <c r="BH67" s="46">
@@ -14399,7 +14836,7 @@
         <v/>
       </c>
       <c r="BK67" s="47">
-        <f t="shared" ref="BK67:BK74" si="84">AM67*24*60</f>
+        <f t="shared" ref="BK67:BK74" si="85">AM67*24*60</f>
         <v>0</v>
       </c>
       <c r="BL67" s="47">
@@ -14411,7 +14848,7 @@
         <v/>
       </c>
       <c r="BN67" s="48" t="str">
-        <f t="shared" ref="BN67:BN74" si="85">IF(B67="No MPC", BB67*K67*BH67/1000,"")</f>
+        <f t="shared" ref="BN67:BN74" si="86">IF(B67="No MPC", BB67*K67*BH67/1000,"")</f>
         <v/>
       </c>
       <c r="BO67" s="47">
@@ -14423,24 +14860,24 @@
         <v/>
       </c>
       <c r="BQ67" s="28">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="BR67" s="49">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="BS67" s="30">
-        <f t="shared" ref="BS67:BS74" si="86">IF(BO67&lt;&gt;"",BO67,BP67)</f>
+        <f t="shared" ref="BS67:BS74" si="87">IF(BO67&lt;&gt;"",BO67,BP67)</f>
         <v>11.512499999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C68" s="5">
         <v>12</v>
@@ -14480,7 +14917,7 @@
       <c r="AF68" s="7"/>
       <c r="AG68" s="7"/>
       <c r="AH68" s="41">
-        <f t="shared" si="77"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="AI68" s="7"/>
@@ -14488,7 +14925,7 @@
       <c r="AK68" s="7"/>
       <c r="AL68" s="7"/>
       <c r="AM68" s="41">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="AN68" s="7"/>
@@ -14499,19 +14936,19 @@
         <v>51.660000000000082</v>
       </c>
       <c r="AS68" s="41">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>-51.660000000000082</v>
       </c>
       <c r="AT68" s="41">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU68" s="41">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV68" s="41">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW68" s="26">
@@ -14536,11 +14973,11 @@
       <c r="BD68" s="5"/>
       <c r="BE68" s="23"/>
       <c r="BF68" s="12">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="BG68" s="13">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="BH68" s="13">
@@ -14548,19 +14985,19 @@
         <v>1535</v>
       </c>
       <c r="BI68" s="14" t="str">
-        <f t="shared" ref="BI68:BI80" si="87">IF(ISBLANK(AN68),"",IFERROR(AN68/BH68,0))</f>
+        <f t="shared" ref="BI68:BI80" si="88">IF(ISBLANK(AN68),"",IFERROR(AN68/BH68,0))</f>
         <v/>
       </c>
       <c r="BJ68" s="14" t="str">
-        <f t="shared" ref="BJ68:BJ80" si="88">IF(ISBLANK(AN68),"",AN68/AX68)</f>
+        <f t="shared" ref="BJ68:BJ80" si="89">IF(ISBLANK(AN68),"",AN68/AX68)</f>
         <v/>
       </c>
       <c r="BK68" s="14">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="BL68" s="14">
-        <f t="shared" ref="BL68:BL80" si="89">IF(B68="Python",BC68*BH68/24/60,"")</f>
+        <f t="shared" ref="BL68:BL80" si="90">IF(B68="Python",BC68*BH68/24/60,"")</f>
         <v>0</v>
       </c>
       <c r="BM68" s="48" t="str">
@@ -14568,7 +15005,7 @@
         <v/>
       </c>
       <c r="BN68" s="36" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="BO68" s="14">
@@ -14580,24 +15017,24 @@
         <v/>
       </c>
       <c r="BQ68" s="29">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="BR68" s="38">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="BS68" s="31">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>11.512499999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C69" s="3">
         <v>12</v>
@@ -14656,19 +15093,19 @@
         <v>137.11999999999989</v>
       </c>
       <c r="AS69" s="40">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>-137.11999999999989</v>
       </c>
       <c r="AT69" s="40">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU69" s="40">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV69" s="40">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW69" s="24">
@@ -14693,11 +15130,11 @@
       <c r="BD69" s="9"/>
       <c r="BE69" s="21"/>
       <c r="BF69" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="BG69" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="BH69" s="9">
@@ -14705,19 +15142,19 @@
         <v>1520</v>
       </c>
       <c r="BI69" s="10" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="BJ69" s="10" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BK69" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="BL69" s="10" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="BM69" s="10">
@@ -14725,7 +15162,7 @@
         <v>0</v>
       </c>
       <c r="BN69" s="35" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="BO69" s="10" t="str">
@@ -14745,16 +15182,16 @@
         <v>0</v>
       </c>
       <c r="BS69" s="32">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B70" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C70">
         <v>12</v>
@@ -14793,7 +15230,7 @@
       <c r="AF70" s="44"/>
       <c r="AG70" s="44"/>
       <c r="AH70" s="45">
-        <f t="shared" ref="AH70:AH74" si="90">AF70/100</f>
+        <f t="shared" ref="AH70:AH74" si="91">AF70/100</f>
         <v>0</v>
       </c>
       <c r="AI70" s="44"/>
@@ -14801,7 +15238,7 @@
       <c r="AK70" s="44"/>
       <c r="AL70" s="44"/>
       <c r="AM70" s="45">
-        <f t="shared" ref="AM70:AM74" si="91">BR70</f>
+        <f t="shared" ref="AM70:AM74" si="92">BR70</f>
         <v>0</v>
       </c>
       <c r="AN70" s="44"/>
@@ -14812,19 +15249,19 @@
         <v>45.769999999999982</v>
       </c>
       <c r="AS70" s="45">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>-45.769999999999982</v>
       </c>
       <c r="AT70" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU70" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV70" s="45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW70" s="25">
@@ -14849,11 +15286,11 @@
       <c r="BD70" s="46"/>
       <c r="BE70" s="22"/>
       <c r="BF70" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="BG70" s="46">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="BH70" s="46">
@@ -14861,19 +15298,19 @@
         <v>1520</v>
       </c>
       <c r="BI70" s="47" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="BJ70" s="47" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BK70" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="BL70" s="47" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="BM70" s="47">
@@ -14881,7 +15318,7 @@
         <v>0</v>
       </c>
       <c r="BN70" s="48" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="BO70" s="47" t="str">
@@ -14889,28 +15326,28 @@
         <v/>
       </c>
       <c r="BP70" s="51">
-        <f t="shared" ref="BP70:BP80" si="92">IF(B70="Julia",BE70*BH70,"")</f>
+        <f t="shared" ref="BP70:BP80" si="93">IF(B70="Julia",BE70*BH70,"")</f>
         <v>0</v>
       </c>
       <c r="BQ70" s="28">
-        <f t="shared" ref="BQ70:BQ74" si="93">IF(BL70&lt;&gt;"",BL70/0.000385,IF(BM70&lt;&gt;"",BM70/0.000385,BN70/0.000385))</f>
+        <f t="shared" ref="BQ70:BQ74" si="94">IF(BL70&lt;&gt;"",BL70/0.000385,IF(BM70&lt;&gt;"",BM70/0.000385,BN70/0.000385))</f>
         <v>0</v>
       </c>
       <c r="BR70" s="49">
-        <f t="shared" ref="BR70:BR74" si="94">IF(BL70&lt;&gt;"",BL70,IF(BM70&lt;&gt;"",BM70,BN70))</f>
+        <f t="shared" ref="BR70:BR74" si="95">IF(BL70&lt;&gt;"",BL70,IF(BM70&lt;&gt;"",BM70,BN70))</f>
         <v>0</v>
       </c>
       <c r="BS70" s="30">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B71" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C71">
         <v>12</v>
@@ -14949,7 +15386,7 @@
       <c r="AF71" s="44"/>
       <c r="AG71" s="44"/>
       <c r="AH71" s="45">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="AI71" s="44"/>
@@ -14957,7 +15394,7 @@
       <c r="AK71" s="44"/>
       <c r="AL71" s="44"/>
       <c r="AM71" s="45">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AN71" s="44"/>
@@ -14968,19 +15405,19 @@
         <v>84.700000000000045</v>
       </c>
       <c r="AS71" s="45">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>-84.700000000000045</v>
       </c>
       <c r="AT71" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU71" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV71" s="45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW71" s="25">
@@ -15005,11 +15442,11 @@
       <c r="BD71" s="46"/>
       <c r="BE71" s="22"/>
       <c r="BF71" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="BG71" s="46">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="BH71" s="46">
@@ -15017,27 +15454,27 @@
         <v>1520</v>
       </c>
       <c r="BI71" s="47" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="BJ71" s="47" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BK71" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="BL71" s="47" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="BM71" s="47">
-        <f t="shared" ref="BM71:BM80" si="95">IF(B71="Julia",BD71*BH71/24/60,"")</f>
+        <f t="shared" ref="BM71:BM80" si="96">IF(B71="Julia",BD71*BH71/24/60,"")</f>
         <v>0</v>
       </c>
       <c r="BN71" s="48" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="BO71" s="47" t="str">
@@ -15045,28 +15482,28 @@
         <v/>
       </c>
       <c r="BP71" s="51">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="BQ71" s="28">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="BR71" s="49">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="BS71" s="30">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C72">
         <v>12</v>
@@ -15105,7 +15542,7 @@
       <c r="AF72" s="44"/>
       <c r="AG72" s="44"/>
       <c r="AH72" s="45">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="AI72" s="44"/>
@@ -15113,7 +15550,7 @@
       <c r="AK72" s="44"/>
       <c r="AL72" s="44"/>
       <c r="AM72" s="45">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AN72" s="44"/>
@@ -15124,19 +15561,19 @@
         <v>47.420000000000073</v>
       </c>
       <c r="AS72" s="45">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>-47.420000000000073</v>
       </c>
       <c r="AT72" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU72" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV72" s="45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="AW72" s="25">
@@ -15160,39 +15597,39 @@
       <c r="BC72" s="11"/>
       <c r="BE72" s="22"/>
       <c r="BF72" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="BG72" s="46">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="BH72" s="46">
-        <f t="shared" ref="BH72:BH80" si="96">AX72+SUM(AJ72:AL72,AN72:AO72)-(AW72*(D72+1))</f>
+        <f t="shared" ref="BH72:BH80" si="97">AX72+SUM(AJ72:AL72,AN72:AO72)-(AW72*(D72+1))</f>
         <v>1520</v>
       </c>
       <c r="BI72" s="47" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v/>
       </c>
       <c r="BJ72" s="47" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BK72" s="47">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="BL72" s="47">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="BM72" s="48" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v/>
       </c>
       <c r="BN72" s="48" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="BO72" s="47">
@@ -15200,28 +15637,28 @@
         <v>11.4</v>
       </c>
       <c r="BP72" s="51" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v/>
       </c>
       <c r="BQ72" s="28">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="BR72" s="49">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="BS72" s="30">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>11.4</v>
       </c>
     </row>
-    <row r="73" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C73">
         <v>12</v>
@@ -15260,7 +15697,7 @@
       <c r="AF73" s="44"/>
       <c r="AG73" s="44"/>
       <c r="AH73" s="45">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="AI73" s="44"/>
@@ -15268,7 +15705,7 @@
       <c r="AK73" s="44"/>
       <c r="AL73" s="44"/>
       <c r="AM73" s="45">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AN73" s="44"/>
@@ -15279,19 +15716,19 @@
         <v>133.55999999999995</v>
       </c>
       <c r="AS73" s="45">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>-133.55999999999995</v>
       </c>
       <c r="AT73" s="45">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AU73" s="45">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AV73" s="45">
-        <f t="shared" si="37"/>
+        <f t="shared" ref="AV73:AV104" si="98">AP67-AP73</f>
         <v>0</v>
       </c>
       <c r="AW73" s="25">
@@ -15315,39 +15752,39 @@
       <c r="BC73" s="11"/>
       <c r="BE73" s="22"/>
       <c r="BF73" s="11">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="BG73" s="46">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="BH73" s="46">
+        <f t="shared" si="97"/>
+        <v>1520</v>
+      </c>
+      <c r="BI73" s="47" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="BJ73" s="47" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="BK73" s="47">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="BL73" s="47">
+        <f t="shared" si="90"/>
+        <v>0</v>
+      </c>
+      <c r="BM73" s="48" t="str">
         <f t="shared" si="96"/>
-        <v>1520</v>
-      </c>
-      <c r="BI73" s="47" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ73" s="47" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BK73" s="47">
-        <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="BL73" s="47">
-        <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="BM73" s="48" t="str">
-        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="BN73" s="48" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="BO73" s="47">
@@ -15355,28 +15792,28 @@
         <v>11.4</v>
       </c>
       <c r="BP73" s="51" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v/>
       </c>
       <c r="BQ73" s="28">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="BR73" s="49">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="BS73" s="30">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>11.4</v>
       </c>
     </row>
-    <row r="74" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C74" s="5">
         <v>12</v>
@@ -15416,7 +15853,7 @@
       <c r="AF74" s="7"/>
       <c r="AG74" s="7"/>
       <c r="AH74" s="41">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="AI74" s="7"/>
@@ -15424,7 +15861,7 @@
       <c r="AK74" s="7"/>
       <c r="AL74" s="7"/>
       <c r="AM74" s="41">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AN74" s="7"/>
@@ -15435,19 +15872,19 @@
         <v>51.660000000000082</v>
       </c>
       <c r="AS74" s="41">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>-51.660000000000082</v>
       </c>
       <c r="AT74" s="41">
-        <f t="shared" ref="AT74:AT80" si="97">AN74-AN68</f>
+        <f t="shared" ref="AT74:AT80" si="99">AN74-AN68</f>
         <v>0</v>
       </c>
       <c r="AU74" s="41">
-        <f t="shared" ref="AU74:AU80" si="98">AO74-AO68</f>
+        <f t="shared" ref="AU74:AU80" si="100">AO74-AO68</f>
         <v>0</v>
       </c>
       <c r="AV74" s="41">
-        <f t="shared" ref="AV74:AV80" si="99">AP74-AP68</f>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="AW74" s="26">
@@ -15472,39 +15909,39 @@
       <c r="BD74" s="5"/>
       <c r="BE74" s="23"/>
       <c r="BF74" s="12">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="BG74" s="13">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="BH74" s="13">
+        <f t="shared" si="97"/>
+        <v>1520</v>
+      </c>
+      <c r="BI74" s="14" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="BJ74" s="14" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="BK74" s="14">
+        <f t="shared" si="85"/>
+        <v>0</v>
+      </c>
+      <c r="BL74" s="14">
+        <f t="shared" si="90"/>
+        <v>0</v>
+      </c>
+      <c r="BM74" s="48" t="str">
         <f t="shared" si="96"/>
-        <v>1520</v>
-      </c>
-      <c r="BI74" s="14" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ74" s="14" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BK74" s="14">
-        <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="BL74" s="14">
-        <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="BM74" s="48" t="str">
-        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="BN74" s="36" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="BO74" s="14">
@@ -15512,28 +15949,28 @@
         <v>11.4</v>
       </c>
       <c r="BP74" s="52" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v/>
       </c>
       <c r="BQ74" s="29">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="BR74" s="38">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="BS74" s="31">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>11.4</v>
       </c>
     </row>
-    <row r="75" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C75" s="3">
         <v>12</v>
@@ -15592,19 +16029,19 @@
         <v>137.11999999999989</v>
       </c>
       <c r="AS75" s="40">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>-137.11999999999989</v>
       </c>
       <c r="AT75" s="40">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="AU75" s="40">
+        <f t="shared" si="100"/>
+        <v>0</v>
+      </c>
+      <c r="AV75" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="AV75" s="40">
-        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="AW75" s="24">
@@ -15629,39 +16066,39 @@
       <c r="BD75" s="9"/>
       <c r="BE75" s="21"/>
       <c r="BF75" s="8">
-        <f t="shared" ref="BF75:BF80" si="100">BB75*K75*BH75/1000</f>
+        <f t="shared" ref="BF75:BF80" si="101">BB75*K75*BH75/1000</f>
         <v>0</v>
       </c>
       <c r="BG75" s="9">
-        <f t="shared" ref="BG75:BG80" si="101">BF75*24*60</f>
+        <f t="shared" ref="BG75:BG80" si="102">BF75*24*60</f>
         <v>0</v>
       </c>
       <c r="BH75" s="9">
+        <f t="shared" si="97"/>
+        <v>1505</v>
+      </c>
+      <c r="BI75" s="10" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="BJ75" s="10" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="BK75" s="10">
+        <f t="shared" ref="BK75:BK80" si="103">AM75*24*60</f>
+        <v>0</v>
+      </c>
+      <c r="BL75" s="10" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="BM75" s="10">
         <f t="shared" si="96"/>
-        <v>1505</v>
-      </c>
-      <c r="BI75" s="10" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ75" s="10" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BK75" s="10">
-        <f t="shared" ref="BK75:BK80" si="102">AM75*24*60</f>
-        <v>0</v>
-      </c>
-      <c r="BL75" s="10" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BM75" s="10">
-        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="BN75" s="35" t="str">
-        <f t="shared" ref="BN75:BN80" si="103">IF(B75="No MPC", BB75*K75*BH75/1000,"")</f>
+        <f t="shared" ref="BN75:BN80" si="104">IF(B75="No MPC", BB75*K75*BH75/1000,"")</f>
         <v/>
       </c>
       <c r="BO75" s="10" t="str">
@@ -15669,7 +16106,7 @@
         <v/>
       </c>
       <c r="BP75" s="50">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="BQ75" s="27">
@@ -15681,16 +16118,16 @@
         <v>0</v>
       </c>
       <c r="BS75" s="32">
-        <f t="shared" ref="BS75:BS80" si="104">IF(BO75&lt;&gt;"",BO75,BP75)</f>
+        <f t="shared" ref="BS75:BS80" si="105">IF(BO75&lt;&gt;"",BO75,BP75)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C76">
         <v>12</v>
@@ -15729,7 +16166,7 @@
       <c r="AF76" s="44"/>
       <c r="AG76" s="44"/>
       <c r="AH76" s="45">
-        <f t="shared" ref="AH76:AH80" si="105">AF76/100</f>
+        <f t="shared" ref="AH76:AH80" si="106">AF76/100</f>
         <v>0</v>
       </c>
       <c r="AI76" s="44"/>
@@ -15737,7 +16174,7 @@
       <c r="AK76" s="44"/>
       <c r="AL76" s="44"/>
       <c r="AM76" s="45">
-        <f t="shared" ref="AM76:AM80" si="106">BR76</f>
+        <f t="shared" ref="AM76:AM80" si="107">BR76</f>
         <v>0</v>
       </c>
       <c r="AN76" s="44"/>
@@ -15748,19 +16185,19 @@
         <v>45.769999999999982</v>
       </c>
       <c r="AS76" s="45">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>-45.769999999999982</v>
       </c>
       <c r="AT76" s="45">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="AU76" s="45">
+        <f t="shared" si="100"/>
+        <v>0</v>
+      </c>
+      <c r="AV76" s="45">
         <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="AV76" s="45">
-        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="AW76" s="25">
@@ -15785,39 +16222,39 @@
       <c r="BD76" s="46"/>
       <c r="BE76" s="22"/>
       <c r="BF76" s="11">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="BG76" s="46">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="BH76" s="46">
+        <f t="shared" si="97"/>
+        <v>1505</v>
+      </c>
+      <c r="BI76" s="47" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="BJ76" s="47" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="BK76" s="47">
+        <f t="shared" si="103"/>
+        <v>0</v>
+      </c>
+      <c r="BL76" s="47" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="BM76" s="47">
         <f t="shared" si="96"/>
-        <v>1505</v>
-      </c>
-      <c r="BI76" s="47" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ76" s="47" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BK76" s="47">
-        <f t="shared" si="102"/>
-        <v>0</v>
-      </c>
-      <c r="BL76" s="47" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BM76" s="47">
-        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="BN76" s="48" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="BO76" s="47" t="str">
@@ -15825,28 +16262,28 @@
         <v/>
       </c>
       <c r="BP76" s="51">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="BQ76" s="28">
-        <f t="shared" ref="BQ76:BQ80" si="107">IF(BL76&lt;&gt;"",BL76/0.000385,IF(BM76&lt;&gt;"",BM76/0.000385,BN76/0.000385))</f>
+        <f t="shared" ref="BQ76:BQ80" si="108">IF(BL76&lt;&gt;"",BL76/0.000385,IF(BM76&lt;&gt;"",BM76/0.000385,BN76/0.000385))</f>
         <v>0</v>
       </c>
       <c r="BR76" s="49">
-        <f t="shared" ref="BR76:BR80" si="108">IF(BL76&lt;&gt;"",BL76,IF(BM76&lt;&gt;"",BM76,BN76))</f>
+        <f t="shared" ref="BR76:BR80" si="109">IF(BL76&lt;&gt;"",BL76,IF(BM76&lt;&gt;"",BM76,BN76))</f>
         <v>0</v>
       </c>
       <c r="BS76" s="30">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B77" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C77">
         <v>12</v>
@@ -15885,7 +16322,7 @@
       <c r="AF77" s="44"/>
       <c r="AG77" s="44"/>
       <c r="AH77" s="45">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="AI77" s="44"/>
@@ -15893,7 +16330,7 @@
       <c r="AK77" s="44"/>
       <c r="AL77" s="44"/>
       <c r="AM77" s="45">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="AN77" s="44"/>
@@ -15904,19 +16341,19 @@
         <v>84.700000000000045</v>
       </c>
       <c r="AS77" s="45">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>-84.700000000000045</v>
       </c>
       <c r="AT77" s="45">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="AU77" s="45">
+        <f t="shared" si="100"/>
+        <v>0</v>
+      </c>
+      <c r="AV77" s="45">
         <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="AV77" s="45">
-        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="AW77" s="25">
@@ -15941,39 +16378,39 @@
       <c r="BD77" s="46"/>
       <c r="BE77" s="22"/>
       <c r="BF77" s="11">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="BG77" s="46">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="BH77" s="46">
+        <f t="shared" si="97"/>
+        <v>1505</v>
+      </c>
+      <c r="BI77" s="47" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="BJ77" s="47" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="BK77" s="47">
+        <f t="shared" si="103"/>
+        <v>0</v>
+      </c>
+      <c r="BL77" s="47" t="str">
+        <f t="shared" si="90"/>
+        <v/>
+      </c>
+      <c r="BM77" s="47">
         <f t="shared" si="96"/>
-        <v>1505</v>
-      </c>
-      <c r="BI77" s="47" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ77" s="47" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BK77" s="47">
-        <f t="shared" si="102"/>
-        <v>0</v>
-      </c>
-      <c r="BL77" s="47" t="str">
-        <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BM77" s="47">
-        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="BN77" s="48" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="BO77" s="47" t="str">
@@ -15981,28 +16418,28 @@
         <v/>
       </c>
       <c r="BP77" s="51">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="BQ77" s="28">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="BR77" s="49">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="BS77" s="30">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B78" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C78">
         <v>12</v>
@@ -16041,7 +16478,7 @@
       <c r="AF78" s="44"/>
       <c r="AG78" s="44"/>
       <c r="AH78" s="45">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="AI78" s="44"/>
@@ -16049,7 +16486,7 @@
       <c r="AK78" s="44"/>
       <c r="AL78" s="44"/>
       <c r="AM78" s="45">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="AN78" s="44"/>
@@ -16060,19 +16497,19 @@
         <v>47.420000000000073</v>
       </c>
       <c r="AS78" s="45">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>-47.420000000000073</v>
       </c>
       <c r="AT78" s="45">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="AU78" s="45">
+        <f t="shared" si="100"/>
+        <v>0</v>
+      </c>
+      <c r="AV78" s="45">
         <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="AV78" s="45">
-        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="AW78" s="25">
@@ -16096,39 +16533,39 @@
       <c r="BC78" s="11"/>
       <c r="BE78" s="22"/>
       <c r="BF78" s="11">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="BG78" s="46">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="BH78" s="46">
+        <f t="shared" si="97"/>
+        <v>1505</v>
+      </c>
+      <c r="BI78" s="47" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="BJ78" s="47" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="BK78" s="47">
+        <f t="shared" si="103"/>
+        <v>0</v>
+      </c>
+      <c r="BL78" s="47">
+        <f t="shared" si="90"/>
+        <v>0</v>
+      </c>
+      <c r="BM78" s="48" t="str">
         <f t="shared" si="96"/>
-        <v>1505</v>
-      </c>
-      <c r="BI78" s="47" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ78" s="47" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BK78" s="47">
-        <f t="shared" si="102"/>
-        <v>0</v>
-      </c>
-      <c r="BL78" s="47">
-        <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="BM78" s="48" t="str">
-        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="BN78" s="48" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="BO78" s="47">
@@ -16136,28 +16573,28 @@
         <v>11.2875</v>
       </c>
       <c r="BP78" s="51" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v/>
       </c>
       <c r="BQ78" s="28">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="BR78" s="49">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="BS78" s="30">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>11.2875</v>
       </c>
     </row>
-    <row r="79" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:71" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C79">
         <v>12</v>
@@ -16196,7 +16633,7 @@
       <c r="AF79" s="44"/>
       <c r="AG79" s="44"/>
       <c r="AH79" s="45">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="AI79" s="44"/>
@@ -16204,7 +16641,7 @@
       <c r="AK79" s="44"/>
       <c r="AL79" s="44"/>
       <c r="AM79" s="45">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="AN79" s="44"/>
@@ -16215,19 +16652,19 @@
         <v>133.55999999999995</v>
       </c>
       <c r="AS79" s="45">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>-133.55999999999995</v>
       </c>
       <c r="AT79" s="45">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="AU79" s="45">
+        <f t="shared" si="100"/>
+        <v>0</v>
+      </c>
+      <c r="AV79" s="45">
         <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="AV79" s="45">
-        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="AW79" s="25">
@@ -16251,39 +16688,39 @@
       <c r="BC79" s="11"/>
       <c r="BE79" s="22"/>
       <c r="BF79" s="11">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="BG79" s="46">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="BH79" s="46">
+        <f t="shared" si="97"/>
+        <v>1505</v>
+      </c>
+      <c r="BI79" s="47" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="BJ79" s="47" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="BK79" s="47">
+        <f t="shared" si="103"/>
+        <v>0</v>
+      </c>
+      <c r="BL79" s="47">
+        <f t="shared" si="90"/>
+        <v>0</v>
+      </c>
+      <c r="BM79" s="48" t="str">
         <f t="shared" si="96"/>
-        <v>1505</v>
-      </c>
-      <c r="BI79" s="47" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ79" s="47" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BK79" s="47">
-        <f t="shared" si="102"/>
-        <v>0</v>
-      </c>
-      <c r="BL79" s="47">
-        <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="BM79" s="48" t="str">
-        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="BN79" s="48" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="BO79" s="47">
@@ -16291,28 +16728,28 @@
         <v>11.2875</v>
       </c>
       <c r="BP79" s="51" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v/>
       </c>
       <c r="BQ79" s="28">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="BR79" s="49">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="BS79" s="30">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>11.2875</v>
       </c>
     </row>
-    <row r="80" spans="1:71" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C80" s="5">
         <v>12</v>
@@ -16352,7 +16789,7 @@
       <c r="AF80" s="7"/>
       <c r="AG80" s="7"/>
       <c r="AH80" s="41">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="AI80" s="7"/>
@@ -16360,7 +16797,7 @@
       <c r="AK80" s="7"/>
       <c r="AL80" s="7"/>
       <c r="AM80" s="41">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0</v>
       </c>
       <c r="AN80" s="7"/>
@@ -16371,19 +16808,19 @@
         <v>51.660000000000082</v>
       </c>
       <c r="AS80" s="41">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>-51.660000000000082</v>
       </c>
       <c r="AT80" s="41">
-        <f t="shared" si="97"/>
+        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="AU80" s="41">
+        <f t="shared" si="100"/>
+        <v>0</v>
+      </c>
+      <c r="AV80" s="41">
         <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="AV80" s="41">
-        <f t="shared" si="99"/>
         <v>0</v>
       </c>
       <c r="AW80" s="26">
@@ -16408,39 +16845,39 @@
       <c r="BD80" s="5"/>
       <c r="BE80" s="23"/>
       <c r="BF80" s="12">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="BG80" s="13">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="BH80" s="13">
+        <f t="shared" si="97"/>
+        <v>1505</v>
+      </c>
+      <c r="BI80" s="14" t="str">
+        <f t="shared" si="88"/>
+        <v/>
+      </c>
+      <c r="BJ80" s="14" t="str">
+        <f t="shared" si="89"/>
+        <v/>
+      </c>
+      <c r="BK80" s="14">
+        <f t="shared" si="103"/>
+        <v>0</v>
+      </c>
+      <c r="BL80" s="14">
+        <f t="shared" si="90"/>
+        <v>0</v>
+      </c>
+      <c r="BM80" s="36" t="str">
         <f t="shared" si="96"/>
-        <v>1505</v>
-      </c>
-      <c r="BI80" s="14" t="str">
-        <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ80" s="14" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BK80" s="14">
-        <f t="shared" si="102"/>
-        <v>0</v>
-      </c>
-      <c r="BL80" s="14">
-        <f t="shared" si="89"/>
-        <v>0</v>
-      </c>
-      <c r="BM80" s="36" t="str">
-        <f t="shared" si="95"/>
         <v/>
       </c>
       <c r="BN80" s="36" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v/>
       </c>
       <c r="BO80" s="14">
@@ -16448,29 +16885,29 @@
         <v>11.2875</v>
       </c>
       <c r="BP80" s="52" t="str">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v/>
       </c>
       <c r="BQ80" s="29">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0</v>
       </c>
       <c r="BR80" s="38">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0</v>
       </c>
       <c r="BS80" s="31">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>11.2875</v>
       </c>
     </row>
-    <row r="83" spans="19:28" x14ac:dyDescent="0.25">
+    <row r="83" spans="19:28" x14ac:dyDescent="0.3">
       <c r="S83" s="39"/>
     </row>
-    <row r="86" spans="19:28" x14ac:dyDescent="0.25">
+    <row r="86" spans="19:28" x14ac:dyDescent="0.3">
       <c r="AB86" s="59"/>
     </row>
-    <row r="87" spans="19:28" x14ac:dyDescent="0.25">
+    <row r="87" spans="19:28" x14ac:dyDescent="0.3">
       <c r="AB87" s="59"/>
     </row>
   </sheetData>
@@ -16794,15 +17231,15 @@
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
+++ b/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-045-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1329" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7BD7647-660D-48B3-A1D1-318A1E7650F5}"/>
+  <xr:revisionPtr revIDLastSave="1426" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F594A91-AAB9-4573-B3C2-D75D850ADE9C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1231,6 +1231,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -10733,7 +10737,7 @@
       </c>
       <c r="AM42" s="45">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>2.5274999999999999E-2</v>
       </c>
       <c r="AN42" s="44">
         <v>88.68</v>
@@ -10784,7 +10788,9 @@
       <c r="BB42" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC42" s="11"/>
+      <c r="BC42" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BE42" s="22"/>
       <c r="BF42" s="11">
         <f t="shared" si="17"/>
@@ -10808,11 +10814,11 @@
       </c>
       <c r="BK42" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>36.396000000000001</v>
       </c>
       <c r="BL42" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.5274999999999999E-2</v>
       </c>
       <c r="BM42" s="48" t="str">
         <f t="shared" si="31"/>
@@ -10832,11 +10838,11 @@
       </c>
       <c r="BQ42" s="28">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>65.649350649350652</v>
       </c>
       <c r="BR42" s="49">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>2.5274999999999999E-2</v>
       </c>
       <c r="BS42" s="30">
         <f t="shared" si="21"/>
@@ -10952,7 +10958,7 @@
       </c>
       <c r="AM43" s="45">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>2.537013888888889E-2</v>
       </c>
       <c r="AN43" s="44">
         <v>111.39</v>
@@ -11003,7 +11009,9 @@
       <c r="BB43" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC43" s="11"/>
+      <c r="BC43" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BE43" s="22"/>
       <c r="BF43" s="11">
         <f t="shared" si="17"/>
@@ -11027,11 +11035,11 @@
       </c>
       <c r="BK43" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>36.533000000000001</v>
       </c>
       <c r="BL43" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.537013888888889E-2</v>
       </c>
       <c r="BM43" s="48" t="str">
         <f t="shared" si="31"/>
@@ -11051,11 +11059,11 @@
       </c>
       <c r="BQ43" s="28">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>65.896464646464651</v>
       </c>
       <c r="BR43" s="49">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>2.537013888888889E-2</v>
       </c>
       <c r="BS43" s="30">
         <f t="shared" si="21"/>
@@ -11174,7 +11182,7 @@
       </c>
       <c r="AM44" s="41">
         <f t="shared" si="62"/>
-        <v>0</v>
+        <v>1.8700519444444445E-2</v>
       </c>
       <c r="AN44" s="7">
         <v>116.7</v>
@@ -11225,7 +11233,9 @@
       <c r="BB44" s="23">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC44" s="12"/>
+      <c r="BC44" s="12">
+        <v>1.4800000000000001E-2</v>
+      </c>
       <c r="BD44" s="5"/>
       <c r="BE44" s="23"/>
       <c r="BF44" s="12">
@@ -11250,11 +11260,11 @@
       </c>
       <c r="BK44" s="14">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>26.928748000000002</v>
       </c>
       <c r="BL44" s="14">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.8700519444444445E-2</v>
       </c>
       <c r="BM44" s="48" t="str">
         <f t="shared" si="31"/>
@@ -11274,11 +11284,11 @@
       </c>
       <c r="BQ44" s="29">
         <f t="shared" si="63"/>
-        <v>0</v>
+        <v>48.57277777777778</v>
       </c>
       <c r="BR44" s="38">
         <f t="shared" si="64"/>
-        <v>0</v>
+        <v>1.8700519444444445E-2</v>
       </c>
       <c r="BS44" s="31">
         <f t="shared" si="21"/>
@@ -11299,70 +11309,136 @@
         <v>7</v>
       </c>
       <c r="E45" s="3"/>
-      <c r="F45" s="60"/>
+      <c r="F45" s="60">
+        <v>45540.387222222198</v>
+      </c>
       <c r="G45" s="3">
         <v>3888.32</v>
       </c>
       <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6"/>
-      <c r="N45" s="6"/>
-      <c r="O45" s="6"/>
-      <c r="P45" s="6"/>
-      <c r="Q45" s="6"/>
+      <c r="I45" s="6">
+        <v>3899.9850000000001</v>
+      </c>
+      <c r="J45" s="6">
+        <v>23.9</v>
+      </c>
+      <c r="K45" s="6">
+        <v>22.6</v>
+      </c>
+      <c r="L45" s="6">
+        <v>94.8</v>
+      </c>
+      <c r="M45" s="6">
+        <v>17.2</v>
+      </c>
+      <c r="N45" s="6">
+        <v>343</v>
+      </c>
+      <c r="O45" s="6">
+        <v>1.26</v>
+      </c>
+      <c r="P45" s="6">
+        <v>0.26</v>
+      </c>
+      <c r="Q45" s="6">
+        <v>3.8</v>
+      </c>
       <c r="R45" s="6"/>
-      <c r="S45" s="6"/>
-      <c r="T45" s="6"/>
-      <c r="U45" s="6"/>
-      <c r="V45" s="6"/>
-      <c r="W45" s="6"/>
-      <c r="X45" s="6"/>
-      <c r="Y45" s="6"/>
-      <c r="Z45" s="6"/>
-      <c r="AA45" s="6"/>
-      <c r="AB45" s="6"/>
-      <c r="AC45" s="6"/>
-      <c r="AD45" s="16"/>
-      <c r="AE45" s="6"/>
-      <c r="AF45" s="6"/>
-      <c r="AG45" s="6"/>
+      <c r="S45" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="T45" s="6">
+        <v>0.11</v>
+      </c>
+      <c r="U45" s="6">
+        <v>1.08</v>
+      </c>
+      <c r="V45" s="6">
+        <v>7.258</v>
+      </c>
+      <c r="W45" s="6">
+        <v>112</v>
+      </c>
+      <c r="X45" s="6">
+        <v>28.6</v>
+      </c>
+      <c r="Y45" s="6">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="Z45" s="6">
+        <v>144.1</v>
+      </c>
+      <c r="AA45" s="6">
+        <v>48.7</v>
+      </c>
+      <c r="AB45" s="6">
+        <v>98.2</v>
+      </c>
+      <c r="AC45" s="6">
+        <v>23.1</v>
+      </c>
+      <c r="AD45" s="16">
+        <v>7.2990000000000004</v>
+      </c>
+      <c r="AE45" s="6">
+        <v>299</v>
+      </c>
+      <c r="AF45" s="6">
+        <v>48.7</v>
+      </c>
+      <c r="AG45" s="6">
+        <v>7.3</v>
+      </c>
       <c r="AH45" s="40">
         <f>AF45/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI45" s="6"/>
-      <c r="AJ45" s="6"/>
-      <c r="AK45" s="44"/>
-      <c r="AL45" s="6"/>
+        <v>0.48700000000000004</v>
+      </c>
+      <c r="AI45" s="6">
+        <v>34</v>
+      </c>
+      <c r="AJ45" s="6">
+        <v>22.07</v>
+      </c>
+      <c r="AK45" s="44">
+        <v>26.19</v>
+      </c>
+      <c r="AL45" s="6">
+        <v>4.54</v>
+      </c>
       <c r="AM45" s="42">
         <f>BR45</f>
-        <v>0</v>
-      </c>
-      <c r="AN45" s="6"/>
-      <c r="AO45" s="6"/>
-      <c r="AP45" s="6"/>
-      <c r="AQ45" s="6"/>
+        <v>1.86276921804269E-2</v>
+      </c>
+      <c r="AN45" s="6">
+        <v>115.26</v>
+      </c>
+      <c r="AO45" s="6">
+        <v>59.14</v>
+      </c>
+      <c r="AP45" s="6">
+        <v>557</v>
+      </c>
+      <c r="AQ45" s="6">
+        <v>1882</v>
+      </c>
       <c r="AR45" s="40">
         <v>137.11999999999989</v>
       </c>
       <c r="AS45" s="40">
         <f t="shared" si="60"/>
-        <v>-137.11999999999989</v>
+        <v>1744.88</v>
       </c>
       <c r="AT45" s="40">
         <f t="shared" si="36"/>
-        <v>-101.83</v>
+        <v>13.430000000000007</v>
       </c>
       <c r="AU45" s="40">
         <f t="shared" si="37"/>
-        <v>-56.98</v>
+        <v>2.1600000000000037</v>
       </c>
       <c r="AV45" s="40">
         <f t="shared" si="65"/>
-        <v>572</v>
+        <v>15</v>
       </c>
       <c r="AW45" s="24">
         <v>15</v>
@@ -11383,39 +11459,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC45" s="8"/>
-      <c r="BD45" s="9"/>
-      <c r="BE45" s="21"/>
+      <c r="BD45" s="46">
+        <f>BM45*24*60/BH45</f>
+        <v>1.4842782613885977E-2</v>
+      </c>
+      <c r="BE45" s="22">
+        <f>BP45/BH45</f>
+        <v>3.0046126474092961E-3</v>
+      </c>
       <c r="BF45" s="8">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.2252816E-2</v>
       </c>
       <c r="BG45" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.644055039999998</v>
       </c>
       <c r="BH45" s="9">
         <f t="shared" si="41"/>
-        <v>1580</v>
-      </c>
-      <c r="BI45" s="10" t="str">
+        <v>1807.2</v>
+      </c>
+      <c r="BI45" s="10">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ45" s="10" t="str">
+        <v>6.3778220451527229E-2</v>
+      </c>
+      <c r="BJ45" s="10">
         <f t="shared" si="9"/>
-        <v/>
+        <v>6.7799999999999999E-2</v>
       </c>
       <c r="BK45" s="10">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>26.82387673981474</v>
       </c>
       <c r="BL45" s="10" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM45" s="10">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.86276921804269E-2</v>
       </c>
       <c r="BN45" s="35" t="str">
         <f t="shared" si="32"/>
@@ -11426,20 +11507,19 @@
         <v/>
       </c>
       <c r="BP45" s="50">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>5.4299359763980801</v>
       </c>
       <c r="BQ45" s="27">
         <f>IF(BL45&lt;&gt;"",BL45/0.000385,IF(BM45&lt;&gt;"",BM45/0.000385,BN45/0.000385))</f>
-        <v>0</v>
+        <v>48.383616053056883</v>
       </c>
       <c r="BR45" s="37">
         <f>IF(BL45&lt;&gt;"",BL45,IF(BM45&lt;&gt;"",BM45,BN45))</f>
-        <v>0</v>
+        <v>1.86276921804269E-2</v>
       </c>
       <c r="BS45" s="32">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>5.4299359763980801</v>
       </c>
     </row>
     <row r="46" spans="1:71" x14ac:dyDescent="0.3">
@@ -11455,70 +11535,136 @@
       <c r="D46">
         <v>7</v>
       </c>
-      <c r="F46" s="61"/>
+      <c r="F46" s="61">
+        <v>45540.391423611101</v>
+      </c>
       <c r="G46">
         <v>3888.32</v>
       </c>
       <c r="H46" s="44"/>
-      <c r="I46" s="44"/>
-      <c r="J46" s="44"/>
-      <c r="K46" s="44"/>
-      <c r="L46" s="44"/>
-      <c r="M46" s="44"/>
-      <c r="N46" s="44"/>
-      <c r="O46" s="44"/>
-      <c r="P46" s="44"/>
-      <c r="Q46" s="44"/>
+      <c r="I46" s="44">
+        <v>3763.38</v>
+      </c>
+      <c r="J46" s="44">
+        <v>22</v>
+      </c>
+      <c r="K46" s="44">
+        <v>20.9</v>
+      </c>
+      <c r="L46" s="44">
+        <v>94.9</v>
+      </c>
+      <c r="M46" s="44">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="N46" s="44">
+        <v>349</v>
+      </c>
+      <c r="O46" s="44">
+        <v>1.37</v>
+      </c>
+      <c r="P46" s="44">
+        <v>0.24</v>
+      </c>
+      <c r="Q46" s="44">
+        <v>3.36</v>
+      </c>
       <c r="R46" s="44"/>
-      <c r="S46" s="44"/>
-      <c r="T46" s="44"/>
-      <c r="U46" s="44"/>
-      <c r="V46" s="44"/>
-      <c r="W46" s="44"/>
-      <c r="X46" s="44"/>
-      <c r="Y46" s="44"/>
-      <c r="Z46" s="44"/>
-      <c r="AA46" s="44"/>
-      <c r="AB46" s="44"/>
-      <c r="AC46" s="44"/>
-      <c r="AD46" s="17"/>
-      <c r="AE46" s="44"/>
-      <c r="AF46" s="44"/>
-      <c r="AG46" s="44"/>
+      <c r="S46" s="44">
+        <v>0.19</v>
+      </c>
+      <c r="T46" s="44">
+        <v>0.09</v>
+      </c>
+      <c r="U46" s="44">
+        <v>0.74</v>
+      </c>
+      <c r="V46" s="44">
+        <v>7.2610000000000001</v>
+      </c>
+      <c r="W46" s="44">
+        <v>137.69999999999999</v>
+      </c>
+      <c r="X46" s="44">
+        <v>35.1</v>
+      </c>
+      <c r="Y46" s="44">
+        <v>2.15</v>
+      </c>
+      <c r="Z46" s="44">
+        <v>149.1</v>
+      </c>
+      <c r="AA46" s="44">
+        <v>60.3</v>
+      </c>
+      <c r="AB46" s="44">
+        <v>120.8</v>
+      </c>
+      <c r="AC46" s="44">
+        <v>28.4</v>
+      </c>
+      <c r="AD46" s="17">
+        <v>7.3019999999999996</v>
+      </c>
+      <c r="AE46" s="44">
+        <v>301</v>
+      </c>
+      <c r="AF46" s="44">
+        <v>49.2</v>
+      </c>
+      <c r="AG46" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH46" s="45">
         <f t="shared" ref="AH46:AH50" si="66">AF46/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI46" s="44"/>
-      <c r="AJ46" s="44"/>
-      <c r="AK46" s="44"/>
-      <c r="AL46" s="44"/>
+        <v>0.49200000000000005</v>
+      </c>
+      <c r="AI46" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ46" s="44">
+        <v>24.57</v>
+      </c>
+      <c r="AK46" s="44">
+        <v>22.86</v>
+      </c>
+      <c r="AL46" s="44">
+        <v>2.59</v>
+      </c>
       <c r="AM46" s="45">
         <f t="shared" ref="AM46:AM50" si="67">BR46</f>
-        <v>0</v>
-      </c>
-      <c r="AN46" s="44"/>
-      <c r="AO46" s="44"/>
-      <c r="AP46" s="44"/>
-      <c r="AQ46" s="44"/>
+        <v>1.7472165513773799E-2</v>
+      </c>
+      <c r="AN46" s="44">
+        <v>123.07</v>
+      </c>
+      <c r="AO46" s="44">
+        <v>57.93</v>
+      </c>
+      <c r="AP46" s="44">
+        <v>553</v>
+      </c>
+      <c r="AQ46" s="44">
+        <v>1813</v>
+      </c>
       <c r="AR46" s="45">
         <v>45.769999999999982</v>
       </c>
       <c r="AS46" s="45">
         <f t="shared" si="60"/>
-        <v>-45.769999999999982</v>
+        <v>1767.23</v>
       </c>
       <c r="AT46" s="45">
         <f t="shared" si="36"/>
-        <v>-103.58</v>
+        <v>19.489999999999995</v>
       </c>
       <c r="AU46" s="45">
         <f t="shared" si="37"/>
-        <v>-57.93</v>
+        <v>0</v>
       </c>
       <c r="AV46" s="45">
         <f t="shared" si="65"/>
-        <v>576</v>
+        <v>23</v>
       </c>
       <c r="AW46" s="25">
         <v>15</v>
@@ -11539,39 +11685,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC46" s="11"/>
-      <c r="BD46" s="46"/>
-      <c r="BE46" s="22"/>
+      <c r="BD46" s="46">
+        <f>BM46*24*60/BH46</f>
+        <v>1.3892678346917356E-2</v>
+      </c>
+      <c r="BE46" s="22">
+        <f>BP46/BH46</f>
+        <v>1.5806774796027598E-3</v>
+      </c>
       <c r="BF46" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.1355095399999997E-2</v>
       </c>
       <c r="BG46" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.351337375999996</v>
       </c>
       <c r="BH46" s="46">
         <f t="shared" si="41"/>
-        <v>1580</v>
-      </c>
-      <c r="BI46" s="47" t="str">
+        <v>1811.02</v>
+      </c>
+      <c r="BI46" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ46" s="47" t="str">
+        <v>6.7956179390619653E-2</v>
+      </c>
+      <c r="BJ46" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>7.2394117647058817E-2</v>
       </c>
       <c r="BK46" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>25.15991833983427</v>
       </c>
       <c r="BL46" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM46" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.7472165513773799E-2</v>
       </c>
       <c r="BN46" s="48" t="str">
         <f t="shared" si="32"/>
@@ -11582,20 +11733,19 @@
         <v/>
       </c>
       <c r="BP46" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>2.8626385291101899</v>
       </c>
       <c r="BQ46" s="28">
         <f t="shared" ref="BQ46:BQ50" si="68">IF(BL46&lt;&gt;"",BL46/0.000385,IF(BM46&lt;&gt;"",BM46/0.000385,BN46/0.000385))</f>
-        <v>0</v>
+        <v>45.382248087724157</v>
       </c>
       <c r="BR46" s="49">
         <f t="shared" ref="BR46:BR50" si="69">IF(BL46&lt;&gt;"",BL46,IF(BM46&lt;&gt;"",BM46,BN46))</f>
-        <v>0</v>
+        <v>1.7472165513773799E-2</v>
       </c>
       <c r="BS46" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>2.8626385291101899</v>
       </c>
     </row>
     <row r="47" spans="1:71" x14ac:dyDescent="0.3">
@@ -11611,70 +11761,136 @@
       <c r="D47">
         <v>7</v>
       </c>
-      <c r="F47" s="61"/>
+      <c r="F47" s="61">
+        <v>45540.395925925899</v>
+      </c>
       <c r="G47">
         <v>3888.32</v>
       </c>
       <c r="H47" s="44"/>
-      <c r="I47" s="44"/>
-      <c r="J47" s="44"/>
-      <c r="K47" s="44"/>
-      <c r="L47" s="44"/>
-      <c r="M47" s="44"/>
-      <c r="N47" s="44"/>
-      <c r="O47" s="44"/>
-      <c r="P47" s="44"/>
-      <c r="Q47" s="44"/>
+      <c r="I47" s="44">
+        <v>3255.375</v>
+      </c>
+      <c r="J47" s="44">
+        <v>21.8</v>
+      </c>
+      <c r="K47" s="44">
+        <v>17.5</v>
+      </c>
+      <c r="L47" s="44">
+        <v>80.400000000000006</v>
+      </c>
+      <c r="M47" s="44">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="N47" s="44">
+        <v>420</v>
+      </c>
+      <c r="O47" s="44">
+        <v>1.52</v>
+      </c>
+      <c r="P47" s="44">
+        <v>0.27</v>
+      </c>
+      <c r="Q47" s="44">
+        <v>5.35</v>
+      </c>
       <c r="R47" s="44"/>
-      <c r="S47" s="44"/>
-      <c r="T47" s="44"/>
-      <c r="U47" s="44"/>
-      <c r="V47" s="44"/>
-      <c r="W47" s="44"/>
-      <c r="X47" s="44"/>
-      <c r="Y47" s="44"/>
-      <c r="Z47" s="44"/>
-      <c r="AA47" s="44"/>
-      <c r="AB47" s="44"/>
-      <c r="AC47" s="44"/>
-      <c r="AD47" s="17"/>
-      <c r="AE47" s="44"/>
-      <c r="AF47" s="44"/>
-      <c r="AG47" s="44"/>
+      <c r="S47" s="44">
+        <v>0.52</v>
+      </c>
+      <c r="T47" s="44">
+        <v>0.76</v>
+      </c>
+      <c r="U47" s="44">
+        <v>3.26</v>
+      </c>
+      <c r="V47" s="44">
+        <v>7.2619999999999996</v>
+      </c>
+      <c r="W47" s="44">
+        <v>118.8</v>
+      </c>
+      <c r="X47" s="44">
+        <v>25.9</v>
+      </c>
+      <c r="Y47" s="44">
+        <v>1.86</v>
+      </c>
+      <c r="Z47" s="44">
+        <v>169.8</v>
+      </c>
+      <c r="AA47" s="44">
+        <v>52.1</v>
+      </c>
+      <c r="AB47" s="44">
+        <v>104.2</v>
+      </c>
+      <c r="AC47" s="44">
+        <v>20.9</v>
+      </c>
+      <c r="AD47" s="17">
+        <v>7.3029999999999999</v>
+      </c>
+      <c r="AE47" s="44">
+        <v>300</v>
+      </c>
+      <c r="AF47" s="44">
+        <v>50.2</v>
+      </c>
+      <c r="AG47" s="44">
+        <v>7.27</v>
+      </c>
       <c r="AH47" s="45">
         <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="AI47" s="44"/>
-      <c r="AJ47" s="44"/>
-      <c r="AK47" s="44"/>
-      <c r="AL47" s="44"/>
+        <v>0.502</v>
+      </c>
+      <c r="AI47" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ47" s="44">
+        <v>38.049999999999997</v>
+      </c>
+      <c r="AK47" s="44">
+        <v>1.24</v>
+      </c>
+      <c r="AL47" s="44">
+        <v>5.72</v>
+      </c>
       <c r="AM47" s="45">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AN47" s="44"/>
-      <c r="AO47" s="44"/>
-      <c r="AP47" s="44"/>
-      <c r="AQ47" s="44"/>
+        <v>2.74293847933831E-2</v>
+      </c>
+      <c r="AN47" s="44">
+        <v>149.62</v>
+      </c>
+      <c r="AO47" s="44">
+        <v>71.12</v>
+      </c>
+      <c r="AP47" s="44">
+        <v>504</v>
+      </c>
+      <c r="AQ47" s="44">
+        <v>1879</v>
+      </c>
       <c r="AR47" s="45">
         <v>84.700000000000045</v>
       </c>
       <c r="AS47" s="45">
         <f t="shared" si="60"/>
-        <v>-84.700000000000045</v>
+        <v>1794.3</v>
       </c>
       <c r="AT47" s="45">
         <f t="shared" si="36"/>
-        <v>-113.88</v>
+        <v>35.740000000000009</v>
       </c>
       <c r="AU47" s="45">
         <f t="shared" si="37"/>
-        <v>-71.12</v>
+        <v>0</v>
       </c>
       <c r="AV47" s="45">
         <f t="shared" si="65"/>
-        <v>547</v>
+        <v>43</v>
       </c>
       <c r="AW47" s="25">
         <v>15</v>
@@ -11695,39 +11911,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC47" s="11"/>
-      <c r="BD47" s="46"/>
-      <c r="BE47" s="22"/>
+      <c r="BD47" s="46">
+        <f>BM47*24*60/BH47</f>
+        <v>2.139960130162355E-2</v>
+      </c>
+      <c r="BE47" s="22">
+        <f>BP47/BH47</f>
+        <v>1.8790139673301152E-4</v>
+      </c>
       <c r="BF47" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>9.6901874999999991E-3</v>
       </c>
       <c r="BG47" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13.953869999999998</v>
       </c>
       <c r="BH47" s="46">
         <f t="shared" si="41"/>
-        <v>1580</v>
-      </c>
-      <c r="BI47" s="47" t="str">
+        <v>1845.75</v>
+      </c>
+      <c r="BI47" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ47" s="47" t="str">
+        <v>8.1061898957063533E-2</v>
+      </c>
+      <c r="BJ47" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>8.8011764705882359E-2</v>
       </c>
       <c r="BK47" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>39.498314102471667</v>
       </c>
       <c r="BL47" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM47" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>2.74293847933831E-2</v>
       </c>
       <c r="BN47" s="48" t="str">
         <f t="shared" si="32"/>
@@ -11738,20 +11959,19 @@
         <v/>
       </c>
       <c r="BP47" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>0.346819003019956</v>
       </c>
       <c r="BQ47" s="28">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>71.245155307488574</v>
       </c>
       <c r="BR47" s="49">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.74293847933831E-2</v>
       </c>
       <c r="BS47" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>0.346819003019956</v>
       </c>
     </row>
     <row r="48" spans="1:71" x14ac:dyDescent="0.3">
@@ -11767,70 +11987,136 @@
       <c r="D48">
         <v>7</v>
       </c>
-      <c r="F48" s="61"/>
+      <c r="F48" s="61">
+        <v>45540.400462963</v>
+      </c>
       <c r="G48">
         <v>3888.32</v>
       </c>
       <c r="H48" s="44"/>
-      <c r="I48" s="44"/>
-      <c r="J48" s="44"/>
-      <c r="K48" s="44"/>
-      <c r="L48" s="44"/>
-      <c r="M48" s="44"/>
-      <c r="N48" s="44"/>
-      <c r="O48" s="44"/>
-      <c r="P48" s="44"/>
-      <c r="Q48" s="44"/>
+      <c r="I48" s="44">
+        <v>3332.46</v>
+      </c>
+      <c r="J48" s="44">
+        <v>20.5</v>
+      </c>
+      <c r="K48" s="44">
+        <v>17.8</v>
+      </c>
+      <c r="L48" s="44">
+        <v>86.7</v>
+      </c>
+      <c r="M48" s="44">
+        <v>18.2</v>
+      </c>
+      <c r="N48" s="44">
+        <v>418</v>
+      </c>
+      <c r="O48" s="44">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="P48" s="44">
+        <v>0.27</v>
+      </c>
+      <c r="Q48" s="44">
+        <v>4.3099999999999996</v>
+      </c>
       <c r="R48" s="44"/>
-      <c r="S48" s="44"/>
-      <c r="T48" s="44"/>
-      <c r="U48" s="44"/>
-      <c r="V48" s="44"/>
-      <c r="W48" s="44"/>
-      <c r="X48" s="44"/>
-      <c r="Y48" s="44"/>
-      <c r="Z48" s="44"/>
-      <c r="AA48" s="44"/>
-      <c r="AB48" s="44"/>
-      <c r="AC48" s="44"/>
-      <c r="AD48" s="17"/>
-      <c r="AE48" s="44"/>
-      <c r="AF48" s="44"/>
-      <c r="AG48" s="44"/>
+      <c r="S48" s="44">
+        <v>0.27</v>
+      </c>
+      <c r="T48" s="44">
+        <v>0.18</v>
+      </c>
+      <c r="U48" s="44">
+        <v>4.25</v>
+      </c>
+      <c r="V48" s="44">
+        <v>7.2770000000000001</v>
+      </c>
+      <c r="W48" s="44">
+        <v>118.2</v>
+      </c>
+      <c r="X48" s="44">
+        <v>23.3</v>
+      </c>
+      <c r="Y48" s="44">
+        <v>1.97</v>
+      </c>
+      <c r="Z48" s="44">
+        <v>175.4</v>
+      </c>
+      <c r="AA48" s="44">
+        <v>53.8</v>
+      </c>
+      <c r="AB48" s="44">
+        <v>103.7</v>
+      </c>
+      <c r="AC48" s="44">
+        <v>18.8</v>
+      </c>
+      <c r="AD48" s="17">
+        <v>7.319</v>
+      </c>
+      <c r="AE48" s="44">
+        <v>300</v>
+      </c>
+      <c r="AF48" s="44">
+        <v>47.3</v>
+      </c>
+      <c r="AG48" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH48" s="45">
         <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="AI48" s="44"/>
-      <c r="AJ48" s="44"/>
-      <c r="AK48" s="44"/>
-      <c r="AL48" s="44"/>
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="AI48" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ48" s="44">
+        <v>43.09</v>
+      </c>
+      <c r="AK48" s="44">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="AL48" s="44">
+        <v>5.81</v>
+      </c>
       <c r="AM48" s="45">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AN48" s="44"/>
-      <c r="AO48" s="44"/>
-      <c r="AP48" s="44"/>
-      <c r="AQ48" s="44"/>
+        <v>2.5469722222222223E-2</v>
+      </c>
+      <c r="AN48" s="44">
+        <v>124.93</v>
+      </c>
+      <c r="AO48" s="44">
+        <v>70.87</v>
+      </c>
+      <c r="AP48" s="44">
+        <v>537</v>
+      </c>
+      <c r="AQ48" s="44">
+        <v>1843</v>
+      </c>
       <c r="AR48" s="45">
         <v>47.420000000000073</v>
       </c>
       <c r="AS48" s="45">
         <f t="shared" si="60"/>
-        <v>-47.420000000000073</v>
+        <v>1795.58</v>
       </c>
       <c r="AT48" s="45">
         <f t="shared" si="36"/>
-        <v>-88.68</v>
+        <v>36.25</v>
       </c>
       <c r="AU48" s="45">
         <f t="shared" si="37"/>
-        <v>-80.87</v>
+        <v>-10</v>
       </c>
       <c r="AV48" s="45">
         <f t="shared" si="65"/>
-        <v>580</v>
+        <v>43</v>
       </c>
       <c r="AW48" s="25">
         <v>15</v>
@@ -11850,35 +12136,37 @@
       <c r="BB48" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC48" s="11"/>
+      <c r="BC48" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BE48" s="22"/>
       <c r="BF48" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>9.7925987999999999E-3</v>
       </c>
       <c r="BG48" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.101342272</v>
       </c>
       <c r="BH48" s="46">
         <f t="shared" si="41"/>
-        <v>1580</v>
-      </c>
-      <c r="BI48" s="47" t="str">
+        <v>1833.82</v>
+      </c>
+      <c r="BI48" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ48" s="47" t="str">
+        <v>6.8125552126162878E-2</v>
+      </c>
+      <c r="BJ48" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>7.3488235294117646E-2</v>
       </c>
       <c r="BK48" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>36.676400000000001</v>
       </c>
       <c r="BL48" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.5469722222222223E-2</v>
       </c>
       <c r="BM48" s="48" t="str">
         <f t="shared" si="31"/>
@@ -11890,7 +12178,7 @@
       </c>
       <c r="BO48" s="47">
         <f t="shared" si="47"/>
-        <v>11.85</v>
+        <v>0</v>
       </c>
       <c r="BP48" s="51" t="str">
         <f t="shared" si="28"/>
@@ -11898,15 +12186,15 @@
       </c>
       <c r="BQ48" s="28">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>66.155122655122668</v>
       </c>
       <c r="BR48" s="49">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.5469722222222223E-2</v>
       </c>
       <c r="BS48" s="30">
         <f t="shared" si="21"/>
-        <v>11.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:71" x14ac:dyDescent="0.3">
@@ -11922,70 +12210,134 @@
       <c r="D49">
         <v>7</v>
       </c>
-      <c r="F49" s="61"/>
+      <c r="F49" s="61">
+        <v>45540.404571759304</v>
+      </c>
       <c r="G49">
         <v>3888.32</v>
       </c>
       <c r="H49" s="44"/>
-      <c r="I49" s="44"/>
-      <c r="J49" s="44"/>
-      <c r="K49" s="44"/>
-      <c r="L49" s="44"/>
-      <c r="M49" s="44"/>
-      <c r="N49" s="44"/>
-      <c r="O49" s="44"/>
-      <c r="P49" s="44"/>
-      <c r="Q49" s="44"/>
+      <c r="I49" s="44">
+        <v>2666.67</v>
+      </c>
+      <c r="J49" s="44">
+        <v>21.5</v>
+      </c>
+      <c r="K49" s="44">
+        <v>14.9</v>
+      </c>
+      <c r="L49" s="44">
+        <v>69.5</v>
+      </c>
+      <c r="M49" s="44">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="N49" s="44">
+        <v>552</v>
+      </c>
+      <c r="O49" s="44">
+        <v>3.84</v>
+      </c>
+      <c r="P49" s="44">
+        <v>0.32</v>
+      </c>
+      <c r="Q49" s="44">
+        <v>1.27</v>
+      </c>
       <c r="R49" s="44"/>
-      <c r="S49" s="44"/>
-      <c r="T49" s="44"/>
+      <c r="S49" s="44">
+        <v>0.54</v>
+      </c>
+      <c r="T49" s="44">
+        <v>2.17</v>
+      </c>
       <c r="U49" s="44"/>
-      <c r="V49" s="44"/>
-      <c r="W49" s="44"/>
-      <c r="X49" s="44"/>
-      <c r="Y49" s="44"/>
-      <c r="Z49" s="44"/>
-      <c r="AA49" s="44"/>
-      <c r="AB49" s="44"/>
-      <c r="AC49" s="44"/>
-      <c r="AD49" s="17"/>
-      <c r="AE49" s="44"/>
-      <c r="AF49" s="44"/>
-      <c r="AG49" s="44"/>
+      <c r="V49" s="44">
+        <v>7.07</v>
+      </c>
+      <c r="W49" s="44">
+        <v>80.599999999999994</v>
+      </c>
+      <c r="X49" s="44">
+        <v>31.6</v>
+      </c>
+      <c r="Y49" s="44">
+        <v>3.52</v>
+      </c>
+      <c r="Z49" s="44">
+        <v>230.7</v>
+      </c>
+      <c r="AA49" s="44">
+        <v>22.6</v>
+      </c>
+      <c r="AB49" s="44">
+        <v>70.7</v>
+      </c>
+      <c r="AC49" s="44">
+        <v>25.6</v>
+      </c>
+      <c r="AD49" s="17">
+        <v>7.1079999999999997</v>
+      </c>
+      <c r="AE49" s="44">
+        <v>298</v>
+      </c>
+      <c r="AF49" s="44">
+        <v>56.7</v>
+      </c>
+      <c r="AG49" s="44">
+        <v>7.11</v>
+      </c>
       <c r="AH49" s="45">
         <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="AI49" s="44"/>
-      <c r="AJ49" s="44"/>
-      <c r="AK49" s="44"/>
-      <c r="AL49" s="44"/>
+        <v>0.56700000000000006</v>
+      </c>
+      <c r="AI49" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ49" s="44">
+        <v>80.680000000000007</v>
+      </c>
+      <c r="AK49" s="44">
+        <v>7.31</v>
+      </c>
+      <c r="AL49" s="44">
+        <v>5.53</v>
+      </c>
       <c r="AM49" s="45">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AN49" s="44"/>
-      <c r="AO49" s="44"/>
-      <c r="AP49" s="44"/>
-      <c r="AQ49" s="44"/>
+        <v>2.6222638888888889E-2</v>
+      </c>
+      <c r="AN49" s="44">
+        <v>145.49</v>
+      </c>
+      <c r="AO49" s="44">
+        <v>69.02</v>
+      </c>
+      <c r="AP49" s="44">
+        <v>491</v>
+      </c>
+      <c r="AQ49" s="44">
+        <v>1902</v>
+      </c>
       <c r="AR49" s="45">
         <v>133.55999999999995</v>
       </c>
       <c r="AS49" s="45">
         <f t="shared" si="60"/>
-        <v>-133.55999999999995</v>
+        <v>1768.44</v>
       </c>
       <c r="AT49" s="45">
         <f t="shared" si="36"/>
-        <v>-111.39</v>
+        <v>34.100000000000009</v>
       </c>
       <c r="AU49" s="45">
         <f t="shared" si="37"/>
-        <v>-54.88</v>
+        <v>14.139999999999993</v>
       </c>
       <c r="AV49" s="45">
         <f t="shared" si="65"/>
-        <v>531</v>
+        <v>40</v>
       </c>
       <c r="AW49" s="25">
         <v>15</v>
@@ -12005,35 +12357,37 @@
       <c r="BB49" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC49" s="11"/>
+      <c r="BC49" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BE49" s="22"/>
       <c r="BF49" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>8.4394940999999984E-3</v>
       </c>
       <c r="BG49" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12.152871503999997</v>
       </c>
       <c r="BH49" s="46">
         <f t="shared" si="41"/>
-        <v>1580</v>
-      </c>
-      <c r="BI49" s="47" t="str">
+        <v>1888.03</v>
+      </c>
+      <c r="BI49" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ49" s="47" t="str">
+        <v>7.7059156898989956E-2</v>
+      </c>
+      <c r="BJ49" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>8.5582352941176471E-2</v>
       </c>
       <c r="BK49" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>37.760600000000004</v>
       </c>
       <c r="BL49" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.6222638888888889E-2</v>
       </c>
       <c r="BM49" s="48" t="str">
         <f t="shared" si="31"/>
@@ -12045,7 +12399,7 @@
       </c>
       <c r="BO49" s="47">
         <f t="shared" si="47"/>
-        <v>11.85</v>
+        <v>8.1657297499999988</v>
       </c>
       <c r="BP49" s="51" t="str">
         <f t="shared" si="28"/>
@@ -12053,15 +12407,15 @@
       </c>
       <c r="BQ49" s="28">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>68.110750360750359</v>
       </c>
       <c r="BR49" s="49">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>2.6222638888888889E-2</v>
       </c>
       <c r="BS49" s="30">
         <f t="shared" si="21"/>
-        <v>11.85</v>
+        <v>8.1657297499999988</v>
       </c>
     </row>
     <row r="50" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -12078,70 +12432,134 @@
         <v>7</v>
       </c>
       <c r="E50" s="5"/>
-      <c r="F50" s="62"/>
+      <c r="F50" s="62">
+        <v>45540.408935185202</v>
+      </c>
       <c r="G50" s="5">
         <v>3888.32</v>
       </c>
       <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
+      <c r="I50" s="7">
+        <v>4031.4749999999999</v>
+      </c>
+      <c r="J50" s="7">
+        <v>21.3</v>
+      </c>
+      <c r="K50" s="7">
+        <v>20.2</v>
+      </c>
+      <c r="L50" s="7">
+        <v>94.8</v>
+      </c>
+      <c r="M50" s="7">
+        <v>17.899999999999999</v>
+      </c>
       <c r="N50" s="7"/>
-      <c r="O50" s="7"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="7"/>
+      <c r="O50" s="7">
+        <v>1.21</v>
+      </c>
+      <c r="P50" s="7">
+        <v>0.24</v>
+      </c>
+      <c r="Q50" s="7">
+        <v>3.47</v>
+      </c>
       <c r="R50" s="7"/>
-      <c r="S50" s="7"/>
-      <c r="T50" s="7"/>
-      <c r="U50" s="7"/>
-      <c r="V50" s="7"/>
-      <c r="W50" s="7"/>
-      <c r="X50" s="7"/>
-      <c r="Y50" s="7"/>
-      <c r="Z50" s="7"/>
-      <c r="AA50" s="7"/>
-      <c r="AB50" s="7"/>
-      <c r="AC50" s="7"/>
-      <c r="AD50" s="18"/>
-      <c r="AE50" s="7"/>
-      <c r="AF50" s="7"/>
-      <c r="AG50" s="7"/>
+      <c r="S50" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="T50" s="7">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="U50" s="7">
+        <v>1.71</v>
+      </c>
+      <c r="V50" s="7">
+        <v>7.2640000000000002</v>
+      </c>
+      <c r="W50" s="7">
+        <v>122.7</v>
+      </c>
+      <c r="X50" s="7">
+        <v>36.4</v>
+      </c>
+      <c r="Y50" s="7">
+        <v>1.76</v>
+      </c>
+      <c r="Z50" s="7">
+        <v>156.4</v>
+      </c>
+      <c r="AA50" s="7">
+        <v>54.1</v>
+      </c>
+      <c r="AB50" s="7">
+        <v>107.6</v>
+      </c>
+      <c r="AC50" s="7">
+        <v>29.4</v>
+      </c>
+      <c r="AD50" s="18">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="AE50" s="7">
+        <v>301</v>
+      </c>
+      <c r="AF50" s="7">
+        <v>49.6</v>
+      </c>
+      <c r="AG50" s="7">
+        <v>7.3</v>
+      </c>
       <c r="AH50" s="41">
         <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="AI50" s="7"/>
-      <c r="AJ50" s="7"/>
-      <c r="AK50" s="7"/>
-      <c r="AL50" s="7"/>
+        <v>0.496</v>
+      </c>
+      <c r="AI50" s="7">
+        <v>34</v>
+      </c>
+      <c r="AJ50" s="7">
+        <v>28.27</v>
+      </c>
+      <c r="AK50" s="7">
+        <v>22.05</v>
+      </c>
+      <c r="AL50" s="7">
+        <v>5.59</v>
+      </c>
       <c r="AM50" s="41">
         <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AN50" s="7"/>
-      <c r="AO50" s="7"/>
-      <c r="AP50" s="7"/>
-      <c r="AQ50" s="7"/>
+        <v>1.4294622222222221E-2</v>
+      </c>
+      <c r="AN50" s="7">
+        <v>145.38</v>
+      </c>
+      <c r="AO50" s="7">
+        <v>56.59</v>
+      </c>
+      <c r="AP50" s="7">
+        <v>525</v>
+      </c>
+      <c r="AQ50" s="7">
+        <v>1846</v>
+      </c>
       <c r="AR50" s="41">
         <v>51.660000000000082</v>
       </c>
       <c r="AS50" s="41">
         <f t="shared" si="60"/>
-        <v>-51.660000000000082</v>
+        <v>1794.34</v>
       </c>
       <c r="AT50" s="41">
         <f t="shared" si="36"/>
-        <v>-116.7</v>
+        <v>28.679999999999993</v>
       </c>
       <c r="AU50" s="41">
         <f t="shared" si="37"/>
-        <v>-56.59</v>
+        <v>0</v>
       </c>
       <c r="AV50" s="41">
         <f t="shared" si="65"/>
-        <v>558</v>
+        <v>33</v>
       </c>
       <c r="AW50" s="26">
         <v>15</v>
@@ -12161,36 +12579,38 @@
       <c r="BB50" s="23">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC50" s="12"/>
+      <c r="BC50" s="12">
+        <v>1.12E-2</v>
+      </c>
       <c r="BD50" s="5"/>
       <c r="BE50" s="23"/>
       <c r="BF50" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.11375528E-2</v>
       </c>
       <c r="BG50" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.038076032000003</v>
       </c>
       <c r="BH50" s="13">
         <f t="shared" si="41"/>
-        <v>1580</v>
-      </c>
-      <c r="BI50" s="14" t="str">
+        <v>1837.88</v>
+      </c>
+      <c r="BI50" s="14">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ50" s="14" t="str">
+        <v>7.9102008836267862E-2</v>
+      </c>
+      <c r="BJ50" s="14">
         <f t="shared" si="9"/>
-        <v/>
+        <v>8.5517647058823532E-2</v>
       </c>
       <c r="BK50" s="14">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>20.584256</v>
       </c>
       <c r="BL50" s="14">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.4294622222222221E-2</v>
       </c>
       <c r="BM50" s="48" t="str">
         <f t="shared" si="31"/>
@@ -12202,7 +12622,7 @@
       </c>
       <c r="BO50" s="14">
         <f t="shared" si="47"/>
-        <v>11.85</v>
+        <v>0</v>
       </c>
       <c r="BP50" s="52" t="str">
         <f t="shared" si="28"/>
@@ -12210,15 +12630,15 @@
       </c>
       <c r="BQ50" s="29">
         <f t="shared" si="68"/>
-        <v>0</v>
+        <v>37.128888888888888</v>
       </c>
       <c r="BR50" s="38">
         <f t="shared" si="69"/>
-        <v>0</v>
+        <v>1.4294622222222221E-2</v>
       </c>
       <c r="BS50" s="31">
         <f t="shared" si="21"/>
-        <v>11.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:71" x14ac:dyDescent="0.3">
@@ -12235,70 +12655,136 @@
         <v>8</v>
       </c>
       <c r="E51" s="3"/>
-      <c r="F51" s="60"/>
+      <c r="F51" s="60">
+        <v>45541.409976851901</v>
+      </c>
       <c r="G51" s="3">
         <v>4309.7</v>
       </c>
       <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="6"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="6"/>
-      <c r="Q51" s="6"/>
+      <c r="I51" s="6">
+        <v>4354.6350000000002</v>
+      </c>
+      <c r="J51" s="6">
+        <v>23.4</v>
+      </c>
+      <c r="K51" s="6">
+        <v>22.2</v>
+      </c>
+      <c r="L51" s="6">
+        <v>94.8</v>
+      </c>
+      <c r="M51" s="6">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="N51" s="6">
+        <v>356</v>
+      </c>
+      <c r="O51" s="6">
+        <v>1.39</v>
+      </c>
+      <c r="P51" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="R51" s="6"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="6"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="6"/>
-      <c r="AB51" s="6"/>
-      <c r="AC51" s="6"/>
-      <c r="AD51" s="16"/>
-      <c r="AE51" s="6"/>
-      <c r="AF51" s="6"/>
-      <c r="AG51" s="6"/>
+      <c r="S51" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="U51" s="6">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="V51" s="6">
+        <v>7.26</v>
+      </c>
+      <c r="W51" s="6">
+        <v>121.2</v>
+      </c>
+      <c r="X51" s="6">
+        <v>29</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>2.21</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>144.5</v>
+      </c>
+      <c r="AA51" s="6">
+        <v>53</v>
+      </c>
+      <c r="AB51" s="6">
+        <v>106.3</v>
+      </c>
+      <c r="AC51" s="6">
+        <v>23.4</v>
+      </c>
+      <c r="AD51" s="16">
+        <v>7.3019999999999996</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>300</v>
+      </c>
+      <c r="AF51" s="6">
+        <v>49.8</v>
+      </c>
+      <c r="AG51" s="6">
+        <v>7.3</v>
+      </c>
       <c r="AH51" s="40">
         <f>AF51/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI51" s="6"/>
-      <c r="AJ51" s="6"/>
-      <c r="AK51" s="44"/>
-      <c r="AL51" s="6"/>
+        <v>0.498</v>
+      </c>
+      <c r="AI51" s="6">
+        <v>34</v>
+      </c>
+      <c r="AJ51" s="6">
+        <v>22.07</v>
+      </c>
+      <c r="AK51" s="44">
+        <v>33.090000000000003</v>
+      </c>
+      <c r="AL51" s="6">
+        <v>5.29</v>
+      </c>
       <c r="AM51" s="42">
         <f>BR51</f>
-        <v>0</v>
-      </c>
-      <c r="AN51" s="6"/>
-      <c r="AO51" s="6"/>
-      <c r="AP51" s="6"/>
-      <c r="AQ51" s="6"/>
+        <v>5.0842500000000002E-3</v>
+      </c>
+      <c r="AN51" s="6">
+        <v>139.57</v>
+      </c>
+      <c r="AO51" s="6">
+        <v>65.31</v>
+      </c>
+      <c r="AP51" s="6">
+        <v>530</v>
+      </c>
+      <c r="AQ51" s="6">
+        <v>1904</v>
+      </c>
       <c r="AR51" s="40">
         <v>137.11999999999989</v>
       </c>
       <c r="AS51" s="40">
         <f t="shared" si="60"/>
-        <v>-137.11999999999989</v>
+        <v>1766.88</v>
       </c>
       <c r="AT51" s="40">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>24.309999999999988</v>
       </c>
       <c r="AU51" s="40">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>6.1700000000000017</v>
       </c>
       <c r="AV51" s="40">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AW51" s="24">
         <v>15</v>
@@ -12319,39 +12805,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC51" s="8"/>
-      <c r="BD51" s="9"/>
-      <c r="BE51" s="21"/>
+      <c r="BD51" s="46">
+        <f>BM51*24*60/BH51</f>
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="BE51" s="22">
+        <f>BP51/BH51</f>
+        <v>1.0000000000000001E-7</v>
+      </c>
       <c r="BF51" s="8">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.2189997799999998E-2</v>
       </c>
       <c r="BG51" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17.553596831999997</v>
       </c>
       <c r="BH51" s="9">
         <f t="shared" si="41"/>
-        <v>1565</v>
-      </c>
-      <c r="BI51" s="10" t="str">
+        <v>1830.33</v>
+      </c>
+      <c r="BI51" s="10">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ51" s="10" t="str">
+        <v>7.6254008839935966E-2</v>
+      </c>
+      <c r="BJ51" s="10">
         <f t="shared" si="9"/>
-        <v/>
+        <v>8.2099999999999992E-2</v>
       </c>
       <c r="BK51" s="10">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>7.3213200000000001</v>
       </c>
       <c r="BL51" s="10" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM51" s="10">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>5.0842500000000002E-3</v>
       </c>
       <c r="BN51" s="35" t="str">
         <f t="shared" si="32"/>
@@ -12362,20 +12853,19 @@
         <v/>
       </c>
       <c r="BP51" s="50">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1.8303300000000001E-4</v>
       </c>
       <c r="BQ51" s="27">
         <f>IF(BL51&lt;&gt;"",BL51/0.000385,IF(BM51&lt;&gt;"",BM51/0.000385,BN51/0.000385))</f>
-        <v>0</v>
+        <v>13.205844155844158</v>
       </c>
       <c r="BR51" s="37">
         <f>IF(BL51&lt;&gt;"",BL51,IF(BM51&lt;&gt;"",BM51,BN51))</f>
-        <v>0</v>
+        <v>5.0842500000000002E-3</v>
       </c>
       <c r="BS51" s="32">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1.8303300000000001E-4</v>
       </c>
     </row>
     <row r="52" spans="1:71" x14ac:dyDescent="0.3">
@@ -12391,70 +12881,136 @@
       <c r="D52">
         <v>8</v>
       </c>
-      <c r="F52" s="61"/>
+      <c r="F52" s="61">
+        <v>45541.414027777799</v>
+      </c>
       <c r="G52">
         <v>4309.7</v>
       </c>
       <c r="H52" s="44"/>
-      <c r="I52" s="44"/>
-      <c r="J52" s="44"/>
-      <c r="K52" s="44"/>
-      <c r="L52" s="44"/>
-      <c r="M52" s="44"/>
-      <c r="N52" s="44"/>
-      <c r="O52" s="44"/>
-      <c r="P52" s="44"/>
-      <c r="Q52" s="44"/>
+      <c r="I52" s="44">
+        <v>4501.3500000000004</v>
+      </c>
+      <c r="J52" s="44">
+        <v>21.1</v>
+      </c>
+      <c r="K52" s="44">
+        <v>20</v>
+      </c>
+      <c r="L52" s="44">
+        <v>94.7</v>
+      </c>
+      <c r="M52" s="44">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="N52" s="44">
+        <v>359</v>
+      </c>
+      <c r="O52" s="44">
+        <v>1.57</v>
+      </c>
+      <c r="P52" s="44">
+        <v>0.22</v>
+      </c>
+      <c r="Q52" s="44">
+        <v>3.24</v>
+      </c>
       <c r="R52" s="44"/>
-      <c r="S52" s="44"/>
-      <c r="T52" s="44"/>
-      <c r="U52" s="44"/>
-      <c r="V52" s="44"/>
-      <c r="W52" s="44"/>
-      <c r="X52" s="44"/>
-      <c r="Y52" s="44"/>
-      <c r="Z52" s="44"/>
-      <c r="AA52" s="44"/>
-      <c r="AB52" s="44"/>
-      <c r="AC52" s="44"/>
-      <c r="AD52" s="17"/>
-      <c r="AE52" s="44"/>
-      <c r="AF52" s="44"/>
-      <c r="AG52" s="44"/>
+      <c r="S52" s="44">
+        <v>0.12</v>
+      </c>
+      <c r="T52" s="44">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="U52" s="44">
+        <v>0.23</v>
+      </c>
+      <c r="V52" s="44">
+        <v>7.266</v>
+      </c>
+      <c r="W52" s="44">
+        <v>142.5</v>
+      </c>
+      <c r="X52" s="44">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="Y52" s="44">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="Z52" s="44">
+        <v>150.6</v>
+      </c>
+      <c r="AA52" s="44">
+        <v>63.1</v>
+      </c>
+      <c r="AB52" s="44">
+        <v>125</v>
+      </c>
+      <c r="AC52" s="44">
+        <v>26.9</v>
+      </c>
+      <c r="AD52" s="17">
+        <v>7.3070000000000004</v>
+      </c>
+      <c r="AE52" s="44">
+        <v>300</v>
+      </c>
+      <c r="AF52" s="44">
+        <v>49.1</v>
+      </c>
+      <c r="AG52" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH52" s="45">
         <f t="shared" ref="AH52:AH56" si="70">AF52/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI52" s="44"/>
-      <c r="AJ52" s="44"/>
-      <c r="AK52" s="44"/>
-      <c r="AL52" s="44"/>
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="AI52" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ52" s="44">
+        <v>24.57</v>
+      </c>
+      <c r="AK52" s="44">
+        <v>26.68</v>
+      </c>
+      <c r="AL52" s="44">
+        <v>3</v>
+      </c>
       <c r="AM52" s="45">
         <f t="shared" ref="AM52:AM56" si="71">BR52</f>
-        <v>0</v>
-      </c>
-      <c r="AN52" s="44"/>
-      <c r="AO52" s="44"/>
-      <c r="AP52" s="44"/>
-      <c r="AQ52" s="44"/>
+        <v>1.16538420964073E-2</v>
+      </c>
+      <c r="AN52" s="44">
+        <v>147.31</v>
+      </c>
+      <c r="AO52" s="44">
+        <v>61.42</v>
+      </c>
+      <c r="AP52" s="44">
+        <v>524</v>
+      </c>
+      <c r="AQ52" s="44">
+        <v>1832</v>
+      </c>
       <c r="AR52" s="45">
         <v>45.769999999999982</v>
       </c>
       <c r="AS52" s="45">
         <f t="shared" si="60"/>
-        <v>-45.769999999999982</v>
+        <v>1786.23</v>
       </c>
       <c r="AT52" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>24.240000000000009</v>
       </c>
       <c r="AU52" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>3.490000000000002</v>
       </c>
       <c r="AV52" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AW52" s="25">
         <v>15</v>
@@ -12475,39 +13031,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC52" s="11"/>
-      <c r="BD52" s="46"/>
-      <c r="BE52" s="22"/>
+      <c r="BD52" s="46">
+        <f>BM52*24*60/BH52</f>
+        <v>9.1803699268189556E-3</v>
+      </c>
+      <c r="BE52" s="22">
+        <f>BP52/BH52</f>
+        <v>9.9999999999999995E-8</v>
+      </c>
       <c r="BF52" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.0967879999999999E-2</v>
       </c>
       <c r="BG52" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15.793747199999999</v>
       </c>
       <c r="BH52" s="46">
         <f t="shared" si="41"/>
-        <v>1565</v>
-      </c>
-      <c r="BI52" s="47" t="str">
+        <v>1827.98</v>
+      </c>
+      <c r="BI52" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ52" s="47" t="str">
+        <v>8.058622085580805E-2</v>
+      </c>
+      <c r="BJ52" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>8.6652941176470585E-2</v>
       </c>
       <c r="BK52" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>16.781532618826514</v>
       </c>
       <c r="BL52" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM52" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.16538420964073E-2</v>
       </c>
       <c r="BN52" s="48" t="str">
         <f t="shared" si="32"/>
@@ -12518,20 +13079,19 @@
         <v/>
       </c>
       <c r="BP52" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1.8279799999999999E-4</v>
       </c>
       <c r="BQ52" s="28">
         <f t="shared" ref="BQ52:BQ56" si="72">IF(BL52&lt;&gt;"",BL52/0.000385,IF(BM52&lt;&gt;"",BM52/0.000385,BN52/0.000385))</f>
-        <v>0</v>
+        <v>30.269719730928053</v>
       </c>
       <c r="BR52" s="49">
         <f t="shared" ref="BR52:BR56" si="73">IF(BL52&lt;&gt;"",BL52,IF(BM52&lt;&gt;"",BM52,BN52))</f>
-        <v>0</v>
+        <v>1.16538420964073E-2</v>
       </c>
       <c r="BS52" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1.8279799999999999E-4</v>
       </c>
     </row>
     <row r="53" spans="1:71" x14ac:dyDescent="0.3">
@@ -12547,70 +13107,136 @@
       <c r="D53">
         <v>8</v>
       </c>
-      <c r="F53" s="61"/>
+      <c r="F53" s="61">
+        <v>45541.418136574102</v>
+      </c>
       <c r="G53">
         <v>4309.7</v>
       </c>
       <c r="H53" s="44"/>
-      <c r="I53" s="44"/>
-      <c r="J53" s="44"/>
-      <c r="K53" s="44"/>
-      <c r="L53" s="44"/>
-      <c r="M53" s="44"/>
-      <c r="N53" s="44"/>
-      <c r="O53" s="44"/>
-      <c r="P53" s="44"/>
-      <c r="Q53" s="44"/>
+      <c r="I53" s="44">
+        <v>4039.83</v>
+      </c>
+      <c r="J53" s="44">
+        <v>21.7</v>
+      </c>
+      <c r="K53" s="44">
+        <v>18.5</v>
+      </c>
+      <c r="L53" s="44">
+        <v>85.3</v>
+      </c>
+      <c r="M53" s="44">
+        <v>18.5</v>
+      </c>
+      <c r="N53" s="44">
+        <v>427</v>
+      </c>
+      <c r="O53" s="44">
+        <v>1.7</v>
+      </c>
+      <c r="P53" s="44">
+        <v>0.25</v>
+      </c>
+      <c r="Q53" s="44">
+        <v>4.8099999999999996</v>
+      </c>
       <c r="R53" s="44"/>
-      <c r="S53" s="44"/>
-      <c r="T53" s="44"/>
-      <c r="U53" s="44"/>
-      <c r="V53" s="44"/>
-      <c r="W53" s="44"/>
-      <c r="X53" s="44"/>
-      <c r="Y53" s="44"/>
-      <c r="Z53" s="44"/>
-      <c r="AA53" s="44"/>
-      <c r="AB53" s="44"/>
-      <c r="AC53" s="44"/>
-      <c r="AD53" s="17"/>
-      <c r="AE53" s="44"/>
-      <c r="AF53" s="44"/>
-      <c r="AG53" s="44"/>
+      <c r="S53" s="44">
+        <v>0.62</v>
+      </c>
+      <c r="T53" s="44">
+        <v>1.62</v>
+      </c>
+      <c r="U53" s="44">
+        <v>2.71</v>
+      </c>
+      <c r="V53" s="44">
+        <v>7.2610000000000001</v>
+      </c>
+      <c r="W53" s="44">
+        <v>119.6</v>
+      </c>
+      <c r="X53" s="44">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="44">
+        <v>1.65</v>
+      </c>
+      <c r="Z53" s="44">
+        <v>173.4</v>
+      </c>
+      <c r="AA53" s="44">
+        <v>52.4</v>
+      </c>
+      <c r="AB53" s="44">
+        <v>104.9</v>
+      </c>
+      <c r="AC53" s="44">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="17">
+        <v>7.3019999999999996</v>
+      </c>
+      <c r="AE53" s="44">
+        <v>299</v>
+      </c>
+      <c r="AF53" s="44">
+        <v>49.5</v>
+      </c>
+      <c r="AG53" s="44">
+        <v>7.27</v>
+      </c>
       <c r="AH53" s="45">
         <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="AI53" s="44"/>
-      <c r="AJ53" s="44"/>
-      <c r="AK53" s="44"/>
-      <c r="AL53" s="44"/>
+        <v>0.495</v>
+      </c>
+      <c r="AI53" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ53" s="44">
+        <v>38.049999999999997</v>
+      </c>
+      <c r="AK53" s="44">
+        <v>1.24</v>
+      </c>
+      <c r="AL53" s="44">
+        <v>6.66</v>
+      </c>
       <c r="AM53" s="45">
         <f t="shared" si="71"/>
-        <v>0</v>
-      </c>
-      <c r="AN53" s="44"/>
-      <c r="AO53" s="44"/>
-      <c r="AP53" s="44"/>
-      <c r="AQ53" s="44"/>
+        <v>1.08215463664599E-2</v>
+      </c>
+      <c r="AN53" s="44">
+        <v>189.85</v>
+      </c>
+      <c r="AO53" s="44">
+        <v>72.11</v>
+      </c>
+      <c r="AP53" s="44">
+        <v>456</v>
+      </c>
+      <c r="AQ53" s="44">
+        <v>1906</v>
+      </c>
       <c r="AR53" s="45">
         <v>84.700000000000045</v>
       </c>
       <c r="AS53" s="45">
         <f t="shared" si="60"/>
-        <v>-84.700000000000045</v>
+        <v>1821.3</v>
       </c>
       <c r="AT53" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>40.22999999999999</v>
       </c>
       <c r="AU53" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>0.98999999999999488</v>
       </c>
       <c r="AV53" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AW53" s="25">
         <v>15</v>
@@ -12631,39 +13257,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC53" s="11"/>
-      <c r="BD53" s="46"/>
-      <c r="BE53" s="22"/>
+      <c r="BD53" s="46">
+        <f>BM53*24*60/BH53</f>
+        <v>8.320221883433938E-3</v>
+      </c>
+      <c r="BE53" s="22">
+        <f>BP53/BH53</f>
+        <v>1.8539189845432401E-3</v>
+      </c>
       <c r="BF53" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.03946505E-2</v>
       </c>
       <c r="BG53" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.968296720000001</v>
       </c>
       <c r="BH53" s="46">
         <f t="shared" si="41"/>
-        <v>1565</v>
-      </c>
-      <c r="BI53" s="47" t="str">
+        <v>1872.91</v>
+      </c>
+      <c r="BI53" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ53" s="47" t="str">
+        <v>0.10136632299469808</v>
+      </c>
+      <c r="BJ53" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0.11167647058823529</v>
       </c>
       <c r="BK53" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>15.583026767702258</v>
       </c>
       <c r="BL53" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM53" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.08215463664599E-2</v>
       </c>
       <c r="BN53" s="48" t="str">
         <f t="shared" si="32"/>
@@ -12674,20 +13305,19 @@
         <v/>
       </c>
       <c r="BP53" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>3.47222340534088</v>
       </c>
       <c r="BQ53" s="28">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>28.107912640155586</v>
       </c>
       <c r="BR53" s="49">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>1.08215463664599E-2</v>
       </c>
       <c r="BS53" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3.47222340534088</v>
       </c>
     </row>
     <row r="54" spans="1:71" x14ac:dyDescent="0.3">
@@ -12703,62 +13333,126 @@
       <c r="D54">
         <v>8</v>
       </c>
-      <c r="F54" s="61"/>
+      <c r="F54" s="61">
+        <v>45541.4217361111</v>
+      </c>
       <c r="G54">
         <v>4309.7</v>
       </c>
       <c r="H54" s="44"/>
-      <c r="I54" s="44"/>
-      <c r="J54" s="44"/>
-      <c r="K54" s="44"/>
-      <c r="L54" s="44"/>
-      <c r="M54" s="44"/>
+      <c r="I54" s="44">
+        <v>3944.52</v>
+      </c>
+      <c r="J54" s="44">
+        <v>18.8</v>
+      </c>
+      <c r="K54" s="44">
+        <v>16.8</v>
+      </c>
+      <c r="L54" s="44">
+        <v>89.2</v>
+      </c>
+      <c r="M54" s="44">
+        <v>18.8</v>
+      </c>
       <c r="N54" s="44"/>
-      <c r="O54" s="44"/>
-      <c r="P54" s="44"/>
-      <c r="Q54" s="44"/>
+      <c r="O54" s="44">
+        <v>1.32</v>
+      </c>
+      <c r="P54" s="44">
+        <v>0.25</v>
+      </c>
+      <c r="Q54" s="44">
+        <v>3.69</v>
+      </c>
       <c r="R54" s="44"/>
-      <c r="S54" s="44"/>
-      <c r="T54" s="44"/>
-      <c r="U54" s="44"/>
-      <c r="V54" s="44"/>
-      <c r="W54" s="44"/>
-      <c r="X54" s="44"/>
-      <c r="Y54" s="44"/>
-      <c r="Z54" s="44"/>
-      <c r="AA54" s="44"/>
-      <c r="AB54" s="44"/>
-      <c r="AC54" s="44"/>
-      <c r="AD54" s="17"/>
-      <c r="AE54" s="44"/>
-      <c r="AF54" s="44"/>
-      <c r="AG54" s="44"/>
+      <c r="S54" s="44">
+        <v>0.36</v>
+      </c>
+      <c r="T54" s="44">
+        <v>0.66</v>
+      </c>
+      <c r="U54" s="44">
+        <v>3.71</v>
+      </c>
+      <c r="V54" s="44">
+        <v>7.2759999999999998</v>
+      </c>
+      <c r="W54" s="44">
+        <v>122.2</v>
+      </c>
+      <c r="X54" s="44">
+        <v>26.4</v>
+      </c>
+      <c r="Y54" s="44">
+        <v>1.73</v>
+      </c>
+      <c r="Z54" s="44">
+        <v>180.5</v>
+      </c>
+      <c r="AA54" s="44">
+        <v>55.4</v>
+      </c>
+      <c r="AB54" s="44">
+        <v>107.2</v>
+      </c>
+      <c r="AC54" s="44">
+        <v>21.3</v>
+      </c>
+      <c r="AD54" s="17">
+        <v>7.3170000000000002</v>
+      </c>
+      <c r="AE54" s="44">
+        <v>301</v>
+      </c>
+      <c r="AF54" s="44">
+        <v>49.6</v>
+      </c>
+      <c r="AG54" s="44">
+        <v>7.29</v>
+      </c>
       <c r="AH54" s="45">
         <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="AI54" s="44"/>
-      <c r="AJ54" s="44"/>
-      <c r="AK54" s="44"/>
-      <c r="AL54" s="44"/>
+        <v>0.496</v>
+      </c>
+      <c r="AI54" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ54" s="44">
+        <v>43.09</v>
+      </c>
+      <c r="AK54" s="44">
+        <v>10.53</v>
+      </c>
+      <c r="AL54" s="44">
+        <v>6.76</v>
+      </c>
       <c r="AM54" s="45">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="AN54" s="44"/>
-      <c r="AO54" s="44"/>
-      <c r="AP54" s="44"/>
-      <c r="AQ54" s="44"/>
+      <c r="AN54" s="44">
+        <v>162.32</v>
+      </c>
+      <c r="AO54" s="44">
+        <v>70.87</v>
+      </c>
+      <c r="AP54" s="44">
+        <v>492</v>
+      </c>
+      <c r="AQ54" s="44">
+        <v>1872</v>
+      </c>
       <c r="AR54" s="45">
         <v>47.420000000000073</v>
       </c>
       <c r="AS54" s="45">
         <f t="shared" si="60"/>
-        <v>-47.420000000000073</v>
+        <v>1824.58</v>
       </c>
       <c r="AT54" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>37.389999999999986</v>
       </c>
       <c r="AU54" s="45">
         <f t="shared" si="37"/>
@@ -12766,7 +13460,7 @@
       </c>
       <c r="AV54" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AW54" s="25">
         <v>15</v>
@@ -12790,23 +13484,23 @@
       <c r="BE54" s="22"/>
       <c r="BF54" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>9.3671927999999984E-3</v>
       </c>
       <c r="BG54" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>13.488757631999997</v>
       </c>
       <c r="BH54" s="46">
         <f t="shared" si="41"/>
-        <v>1565</v>
-      </c>
-      <c r="BI54" s="47" t="str">
+        <v>1858.57</v>
+      </c>
+      <c r="BI54" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ54" s="47" t="str">
+        <v>8.7335962594898231E-2</v>
+      </c>
+      <c r="BJ54" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>9.5482352941176463E-2</v>
       </c>
       <c r="BK54" s="47">
         <f t="shared" si="18"/>
@@ -12826,7 +13520,7 @@
       </c>
       <c r="BO54" s="47">
         <f t="shared" si="47"/>
-        <v>11.737500000000001</v>
+        <v>0</v>
       </c>
       <c r="BP54" s="51" t="str">
         <f t="shared" si="28"/>
@@ -12842,7 +13536,7 @@
       </c>
       <c r="BS54" s="30">
         <f t="shared" si="21"/>
-        <v>11.737500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:71" x14ac:dyDescent="0.3">
@@ -12858,70 +13552,134 @@
       <c r="D55">
         <v>8</v>
       </c>
-      <c r="F55" s="61"/>
+      <c r="F55" s="61">
+        <v>45541.425601851901</v>
+      </c>
       <c r="G55">
         <v>4309.7</v>
       </c>
       <c r="H55" s="44"/>
-      <c r="I55" s="44"/>
-      <c r="J55" s="44"/>
-      <c r="K55" s="44"/>
-      <c r="L55" s="44"/>
-      <c r="M55" s="44"/>
-      <c r="N55" s="44"/>
-      <c r="O55" s="44"/>
-      <c r="P55" s="44"/>
-      <c r="Q55" s="44"/>
+      <c r="I55" s="44">
+        <v>2821.47</v>
+      </c>
+      <c r="J55" s="44">
+        <v>20.9</v>
+      </c>
+      <c r="K55" s="44">
+        <v>14</v>
+      </c>
+      <c r="L55" s="44">
+        <v>67.099999999999994</v>
+      </c>
+      <c r="M55" s="44">
+        <v>18.2</v>
+      </c>
+      <c r="N55" s="44">
+        <v>600</v>
+      </c>
+      <c r="O55" s="44">
+        <v>5.43</v>
+      </c>
+      <c r="P55" s="44">
+        <v>0.31</v>
+      </c>
+      <c r="Q55" s="44">
+        <v>3.79</v>
+      </c>
       <c r="R55" s="44"/>
-      <c r="S55" s="44"/>
-      <c r="T55" s="44"/>
+      <c r="S55" s="44">
+        <v>0.64</v>
+      </c>
+      <c r="T55" s="44">
+        <v>2.4300000000000002</v>
+      </c>
       <c r="U55" s="44"/>
-      <c r="V55" s="44"/>
-      <c r="W55" s="44"/>
-      <c r="X55" s="44"/>
-      <c r="Y55" s="44"/>
-      <c r="Z55" s="44"/>
-      <c r="AA55" s="44"/>
-      <c r="AB55" s="44"/>
-      <c r="AC55" s="44"/>
-      <c r="AD55" s="17"/>
-      <c r="AE55" s="44"/>
-      <c r="AF55" s="44"/>
-      <c r="AG55" s="44"/>
+      <c r="V55" s="44">
+        <v>7.0570000000000004</v>
+      </c>
+      <c r="W55" s="44">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="X55" s="44">
+        <v>75.400000000000006</v>
+      </c>
+      <c r="Y55" s="44">
+        <v>3.62</v>
+      </c>
+      <c r="Z55" s="44">
+        <v>241.4</v>
+      </c>
+      <c r="AA55" s="44">
+        <v>21.2</v>
+      </c>
+      <c r="AB55" s="44">
+        <v>68.5</v>
+      </c>
+      <c r="AC55" s="44">
+        <v>61.7</v>
+      </c>
+      <c r="AD55" s="17">
+        <v>7.0940000000000003</v>
+      </c>
+      <c r="AE55" s="44">
+        <v>298</v>
+      </c>
+      <c r="AF55" s="44">
+        <v>48.9</v>
+      </c>
+      <c r="AG55" s="44">
+        <v>7.1</v>
+      </c>
       <c r="AH55" s="45">
         <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="AI55" s="44"/>
-      <c r="AJ55" s="44"/>
-      <c r="AK55" s="44"/>
-      <c r="AL55" s="44"/>
+        <v>0.48899999999999999</v>
+      </c>
+      <c r="AI55" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ55" s="44">
+        <v>86.93</v>
+      </c>
+      <c r="AK55" s="44">
+        <v>7.31</v>
+      </c>
+      <c r="AL55" s="44">
+        <v>6.44</v>
+      </c>
       <c r="AM55" s="45">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="AN55" s="44"/>
-      <c r="AO55" s="44"/>
-      <c r="AP55" s="44"/>
-      <c r="AQ55" s="44"/>
+      <c r="AN55" s="44">
+        <v>183.8</v>
+      </c>
+      <c r="AO55" s="44">
+        <v>77.819999999999993</v>
+      </c>
+      <c r="AP55" s="44">
+        <v>445</v>
+      </c>
+      <c r="AQ55" s="44">
+        <v>1964</v>
+      </c>
       <c r="AR55" s="45">
         <v>133.55999999999995</v>
       </c>
       <c r="AS55" s="45">
         <f t="shared" si="60"/>
-        <v>-133.55999999999995</v>
+        <v>1830.44</v>
       </c>
       <c r="AT55" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>38.31</v>
       </c>
       <c r="AU55" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>8.7999999999999972</v>
       </c>
       <c r="AV55" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AW55" s="25">
         <v>15</v>
@@ -12945,23 +13703,23 @@
       <c r="BE55" s="22"/>
       <c r="BF55" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>8.0946600000000018E-3</v>
       </c>
       <c r="BG55" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11.656310400000002</v>
       </c>
       <c r="BH55" s="46">
         <f t="shared" si="41"/>
-        <v>1565</v>
-      </c>
-      <c r="BI55" s="47" t="str">
+        <v>1927.3000000000002</v>
+      </c>
+      <c r="BI55" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ55" s="47" t="str">
+        <v>9.5366575001297152E-2</v>
+      </c>
+      <c r="BJ55" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0.10811764705882354</v>
       </c>
       <c r="BK55" s="47">
         <f t="shared" si="18"/>
@@ -12981,7 +13739,7 @@
       </c>
       <c r="BO55" s="47">
         <f t="shared" si="47"/>
-        <v>11.737500000000001</v>
+        <v>0</v>
       </c>
       <c r="BP55" s="51" t="str">
         <f t="shared" si="28"/>
@@ -12997,7 +13755,7 @@
       </c>
       <c r="BS55" s="30">
         <f t="shared" si="21"/>
-        <v>11.737500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -13014,62 +13772,128 @@
         <v>8</v>
       </c>
       <c r="E56" s="5"/>
-      <c r="F56" s="62"/>
+      <c r="F56" s="62">
+        <v>45541.429097222201</v>
+      </c>
       <c r="G56" s="5">
         <v>4309.7</v>
       </c>
       <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
-      <c r="K56" s="7"/>
-      <c r="L56" s="7"/>
-      <c r="M56" s="7"/>
-      <c r="N56" s="7"/>
-      <c r="O56" s="7"/>
-      <c r="P56" s="7"/>
-      <c r="Q56" s="7"/>
+      <c r="I56" s="7">
+        <v>4621.9350000000004</v>
+      </c>
+      <c r="J56" s="7">
+        <v>22.6</v>
+      </c>
+      <c r="K56" s="7">
+        <v>21.2</v>
+      </c>
+      <c r="L56" s="7">
+        <v>94</v>
+      </c>
+      <c r="M56" s="7">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="N56" s="7">
+        <v>362</v>
+      </c>
+      <c r="O56" s="7">
+        <v>1.36</v>
+      </c>
+      <c r="P56" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="Q56" s="7">
+        <v>1.76</v>
+      </c>
       <c r="R56" s="7"/>
-      <c r="S56" s="7"/>
-      <c r="T56" s="7"/>
-      <c r="U56" s="7"/>
-      <c r="V56" s="7"/>
-      <c r="W56" s="7"/>
-      <c r="X56" s="7"/>
-      <c r="Y56" s="7"/>
-      <c r="Z56" s="7"/>
-      <c r="AA56" s="7"/>
-      <c r="AB56" s="7"/>
-      <c r="AC56" s="7"/>
-      <c r="AD56" s="18"/>
-      <c r="AE56" s="7"/>
-      <c r="AF56" s="7"/>
-      <c r="AG56" s="7"/>
+      <c r="S56" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="T56" s="7">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="U56" s="7">
+        <v>1.31</v>
+      </c>
+      <c r="V56" s="7">
+        <v>7.266</v>
+      </c>
+      <c r="W56" s="7">
+        <v>124</v>
+      </c>
+      <c r="X56" s="7">
+        <v>31.7</v>
+      </c>
+      <c r="Y56" s="7">
+        <v>1.76</v>
+      </c>
+      <c r="Z56" s="7">
+        <v>157.69999999999999</v>
+      </c>
+      <c r="AA56" s="7">
+        <v>55</v>
+      </c>
+      <c r="AB56" s="7">
+        <v>108.7</v>
+      </c>
+      <c r="AC56" s="7">
+        <v>25.6</v>
+      </c>
+      <c r="AD56" s="18">
+        <v>7.3079999999999998</v>
+      </c>
+      <c r="AE56" s="7">
+        <v>301</v>
+      </c>
+      <c r="AF56" s="7">
+        <v>50.2</v>
+      </c>
+      <c r="AG56" s="7">
+        <v>7.3</v>
+      </c>
       <c r="AH56" s="41">
         <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="AI56" s="7"/>
-      <c r="AJ56" s="7"/>
-      <c r="AK56" s="7"/>
-      <c r="AL56" s="7"/>
+        <v>0.502</v>
+      </c>
+      <c r="AI56" s="7">
+        <v>34</v>
+      </c>
+      <c r="AJ56" s="7">
+        <v>28.27</v>
+      </c>
+      <c r="AK56" s="7">
+        <v>28.23</v>
+      </c>
+      <c r="AL56" s="7">
+        <v>6.52</v>
+      </c>
       <c r="AM56" s="41">
         <f t="shared" si="71"/>
         <v>0</v>
       </c>
-      <c r="AN56" s="7"/>
-      <c r="AO56" s="7"/>
-      <c r="AP56" s="7"/>
-      <c r="AQ56" s="7"/>
+      <c r="AN56" s="7">
+        <v>167.66</v>
+      </c>
+      <c r="AO56" s="7">
+        <v>56.59</v>
+      </c>
+      <c r="AP56" s="7">
+        <v>500</v>
+      </c>
+      <c r="AQ56" s="7">
+        <v>1870</v>
+      </c>
       <c r="AR56" s="41">
         <v>51.660000000000082</v>
       </c>
       <c r="AS56" s="41">
         <f t="shared" si="60"/>
-        <v>-51.660000000000082</v>
+        <v>1818.34</v>
       </c>
       <c r="AT56" s="41">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>22.28</v>
       </c>
       <c r="AU56" s="41">
         <f t="shared" si="37"/>
@@ -13077,7 +13901,7 @@
       </c>
       <c r="AV56" s="41">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AW56" s="26">
         <v>15</v>
@@ -13102,23 +13926,23 @@
       <c r="BE56" s="23"/>
       <c r="BF56" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.1780437199999999E-2</v>
       </c>
       <c r="BG56" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.963829567999998</v>
       </c>
       <c r="BH56" s="13">
         <f t="shared" si="41"/>
-        <v>1565</v>
-      </c>
-      <c r="BI56" s="14" t="str">
+        <v>1852.27</v>
+      </c>
+      <c r="BI56" s="14">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ56" s="14" t="str">
+        <v>9.051596149589422E-2</v>
+      </c>
+      <c r="BJ56" s="14">
         <f t="shared" si="9"/>
-        <v/>
+        <v>9.8623529411764707E-2</v>
       </c>
       <c r="BK56" s="14">
         <f t="shared" si="18"/>
@@ -13138,7 +13962,7 @@
       </c>
       <c r="BO56" s="14">
         <f t="shared" si="47"/>
-        <v>11.737500000000001</v>
+        <v>0</v>
       </c>
       <c r="BP56" s="52" t="str">
         <f t="shared" si="28"/>
@@ -13154,7 +13978,7 @@
       </c>
       <c r="BS56" s="31">
         <f t="shared" si="21"/>
-        <v>11.737500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:71" x14ac:dyDescent="0.3">
@@ -13226,15 +14050,15 @@
       </c>
       <c r="AT57" s="40">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-139.57</v>
       </c>
       <c r="AU57" s="40">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-65.31</v>
       </c>
       <c r="AV57" s="40">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>530</v>
       </c>
       <c r="AW57" s="24">
         <v>15</v>
@@ -13382,15 +14206,15 @@
       </c>
       <c r="AT58" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-147.31</v>
       </c>
       <c r="AU58" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-61.42</v>
       </c>
       <c r="AV58" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="AW58" s="25">
         <v>15</v>
@@ -13538,15 +14362,15 @@
       </c>
       <c r="AT59" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-189.85</v>
       </c>
       <c r="AU59" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-72.11</v>
       </c>
       <c r="AV59" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>456</v>
       </c>
       <c r="AW59" s="25">
         <v>15</v>
@@ -13694,15 +14518,15 @@
       </c>
       <c r="AT60" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-162.32</v>
       </c>
       <c r="AU60" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-70.87</v>
       </c>
       <c r="AV60" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>492</v>
       </c>
       <c r="AW60" s="25">
         <v>15</v>
@@ -13849,15 +14673,15 @@
       </c>
       <c r="AT61" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-183.8</v>
       </c>
       <c r="AU61" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-77.819999999999993</v>
       </c>
       <c r="AV61" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="AW61" s="25">
         <v>15</v>
@@ -14005,15 +14829,15 @@
       </c>
       <c r="AT62" s="41">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-167.66</v>
       </c>
       <c r="AU62" s="41">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-56.59</v>
       </c>
       <c r="AV62" s="41">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AW62" s="26">
         <v>15</v>
@@ -15728,7 +16552,7 @@
         <v>0</v>
       </c>
       <c r="AV73" s="45">
-        <f t="shared" ref="AV73:AV104" si="98">AP67-AP73</f>
+        <f t="shared" ref="AV73:AV80" si="98">AP67-AP73</f>
         <v>0</v>
       </c>
       <c r="AW73" s="25">
@@ -16951,6 +17775,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -17173,15 +18006,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -17201,6 +18025,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17219,27 +18051,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
     <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
+++ b/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-045-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1426" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F594A91-AAB9-4573-B3C2-D75D850ADE9C}"/>
+  <xr:revisionPtr revIDLastSave="1470" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{970C3D87-E5E3-4C81-A6EA-E66F76EC7286}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -1231,10 +1231,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -13429,7 +13425,7 @@
       </c>
       <c r="AM54" s="45">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>2.5813472222222224E-2</v>
       </c>
       <c r="AN54" s="44">
         <v>162.32</v>
@@ -13480,7 +13476,9 @@
       <c r="BB54" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC54" s="11"/>
+      <c r="BC54" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BE54" s="22"/>
       <c r="BF54" s="11">
         <f t="shared" si="17"/>
@@ -13504,11 +13502,11 @@
       </c>
       <c r="BK54" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>37.171400000000006</v>
       </c>
       <c r="BL54" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.5813472222222224E-2</v>
       </c>
       <c r="BM54" s="48" t="str">
         <f t="shared" si="31"/>
@@ -13528,11 +13526,11 @@
       </c>
       <c r="BQ54" s="28">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>67.047979797979806</v>
       </c>
       <c r="BR54" s="49">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>2.5813472222222224E-2</v>
       </c>
       <c r="BS54" s="30">
         <f t="shared" si="21"/>
@@ -13648,7 +13646,7 @@
       </c>
       <c r="AM55" s="45">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>2.6768055555555559E-2</v>
       </c>
       <c r="AN55" s="44">
         <v>183.8</v>
@@ -13699,7 +13697,9 @@
       <c r="BB55" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC55" s="11"/>
+      <c r="BC55" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BE55" s="22"/>
       <c r="BF55" s="11">
         <f t="shared" si="17"/>
@@ -13723,11 +13723,11 @@
       </c>
       <c r="BK55" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>38.546000000000006</v>
       </c>
       <c r="BL55" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.6768055555555559E-2</v>
       </c>
       <c r="BM55" s="48" t="str">
         <f t="shared" si="31"/>
@@ -13747,11 +13747,11 @@
       </c>
       <c r="BQ55" s="28">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>69.527417027417044</v>
       </c>
       <c r="BR55" s="49">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>2.6768055555555559E-2</v>
       </c>
       <c r="BS55" s="30">
         <f t="shared" si="21"/>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="AM56" s="41">
         <f t="shared" si="71"/>
-        <v>0</v>
+        <v>1.2219836805555554E-2</v>
       </c>
       <c r="AN56" s="7">
         <v>167.66</v>
@@ -13921,7 +13921,9 @@
       <c r="BB56" s="23">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC56" s="12"/>
+      <c r="BC56" s="12">
+        <v>9.4999999999999998E-3</v>
+      </c>
       <c r="BD56" s="5"/>
       <c r="BE56" s="23"/>
       <c r="BF56" s="12">
@@ -13946,11 +13948,11 @@
       </c>
       <c r="BK56" s="14">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>17.596564999999998</v>
       </c>
       <c r="BL56" s="14">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.2219836805555554E-2</v>
       </c>
       <c r="BM56" s="48" t="str">
         <f t="shared" si="31"/>
@@ -13970,11 +13972,11 @@
       </c>
       <c r="BQ56" s="29">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>31.739835858585856</v>
       </c>
       <c r="BR56" s="38">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>1.2219836805555554E-2</v>
       </c>
       <c r="BS56" s="31">
         <f t="shared" si="21"/>
@@ -14000,65 +14002,130 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="6"/>
-      <c r="M57" s="6"/>
-      <c r="N57" s="6"/>
-      <c r="O57" s="6"/>
-      <c r="P57" s="6"/>
-      <c r="Q57" s="6"/>
+      <c r="I57" s="6">
+        <v>4962.95</v>
+      </c>
+      <c r="J57" s="6">
+        <v>22.1</v>
+      </c>
+      <c r="K57" s="6">
+        <v>20.6</v>
+      </c>
+      <c r="L57" s="6">
+        <v>93.2</v>
+      </c>
+      <c r="M57" s="6">
+        <v>17.3</v>
+      </c>
+      <c r="N57" s="6">
+        <v>344</v>
+      </c>
+      <c r="O57" s="6">
+        <v>1.42</v>
+      </c>
+      <c r="P57" s="6">
+        <v>0.21</v>
+      </c>
+      <c r="Q57" s="6">
+        <v>2.37</v>
+      </c>
       <c r="R57" s="6"/>
-      <c r="S57" s="6"/>
-      <c r="T57" s="6"/>
-      <c r="U57" s="6"/>
-      <c r="V57" s="6"/>
-      <c r="W57" s="6"/>
-      <c r="X57" s="6"/>
-      <c r="Y57" s="6"/>
-      <c r="Z57" s="6"/>
-      <c r="AA57" s="6"/>
-      <c r="AB57" s="6"/>
-      <c r="AC57" s="6"/>
-      <c r="AD57" s="16"/>
-      <c r="AE57" s="6"/>
-      <c r="AF57" s="6"/>
-      <c r="AG57" s="6"/>
+      <c r="S57" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="T57" s="6">
+        <v>0.13</v>
+      </c>
+      <c r="U57" s="6">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="V57" s="6">
+        <v>7.2480000000000002</v>
+      </c>
+      <c r="W57" s="6">
+        <v>109.4</v>
+      </c>
+      <c r="X57" s="6">
+        <v>40.4</v>
+      </c>
+      <c r="Y57" s="6">
+        <v>2.44</v>
+      </c>
+      <c r="Z57" s="6">
+        <v>147.1</v>
+      </c>
+      <c r="AA57" s="6">
+        <v>46.5</v>
+      </c>
+      <c r="AB57" s="6">
+        <v>96</v>
+      </c>
+      <c r="AC57" s="6">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="AD57" s="16">
+        <v>7.29</v>
+      </c>
+      <c r="AE57" s="6">
+        <v>301</v>
+      </c>
+      <c r="AF57" s="6">
+        <v>50.2</v>
+      </c>
+      <c r="AG57" s="6">
+        <v>7.3</v>
+      </c>
       <c r="AH57" s="40">
         <f>AF57/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI57" s="6"/>
-      <c r="AJ57" s="6"/>
-      <c r="AK57" s="44"/>
-      <c r="AL57" s="6"/>
+        <v>0.502</v>
+      </c>
+      <c r="AI57" s="6">
+        <v>34</v>
+      </c>
+      <c r="AJ57" s="6">
+        <v>22.065000000000001</v>
+      </c>
+      <c r="AK57" s="44">
+        <v>41.161000000000001</v>
+      </c>
+      <c r="AL57" s="6">
+        <f>AL51+0.95</f>
+        <v>6.24</v>
+      </c>
       <c r="AM57" s="42">
         <f>BR57</f>
         <v>0</v>
       </c>
-      <c r="AN57" s="6"/>
-      <c r="AO57" s="6"/>
-      <c r="AP57" s="6"/>
-      <c r="AQ57" s="6"/>
+      <c r="AN57" s="6">
+        <v>150.99</v>
+      </c>
+      <c r="AO57" s="6">
+        <v>65.31</v>
+      </c>
+      <c r="AP57" s="6">
+        <v>518</v>
+      </c>
+      <c r="AQ57" s="6">
+        <v>1886</v>
+      </c>
       <c r="AR57" s="40">
         <v>137.11999999999989</v>
       </c>
       <c r="AS57" s="40">
         <f t="shared" si="60"/>
-        <v>-137.11999999999989</v>
+        <v>1748.88</v>
       </c>
       <c r="AT57" s="40">
         <f t="shared" si="36"/>
-        <v>-139.57</v>
+        <v>11.420000000000016</v>
       </c>
       <c r="AU57" s="40">
         <f t="shared" si="37"/>
-        <v>-65.31</v>
+        <v>0</v>
       </c>
       <c r="AV57" s="40">
         <f t="shared" si="65"/>
-        <v>530</v>
+        <v>12</v>
       </c>
       <c r="AW57" s="24">
         <v>15</v>
@@ -14083,23 +14150,23 @@
       <c r="BE57" s="21"/>
       <c r="BF57" s="8">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.1345033880000001E-2</v>
       </c>
       <c r="BG57" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.336848787200001</v>
       </c>
       <c r="BH57" s="9">
         <f t="shared" si="41"/>
-        <v>1550</v>
-      </c>
-      <c r="BI57" s="10" t="str">
+        <v>1835.7660000000001</v>
+      </c>
+      <c r="BI57" s="10">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ57" s="10" t="str">
+        <v>8.224904481290099E-2</v>
+      </c>
+      <c r="BJ57" s="10">
         <f t="shared" si="9"/>
-        <v/>
+        <v>8.8817647058823529E-2</v>
       </c>
       <c r="BK57" s="10">
         <f t="shared" si="18"/>
@@ -14156,65 +14223,130 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="H58" s="44"/>
-      <c r="I58" s="44"/>
-      <c r="J58" s="44"/>
-      <c r="K58" s="44"/>
-      <c r="L58" s="44"/>
-      <c r="M58" s="44"/>
-      <c r="N58" s="44"/>
-      <c r="O58" s="44"/>
-      <c r="P58" s="44"/>
-      <c r="Q58" s="44"/>
+      <c r="I58" s="44">
+        <v>5081.96</v>
+      </c>
+      <c r="J58" s="44">
+        <v>22.2</v>
+      </c>
+      <c r="K58" s="44">
+        <v>20.9</v>
+      </c>
+      <c r="L58" s="44">
+        <v>94.3</v>
+      </c>
+      <c r="M58" s="44">
+        <v>18</v>
+      </c>
+      <c r="N58" s="44">
+        <v>340</v>
+      </c>
+      <c r="O58" s="44">
+        <v>1.74</v>
+      </c>
+      <c r="P58" s="44">
+        <v>0.21</v>
+      </c>
+      <c r="Q58" s="44">
+        <v>0.49</v>
+      </c>
       <c r="R58" s="44"/>
-      <c r="S58" s="44"/>
-      <c r="T58" s="44"/>
-      <c r="U58" s="44"/>
-      <c r="V58" s="44"/>
-      <c r="W58" s="44"/>
-      <c r="X58" s="44"/>
-      <c r="Y58" s="44"/>
-      <c r="Z58" s="44"/>
-      <c r="AA58" s="44"/>
-      <c r="AB58" s="44"/>
-      <c r="AC58" s="44"/>
-      <c r="AD58" s="17"/>
-      <c r="AE58" s="44"/>
-      <c r="AF58" s="44"/>
-      <c r="AG58" s="44"/>
+      <c r="S58" s="44">
+        <v>0.12</v>
+      </c>
+      <c r="T58" s="44">
+        <v>0.11</v>
+      </c>
+      <c r="U58" s="44">
+        <v>0.16</v>
+      </c>
+      <c r="V58" s="44">
+        <v>7.2590000000000003</v>
+      </c>
+      <c r="W58" s="44">
+        <v>134.1</v>
+      </c>
+      <c r="X58" s="44">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="Y58" s="44">
+        <v>1.99</v>
+      </c>
+      <c r="Z58" s="44">
+        <v>153.1</v>
+      </c>
+      <c r="AA58" s="44">
+        <v>58.4</v>
+      </c>
+      <c r="AB58" s="44">
+        <v>117.6</v>
+      </c>
+      <c r="AC58" s="44">
+        <v>28.9</v>
+      </c>
+      <c r="AD58" s="17">
+        <v>7.3</v>
+      </c>
+      <c r="AE58" s="44">
+        <v>299</v>
+      </c>
+      <c r="AF58" s="44">
+        <v>50.7</v>
+      </c>
+      <c r="AG58" s="44">
+        <v>7.28</v>
+      </c>
       <c r="AH58" s="45">
         <f t="shared" ref="AH58:AH62" si="74">AF58/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI58" s="44"/>
-      <c r="AJ58" s="44"/>
-      <c r="AK58" s="44"/>
-      <c r="AL58" s="44"/>
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="AI58" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ58" s="44">
+        <v>24.568000000000001</v>
+      </c>
+      <c r="AK58" s="44">
+        <v>27.052</v>
+      </c>
+      <c r="AL58" s="44">
+        <f>AL52+0.94</f>
+        <v>3.94</v>
+      </c>
       <c r="AM58" s="45">
         <f t="shared" ref="AM58:AM62" si="75">BR58</f>
         <v>0</v>
       </c>
-      <c r="AN58" s="44"/>
-      <c r="AO58" s="44"/>
-      <c r="AP58" s="44"/>
-      <c r="AQ58" s="44"/>
+      <c r="AN58" s="44">
+        <v>167.56</v>
+      </c>
+      <c r="AO58" s="44">
+        <v>61.42</v>
+      </c>
+      <c r="AP58" s="44">
+        <v>501</v>
+      </c>
+      <c r="AQ58" s="44">
+        <v>1816</v>
+      </c>
       <c r="AR58" s="45">
         <v>45.769999999999982</v>
       </c>
       <c r="AS58" s="45">
         <f t="shared" si="60"/>
-        <v>-45.769999999999982</v>
+        <v>1770.23</v>
       </c>
       <c r="AT58" s="45">
         <f t="shared" si="36"/>
-        <v>-147.31</v>
+        <v>20.25</v>
       </c>
       <c r="AU58" s="45">
         <f t="shared" si="37"/>
-        <v>-61.42</v>
+        <v>0</v>
       </c>
       <c r="AV58" s="45">
         <f t="shared" si="65"/>
-        <v>524</v>
+        <v>23</v>
       </c>
       <c r="AW58" s="25">
         <v>15</v>
@@ -14239,23 +14371,23 @@
       <c r="BE58" s="22"/>
       <c r="BF58" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.1502565799999998E-2</v>
       </c>
       <c r="BG58" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.563694751999996</v>
       </c>
       <c r="BH58" s="46">
         <f t="shared" si="41"/>
-        <v>1550</v>
-      </c>
-      <c r="BI58" s="47" t="str">
+        <v>1834.54</v>
+      </c>
+      <c r="BI58" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ58" s="47" t="str">
+        <v>9.1336247778734725E-2</v>
+      </c>
+      <c r="BJ58" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>9.8564705882352943E-2</v>
       </c>
       <c r="BK58" s="47">
         <f t="shared" si="18"/>
@@ -14312,65 +14444,130 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="H59" s="44"/>
-      <c r="I59" s="44"/>
-      <c r="J59" s="44"/>
-      <c r="K59" s="44"/>
-      <c r="L59" s="44"/>
-      <c r="M59" s="44"/>
-      <c r="N59" s="44"/>
-      <c r="O59" s="44"/>
-      <c r="P59" s="44"/>
-      <c r="Q59" s="44"/>
+      <c r="I59" s="44">
+        <v>4467.1400000000003</v>
+      </c>
+      <c r="J59" s="44">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="K59" s="44">
+        <v>17.5</v>
+      </c>
+      <c r="L59" s="44">
+        <v>87.6</v>
+      </c>
+      <c r="M59" s="44">
+        <v>18.8</v>
+      </c>
+      <c r="N59" s="44">
+        <v>412</v>
+      </c>
+      <c r="O59" s="44">
+        <v>1.83</v>
+      </c>
+      <c r="P59" s="44">
+        <v>0.22</v>
+      </c>
+      <c r="Q59" s="44">
+        <v>2.14</v>
+      </c>
       <c r="R59" s="44"/>
-      <c r="S59" s="44"/>
-      <c r="T59" s="44"/>
-      <c r="U59" s="44"/>
-      <c r="V59" s="44"/>
-      <c r="W59" s="44"/>
-      <c r="X59" s="44"/>
-      <c r="Y59" s="44"/>
-      <c r="Z59" s="44"/>
-      <c r="AA59" s="44"/>
-      <c r="AB59" s="44"/>
-      <c r="AC59" s="44"/>
-      <c r="AD59" s="17"/>
-      <c r="AE59" s="44"/>
-      <c r="AF59" s="44"/>
-      <c r="AG59" s="44"/>
+      <c r="S59" s="44">
+        <v>0.49</v>
+      </c>
+      <c r="T59" s="44">
+        <v>0.82</v>
+      </c>
+      <c r="U59" s="44">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="V59" s="44">
+        <v>7.3280000000000003</v>
+      </c>
+      <c r="W59" s="44">
+        <v>119.4</v>
+      </c>
+      <c r="X59" s="44">
+        <v>8.6</v>
+      </c>
+      <c r="Y59" s="44">
+        <v>1.54</v>
+      </c>
+      <c r="Z59" s="44">
+        <v>175.6</v>
+      </c>
+      <c r="AA59" s="44">
+        <v>61.1</v>
+      </c>
+      <c r="AB59" s="44">
+        <v>104.7</v>
+      </c>
+      <c r="AC59" s="44">
+        <v>6.9</v>
+      </c>
+      <c r="AD59" s="17">
+        <v>7.37</v>
+      </c>
+      <c r="AE59" s="44">
+        <v>298</v>
+      </c>
+      <c r="AF59" s="44">
+        <v>51.5</v>
+      </c>
+      <c r="AG59" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH59" s="45">
         <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="AI59" s="44"/>
-      <c r="AJ59" s="44"/>
-      <c r="AK59" s="44"/>
-      <c r="AL59" s="44"/>
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="AI59" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ59" s="44">
+        <v>38.045999999999999</v>
+      </c>
+      <c r="AK59" s="44">
+        <v>2.4567000000000001</v>
+      </c>
+      <c r="AL59" s="44">
+        <f>AL53+0.93</f>
+        <v>7.59</v>
+      </c>
       <c r="AM59" s="45">
         <f t="shared" si="75"/>
         <v>0</v>
       </c>
-      <c r="AN59" s="44"/>
-      <c r="AO59" s="44"/>
-      <c r="AP59" s="44"/>
-      <c r="AQ59" s="44"/>
+      <c r="AN59" s="44">
+        <v>211.31</v>
+      </c>
+      <c r="AO59" s="44">
+        <v>76.27</v>
+      </c>
+      <c r="AP59" s="44">
+        <v>430</v>
+      </c>
+      <c r="AQ59" s="44">
+        <v>1900</v>
+      </c>
       <c r="AR59" s="45">
         <v>84.700000000000045</v>
       </c>
       <c r="AS59" s="45">
         <f t="shared" si="60"/>
-        <v>-84.700000000000045</v>
+        <v>1815.3</v>
       </c>
       <c r="AT59" s="45">
         <f t="shared" si="36"/>
-        <v>-189.85</v>
+        <v>21.460000000000008</v>
       </c>
       <c r="AU59" s="45">
         <f t="shared" si="37"/>
-        <v>-72.11</v>
+        <v>4.1599999999999966</v>
       </c>
       <c r="AV59" s="45">
         <f t="shared" si="65"/>
-        <v>456</v>
+        <v>26</v>
       </c>
       <c r="AW59" s="25">
         <v>15</v>
@@ -14395,23 +14592,23 @@
       <c r="BE59" s="22"/>
       <c r="BF59" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>9.8997816750000002E-3</v>
       </c>
       <c r="BG59" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.255685612000001</v>
       </c>
       <c r="BH59" s="46">
         <f t="shared" si="41"/>
-        <v>1550</v>
-      </c>
-      <c r="BI59" s="47" t="str">
+        <v>1885.6727000000001</v>
+      </c>
+      <c r="BI59" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ59" s="47" t="str">
+        <v>0.11206080461365325</v>
+      </c>
+      <c r="BJ59" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0.12430000000000001</v>
       </c>
       <c r="BK59" s="47">
         <f t="shared" si="18"/>
@@ -14468,65 +14665,130 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="H60" s="44"/>
-      <c r="I60" s="44"/>
-      <c r="J60" s="44"/>
-      <c r="K60" s="44"/>
-      <c r="L60" s="44"/>
-      <c r="M60" s="44"/>
-      <c r="N60" s="44"/>
-      <c r="O60" s="44"/>
-      <c r="P60" s="44"/>
-      <c r="Q60" s="44"/>
+      <c r="I60" s="44">
+        <v>4576.09</v>
+      </c>
+      <c r="J60" s="44">
+        <v>19.2</v>
+      </c>
+      <c r="K60" s="44">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="L60" s="44">
+        <v>90.3</v>
+      </c>
+      <c r="M60" s="44">
+        <v>19.2</v>
+      </c>
+      <c r="N60" s="44">
+        <v>424</v>
+      </c>
+      <c r="O60" s="44">
+        <v>1.5</v>
+      </c>
+      <c r="P60" s="44">
+        <v>0.22</v>
+      </c>
+      <c r="Q60" s="44">
+        <v>2.46</v>
+      </c>
       <c r="R60" s="44"/>
-      <c r="S60" s="44"/>
-      <c r="T60" s="44"/>
-      <c r="U60" s="44"/>
-      <c r="V60" s="44"/>
-      <c r="W60" s="44"/>
-      <c r="X60" s="44"/>
-      <c r="Y60" s="44"/>
-      <c r="Z60" s="44"/>
-      <c r="AA60" s="44"/>
-      <c r="AB60" s="44"/>
-      <c r="AC60" s="44"/>
-      <c r="AD60" s="17"/>
-      <c r="AE60" s="44"/>
-      <c r="AF60" s="44"/>
-      <c r="AG60" s="44"/>
+      <c r="S60" s="44">
+        <v>0.49</v>
+      </c>
+      <c r="T60" s="44">
+        <v>1.48</v>
+      </c>
+      <c r="U60" s="44">
+        <v>2.97</v>
+      </c>
+      <c r="V60" s="44">
+        <v>7.27</v>
+      </c>
+      <c r="W60" s="44">
+        <v>131.4</v>
+      </c>
+      <c r="X60" s="44">
+        <v>5.3</v>
+      </c>
+      <c r="Y60" s="44">
+        <v>1.55</v>
+      </c>
+      <c r="Z60" s="44">
+        <v>181.8</v>
+      </c>
+      <c r="AA60" s="44">
+        <v>58.8</v>
+      </c>
+      <c r="AB60" s="44">
+        <v>115.2</v>
+      </c>
+      <c r="AC60" s="44">
+        <v>4.3</v>
+      </c>
+      <c r="AD60" s="17">
+        <v>7.3120000000000003</v>
+      </c>
+      <c r="AE60" s="44">
+        <v>298</v>
+      </c>
+      <c r="AF60" s="44">
+        <v>52</v>
+      </c>
+      <c r="AG60" s="44">
+        <v>7.29</v>
+      </c>
       <c r="AH60" s="45">
         <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="AI60" s="44"/>
-      <c r="AJ60" s="44"/>
-      <c r="AK60" s="44"/>
-      <c r="AL60" s="44"/>
+        <v>0.52</v>
+      </c>
+      <c r="AI60" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ60" s="44">
+        <v>43.091000000000001</v>
+      </c>
+      <c r="AK60" s="44">
+        <v>11.292</v>
+      </c>
+      <c r="AL60" s="44">
+        <f>AL54+0.95</f>
+        <v>7.71</v>
+      </c>
       <c r="AM60" s="45">
         <f t="shared" si="75"/>
         <v>0</v>
       </c>
-      <c r="AN60" s="44"/>
-      <c r="AO60" s="44"/>
-      <c r="AP60" s="44"/>
-      <c r="AQ60" s="44"/>
+      <c r="AN60" s="44">
+        <v>204.07</v>
+      </c>
+      <c r="AO60" s="44">
+        <v>70.87</v>
+      </c>
+      <c r="AP60" s="44">
+        <v>443</v>
+      </c>
+      <c r="AQ60" s="44">
+        <v>1888</v>
+      </c>
       <c r="AR60" s="45">
         <v>47.420000000000073</v>
       </c>
       <c r="AS60" s="45">
         <f t="shared" si="60"/>
-        <v>-47.420000000000073</v>
+        <v>1840.58</v>
       </c>
       <c r="AT60" s="45">
         <f t="shared" si="36"/>
-        <v>-162.32</v>
+        <v>41.75</v>
       </c>
       <c r="AU60" s="45">
         <f t="shared" si="37"/>
-        <v>-70.87</v>
+        <v>0</v>
       </c>
       <c r="AV60" s="45">
         <f t="shared" si="65"/>
-        <v>492</v>
+        <v>49</v>
       </c>
       <c r="AW60" s="25">
         <v>15</v>
@@ -14550,23 +14812,23 @@
       <c r="BE60" s="22"/>
       <c r="BF60" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>9.8503122599999972E-3</v>
       </c>
       <c r="BG60" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.184449654399996</v>
       </c>
       <c r="BH60" s="46">
         <f t="shared" si="41"/>
-        <v>1550</v>
-      </c>
-      <c r="BI60" s="47" t="str">
+        <v>1887.0329999999999</v>
+      </c>
+      <c r="BI60" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ60" s="47" t="str">
+        <v>0.10814331280904997</v>
+      </c>
+      <c r="BJ60" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0.12004117647058823</v>
       </c>
       <c r="BK60" s="47">
         <f t="shared" si="18"/>
@@ -14586,7 +14848,7 @@
       </c>
       <c r="BO60" s="47">
         <f t="shared" si="47"/>
-        <v>11.625</v>
+        <v>0</v>
       </c>
       <c r="BP60" s="51" t="str">
         <f t="shared" si="28"/>
@@ -14602,7 +14864,7 @@
       </c>
       <c r="BS60" s="30">
         <f t="shared" si="21"/>
-        <v>11.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:71" x14ac:dyDescent="0.3">
@@ -14623,65 +14885,128 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="H61" s="44"/>
-      <c r="I61" s="44"/>
-      <c r="J61" s="44"/>
-      <c r="K61" s="44"/>
-      <c r="L61" s="44"/>
-      <c r="M61" s="44"/>
-      <c r="N61" s="44"/>
-      <c r="O61" s="44"/>
-      <c r="P61" s="44"/>
-      <c r="Q61" s="44"/>
+      <c r="I61" s="44">
+        <v>2904.25</v>
+      </c>
+      <c r="J61" s="44">
+        <v>20.7</v>
+      </c>
+      <c r="K61" s="44">
+        <v>12.9</v>
+      </c>
+      <c r="L61" s="44">
+        <v>62</v>
+      </c>
+      <c r="M61" s="44">
+        <v>18</v>
+      </c>
+      <c r="N61" s="44">
+        <v>687</v>
+      </c>
+      <c r="O61" s="44">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="P61" s="44">
+        <v>0.3</v>
+      </c>
+      <c r="Q61" s="44">
+        <v>2.75</v>
+      </c>
       <c r="R61" s="44"/>
-      <c r="S61" s="44"/>
-      <c r="T61" s="44"/>
+      <c r="S61" s="44">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="T61" s="44">
+        <v>3.07</v>
+      </c>
       <c r="U61" s="44"/>
-      <c r="V61" s="44"/>
-      <c r="W61" s="44"/>
-      <c r="X61" s="44"/>
-      <c r="Y61" s="44"/>
-      <c r="Z61" s="44"/>
-      <c r="AA61" s="44"/>
-      <c r="AB61" s="44"/>
-      <c r="AC61" s="44"/>
-      <c r="AD61" s="17"/>
-      <c r="AE61" s="44"/>
-      <c r="AF61" s="44"/>
-      <c r="AG61" s="44"/>
+      <c r="V61" s="44">
+        <v>7.0490000000000004</v>
+      </c>
+      <c r="W61" s="44">
+        <v>78.2</v>
+      </c>
+      <c r="X61" s="44">
+        <v>86</v>
+      </c>
+      <c r="Y61" s="44">
+        <v>5.17</v>
+      </c>
+      <c r="Z61" s="44">
+        <v>275.89999999999998</v>
+      </c>
+      <c r="AA61" s="44">
+        <v>20.8</v>
+      </c>
+      <c r="AB61" s="44">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="AC61" s="44">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="AD61" s="17">
+        <v>7.0869999999999997</v>
+      </c>
+      <c r="AE61" s="44">
+        <v>300</v>
+      </c>
+      <c r="AF61" s="44">
+        <v>49.7</v>
+      </c>
+      <c r="AG61" s="44">
+        <v>7.09</v>
+      </c>
       <c r="AH61" s="45">
         <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="AI61" s="44"/>
-      <c r="AJ61" s="44"/>
-      <c r="AK61" s="44"/>
-      <c r="AL61" s="44"/>
+        <v>0.49700000000000005</v>
+      </c>
+      <c r="AI61" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ61" s="44">
+        <v>112.39</v>
+      </c>
+      <c r="AK61" s="44">
+        <v>7.3125999999999998</v>
+      </c>
+      <c r="AL61" s="44">
+        <f>AL55+0.92</f>
+        <v>7.36</v>
+      </c>
       <c r="AM61" s="45">
         <f t="shared" si="75"/>
         <v>0</v>
       </c>
-      <c r="AN61" s="44"/>
-      <c r="AO61" s="44"/>
-      <c r="AP61" s="44"/>
-      <c r="AQ61" s="44"/>
+      <c r="AN61" s="44">
+        <v>227.05</v>
+      </c>
+      <c r="AO61" s="44">
+        <v>77.819999999999993</v>
+      </c>
+      <c r="AP61" s="44">
+        <v>394</v>
+      </c>
+      <c r="AQ61" s="44">
+        <v>2019</v>
+      </c>
       <c r="AR61" s="45">
         <v>133.55999999999995</v>
       </c>
       <c r="AS61" s="45">
         <f t="shared" si="60"/>
-        <v>-133.55999999999995</v>
+        <v>1885.44</v>
       </c>
       <c r="AT61" s="45">
         <f t="shared" si="36"/>
-        <v>-183.8</v>
+        <v>43.25</v>
       </c>
       <c r="AU61" s="45">
         <f t="shared" si="37"/>
-        <v>-77.819999999999993</v>
+        <v>0</v>
       </c>
       <c r="AV61" s="45">
         <f t="shared" si="65"/>
-        <v>445</v>
+        <v>51</v>
       </c>
       <c r="AW61" s="25">
         <v>15</v>
@@ -14705,23 +15030,23 @@
       <c r="BE61" s="22"/>
       <c r="BF61" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>7.6700791619999991E-3</v>
       </c>
       <c r="BG61" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11.044913993279998</v>
       </c>
       <c r="BH61" s="46">
         <f t="shared" si="41"/>
-        <v>1550</v>
-      </c>
-      <c r="BI61" s="47" t="str">
+        <v>1981.9326000000001</v>
+      </c>
+      <c r="BI61" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ61" s="47" t="str">
+        <v>0.11455989976652083</v>
+      </c>
+      <c r="BJ61" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0.13355882352941176</v>
       </c>
       <c r="BK61" s="47">
         <f t="shared" si="18"/>
@@ -14741,7 +15066,7 @@
       </c>
       <c r="BO61" s="47">
         <f t="shared" si="47"/>
-        <v>11.625</v>
+        <v>0</v>
       </c>
       <c r="BP61" s="51" t="str">
         <f t="shared" si="28"/>
@@ -14757,7 +15082,7 @@
       </c>
       <c r="BS61" s="30">
         <f t="shared" si="21"/>
-        <v>11.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -14779,65 +15104,130 @@
         <v>4805.7299999999996</v>
       </c>
       <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="7"/>
-      <c r="K62" s="7"/>
-      <c r="L62" s="7"/>
-      <c r="M62" s="7"/>
-      <c r="N62" s="7"/>
-      <c r="O62" s="7"/>
-      <c r="P62" s="7"/>
-      <c r="Q62" s="7"/>
+      <c r="I62" s="7">
+        <v>5225.28</v>
+      </c>
+      <c r="J62" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="K62" s="7">
+        <v>20</v>
+      </c>
+      <c r="L62" s="7">
+        <v>93.3</v>
+      </c>
+      <c r="M62" s="7">
+        <v>18</v>
+      </c>
+      <c r="N62" s="7">
+        <v>352</v>
+      </c>
+      <c r="O62" s="7">
+        <v>1.49</v>
+      </c>
+      <c r="P62" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="Q62" s="7">
+        <v>0.32</v>
+      </c>
       <c r="R62" s="7"/>
-      <c r="S62" s="7"/>
-      <c r="T62" s="7"/>
-      <c r="U62" s="7"/>
-      <c r="V62" s="7"/>
-      <c r="W62" s="7"/>
-      <c r="X62" s="7"/>
-      <c r="Y62" s="7"/>
-      <c r="Z62" s="7"/>
-      <c r="AA62" s="7"/>
-      <c r="AB62" s="7"/>
-      <c r="AC62" s="7"/>
-      <c r="AD62" s="18"/>
-      <c r="AE62" s="7"/>
-      <c r="AF62" s="7"/>
-      <c r="AG62" s="7"/>
+      <c r="S62" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="T62" s="7">
+        <v>0.08</v>
+      </c>
+      <c r="U62" s="7">
+        <v>1</v>
+      </c>
+      <c r="V62" s="7">
+        <v>7.2679999999999998</v>
+      </c>
+      <c r="W62" s="7">
+        <v>124.2</v>
+      </c>
+      <c r="X62" s="7">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="Y62" s="7">
+        <v>1.79</v>
+      </c>
+      <c r="Z62" s="7">
+        <v>158.6</v>
+      </c>
+      <c r="AA62" s="7">
+        <v>55.3</v>
+      </c>
+      <c r="AB62" s="7">
+        <v>108.9</v>
+      </c>
+      <c r="AC62" s="7">
+        <v>27.7</v>
+      </c>
+      <c r="AD62" s="18">
+        <v>7.3090000000000002</v>
+      </c>
+      <c r="AE62" s="7">
+        <v>302</v>
+      </c>
+      <c r="AF62" s="7">
+        <v>49.1</v>
+      </c>
+      <c r="AG62" s="7">
+        <v>7.3</v>
+      </c>
       <c r="AH62" s="41">
         <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="AI62" s="7"/>
-      <c r="AJ62" s="7"/>
-      <c r="AK62" s="7"/>
-      <c r="AL62" s="7"/>
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="AI62" s="7">
+        <v>34</v>
+      </c>
+      <c r="AJ62" s="7">
+        <v>28.271000000000001</v>
+      </c>
+      <c r="AK62" s="7">
+        <v>38.732999999999997</v>
+      </c>
+      <c r="AL62" s="7">
+        <f>AL56+0.93</f>
+        <v>7.4499999999999993</v>
+      </c>
       <c r="AM62" s="41">
         <f t="shared" si="75"/>
         <v>0</v>
       </c>
-      <c r="AN62" s="7"/>
-      <c r="AO62" s="7"/>
-      <c r="AP62" s="7"/>
-      <c r="AQ62" s="7"/>
+      <c r="AN62" s="7">
+        <v>187.96</v>
+      </c>
+      <c r="AO62" s="7">
+        <v>56.59</v>
+      </c>
+      <c r="AP62" s="7">
+        <v>476</v>
+      </c>
+      <c r="AQ62" s="7">
+        <v>1867</v>
+      </c>
       <c r="AR62" s="41">
         <v>51.660000000000082</v>
       </c>
       <c r="AS62" s="41">
         <f t="shared" si="60"/>
-        <v>-51.660000000000082</v>
+        <v>1815.34</v>
       </c>
       <c r="AT62" s="41">
         <f t="shared" si="36"/>
-        <v>-167.66</v>
+        <v>20.300000000000011</v>
       </c>
       <c r="AU62" s="41">
         <f t="shared" si="37"/>
-        <v>-56.59</v>
+        <v>0</v>
       </c>
       <c r="AV62" s="41">
         <f t="shared" si="65"/>
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AW62" s="26">
         <v>15</v>
@@ -14862,23 +15252,23 @@
       <c r="BE62" s="23"/>
       <c r="BF62" s="12">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.1214023999999998E-2</v>
       </c>
       <c r="BG62" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16.148194559999997</v>
       </c>
       <c r="BH62" s="13">
         <f t="shared" si="41"/>
-        <v>1550</v>
-      </c>
-      <c r="BI62" s="14" t="str">
+        <v>1869.0039999999999</v>
+      </c>
+      <c r="BI62" s="14">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ62" s="14" t="str">
+        <v>0.10056693297606641</v>
+      </c>
+      <c r="BJ62" s="14">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0.11056470588235294</v>
       </c>
       <c r="BK62" s="14">
         <f t="shared" si="18"/>
@@ -14898,7 +15288,7 @@
       </c>
       <c r="BO62" s="14">
         <f t="shared" si="47"/>
-        <v>11.625</v>
+        <v>12.5223268</v>
       </c>
       <c r="BP62" s="52" t="str">
         <f t="shared" si="28"/>
@@ -14914,7 +15304,7 @@
       </c>
       <c r="BS62" s="31">
         <f t="shared" si="21"/>
-        <v>11.625</v>
+        <v>12.5223268</v>
       </c>
     </row>
     <row r="63" spans="1:71" x14ac:dyDescent="0.3">
@@ -14986,15 +15376,15 @@
       </c>
       <c r="AT63" s="40">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-150.99</v>
       </c>
       <c r="AU63" s="40">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-65.31</v>
       </c>
       <c r="AV63" s="40">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>518</v>
       </c>
       <c r="AW63" s="24">
         <v>15</v>
@@ -15142,15 +15532,15 @@
       </c>
       <c r="AT64" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-167.56</v>
       </c>
       <c r="AU64" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-61.42</v>
       </c>
       <c r="AV64" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>501</v>
       </c>
       <c r="AW64" s="25">
         <v>15</v>
@@ -15298,15 +15688,15 @@
       </c>
       <c r="AT65" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-211.31</v>
       </c>
       <c r="AU65" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-76.27</v>
       </c>
       <c r="AV65" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="AW65" s="25">
         <v>15</v>
@@ -15454,15 +15844,15 @@
       </c>
       <c r="AT66" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-204.07</v>
       </c>
       <c r="AU66" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-70.87</v>
       </c>
       <c r="AV66" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="AW66" s="25">
         <v>15</v>
@@ -15609,15 +15999,15 @@
       </c>
       <c r="AT67" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-227.05</v>
       </c>
       <c r="AU67" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-77.819999999999993</v>
       </c>
       <c r="AV67" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="AW67" s="25">
         <v>15</v>
@@ -15765,15 +16155,15 @@
       </c>
       <c r="AT68" s="41">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-187.96</v>
       </c>
       <c r="AU68" s="41">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-56.59</v>
       </c>
       <c r="AV68" s="41">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>476</v>
       </c>
       <c r="AW68" s="26">
         <v>15</v>
@@ -17775,15 +18165,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -18006,7 +18387,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
@@ -18024,15 +18405,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18051,7 +18433,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -18066,4 +18448,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
+++ b/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-045-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1470" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{970C3D87-E5E3-4C81-A6EA-E66F76EC7286}"/>
+  <xr:revisionPtr revIDLastSave="1540" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A3C3CC1-DA82-4F96-AE15-07BC88948B97}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="90">
   <si>
     <t>Batch Data</t>
   </si>
@@ -307,6 +307,9 @@
   <si>
     <t>MR24-045-806</t>
   </si>
+  <si>
+    <t>Antifoam totalizer reset due to schedule restart</t>
+  </si>
 </sst>
 </file>
 
@@ -318,7 +321,7 @@
     <numFmt numFmtId="166" formatCode="0.00000"/>
     <numFmt numFmtId="167" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -510,6 +513,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -990,7 +1000,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -1134,6 +1144,9 @@
     <xf numFmtId="0" fontId="19" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1229,6 +1242,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9172,7 +9189,7 @@
         <v>84.700000000000045</v>
       </c>
       <c r="AS35" s="45">
-        <f t="shared" ref="AS35:AS66" si="60">AQ35-AR35</f>
+        <f t="shared" ref="AS35:AS65" si="60">AQ35-AR35</f>
         <v>1755.3</v>
       </c>
       <c r="AT35" s="45">
@@ -12650,7 +12667,9 @@
       <c r="D51" s="3">
         <v>8</v>
       </c>
-      <c r="E51" s="3"/>
+      <c r="E51" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="F51" s="60">
         <v>45541.409976851901</v>
       </c>
@@ -12744,7 +12763,7 @@
       <c r="AK51" s="44">
         <v>33.090000000000003</v>
       </c>
-      <c r="AL51" s="6">
+      <c r="AL51" s="87">
         <v>5.29</v>
       </c>
       <c r="AM51" s="42">
@@ -12877,6 +12896,9 @@
       <c r="D52">
         <v>8</v>
       </c>
+      <c r="E52" t="s">
+        <v>89</v>
+      </c>
       <c r="F52" s="61">
         <v>45541.414027777799</v>
       </c>
@@ -12970,7 +12992,7 @@
       <c r="AK52" s="44">
         <v>26.68</v>
       </c>
-      <c r="AL52" s="44">
+      <c r="AL52" s="88">
         <v>3</v>
       </c>
       <c r="AM52" s="45">
@@ -13103,6 +13125,9 @@
       <c r="D53">
         <v>8</v>
       </c>
+      <c r="E53" t="s">
+        <v>89</v>
+      </c>
       <c r="F53" s="61">
         <v>45541.418136574102</v>
       </c>
@@ -13196,7 +13221,7 @@
       <c r="AK53" s="44">
         <v>1.24</v>
       </c>
-      <c r="AL53" s="44">
+      <c r="AL53" s="88">
         <v>6.66</v>
       </c>
       <c r="AM53" s="45">
@@ -13329,6 +13354,9 @@
       <c r="D54">
         <v>8</v>
       </c>
+      <c r="E54" t="s">
+        <v>89</v>
+      </c>
       <c r="F54" s="61">
         <v>45541.4217361111</v>
       </c>
@@ -13420,7 +13448,7 @@
       <c r="AK54" s="44">
         <v>10.53</v>
       </c>
-      <c r="AL54" s="44">
+      <c r="AL54" s="88">
         <v>6.76</v>
       </c>
       <c r="AM54" s="45">
@@ -13550,6 +13578,9 @@
       <c r="D55">
         <v>8</v>
       </c>
+      <c r="E55" t="s">
+        <v>89</v>
+      </c>
       <c r="F55" s="61">
         <v>45541.425601851901</v>
       </c>
@@ -13641,7 +13672,7 @@
       <c r="AK55" s="44">
         <v>7.31</v>
       </c>
-      <c r="AL55" s="44">
+      <c r="AL55" s="88">
         <v>6.44</v>
       </c>
       <c r="AM55" s="45">
@@ -13771,7 +13802,9 @@
       <c r="D56" s="5">
         <v>8</v>
       </c>
-      <c r="E56" s="5"/>
+      <c r="E56" s="5" t="s">
+        <v>89</v>
+      </c>
       <c r="F56" s="62">
         <v>45541.429097222201</v>
       </c>
@@ -13865,7 +13898,7 @@
       <c r="AK56" s="7">
         <v>28.23</v>
       </c>
-      <c r="AL56" s="7">
+      <c r="AL56" s="89">
         <v>6.52</v>
       </c>
       <c r="AM56" s="41">
@@ -13997,7 +14030,9 @@
         <v>9</v>
       </c>
       <c r="E57" s="3"/>
-      <c r="F57" s="60"/>
+      <c r="F57" s="60">
+        <v>45542.536215277803</v>
+      </c>
       <c r="G57" s="3">
         <v>4805.7299999999996</v>
       </c>
@@ -14094,7 +14129,7 @@
       </c>
       <c r="AM57" s="42">
         <f>BR57</f>
-        <v>0</v>
+        <v>1.55878779022903E-2</v>
       </c>
       <c r="AN57" s="6">
         <v>150.99</v>
@@ -14146,8 +14181,14 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC57" s="8"/>
-      <c r="BD57" s="9"/>
-      <c r="BE57" s="21"/>
+      <c r="BD57" s="46">
+        <f>BM57*24*60/BH57</f>
+        <v>1.2227344977136538E-2</v>
+      </c>
+      <c r="BE57" s="22">
+        <f>BP57/BH57</f>
+        <v>9.9999999999999995E-8</v>
+      </c>
       <c r="BF57" s="8">
         <f t="shared" si="17"/>
         <v>1.1345033880000001E-2</v>
@@ -14170,15 +14211,14 @@
       </c>
       <c r="BK57" s="10">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>22.446544179298034</v>
       </c>
       <c r="BL57" s="10" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM57" s="10">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.55878779022903E-2</v>
       </c>
       <c r="BN57" s="35" t="str">
         <f t="shared" si="32"/>
@@ -14189,20 +14229,19 @@
         <v/>
       </c>
       <c r="BP57" s="50">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1.8357660000000001E-4</v>
       </c>
       <c r="BQ57" s="27">
         <f>IF(BL57&lt;&gt;"",BL57/0.000385,IF(BM57&lt;&gt;"",BM57/0.000385,BN57/0.000385))</f>
-        <v>0</v>
+        <v>40.487994551403375</v>
       </c>
       <c r="BR57" s="37">
         <f>IF(BL57&lt;&gt;"",BL57,IF(BM57&lt;&gt;"",BM57,BN57))</f>
-        <v>0</v>
+        <v>1.55878779022903E-2</v>
       </c>
       <c r="BS57" s="32">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1.8357660000000001E-4</v>
       </c>
     </row>
     <row r="58" spans="1:71" x14ac:dyDescent="0.3">
@@ -14218,7 +14257,9 @@
       <c r="D58">
         <v>9</v>
       </c>
-      <c r="F58" s="61"/>
+      <c r="F58" s="61">
+        <v>45542.542280092603</v>
+      </c>
       <c r="G58">
         <v>4805.7299999999996</v>
       </c>
@@ -14315,7 +14356,7 @@
       </c>
       <c r="AM58" s="45">
         <f t="shared" ref="AM58:AM62" si="75">BR58</f>
-        <v>0</v>
+        <v>1.4239072354215201E-2</v>
       </c>
       <c r="AN58" s="44">
         <v>167.56</v>
@@ -14367,8 +14408,14 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC58" s="11"/>
-      <c r="BD58" s="46"/>
-      <c r="BE58" s="22"/>
+      <c r="BD58" s="46">
+        <f>BM58*24*60/BH58</f>
+        <v>1.1176787745194918E-2</v>
+      </c>
+      <c r="BE58" s="22">
+        <f>BP58/BH58</f>
+        <v>3.3316909083529549E-3</v>
+      </c>
       <c r="BF58" s="11">
         <f t="shared" si="17"/>
         <v>1.1502565799999998E-2</v>
@@ -14391,15 +14438,14 @@
       </c>
       <c r="BK58" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>20.504264190069886</v>
       </c>
       <c r="BL58" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM58" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.4239072354215201E-2</v>
       </c>
       <c r="BN58" s="48" t="str">
         <f t="shared" si="32"/>
@@ -14410,20 +14456,19 @@
         <v/>
       </c>
       <c r="BP58" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>6.1121202390098297</v>
       </c>
       <c r="BQ58" s="28">
         <f t="shared" ref="BQ58:BQ62" si="76">IF(BL58&lt;&gt;"",BL58/0.000385,IF(BM58&lt;&gt;"",BM58/0.000385,BN58/0.000385))</f>
-        <v>0</v>
+        <v>36.984603517442082</v>
       </c>
       <c r="BR58" s="49">
         <f t="shared" ref="BR58:BR62" si="77">IF(BL58&lt;&gt;"",BL58,IF(BM58&lt;&gt;"",BM58,BN58))</f>
-        <v>0</v>
+        <v>1.4239072354215201E-2</v>
       </c>
       <c r="BS58" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>6.1121202390098297</v>
       </c>
     </row>
     <row r="59" spans="1:71" x14ac:dyDescent="0.3">
@@ -14439,7 +14484,9 @@
       <c r="D59">
         <v>9</v>
       </c>
-      <c r="F59" s="61"/>
+      <c r="F59" s="61">
+        <v>45542.544826388897</v>
+      </c>
       <c r="G59">
         <v>4805.7299999999996</v>
       </c>
@@ -14536,7 +14583,7 @@
       </c>
       <c r="AM59" s="45">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>3.1427878333333298E-2</v>
       </c>
       <c r="AN59" s="44">
         <v>211.31</v>
@@ -14588,8 +14635,14 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC59" s="11"/>
-      <c r="BD59" s="46"/>
-      <c r="BE59" s="22"/>
+      <c r="BD59" s="46">
+        <f>BM59*24*60/BH59</f>
+        <v>2.3999999999999973E-2</v>
+      </c>
+      <c r="BE59" s="22">
+        <f>BP59/BH59</f>
+        <v>4.1250564909925723E-3</v>
+      </c>
       <c r="BF59" s="11">
         <f t="shared" si="17"/>
         <v>9.8997816750000002E-3</v>
@@ -14612,15 +14665,14 @@
       </c>
       <c r="BK59" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>45.256144799999952</v>
       </c>
       <c r="BL59" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM59" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>3.1427878333333298E-2</v>
       </c>
       <c r="BN59" s="48" t="str">
         <f t="shared" si="32"/>
@@ -14631,20 +14683,19 @@
         <v/>
       </c>
       <c r="BP59" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>7.77850641102249</v>
       </c>
       <c r="BQ59" s="28">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>81.630852813852727</v>
       </c>
       <c r="BR59" s="49">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>3.1427878333333298E-2</v>
       </c>
       <c r="BS59" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>7.77850641102249</v>
       </c>
     </row>
     <row r="60" spans="1:71" x14ac:dyDescent="0.3">
@@ -14660,13 +14711,15 @@
       <c r="D60">
         <v>9</v>
       </c>
-      <c r="F60" s="61"/>
+      <c r="F60" s="61">
+        <v>45542.547604166699</v>
+      </c>
       <c r="G60">
         <v>4805.7299999999996</v>
       </c>
       <c r="H60" s="44"/>
       <c r="I60" s="44">
-        <v>4576.09</v>
+        <v>4576.0950000000003</v>
       </c>
       <c r="J60" s="44">
         <v>19.2</v>
@@ -14757,7 +14810,7 @@
       </c>
       <c r="AM60" s="45">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>2.3587912499999995E-2</v>
       </c>
       <c r="AN60" s="44">
         <v>204.07</v>
@@ -14808,7 +14861,9 @@
       <c r="BB60" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC60" s="11"/>
+      <c r="BC60" s="11">
+        <v>1.7999999999999999E-2</v>
+      </c>
       <c r="BE60" s="22"/>
       <c r="BF60" s="11">
         <f t="shared" si="17"/>
@@ -14832,11 +14887,11 @@
       </c>
       <c r="BK60" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>33.966593999999986</v>
       </c>
       <c r="BL60" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.3587912499999995E-2</v>
       </c>
       <c r="BM60" s="48" t="str">
         <f t="shared" si="31"/>
@@ -14856,11 +14911,11 @@
       </c>
       <c r="BQ60" s="28">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>61.267305194805189</v>
       </c>
       <c r="BR60" s="49">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>2.3587912499999995E-2</v>
       </c>
       <c r="BS60" s="30">
         <f t="shared" si="21"/>
@@ -14880,7 +14935,9 @@
       <c r="D61">
         <v>9</v>
       </c>
-      <c r="F61" s="61"/>
+      <c r="F61" s="61">
+        <v>45542.550289351901</v>
+      </c>
       <c r="G61">
         <v>4805.7299999999996</v>
       </c>
@@ -14975,7 +15032,7 @@
       </c>
       <c r="AM61" s="45">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>2.752684166666667E-2</v>
       </c>
       <c r="AN61" s="44">
         <v>227.05</v>
@@ -15026,7 +15083,9 @@
       <c r="BB61" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC61" s="11"/>
+      <c r="BC61" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BE61" s="22"/>
       <c r="BF61" s="11">
         <f t="shared" si="17"/>
@@ -15050,11 +15109,11 @@
       </c>
       <c r="BK61" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>39.638652000000008</v>
       </c>
       <c r="BL61" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.752684166666667E-2</v>
       </c>
       <c r="BM61" s="48" t="str">
         <f t="shared" si="31"/>
@@ -15074,11 +15133,11 @@
       </c>
       <c r="BQ61" s="28">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>71.498290043290055</v>
       </c>
       <c r="BR61" s="49">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>2.752684166666667E-2</v>
       </c>
       <c r="BS61" s="30">
         <f t="shared" si="21"/>
@@ -15099,7 +15158,9 @@
         <v>9</v>
       </c>
       <c r="E62" s="5"/>
-      <c r="F62" s="62"/>
+      <c r="F62" s="62">
+        <v>45542.552824074097</v>
+      </c>
       <c r="G62" s="5">
         <v>4805.7299999999996</v>
       </c>
@@ -15196,7 +15257,7 @@
       </c>
       <c r="AM62" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>1.1032315277777779E-2</v>
       </c>
       <c r="AN62" s="7">
         <v>187.96</v>
@@ -15247,7 +15308,9 @@
       <c r="BB62" s="23">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC62" s="12"/>
+      <c r="BC62" s="12">
+        <v>8.5000000000000006E-3</v>
+      </c>
       <c r="BD62" s="5"/>
       <c r="BE62" s="23"/>
       <c r="BF62" s="12">
@@ -15272,11 +15335,11 @@
       </c>
       <c r="BK62" s="14">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>15.886534000000001</v>
       </c>
       <c r="BL62" s="14">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.1032315277777779E-2</v>
       </c>
       <c r="BM62" s="48" t="str">
         <f t="shared" si="31"/>
@@ -15296,11 +15359,11 @@
       </c>
       <c r="BQ62" s="29">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>28.655364357864364</v>
       </c>
       <c r="BR62" s="38">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>1.1032315277777779E-2</v>
       </c>
       <c r="BS62" s="31">
         <f t="shared" si="21"/>
@@ -15321,70 +15384,135 @@
         <v>10</v>
       </c>
       <c r="E63" s="3"/>
-      <c r="F63" s="60"/>
+      <c r="F63" s="60">
+        <v>45543.405208333301</v>
+      </c>
       <c r="G63" s="63">
         <v>5497.99</v>
       </c>
       <c r="H63" s="6"/>
       <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="6"/>
-      <c r="N63" s="6"/>
-      <c r="O63" s="6"/>
-      <c r="P63" s="6"/>
-      <c r="Q63" s="6"/>
+      <c r="J63" s="6">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="K63" s="6">
+        <v>18.7</v>
+      </c>
+      <c r="L63" s="6">
+        <v>91.5</v>
+      </c>
+      <c r="M63" s="6">
+        <v>17.3</v>
+      </c>
+      <c r="N63" s="6">
+        <v>347</v>
+      </c>
+      <c r="O63" s="6">
+        <v>1.72</v>
+      </c>
+      <c r="P63" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>1.64</v>
+      </c>
       <c r="R63" s="6"/>
-      <c r="S63" s="6"/>
-      <c r="T63" s="6"/>
-      <c r="U63" s="6"/>
-      <c r="V63" s="6"/>
-      <c r="W63" s="6"/>
-      <c r="X63" s="6"/>
-      <c r="Y63" s="6"/>
-      <c r="Z63" s="6"/>
-      <c r="AA63" s="6"/>
-      <c r="AB63" s="6"/>
-      <c r="AC63" s="6"/>
-      <c r="AD63" s="16"/>
-      <c r="AE63" s="6"/>
-      <c r="AF63" s="6"/>
-      <c r="AG63" s="6"/>
+      <c r="S63" s="6">
+        <v>0.11</v>
+      </c>
+      <c r="T63" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="U63" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="V63" s="6">
+        <v>7.2460000000000004</v>
+      </c>
+      <c r="W63" s="6">
+        <v>95.9</v>
+      </c>
+      <c r="X63" s="6">
+        <v>11.5</v>
+      </c>
+      <c r="Y63" s="6">
+        <v>2.23</v>
+      </c>
+      <c r="Z63" s="6">
+        <v>146.4</v>
+      </c>
+      <c r="AA63" s="6">
+        <v>40.6</v>
+      </c>
+      <c r="AB63" s="6">
+        <v>84.1</v>
+      </c>
+      <c r="AC63" s="6">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="AD63" s="16">
+        <v>7.2869999999999999</v>
+      </c>
+      <c r="AE63" s="6">
+        <v>300</v>
+      </c>
+      <c r="AF63" s="6">
+        <v>47.8</v>
+      </c>
+      <c r="AG63" s="6">
+        <v>7.29</v>
+      </c>
       <c r="AH63" s="40">
         <f>AF63/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI63" s="6"/>
-      <c r="AJ63" s="6"/>
-      <c r="AK63" s="44"/>
-      <c r="AL63" s="6"/>
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="AI63" s="6">
+        <v>34</v>
+      </c>
+      <c r="AJ63" s="6">
+        <v>22.065000000000001</v>
+      </c>
+      <c r="AK63" s="44">
+        <v>44.018999999999998</v>
+      </c>
+      <c r="AL63" s="6">
+        <f>AL51+1.91</f>
+        <v>7.2</v>
+      </c>
       <c r="AM63" s="42">
         <f>BR63</f>
-        <v>0</v>
-      </c>
-      <c r="AN63" s="6"/>
-      <c r="AO63" s="6"/>
-      <c r="AP63" s="6"/>
-      <c r="AQ63" s="6"/>
+        <v>5.1207888888888803E-3</v>
+      </c>
+      <c r="AN63" s="6">
+        <v>169.89</v>
+      </c>
+      <c r="AO63" s="6">
+        <v>65.31</v>
+      </c>
+      <c r="AP63" s="6">
+        <v>497</v>
+      </c>
+      <c r="AQ63" s="6">
+        <v>1984</v>
+      </c>
       <c r="AR63" s="40">
         <v>137.11999999999989</v>
       </c>
       <c r="AS63" s="40">
         <f t="shared" si="60"/>
-        <v>-137.11999999999989</v>
+        <v>1846.88</v>
       </c>
       <c r="AT63" s="40">
         <f t="shared" si="36"/>
-        <v>-150.99</v>
+        <v>18.899999999999977</v>
       </c>
       <c r="AU63" s="40">
         <f t="shared" si="37"/>
-        <v>-65.31</v>
+        <v>0</v>
       </c>
       <c r="AV63" s="40">
         <f t="shared" si="65"/>
-        <v>518</v>
+        <v>21</v>
       </c>
       <c r="AW63" s="24">
         <v>15</v>
@@ -15405,39 +15533,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC63" s="8"/>
-      <c r="BD63" s="9"/>
-      <c r="BE63" s="21"/>
+      <c r="BD63" s="46">
+        <f>BM63*24*60/BH63</f>
+        <v>3.999999999999994E-3</v>
+      </c>
+      <c r="BE63" s="22">
+        <f>BP63/BH63</f>
+        <v>3.9797979551218672E-3</v>
+      </c>
       <c r="BF63" s="8">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.0341945239999999E-2</v>
       </c>
       <c r="BG63" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.892401145599999</v>
       </c>
       <c r="BH63" s="9">
         <f t="shared" si="41"/>
-        <v>1535</v>
-      </c>
-      <c r="BI63" s="10" t="str">
+        <v>1843.4839999999999</v>
+      </c>
+      <c r="BI63" s="10">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ63" s="10" t="str">
+        <v>9.2157024416810771E-2</v>
+      </c>
+      <c r="BJ63" s="10">
         <f t="shared" si="9"/>
-        <v/>
+        <v>9.9935294117647053E-2</v>
       </c>
       <c r="BK63" s="10">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>7.3739359999999881</v>
       </c>
       <c r="BL63" s="10" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM63" s="10">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>5.1207888888888803E-3</v>
       </c>
       <c r="BN63" s="35" t="str">
         <f t="shared" si="32"/>
@@ -15448,20 +15581,19 @@
         <v/>
       </c>
       <c r="BP63" s="50">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>7.33669385349988</v>
       </c>
       <c r="BQ63" s="27">
         <f>IF(BL63&lt;&gt;"",BL63/0.000385,IF(BM63&lt;&gt;"",BM63/0.000385,BN63/0.000385))</f>
-        <v>0</v>
+        <v>13.300750360750339</v>
       </c>
       <c r="BR63" s="37">
         <f>IF(BL63&lt;&gt;"",BL63,IF(BM63&lt;&gt;"",BM63,BN63))</f>
-        <v>0</v>
+        <v>5.1207888888888803E-3</v>
       </c>
       <c r="BS63" s="32">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>7.33669385349988</v>
       </c>
     </row>
     <row r="64" spans="1:71" x14ac:dyDescent="0.3">
@@ -15477,70 +15609,135 @@
       <c r="D64">
         <v>10</v>
       </c>
-      <c r="F64" s="61"/>
+      <c r="F64" s="61">
+        <v>45543.413275462997</v>
+      </c>
       <c r="G64" s="64">
         <v>5497.99</v>
       </c>
       <c r="H64" s="44"/>
       <c r="I64" s="44"/>
-      <c r="J64" s="44"/>
-      <c r="K64" s="44"/>
-      <c r="L64" s="44"/>
-      <c r="M64" s="44"/>
-      <c r="N64" s="44"/>
-      <c r="O64" s="44"/>
-      <c r="P64" s="44"/>
-      <c r="Q64" s="44"/>
+      <c r="J64" s="44">
+        <v>20.6</v>
+      </c>
+      <c r="K64" s="44">
+        <v>19.3</v>
+      </c>
+      <c r="L64" s="44">
+        <v>93.9</v>
+      </c>
+      <c r="M64" s="44">
+        <v>17.8</v>
+      </c>
+      <c r="N64" s="44">
+        <v>348</v>
+      </c>
+      <c r="O64" s="44">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="P64" s="44">
+        <v>0.21</v>
+      </c>
+      <c r="Q64" s="44">
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="R64" s="44"/>
-      <c r="S64" s="44"/>
-      <c r="T64" s="44"/>
-      <c r="U64" s="44"/>
-      <c r="V64" s="44"/>
-      <c r="W64" s="44"/>
-      <c r="X64" s="44"/>
-      <c r="Y64" s="44"/>
-      <c r="Z64" s="44"/>
-      <c r="AA64" s="44"/>
-      <c r="AB64" s="44"/>
-      <c r="AC64" s="44"/>
-      <c r="AD64" s="17"/>
-      <c r="AE64" s="44"/>
-      <c r="AF64" s="44"/>
-      <c r="AG64" s="44"/>
+      <c r="S64" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="T64" s="44">
+        <v>0.15</v>
+      </c>
+      <c r="U64" s="44">
+        <v>0.16</v>
+      </c>
+      <c r="V64" s="44">
+        <v>7.2619999999999996</v>
+      </c>
+      <c r="W64" s="44">
+        <v>105</v>
+      </c>
+      <c r="X64" s="44">
+        <v>55.7</v>
+      </c>
+      <c r="Y64" s="44">
+        <v>2.15</v>
+      </c>
+      <c r="Z64" s="44">
+        <v>154.19999999999999</v>
+      </c>
+      <c r="AA64" s="44">
+        <v>46.1</v>
+      </c>
+      <c r="AB64" s="44">
+        <v>92.1</v>
+      </c>
+      <c r="AC64" s="44">
+        <v>45.2</v>
+      </c>
+      <c r="AD64" s="17">
+        <v>7.3029999999999999</v>
+      </c>
+      <c r="AE64" s="44">
+        <v>300</v>
+      </c>
+      <c r="AF64" s="44">
+        <v>49.9</v>
+      </c>
+      <c r="AG64" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH64" s="45">
         <f t="shared" ref="AH64:AH68" si="78">AF64/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI64" s="44"/>
-      <c r="AJ64" s="44"/>
-      <c r="AK64" s="44"/>
-      <c r="AL64" s="44"/>
+        <v>0.499</v>
+      </c>
+      <c r="AI64" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ64" s="44">
+        <v>24.568000000000001</v>
+      </c>
+      <c r="AK64" s="44">
+        <v>27.469000000000001</v>
+      </c>
+      <c r="AL64" s="44">
+        <f>AL52+1.86</f>
+        <v>4.8600000000000003</v>
+      </c>
       <c r="AM64" s="45">
         <f t="shared" ref="AM64:AM68" si="79">BR64</f>
-        <v>0</v>
-      </c>
-      <c r="AN64" s="44"/>
-      <c r="AO64" s="44"/>
-      <c r="AP64" s="44"/>
-      <c r="AQ64" s="44"/>
+        <v>1.1401776999282799E-2</v>
+      </c>
+      <c r="AN64" s="44">
+        <v>185.31</v>
+      </c>
+      <c r="AO64" s="44">
+        <v>68.25</v>
+      </c>
+      <c r="AP64" s="44">
+        <v>481</v>
+      </c>
+      <c r="AQ64" s="44">
+        <v>1988</v>
+      </c>
       <c r="AR64" s="45">
         <v>45.769999999999982</v>
       </c>
       <c r="AS64" s="45">
         <f t="shared" si="60"/>
-        <v>-45.769999999999982</v>
+        <v>1942.23</v>
       </c>
       <c r="AT64" s="45">
         <f t="shared" si="36"/>
-        <v>-167.56</v>
+        <v>17.75</v>
       </c>
       <c r="AU64" s="45">
         <f t="shared" si="37"/>
-        <v>-61.42</v>
+        <v>6.8299999999999983</v>
       </c>
       <c r="AV64" s="45">
         <f t="shared" si="65"/>
-        <v>501</v>
+        <v>20</v>
       </c>
       <c r="AW64" s="25">
         <v>15</v>
@@ -15561,39 +15758,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC64" s="11"/>
-      <c r="BD64" s="46"/>
-      <c r="BE64" s="22"/>
+      <c r="BD64" s="46">
+        <f>BM64*24*60/BH64</f>
+        <v>8.8967442096820649E-3</v>
+      </c>
+      <c r="BE64" s="22">
+        <f>BP64/BH64</f>
+        <v>5.5208033108114681E-3</v>
+      </c>
       <c r="BF64" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.068519603E-2</v>
       </c>
       <c r="BG64" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15.386682283200003</v>
       </c>
       <c r="BH64" s="46">
         <f t="shared" si="41"/>
-        <v>1535</v>
-      </c>
-      <c r="BI64" s="47" t="str">
+        <v>1845.4569999999999</v>
+      </c>
+      <c r="BI64" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ64" s="47" t="str">
+        <v>0.10041415215851685</v>
+      </c>
+      <c r="BJ64" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0.10900588235294117</v>
       </c>
       <c r="BK64" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>16.418558878967232</v>
       </c>
       <c r="BL64" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM64" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.1401776999282799E-2</v>
       </c>
       <c r="BN64" s="48" t="str">
         <f t="shared" si="32"/>
@@ -15604,20 +15806,19 @@
         <v/>
       </c>
       <c r="BP64" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>10.188405115560199</v>
       </c>
       <c r="BQ64" s="28">
         <f t="shared" ref="BQ64:BQ68" si="80">IF(BL64&lt;&gt;"",BL64/0.000385,IF(BM64&lt;&gt;"",BM64/0.000385,BN64/0.000385))</f>
-        <v>0</v>
+        <v>29.615005192942338</v>
       </c>
       <c r="BR64" s="49">
         <f t="shared" ref="BR64:BR68" si="81">IF(BL64&lt;&gt;"",BL64,IF(BM64&lt;&gt;"",BM64,BN64))</f>
-        <v>0</v>
+        <v>1.1401776999282799E-2</v>
       </c>
       <c r="BS64" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>10.188405115560199</v>
       </c>
     </row>
     <row r="65" spans="1:71" x14ac:dyDescent="0.3">
@@ -15633,70 +15834,135 @@
       <c r="D65">
         <v>10</v>
       </c>
-      <c r="F65" s="61"/>
+      <c r="F65" s="61">
+        <v>45543.423032407401</v>
+      </c>
       <c r="G65" s="64">
         <v>5497.99</v>
       </c>
       <c r="H65" s="44"/>
       <c r="I65" s="44"/>
-      <c r="J65" s="44"/>
-      <c r="K65" s="44"/>
-      <c r="L65" s="44"/>
-      <c r="M65" s="44"/>
-      <c r="N65" s="44"/>
-      <c r="O65" s="44"/>
-      <c r="P65" s="44"/>
-      <c r="Q65" s="44"/>
+      <c r="J65" s="44">
+        <v>20.2</v>
+      </c>
+      <c r="K65" s="44">
+        <v>18</v>
+      </c>
+      <c r="L65" s="44">
+        <v>89.1</v>
+      </c>
+      <c r="M65" s="44">
+        <v>19.2</v>
+      </c>
+      <c r="N65" s="44">
+        <v>438</v>
+      </c>
+      <c r="O65" s="44">
+        <v>2.36</v>
+      </c>
+      <c r="P65" s="44">
+        <v>0.22</v>
+      </c>
+      <c r="Q65" s="44">
+        <v>3.22</v>
+      </c>
       <c r="R65" s="44"/>
-      <c r="S65" s="44"/>
-      <c r="T65" s="44"/>
-      <c r="U65" s="44"/>
-      <c r="V65" s="44"/>
-      <c r="W65" s="44"/>
-      <c r="X65" s="44"/>
-      <c r="Y65" s="44"/>
-      <c r="Z65" s="44"/>
-      <c r="AA65" s="44"/>
-      <c r="AB65" s="44"/>
-      <c r="AC65" s="44"/>
-      <c r="AD65" s="17"/>
-      <c r="AE65" s="44"/>
-      <c r="AF65" s="44"/>
-      <c r="AG65" s="44"/>
+      <c r="S65" s="44">
+        <v>0.78</v>
+      </c>
+      <c r="T65" s="44">
+        <v>2.21</v>
+      </c>
+      <c r="U65" s="44">
+        <v>2.19</v>
+      </c>
+      <c r="V65" s="44">
+        <v>7.2469999999999999</v>
+      </c>
+      <c r="W65" s="44">
+        <v>118.5</v>
+      </c>
+      <c r="X65" s="44">
+        <v>46.8</v>
+      </c>
+      <c r="Y65" s="44">
+        <v>1.5</v>
+      </c>
+      <c r="Z65" s="44">
+        <v>176.3</v>
+      </c>
+      <c r="AA65" s="44">
+        <v>50.2</v>
+      </c>
+      <c r="AB65" s="44">
+        <v>104</v>
+      </c>
+      <c r="AC65" s="44">
+        <v>37.9</v>
+      </c>
+      <c r="AD65" s="17">
+        <v>7.2880000000000003</v>
+      </c>
+      <c r="AE65" s="44">
+        <v>298</v>
+      </c>
+      <c r="AF65" s="44">
+        <v>50.4</v>
+      </c>
+      <c r="AG65" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH65" s="45">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="AI65" s="44"/>
-      <c r="AJ65" s="44"/>
-      <c r="AK65" s="44"/>
-      <c r="AL65" s="44"/>
+        <v>0.504</v>
+      </c>
+      <c r="AI65" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ65" s="44">
+        <v>38.045999999999999</v>
+      </c>
+      <c r="AK65" s="44">
+        <v>5.1144999999999996</v>
+      </c>
+      <c r="AL65" s="44">
+        <f>AL53+1.87</f>
+        <v>8.5300000000000011</v>
+      </c>
       <c r="AM65" s="45">
         <f t="shared" si="79"/>
-        <v>0</v>
-      </c>
-      <c r="AN65" s="44"/>
-      <c r="AO65" s="44"/>
-      <c r="AP65" s="44"/>
-      <c r="AQ65" s="44"/>
+        <v>2.08588154275034E-2</v>
+      </c>
+      <c r="AN65" s="44">
+        <v>249.44</v>
+      </c>
+      <c r="AO65" s="44">
+        <v>84.76</v>
+      </c>
+      <c r="AP65" s="44">
+        <v>384</v>
+      </c>
+      <c r="AQ65" s="44">
+        <v>2061</v>
+      </c>
       <c r="AR65" s="45">
         <v>84.700000000000045</v>
       </c>
       <c r="AS65" s="45">
         <f t="shared" si="60"/>
-        <v>-84.700000000000045</v>
+        <v>1976.3</v>
       </c>
       <c r="AT65" s="45">
         <f t="shared" si="36"/>
-        <v>-211.31</v>
+        <v>38.129999999999995</v>
       </c>
       <c r="AU65" s="45">
         <f t="shared" si="37"/>
-        <v>-76.27</v>
+        <v>8.4900000000000091</v>
       </c>
       <c r="AV65" s="45">
         <f t="shared" si="65"/>
-        <v>430</v>
+        <v>46</v>
       </c>
       <c r="AW65" s="25">
         <v>15</v>
@@ -15717,39 +15983,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC65" s="11"/>
-      <c r="BD65" s="46"/>
-      <c r="BE65" s="22"/>
+      <c r="BD65" s="46">
+        <f>BM65*24*60/BH65</f>
+        <v>1.5636859162771067E-2</v>
+      </c>
+      <c r="BE65" s="22">
+        <f>BP65/BH65</f>
+        <v>1.6524849493275854E-3</v>
+      </c>
       <c r="BF65" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.0372808699999998E-2</v>
       </c>
       <c r="BG65" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.936844527999996</v>
       </c>
       <c r="BH65" s="46">
         <f t="shared" si="41"/>
-        <v>1535</v>
-      </c>
-      <c r="BI65" s="47" t="str">
+        <v>1920.8905</v>
+      </c>
+      <c r="BI65" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ65" s="47" t="str">
+        <v>0.12985643897973362</v>
+      </c>
+      <c r="BJ65" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0.14672941176470589</v>
       </c>
       <c r="BK65" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>30.036694215604896</v>
       </c>
       <c r="BL65" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM65" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>2.08588154275034E-2</v>
       </c>
       <c r="BN65" s="48" t="str">
         <f t="shared" si="32"/>
@@ -15760,20 +16031,19 @@
         <v/>
       </c>
       <c r="BP65" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>3.17424264055634</v>
       </c>
       <c r="BQ65" s="28">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>54.178741370138702</v>
       </c>
       <c r="BR65" s="49">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>2.08588154275034E-2</v>
       </c>
       <c r="BS65" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3.17424264055634</v>
       </c>
     </row>
     <row r="66" spans="1:71" x14ac:dyDescent="0.3">
@@ -15789,70 +16059,135 @@
       <c r="D66">
         <v>10</v>
       </c>
-      <c r="F66" s="61"/>
+      <c r="F66" s="61">
+        <v>45543.425671296303</v>
+      </c>
       <c r="G66" s="64">
         <v>5497.99</v>
       </c>
       <c r="H66" s="44"/>
       <c r="I66" s="44"/>
-      <c r="J66" s="44"/>
-      <c r="K66" s="44"/>
-      <c r="L66" s="44"/>
-      <c r="M66" s="44"/>
-      <c r="N66" s="44"/>
-      <c r="O66" s="44"/>
-      <c r="P66" s="44"/>
-      <c r="Q66" s="44"/>
+      <c r="J66" s="44">
+        <v>20.2</v>
+      </c>
+      <c r="K66" s="44">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="L66" s="44">
+        <v>89.7</v>
+      </c>
+      <c r="M66" s="44">
+        <v>19</v>
+      </c>
+      <c r="N66" s="44">
+        <v>430</v>
+      </c>
+      <c r="O66" s="44">
+        <v>1.71</v>
+      </c>
+      <c r="P66" s="44">
+        <v>0.21</v>
+      </c>
+      <c r="Q66" s="44">
+        <v>1.31</v>
+      </c>
       <c r="R66" s="44"/>
-      <c r="S66" s="44"/>
-      <c r="T66" s="44"/>
-      <c r="U66" s="44"/>
-      <c r="V66" s="44"/>
-      <c r="W66" s="44"/>
-      <c r="X66" s="44"/>
-      <c r="Y66" s="44"/>
-      <c r="Z66" s="44"/>
-      <c r="AA66" s="44"/>
-      <c r="AB66" s="44"/>
-      <c r="AC66" s="44"/>
-      <c r="AD66" s="17"/>
-      <c r="AE66" s="44"/>
-      <c r="AF66" s="44"/>
-      <c r="AG66" s="44"/>
+      <c r="S66" s="44">
+        <v>0.6</v>
+      </c>
+      <c r="T66" s="44">
+        <v>2.08</v>
+      </c>
+      <c r="U66" s="44">
+        <v>2.54</v>
+      </c>
+      <c r="V66" s="44">
+        <v>7.2779999999999996</v>
+      </c>
+      <c r="W66" s="44">
+        <v>128.30000000000001</v>
+      </c>
+      <c r="X66" s="44">
+        <v>30</v>
+      </c>
+      <c r="Y66" s="44">
+        <v>1.48</v>
+      </c>
+      <c r="Z66" s="44">
+        <v>183.1</v>
+      </c>
+      <c r="AA66" s="44">
+        <v>58.4</v>
+      </c>
+      <c r="AB66" s="44">
+        <v>112.5</v>
+      </c>
+      <c r="AC66" s="44">
+        <v>24.3</v>
+      </c>
+      <c r="AD66" s="17">
+        <v>7.319</v>
+      </c>
+      <c r="AE66" s="44">
+        <v>301</v>
+      </c>
+      <c r="AF66" s="44">
+        <v>51.1</v>
+      </c>
+      <c r="AG66" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH66" s="45">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="AI66" s="44"/>
-      <c r="AJ66" s="44"/>
-      <c r="AK66" s="44"/>
-      <c r="AL66" s="44"/>
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="AI66" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ66" s="44">
+        <v>43.091000000000001</v>
+      </c>
+      <c r="AK66" s="44">
+        <v>13.548</v>
+      </c>
+      <c r="AL66" s="44">
+        <f>AL54+1.91</f>
+        <v>8.67</v>
+      </c>
       <c r="AM66" s="45">
         <f t="shared" si="79"/>
         <v>0</v>
       </c>
-      <c r="AN66" s="44"/>
-      <c r="AO66" s="44"/>
-      <c r="AP66" s="44"/>
-      <c r="AQ66" s="44"/>
+      <c r="AN66" s="44">
+        <v>233.93</v>
+      </c>
+      <c r="AO66" s="44">
+        <v>70.87</v>
+      </c>
+      <c r="AP66" s="44">
+        <v>406</v>
+      </c>
+      <c r="AQ66" s="44">
+        <v>2044</v>
+      </c>
       <c r="AR66" s="45">
         <v>47.420000000000073</v>
       </c>
       <c r="AS66" s="45">
-        <f t="shared" si="60"/>
-        <v>-47.420000000000073</v>
+        <f>AQ66-AR66</f>
+        <v>1996.58</v>
       </c>
       <c r="AT66" s="45">
         <f t="shared" si="36"/>
-        <v>-204.07</v>
+        <v>29.860000000000014</v>
       </c>
       <c r="AU66" s="45">
         <f t="shared" si="37"/>
-        <v>-70.87</v>
+        <v>0</v>
       </c>
       <c r="AV66" s="45">
         <f t="shared" si="65"/>
-        <v>443</v>
+        <v>37</v>
       </c>
       <c r="AW66" s="25">
         <v>15</v>
@@ -15876,23 +16211,23 @@
       <c r="BE66" s="22"/>
       <c r="BF66" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.034474187E-2</v>
       </c>
       <c r="BG66" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.8964282928</v>
       </c>
       <c r="BH66" s="46">
         <f t="shared" si="41"/>
-        <v>1535</v>
-      </c>
-      <c r="BI66" s="47" t="str">
+        <v>1905.1089999999999</v>
+      </c>
+      <c r="BI66" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ66" s="47" t="str">
+        <v>0.12279087443290647</v>
+      </c>
+      <c r="BJ66" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0.13760588235294119</v>
       </c>
       <c r="BK66" s="47">
         <f t="shared" si="18"/>
@@ -15912,7 +16247,7 @@
       </c>
       <c r="BO66" s="47">
         <f t="shared" si="47"/>
-        <v>11.512499999999999</v>
+        <v>8.0490855249999989</v>
       </c>
       <c r="BP66" s="51" t="str">
         <f t="shared" si="28"/>
@@ -15928,7 +16263,7 @@
       </c>
       <c r="BS66" s="30">
         <f t="shared" si="21"/>
-        <v>11.512499999999999</v>
+        <v>8.0490855249999989</v>
       </c>
     </row>
     <row r="67" spans="1:71" x14ac:dyDescent="0.3">
@@ -15944,70 +16279,131 @@
       <c r="D67">
         <v>10</v>
       </c>
-      <c r="F67" s="61"/>
+      <c r="F67" s="61">
+        <v>45543.428912037001</v>
+      </c>
       <c r="G67" s="64">
         <v>5497.99</v>
       </c>
       <c r="H67" s="44"/>
       <c r="I67" s="44"/>
-      <c r="J67" s="44"/>
-      <c r="K67" s="44"/>
-      <c r="L67" s="44"/>
-      <c r="M67" s="44"/>
-      <c r="N67" s="44"/>
+      <c r="J67" s="44">
+        <v>21.1</v>
+      </c>
+      <c r="K67" s="44">
+        <v>8.32</v>
+      </c>
+      <c r="L67" s="44">
+        <v>39.5</v>
+      </c>
+      <c r="M67" s="44">
+        <v>15.6</v>
+      </c>
+      <c r="N67" s="44">
+        <v>818</v>
+      </c>
       <c r="O67" s="44"/>
-      <c r="P67" s="44"/>
-      <c r="Q67" s="44"/>
+      <c r="P67" s="44">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="Q67" s="44">
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="R67" s="44"/>
-      <c r="S67" s="44"/>
-      <c r="T67" s="44"/>
+      <c r="S67" s="44">
+        <v>0.75</v>
+      </c>
+      <c r="T67" s="44">
+        <v>3.48</v>
+      </c>
       <c r="U67" s="44"/>
-      <c r="V67" s="44"/>
-      <c r="W67" s="44"/>
-      <c r="X67" s="44"/>
-      <c r="Y67" s="44"/>
-      <c r="Z67" s="44"/>
-      <c r="AA67" s="44"/>
-      <c r="AB67" s="44"/>
-      <c r="AC67" s="44"/>
-      <c r="AD67" s="17"/>
-      <c r="AE67" s="44"/>
-      <c r="AF67" s="44"/>
-      <c r="AG67" s="44"/>
+      <c r="V67" s="44">
+        <v>7.032</v>
+      </c>
+      <c r="W67" s="44">
+        <v>66.3</v>
+      </c>
+      <c r="X67" s="44">
+        <v>86</v>
+      </c>
+      <c r="Y67" s="44">
+        <v>7.2</v>
+      </c>
+      <c r="Z67" s="44">
+        <v>327.9</v>
+      </c>
+      <c r="AA67" s="44">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="AB67" s="44">
+        <v>58.1</v>
+      </c>
+      <c r="AC67" s="44">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="AD67" s="17">
+        <v>7.069</v>
+      </c>
+      <c r="AE67" s="44">
+        <v>301</v>
+      </c>
+      <c r="AF67" s="44">
+        <v>45.2</v>
+      </c>
+      <c r="AG67" s="44">
+        <v>7.09</v>
+      </c>
       <c r="AH67" s="45">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="AI67" s="44"/>
-      <c r="AJ67" s="44"/>
-      <c r="AK67" s="44"/>
-      <c r="AL67" s="44"/>
+        <v>0.45200000000000001</v>
+      </c>
+      <c r="AI67" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ67" s="44">
+        <v>157.88999999999999</v>
+      </c>
+      <c r="AK67" s="44">
+        <v>7.3125999999999998</v>
+      </c>
+      <c r="AL67" s="44">
+        <f>AL55+1.84</f>
+        <v>8.2800000000000011</v>
+      </c>
       <c r="AM67" s="45">
         <f t="shared" si="79"/>
         <v>0</v>
       </c>
-      <c r="AN67" s="44"/>
-      <c r="AO67" s="44"/>
-      <c r="AP67" s="44"/>
-      <c r="AQ67" s="44"/>
+      <c r="AN67" s="44">
+        <v>261.68</v>
+      </c>
+      <c r="AO67" s="44">
+        <v>77.819999999999993</v>
+      </c>
+      <c r="AP67" s="44">
+        <v>353</v>
+      </c>
+      <c r="AQ67" s="44">
+        <v>2185</v>
+      </c>
       <c r="AR67" s="45">
         <v>133.55999999999995</v>
       </c>
       <c r="AS67" s="45">
-        <f t="shared" ref="AS67:AS80" si="82">AQ67-AR67</f>
-        <v>-133.55999999999995</v>
+        <f>AQ67-AR67</f>
+        <v>2051.44</v>
       </c>
       <c r="AT67" s="45">
         <f t="shared" si="36"/>
-        <v>-227.05</v>
+        <v>34.629999999999995</v>
       </c>
       <c r="AU67" s="45">
         <f t="shared" si="37"/>
-        <v>-77.819999999999993</v>
+        <v>0</v>
       </c>
       <c r="AV67" s="45">
         <f t="shared" si="65"/>
-        <v>394</v>
+        <v>41</v>
       </c>
       <c r="AW67" s="25">
         <v>15</v>
@@ -16030,27 +16426,27 @@
       <c r="BC67" s="11"/>
       <c r="BE67" s="22"/>
       <c r="BF67" s="11">
-        <f t="shared" ref="BF67:BF74" si="83">BB67*K67*BH67/1000</f>
-        <v>0</v>
+        <f t="shared" ref="BF67:BF74" si="82">BB67*K67*BH67/1000</f>
+        <v>5.1117645696000013E-3</v>
       </c>
       <c r="BG67" s="46">
-        <f t="shared" ref="BG67:BG74" si="84">BF67*24*60</f>
-        <v>0</v>
+        <f t="shared" ref="BG67:BG74" si="83">BF67*24*60</f>
+        <v>7.3609409802240027</v>
       </c>
       <c r="BH67" s="46">
         <f t="shared" si="41"/>
-        <v>1535</v>
-      </c>
-      <c r="BI67" s="47" t="str">
+        <v>2047.9826000000003</v>
+      </c>
+      <c r="BI67" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ67" s="47" t="str">
+        <v>0.12777452308432696</v>
+      </c>
+      <c r="BJ67" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0.1539294117647059</v>
       </c>
       <c r="BK67" s="47">
-        <f t="shared" ref="BK67:BK74" si="85">AM67*24*60</f>
+        <f t="shared" ref="BK67:BK74" si="84">AM67*24*60</f>
         <v>0</v>
       </c>
       <c r="BL67" s="47">
@@ -16062,12 +16458,12 @@
         <v/>
       </c>
       <c r="BN67" s="48" t="str">
-        <f t="shared" ref="BN67:BN74" si="86">IF(B67="No MPC", BB67*K67*BH67/1000,"")</f>
+        <f t="shared" ref="BN67:BN74" si="85">IF(B67="No MPC", BB67*K67*BH67/1000,"")</f>
         <v/>
       </c>
       <c r="BO67" s="47">
         <f t="shared" si="47"/>
-        <v>11.512499999999999</v>
+        <v>15.001472545000004</v>
       </c>
       <c r="BP67" s="51" t="str">
         <f t="shared" si="28"/>
@@ -16082,8 +16478,8 @@
         <v>0</v>
       </c>
       <c r="BS67" s="30">
-        <f t="shared" ref="BS67:BS74" si="87">IF(BO67&lt;&gt;"",BO67,BP67)</f>
-        <v>11.512499999999999</v>
+        <f t="shared" ref="BS67:BS74" si="86">IF(BO67&lt;&gt;"",BO67,BP67)</f>
+        <v>15.001472545000004</v>
       </c>
     </row>
     <row r="68" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -16100,70 +16496,135 @@
         <v>10</v>
       </c>
       <c r="E68" s="5"/>
-      <c r="F68" s="62"/>
+      <c r="F68" s="62">
+        <v>45543.4315740741</v>
+      </c>
       <c r="G68" s="65">
         <v>5497.99</v>
       </c>
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
-      <c r="J68" s="7"/>
-      <c r="K68" s="7"/>
-      <c r="L68" s="7"/>
-      <c r="M68" s="7"/>
-      <c r="N68" s="7"/>
-      <c r="O68" s="7"/>
-      <c r="P68" s="7"/>
-      <c r="Q68" s="7"/>
+      <c r="J68" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="K68" s="7">
+        <v>19.7</v>
+      </c>
+      <c r="L68" s="7">
+        <v>92</v>
+      </c>
+      <c r="M68" s="7">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="N68" s="7">
+        <v>367</v>
+      </c>
+      <c r="O68" s="7">
+        <v>1.57</v>
+      </c>
+      <c r="P68" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="Q68" s="7">
+        <v>0.66</v>
+      </c>
       <c r="R68" s="7"/>
-      <c r="S68" s="7"/>
-      <c r="T68" s="7"/>
-      <c r="U68" s="7"/>
-      <c r="V68" s="7"/>
-      <c r="W68" s="7"/>
-      <c r="X68" s="7"/>
-      <c r="Y68" s="7"/>
-      <c r="Z68" s="7"/>
-      <c r="AA68" s="7"/>
-      <c r="AB68" s="7"/>
-      <c r="AC68" s="7"/>
-      <c r="AD68" s="18"/>
-      <c r="AE68" s="7"/>
-      <c r="AF68" s="7"/>
-      <c r="AG68" s="7"/>
+      <c r="S68" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="T68" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="U68" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="V68" s="7">
+        <v>7.2640000000000002</v>
+      </c>
+      <c r="W68" s="7">
+        <v>120.2</v>
+      </c>
+      <c r="X68" s="7">
+        <v>31.7</v>
+      </c>
+      <c r="Y68" s="7">
+        <v>1.79</v>
+      </c>
+      <c r="Z68" s="7">
+        <v>160</v>
+      </c>
+      <c r="AA68" s="7">
+        <v>53</v>
+      </c>
+      <c r="AB68" s="7">
+        <v>105.4</v>
+      </c>
+      <c r="AC68" s="7">
+        <v>25.6</v>
+      </c>
+      <c r="AD68" s="18">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="AE68" s="7">
+        <v>299</v>
+      </c>
+      <c r="AF68" s="7">
+        <v>49.3</v>
+      </c>
+      <c r="AG68" s="7">
+        <v>7.3</v>
+      </c>
       <c r="AH68" s="41">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="AI68" s="7"/>
-      <c r="AJ68" s="7"/>
-      <c r="AK68" s="7"/>
-      <c r="AL68" s="7"/>
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="AI68" s="7">
+        <v>34</v>
+      </c>
+      <c r="AJ68" s="7">
+        <v>28.271000000000001</v>
+      </c>
+      <c r="AK68" s="7">
+        <v>45.024999999999999</v>
+      </c>
+      <c r="AL68" s="7">
+        <f>AL56+1.86</f>
+        <v>8.379999999999999</v>
+      </c>
       <c r="AM68" s="41">
         <f t="shared" si="79"/>
         <v>0</v>
       </c>
-      <c r="AN68" s="7"/>
-      <c r="AO68" s="7"/>
-      <c r="AP68" s="7"/>
-      <c r="AQ68" s="7"/>
+      <c r="AN68" s="7">
+        <v>201.93</v>
+      </c>
+      <c r="AO68" s="7">
+        <v>69.75</v>
+      </c>
+      <c r="AP68" s="7">
+        <v>460</v>
+      </c>
+      <c r="AQ68" s="7">
+        <v>2025</v>
+      </c>
       <c r="AR68" s="41">
         <v>51.660000000000082</v>
       </c>
       <c r="AS68" s="41">
-        <f t="shared" si="82"/>
-        <v>-51.660000000000082</v>
+        <f>AQ68-AR68</f>
+        <v>1973.34</v>
       </c>
       <c r="AT68" s="41">
         <f t="shared" si="36"/>
-        <v>-187.96</v>
+        <v>13.969999999999999</v>
       </c>
       <c r="AU68" s="41">
         <f t="shared" si="37"/>
-        <v>-56.59</v>
+        <v>13.159999999999997</v>
       </c>
       <c r="AV68" s="41">
         <f t="shared" si="65"/>
-        <v>476</v>
+        <v>16</v>
       </c>
       <c r="AW68" s="26">
         <v>15</v>
@@ -16187,31 +16648,31 @@
       <c r="BD68" s="5"/>
       <c r="BE68" s="23"/>
       <c r="BF68" s="12">
+        <f t="shared" si="82"/>
+        <v>1.1160183959999999E-2</v>
+      </c>
+      <c r="BG68" s="13">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="BG68" s="13">
-        <f t="shared" si="84"/>
-        <v>0</v>
+        <v>16.070664902399997</v>
       </c>
       <c r="BH68" s="13">
         <f t="shared" si="41"/>
-        <v>1535</v>
-      </c>
-      <c r="BI68" s="14" t="str">
-        <f t="shared" ref="BI68:BI80" si="88">IF(ISBLANK(AN68),"",IFERROR(AN68/BH68,0))</f>
-        <v/>
-      </c>
-      <c r="BJ68" s="14" t="str">
-        <f t="shared" ref="BJ68:BJ80" si="89">IF(ISBLANK(AN68),"",AN68/AX68)</f>
-        <v/>
+        <v>1888.3559999999998</v>
+      </c>
+      <c r="BI68" s="14">
+        <f t="shared" ref="BI68:BI80" si="87">IF(ISBLANK(AN68),"",IFERROR(AN68/BH68,0))</f>
+        <v>0.10693428569612935</v>
+      </c>
+      <c r="BJ68" s="14">
+        <f t="shared" ref="BJ68:BJ80" si="88">IF(ISBLANK(AN68),"",AN68/AX68)</f>
+        <v>0.11878235294117648</v>
       </c>
       <c r="BK68" s="14">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="BL68" s="14">
-        <f t="shared" ref="BL68:BL80" si="90">IF(B68="Python",BC68*BH68/24/60,"")</f>
+        <f t="shared" ref="BL68:BL80" si="89">IF(B68="Python",BC68*BH68/24/60,"")</f>
         <v>0</v>
       </c>
       <c r="BM68" s="48" t="str">
@@ -16219,12 +16680,12 @@
         <v/>
       </c>
       <c r="BN68" s="36" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v/>
       </c>
       <c r="BO68" s="14">
         <f t="shared" si="47"/>
-        <v>11.512499999999999</v>
+        <v>11.046882599999998</v>
       </c>
       <c r="BP68" s="52" t="str">
         <f t="shared" si="28"/>
@@ -16239,8 +16700,8 @@
         <v>0</v>
       </c>
       <c r="BS68" s="31">
-        <f t="shared" si="87"/>
-        <v>11.512499999999999</v>
+        <f t="shared" si="86"/>
+        <v>11.046882599999998</v>
       </c>
     </row>
     <row r="69" spans="1:71" x14ac:dyDescent="0.3">
@@ -16307,20 +16768,20 @@
         <v>137.11999999999989</v>
       </c>
       <c r="AS69" s="40">
-        <f t="shared" si="82"/>
+        <f t="shared" ref="AS67:AS80" si="90">AQ69-AR69</f>
         <v>-137.11999999999989</v>
       </c>
       <c r="AT69" s="40">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-169.89</v>
       </c>
       <c r="AU69" s="40">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-65.31</v>
       </c>
       <c r="AV69" s="40">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="AW69" s="24">
         <v>15</v>
@@ -16344,11 +16805,11 @@
       <c r="BD69" s="9"/>
       <c r="BE69" s="21"/>
       <c r="BF69" s="8">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="BG69" s="9">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="BG69" s="9">
-        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="BH69" s="9">
@@ -16356,19 +16817,19 @@
         <v>1520</v>
       </c>
       <c r="BI69" s="10" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ69" s="10" t="str">
         <f t="shared" si="88"/>
         <v/>
       </c>
-      <c r="BJ69" s="10" t="str">
+      <c r="BK69" s="10">
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="BL69" s="10" t="str">
         <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BK69" s="10">
-        <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-      <c r="BL69" s="10" t="str">
-        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="BM69" s="10">
@@ -16376,7 +16837,7 @@
         <v>0</v>
       </c>
       <c r="BN69" s="35" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v/>
       </c>
       <c r="BO69" s="10" t="str">
@@ -16396,7 +16857,7 @@
         <v>0</v>
       </c>
       <c r="BS69" s="32">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
     </row>
@@ -16463,20 +16924,20 @@
         <v>45.769999999999982</v>
       </c>
       <c r="AS70" s="45">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>-45.769999999999982</v>
       </c>
       <c r="AT70" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-185.31</v>
       </c>
       <c r="AU70" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-68.25</v>
       </c>
       <c r="AV70" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>481</v>
       </c>
       <c r="AW70" s="25">
         <v>15</v>
@@ -16500,11 +16961,11 @@
       <c r="BD70" s="46"/>
       <c r="BE70" s="22"/>
       <c r="BF70" s="11">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="BG70" s="46">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="BG70" s="46">
-        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="BH70" s="46">
@@ -16512,19 +16973,19 @@
         <v>1520</v>
       </c>
       <c r="BI70" s="47" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ70" s="47" t="str">
         <f t="shared" si="88"/>
         <v/>
       </c>
-      <c r="BJ70" s="47" t="str">
+      <c r="BK70" s="47">
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="BL70" s="47" t="str">
         <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BK70" s="47">
-        <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-      <c r="BL70" s="47" t="str">
-        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="BM70" s="47">
@@ -16532,7 +16993,7 @@
         <v>0</v>
       </c>
       <c r="BN70" s="48" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v/>
       </c>
       <c r="BO70" s="47" t="str">
@@ -16552,7 +17013,7 @@
         <v>0</v>
       </c>
       <c r="BS70" s="30">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
     </row>
@@ -16619,20 +17080,20 @@
         <v>84.700000000000045</v>
       </c>
       <c r="AS71" s="45">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>-84.700000000000045</v>
       </c>
       <c r="AT71" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-249.44</v>
       </c>
       <c r="AU71" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-84.76</v>
       </c>
       <c r="AV71" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="AW71" s="25">
         <v>15</v>
@@ -16656,11 +17117,11 @@
       <c r="BD71" s="46"/>
       <c r="BE71" s="22"/>
       <c r="BF71" s="11">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="BG71" s="46">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="BG71" s="46">
-        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="BH71" s="46">
@@ -16668,19 +17129,19 @@
         <v>1520</v>
       </c>
       <c r="BI71" s="47" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ71" s="47" t="str">
         <f t="shared" si="88"/>
         <v/>
       </c>
-      <c r="BJ71" s="47" t="str">
+      <c r="BK71" s="47">
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="BL71" s="47" t="str">
         <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BK71" s="47">
-        <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-      <c r="BL71" s="47" t="str">
-        <f t="shared" si="90"/>
         <v/>
       </c>
       <c r="BM71" s="47">
@@ -16688,7 +17149,7 @@
         <v>0</v>
       </c>
       <c r="BN71" s="48" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v/>
       </c>
       <c r="BO71" s="47" t="str">
@@ -16708,7 +17169,7 @@
         <v>0</v>
       </c>
       <c r="BS71" s="30">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
     </row>
@@ -16775,20 +17236,20 @@
         <v>47.420000000000073</v>
       </c>
       <c r="AS72" s="45">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>-47.420000000000073</v>
       </c>
       <c r="AT72" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-233.93</v>
       </c>
       <c r="AU72" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-70.87</v>
       </c>
       <c r="AV72" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>406</v>
       </c>
       <c r="AW72" s="25">
         <v>15</v>
@@ -16811,11 +17272,11 @@
       <c r="BC72" s="11"/>
       <c r="BE72" s="22"/>
       <c r="BF72" s="11">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="BG72" s="46">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="BG72" s="46">
-        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="BH72" s="46">
@@ -16823,19 +17284,19 @@
         <v>1520</v>
       </c>
       <c r="BI72" s="47" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ72" s="47" t="str">
         <f t="shared" si="88"/>
         <v/>
       </c>
-      <c r="BJ72" s="47" t="str">
+      <c r="BK72" s="47">
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="BL72" s="47">
         <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BK72" s="47">
-        <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-      <c r="BL72" s="47">
-        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="BM72" s="48" t="str">
@@ -16843,7 +17304,7 @@
         <v/>
       </c>
       <c r="BN72" s="48" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v/>
       </c>
       <c r="BO72" s="47">
@@ -16863,7 +17324,7 @@
         <v>0</v>
       </c>
       <c r="BS72" s="30">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>11.4</v>
       </c>
     </row>
@@ -16930,20 +17391,20 @@
         <v>133.55999999999995</v>
       </c>
       <c r="AS73" s="45">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>-133.55999999999995</v>
       </c>
       <c r="AT73" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>-261.68</v>
       </c>
       <c r="AU73" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>-77.819999999999993</v>
       </c>
       <c r="AV73" s="45">
         <f t="shared" ref="AV73:AV80" si="98">AP67-AP73</f>
-        <v>0</v>
+        <v>353</v>
       </c>
       <c r="AW73" s="25">
         <v>15</v>
@@ -16966,11 +17427,11 @@
       <c r="BC73" s="11"/>
       <c r="BE73" s="22"/>
       <c r="BF73" s="11">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="BG73" s="46">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="BG73" s="46">
-        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="BH73" s="46">
@@ -16978,19 +17439,19 @@
         <v>1520</v>
       </c>
       <c r="BI73" s="47" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ73" s="47" t="str">
         <f t="shared" si="88"/>
         <v/>
       </c>
-      <c r="BJ73" s="47" t="str">
+      <c r="BK73" s="47">
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="BL73" s="47">
         <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BK73" s="47">
-        <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-      <c r="BL73" s="47">
-        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="BM73" s="48" t="str">
@@ -16998,7 +17459,7 @@
         <v/>
       </c>
       <c r="BN73" s="48" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v/>
       </c>
       <c r="BO73" s="47">
@@ -17018,7 +17479,7 @@
         <v>0</v>
       </c>
       <c r="BS73" s="30">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>11.4</v>
       </c>
     </row>
@@ -17086,20 +17547,20 @@
         <v>51.660000000000082</v>
       </c>
       <c r="AS74" s="41">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>-51.660000000000082</v>
       </c>
       <c r="AT74" s="41">
         <f t="shared" ref="AT74:AT80" si="99">AN74-AN68</f>
-        <v>0</v>
+        <v>-201.93</v>
       </c>
       <c r="AU74" s="41">
         <f t="shared" ref="AU74:AU80" si="100">AO74-AO68</f>
-        <v>0</v>
+        <v>-69.75</v>
       </c>
       <c r="AV74" s="41">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="AW74" s="26">
         <v>15</v>
@@ -17123,11 +17584,11 @@
       <c r="BD74" s="5"/>
       <c r="BE74" s="23"/>
       <c r="BF74" s="12">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="BG74" s="13">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="BG74" s="13">
-        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="BH74" s="13">
@@ -17135,19 +17596,19 @@
         <v>1520</v>
       </c>
       <c r="BI74" s="14" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ74" s="14" t="str">
         <f t="shared" si="88"/>
         <v/>
       </c>
-      <c r="BJ74" s="14" t="str">
+      <c r="BK74" s="14">
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="BL74" s="14">
         <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BK74" s="14">
-        <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-      <c r="BL74" s="14">
-        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="BM74" s="48" t="str">
@@ -17155,7 +17616,7 @@
         <v/>
       </c>
       <c r="BN74" s="36" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v/>
       </c>
       <c r="BO74" s="14">
@@ -17175,7 +17636,7 @@
         <v>0</v>
       </c>
       <c r="BS74" s="31">
-        <f t="shared" si="87"/>
+        <f t="shared" si="86"/>
         <v>11.4</v>
       </c>
     </row>
@@ -17243,7 +17704,7 @@
         <v>137.11999999999989</v>
       </c>
       <c r="AS75" s="40">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>-137.11999999999989</v>
       </c>
       <c r="AT75" s="40">
@@ -17292,11 +17753,11 @@
         <v>1505</v>
       </c>
       <c r="BI75" s="10" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ75" s="10" t="str">
         <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ75" s="10" t="str">
-        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BK75" s="10">
@@ -17304,7 +17765,7 @@
         <v>0</v>
       </c>
       <c r="BL75" s="10" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BM75" s="10">
@@ -17399,7 +17860,7 @@
         <v>45.769999999999982</v>
       </c>
       <c r="AS76" s="45">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>-45.769999999999982</v>
       </c>
       <c r="AT76" s="45">
@@ -17448,11 +17909,11 @@
         <v>1505</v>
       </c>
       <c r="BI76" s="47" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ76" s="47" t="str">
         <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ76" s="47" t="str">
-        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BK76" s="47">
@@ -17460,7 +17921,7 @@
         <v>0</v>
       </c>
       <c r="BL76" s="47" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BM76" s="47">
@@ -17555,7 +18016,7 @@
         <v>84.700000000000045</v>
       </c>
       <c r="AS77" s="45">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>-84.700000000000045</v>
       </c>
       <c r="AT77" s="45">
@@ -17604,11 +18065,11 @@
         <v>1505</v>
       </c>
       <c r="BI77" s="47" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ77" s="47" t="str">
         <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ77" s="47" t="str">
-        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BK77" s="47">
@@ -17616,7 +18077,7 @@
         <v>0</v>
       </c>
       <c r="BL77" s="47" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BM77" s="47">
@@ -17711,7 +18172,7 @@
         <v>47.420000000000073</v>
       </c>
       <c r="AS78" s="45">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>-47.420000000000073</v>
       </c>
       <c r="AT78" s="45">
@@ -17759,11 +18220,11 @@
         <v>1505</v>
       </c>
       <c r="BI78" s="47" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ78" s="47" t="str">
         <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ78" s="47" t="str">
-        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BK78" s="47">
@@ -17771,7 +18232,7 @@
         <v>0</v>
       </c>
       <c r="BL78" s="47">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="BM78" s="48" t="str">
@@ -17866,7 +18327,7 @@
         <v>133.55999999999995</v>
       </c>
       <c r="AS79" s="45">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>-133.55999999999995</v>
       </c>
       <c r="AT79" s="45">
@@ -17914,11 +18375,11 @@
         <v>1505</v>
       </c>
       <c r="BI79" s="47" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ79" s="47" t="str">
         <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ79" s="47" t="str">
-        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BK79" s="47">
@@ -17926,7 +18387,7 @@
         <v>0</v>
       </c>
       <c r="BL79" s="47">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="BM79" s="48" t="str">
@@ -18022,7 +18483,7 @@
         <v>51.660000000000082</v>
       </c>
       <c r="AS80" s="41">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>-51.660000000000082</v>
       </c>
       <c r="AT80" s="41">
@@ -18071,11 +18532,11 @@
         <v>1505</v>
       </c>
       <c r="BI80" s="14" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ80" s="14" t="str">
         <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ80" s="14" t="str">
-        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BK80" s="14">
@@ -18083,7 +18544,7 @@
         <v>0</v>
       </c>
       <c r="BL80" s="14">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="BM80" s="36" t="str">
@@ -18165,6 +18626,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -18387,34 +18875,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18431,29 +18917,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
+++ b/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28103"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-045-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1540" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A3C3CC1-DA82-4F96-AE15-07BC88948B97}"/>
+  <xr:revisionPtr revIDLastSave="1701" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCEE6FA6-4FF8-4207-AB7E-854520FD7A84}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="98">
   <si>
     <t>Batch Data</t>
   </si>
@@ -188,6 +188,15 @@
     <t>Feed Bottle Weight (g)</t>
   </si>
   <si>
+    <t>Reactor Scale Weight (g)</t>
+  </si>
+  <si>
+    <t>Reactor Scale Offset (g)</t>
+  </si>
+  <si>
+    <t>Reactor Scale True Weight (g)</t>
+  </si>
+  <si>
     <t>Daily Feed Amount (mL)</t>
   </si>
   <si>
@@ -263,34 +272,10 @@
     <t>Glucose to Copy to System</t>
   </si>
   <si>
-    <t>Julia</t>
+    <t>MR24-045-801</t>
   </si>
   <si>
-    <t>Python</t>
-  </si>
-  <si>
-    <t>Glucose Strategy: feed up to 5g/L</t>
-  </si>
-  <si>
-    <t>Reactor Scale Weight (g)</t>
-  </si>
-  <si>
-    <t>Reactor Scale Offset (g)</t>
-  </si>
-  <si>
-    <t>Reactor Scale True Weight (g)</t>
-  </si>
-  <si>
-    <t>Glucose Strategy: feed up to 3g/L if under 1.5 g/L, CSFR was used since model predicted low feed</t>
-  </si>
-  <si>
-    <t>pH, pCO2, pO2, bicarb, pCO2 at temp, pO2 at temp, and pH at temp were not measured in BR05's first sample</t>
-  </si>
-  <si>
-    <t>Switched to optical DO probe</t>
-  </si>
-  <si>
-    <t>MR24-045-801</t>
+    <t>Julia</t>
   </si>
   <si>
     <t>MR24-045-802</t>
@@ -302,13 +287,52 @@
     <t>MR24-045-804</t>
   </si>
   <si>
+    <t>Python</t>
+  </si>
+  <si>
     <t>MR24-045-805</t>
   </si>
   <si>
     <t>MR24-045-806</t>
   </si>
   <si>
+    <t>Glucose Strategy: feed up to 5g/L</t>
+  </si>
+  <si>
+    <t>Glucose Strategy: feed up to 3g/L if under 1.5 g/L, CSFR was used since model predicted low feed</t>
+  </si>
+  <si>
+    <t>Switched to optical DO probe</t>
+  </si>
+  <si>
+    <t>pH, pCO2, pO2, bicarb, pCO2 at temp, pO2 at temp, and pH at temp were not measured in BR05's first sample</t>
+  </si>
+  <si>
     <t>Antifoam totalizer reset due to schedule restart</t>
+  </si>
+  <si>
+    <t>Cedex Sample was concentrated due to being left over night. Samples were re-run but the original value used for modeling was: 5803.62</t>
+  </si>
+  <si>
+    <t>Cedex Sample was concentrated due to being left over night. Samples were re-run but the original value used for modeling was: 5945.67</t>
+  </si>
+  <si>
+    <t>Cedex Sample was concentrated due to being left over night. Samples were re-run but the original value used for modeling was: 5235.63</t>
+  </si>
+  <si>
+    <t>Cedex Sample was concentrated due to being left over night. Samples were re-run but the original value used for modeling was: 5350.905</t>
+  </si>
+  <si>
+    <t>Cedex Sample was concentrated due to being left over night. Samples were re-run but the original value used for modeling was: 2975.505</t>
+  </si>
+  <si>
+    <t>Cedex Sample was concentrated due to being left over night. Samples were re-run but the original value used for modeling was: 5979</t>
+  </si>
+  <si>
+    <t>801 DO probe was switched back to probe 1 due to large fluctuations in probe 2</t>
+  </si>
+  <si>
+    <t>805 was considered dead 2 days before this so feed was turned off</t>
   </si>
 </sst>
 </file>
@@ -321,7 +345,7 @@
     <numFmt numFmtId="166" formatCode="0.00000"/>
     <numFmt numFmtId="167" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1000,7 +1024,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -1087,6 +1111,12 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1144,9 +1174,6 @@
     <xf numFmtId="0" fontId="19" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="26" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="26" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1242,10 +1269,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1547,109 +1570,109 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:BS87"/>
-  <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" customWidth="1"/>
-    <col min="7" max="18" width="12.6640625" customWidth="1"/>
-    <col min="19" max="19" width="15.109375" customWidth="1"/>
-    <col min="20" max="20" width="16.109375" customWidth="1"/>
-    <col min="21" max="43" width="12.6640625" customWidth="1"/>
-    <col min="44" max="44" width="12.6640625" hidden="1" customWidth="1"/>
-    <col min="45" max="68" width="12.6640625" customWidth="1"/>
-    <col min="69" max="69" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="70" max="71" width="16.33203125" customWidth="1"/>
+    <col min="2" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" customWidth="1"/>
+    <col min="7" max="18" width="12.7109375" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" customWidth="1"/>
+    <col min="20" max="20" width="16.140625" customWidth="1"/>
+    <col min="21" max="43" width="12.7109375" customWidth="1"/>
+    <col min="44" max="44" width="12.7109375" hidden="1" customWidth="1"/>
+    <col min="45" max="68" width="12.7109375" customWidth="1"/>
+    <col min="69" max="69" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="70" max="71" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="68" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="69" t="s">
+    <row r="1" spans="1:71" ht="21">
+      <c r="A1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
-      <c r="R1" s="70"/>
-      <c r="S1" s="70"/>
-      <c r="T1" s="70"/>
-      <c r="U1" s="70"/>
-      <c r="V1" s="70"/>
-      <c r="W1" s="70"/>
-      <c r="X1" s="70"/>
-      <c r="Y1" s="70"/>
-      <c r="Z1" s="70"/>
-      <c r="AA1" s="70"/>
-      <c r="AB1" s="70"/>
-      <c r="AC1" s="70"/>
-      <c r="AD1" s="71"/>
-      <c r="AE1" s="84" t="s">
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="76"/>
+      <c r="V1" s="76"/>
+      <c r="W1" s="76"/>
+      <c r="X1" s="76"/>
+      <c r="Y1" s="76"/>
+      <c r="Z1" s="76"/>
+      <c r="AA1" s="76"/>
+      <c r="AB1" s="76"/>
+      <c r="AC1" s="76"/>
+      <c r="AD1" s="77"/>
+      <c r="AE1" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="AF1" s="85"/>
-      <c r="AG1" s="85"/>
-      <c r="AH1" s="85"/>
-      <c r="AI1" s="85"/>
-      <c r="AJ1" s="85"/>
-      <c r="AK1" s="85"/>
-      <c r="AL1" s="85"/>
-      <c r="AM1" s="85"/>
-      <c r="AN1" s="85"/>
-      <c r="AO1" s="85"/>
-      <c r="AP1" s="85"/>
-      <c r="AQ1" s="85"/>
-      <c r="AR1" s="85"/>
-      <c r="AS1" s="85"/>
-      <c r="AT1" s="85"/>
-      <c r="AU1" s="85"/>
-      <c r="AV1" s="85"/>
-      <c r="AW1" s="86"/>
-      <c r="AX1" s="78" t="s">
+      <c r="AF1" s="91"/>
+      <c r="AG1" s="91"/>
+      <c r="AH1" s="91"/>
+      <c r="AI1" s="91"/>
+      <c r="AJ1" s="91"/>
+      <c r="AK1" s="91"/>
+      <c r="AL1" s="91"/>
+      <c r="AM1" s="91"/>
+      <c r="AN1" s="91"/>
+      <c r="AO1" s="91"/>
+      <c r="AP1" s="91"/>
+      <c r="AQ1" s="91"/>
+      <c r="AR1" s="91"/>
+      <c r="AS1" s="91"/>
+      <c r="AT1" s="91"/>
+      <c r="AU1" s="91"/>
+      <c r="AV1" s="91"/>
+      <c r="AW1" s="92"/>
+      <c r="AX1" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="AY1" s="79"/>
-      <c r="AZ1" s="79"/>
-      <c r="BA1" s="79"/>
-      <c r="BB1" s="80"/>
-      <c r="BC1" s="81" t="s">
+      <c r="AY1" s="85"/>
+      <c r="AZ1" s="85"/>
+      <c r="BA1" s="85"/>
+      <c r="BB1" s="86"/>
+      <c r="BC1" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="BD1" s="82"/>
-      <c r="BE1" s="83"/>
-      <c r="BF1" s="75" t="s">
+      <c r="BD1" s="88"/>
+      <c r="BE1" s="89"/>
+      <c r="BF1" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="BG1" s="76"/>
-      <c r="BH1" s="76"/>
-      <c r="BI1" s="76"/>
-      <c r="BJ1" s="76"/>
-      <c r="BK1" s="76"/>
-      <c r="BL1" s="76"/>
-      <c r="BM1" s="76"/>
-      <c r="BN1" s="76"/>
-      <c r="BO1" s="76"/>
-      <c r="BP1" s="77"/>
-      <c r="BQ1" s="72" t="s">
+      <c r="BG1" s="82"/>
+      <c r="BH1" s="82"/>
+      <c r="BI1" s="82"/>
+      <c r="BJ1" s="82"/>
+      <c r="BK1" s="82"/>
+      <c r="BL1" s="82"/>
+      <c r="BM1" s="82"/>
+      <c r="BN1" s="82"/>
+      <c r="BO1" s="82"/>
+      <c r="BP1" s="83"/>
+      <c r="BQ1" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="BR1" s="73"/>
-      <c r="BS1" s="74"/>
+      <c r="BR1" s="79"/>
+      <c r="BS1" s="80"/>
     </row>
-    <row r="2" spans="1:71" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:71" ht="60.6" thickBot="1">
       <c r="A2" s="19" t="s">
         <v>7</v>
       </c>
@@ -1777,99 +1800,99 @@
         <v>48</v>
       </c>
       <c r="AQ2" s="19" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="AR2" s="19" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="AS2" s="19" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="AT2" s="19" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AU2" s="19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AV2" s="19" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AW2" s="15" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AX2" s="20" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AY2" s="19" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AZ2" s="19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="BA2" s="19" t="s">
         <v>40</v>
       </c>
       <c r="BB2" s="15" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="BC2" s="20" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="BD2" s="19" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="BE2" s="15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="BF2" s="20" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="BG2" s="19" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="BH2" s="19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="BI2" s="19" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="BJ2" s="19" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="BK2" s="19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="BL2" s="19" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="BM2" s="19" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="BN2" s="19" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="BO2" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="BP2" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="BQ2" s="20" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="BR2" s="19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="BS2" s="15" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:71">
       <c r="A3" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3">
         <v>12</v>
@@ -2088,12 +2111,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:71">
       <c r="A4" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C4">
         <v>12</v>
@@ -2311,12 +2334,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:71">
       <c r="A5" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C5">
         <v>12</v>
@@ -2534,12 +2557,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:71">
       <c r="A6" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C6">
         <v>12</v>
@@ -2737,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="BP6" s="51" t="str">
-        <f t="shared" ref="BP6:BP69" si="28">IF(B6="Julia",BE6*BH6,"")</f>
+        <f t="shared" ref="BP6:BP68" si="28">IF(B6="Julia",BE6*BH6,"")</f>
         <v/>
       </c>
       <c r="BQ6" s="28">
@@ -2753,12 +2776,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:71">
       <c r="A7" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C7">
         <v>12</v>
@@ -2945,7 +2968,7 @@
         <v>9.3013722222222237E-3</v>
       </c>
       <c r="BM7" s="48" t="str">
-        <f t="shared" ref="BM7:BM70" si="31">IF(B7="Julia",BD7*BH7/24/60,"")</f>
+        <f t="shared" ref="BM7:BM68" si="31">IF(B7="Julia",BD7*BH7/24/60,"")</f>
         <v/>
       </c>
       <c r="BN7" s="48" t="str">
@@ -2972,12 +2995,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:71" ht="15" thickBot="1">
       <c r="A8" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C8" s="5">
         <v>12</v>
@@ -3193,12 +3216,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:71">
       <c r="A9" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C9" s="3">
         <v>12</v>
@@ -3420,12 +3443,12 @@
         <v>17.2171504761906</v>
       </c>
     </row>
-    <row r="10" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:71">
       <c r="A10" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C10">
         <v>12</v>
@@ -3646,12 +3669,12 @@
         <v>16.819329499794499</v>
       </c>
     </row>
-    <row r="11" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:71">
       <c r="A11" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C11">
         <v>12</v>
@@ -3872,12 +3895,12 @@
         <v>14.550506861694201</v>
       </c>
     </row>
-    <row r="12" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:71">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C12">
         <v>12</v>
@@ -3886,7 +3909,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F12" s="61">
         <v>45534.389444444401</v>
@@ -4098,12 +4121,12 @@
         <v>16.305808749999997</v>
       </c>
     </row>
-    <row r="13" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:71">
       <c r="A13" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C13">
         <v>12</v>
@@ -4112,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F13" s="61">
         <v>45534.406238425901</v>
@@ -4324,12 +4347,12 @@
         <v>14.226947500000001</v>
       </c>
     </row>
-    <row r="14" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:71" ht="15" thickBot="1">
       <c r="A14" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C14" s="5">
         <v>12</v>
@@ -4338,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F14" s="62">
         <v>45534.411597222199</v>
@@ -4551,12 +4574,12 @@
         <v>15.542739000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:71">
       <c r="A15" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C15" s="3">
         <v>12</v>
@@ -4778,12 +4801,12 @@
         <v>13.5648651</v>
       </c>
     </row>
-    <row r="16" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:71">
       <c r="A16" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C16">
         <v>12</v>
@@ -5004,12 +5027,12 @@
         <v>14.26370168</v>
       </c>
     </row>
-    <row r="17" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:71">
       <c r="A17" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C17">
         <v>12</v>
@@ -5228,12 +5251,12 @@
         <v>16.831299229999999</v>
       </c>
     </row>
-    <row r="18" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:71">
       <c r="A18" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C18">
         <v>12</v>
@@ -5242,7 +5265,7 @@
         <v>2</v>
       </c>
       <c r="E18" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F18" s="61">
         <v>45535.493217592601</v>
@@ -5452,12 +5475,12 @@
         <v>11.53943145</v>
       </c>
     </row>
-    <row r="19" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:71">
       <c r="A19" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C19">
         <v>12</v>
@@ -5466,7 +5489,7 @@
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F19" s="61">
         <v>45535.496261574102</v>
@@ -5676,12 +5699,12 @@
         <v>11.368347625000002</v>
       </c>
     </row>
-    <row r="20" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:71" ht="15" thickBot="1">
       <c r="A20" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C20" s="5">
         <v>12</v>
@@ -5690,7 +5713,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F20" s="62">
         <v>45535.499872685199</v>
@@ -5901,12 +5924,12 @@
         <v>11.9207928305</v>
       </c>
     </row>
-    <row r="21" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:71">
       <c r="A21" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C21" s="3">
         <v>12</v>
@@ -6128,12 +6151,12 @@
         <v>13.723596207991401</v>
       </c>
     </row>
-    <row r="22" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:71">
       <c r="A22" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C22">
         <v>12</v>
@@ -6354,12 +6377,12 @@
         <v>13.348472984178301</v>
       </c>
     </row>
-    <row r="23" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:71">
       <c r="A23" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C23">
         <v>12</v>
@@ -6580,12 +6603,12 @@
         <v>12.287615485800799</v>
       </c>
     </row>
-    <row r="24" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:71">
       <c r="A24" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C24">
         <v>12</v>
@@ -6803,12 +6826,12 @@
         <v>12.796550562500002</v>
       </c>
     </row>
-    <row r="25" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:71">
       <c r="A25" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C25">
         <v>12</v>
@@ -7026,12 +7049,12 @@
         <v>12.811264425000001</v>
       </c>
     </row>
-    <row r="26" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:71" ht="15" thickBot="1">
       <c r="A26" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C26" s="5">
         <v>12</v>
@@ -7251,12 +7274,12 @@
         <v>12.663445545</v>
       </c>
     </row>
-    <row r="27" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:71">
       <c r="A27" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C27" s="3">
         <v>12</v>
@@ -7478,12 +7501,12 @@
         <v>5.4753488007971303</v>
       </c>
     </row>
-    <row r="28" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:71">
       <c r="A28" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C28">
         <v>12</v>
@@ -7704,12 +7727,12 @@
         <v>4.1911080797985401</v>
       </c>
     </row>
-    <row r="29" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:71">
       <c r="A29" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C29">
         <v>12</v>
@@ -7718,7 +7741,7 @@
         <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F29" s="61">
         <v>45537.441435185203</v>
@@ -7933,12 +7956,12 @@
         <v>14.9699177567385</v>
       </c>
     </row>
-    <row r="30" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:71">
       <c r="A30" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C30">
         <v>12</v>
@@ -8156,12 +8179,12 @@
         <v>8.5762441099999993</v>
       </c>
     </row>
-    <row r="31" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:71">
       <c r="A31" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C31">
         <v>12</v>
@@ -8170,7 +8193,7 @@
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F31" s="61">
         <v>45537.449282407397</v>
@@ -8382,12 +8405,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:71" ht="15" thickBot="1">
       <c r="A32" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C32" s="5">
         <v>12</v>
@@ -8607,12 +8630,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:71">
       <c r="A33" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C33" s="3">
         <v>12</v>
@@ -8621,7 +8644,7 @@
         <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F33" s="60">
         <v>45538.412222222199</v>
@@ -8836,12 +8859,12 @@
         <v>3.8849291120924798</v>
       </c>
     </row>
-    <row r="34" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:71">
       <c r="A34" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C34">
         <v>12</v>
@@ -9062,12 +9085,12 @@
         <v>6.0395246228217703</v>
       </c>
     </row>
-    <row r="35" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:71">
       <c r="A35" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C35">
         <v>12</v>
@@ -9286,12 +9309,12 @@
         <v>9.1633763360957392</v>
       </c>
     </row>
-    <row r="36" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:71">
       <c r="A36" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C36">
         <v>12</v>
@@ -9300,7 +9323,7 @@
         <v>5</v>
       </c>
       <c r="E36" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F36" s="61">
         <v>45538.430219907401</v>
@@ -9512,12 +9535,12 @@
         <v>13.155942</v>
       </c>
     </row>
-    <row r="37" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:71">
       <c r="A37" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C37">
         <v>12</v>
@@ -9735,12 +9758,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:71" ht="15" thickBot="1">
       <c r="A38" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C38" s="5">
         <v>12</v>
@@ -9960,12 +9983,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:71">
       <c r="A39" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C39" s="3">
         <v>12</v>
@@ -10187,12 +10210,12 @@
         <v>1.5440621609410801</v>
       </c>
     </row>
-    <row r="40" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:71">
       <c r="A40" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B40" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C40">
         <v>12</v>
@@ -10413,12 +10436,12 @@
         <v>1.80037E-4</v>
       </c>
     </row>
-    <row r="41" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:71">
       <c r="A41" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C41">
         <v>12</v>
@@ -10639,12 +10662,12 @@
         <v>1.8240800000000001E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:71">
       <c r="A42" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C42">
         <v>12</v>
@@ -10862,12 +10885,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:71">
       <c r="A43" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B43" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C43">
         <v>12</v>
@@ -11083,12 +11106,12 @@
         <v>13.51721</v>
       </c>
     </row>
-    <row r="44" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:71" ht="15" thickBot="1">
       <c r="A44" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C44" s="5">
         <v>12</v>
@@ -11308,12 +11331,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:71">
       <c r="A45" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C45" s="3">
         <v>12</v>
@@ -11535,12 +11558,12 @@
         <v>5.4299359763980801</v>
       </c>
     </row>
-    <row r="46" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:71">
       <c r="A46" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B46" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C46">
         <v>12</v>
@@ -11761,12 +11784,12 @@
         <v>2.8626385291101899</v>
       </c>
     </row>
-    <row r="47" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:71">
       <c r="A47" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C47">
         <v>12</v>
@@ -11987,12 +12010,12 @@
         <v>0.346819003019956</v>
       </c>
     </row>
-    <row r="48" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:71">
       <c r="A48" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C48">
         <v>12</v>
@@ -12210,12 +12233,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:71">
       <c r="A49" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C49">
         <v>12</v>
@@ -12431,12 +12454,12 @@
         <v>8.1657297499999988</v>
       </c>
     </row>
-    <row r="50" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:71" ht="15" thickBot="1">
       <c r="A50" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C50" s="5">
         <v>12</v>
@@ -12654,12 +12677,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:71">
       <c r="A51" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C51" s="3">
         <v>12</v>
@@ -12763,7 +12786,7 @@
       <c r="AK51" s="44">
         <v>33.090000000000003</v>
       </c>
-      <c r="AL51" s="87">
+      <c r="AL51" s="68">
         <v>5.29</v>
       </c>
       <c r="AM51" s="42">
@@ -12883,12 +12906,12 @@
         <v>1.8303300000000001E-4</v>
       </c>
     </row>
-    <row r="52" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:71">
       <c r="A52" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B52" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C52">
         <v>12</v>
@@ -12992,7 +13015,7 @@
       <c r="AK52" s="44">
         <v>26.68</v>
       </c>
-      <c r="AL52" s="88">
+      <c r="AL52" s="69">
         <v>3</v>
       </c>
       <c r="AM52" s="45">
@@ -13112,12 +13135,12 @@
         <v>1.8279799999999999E-4</v>
       </c>
     </row>
-    <row r="53" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:71">
       <c r="A53" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B53" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C53">
         <v>12</v>
@@ -13221,7 +13244,7 @@
       <c r="AK53" s="44">
         <v>1.24</v>
       </c>
-      <c r="AL53" s="88">
+      <c r="AL53" s="69">
         <v>6.66</v>
       </c>
       <c r="AM53" s="45">
@@ -13341,12 +13364,12 @@
         <v>3.47222340534088</v>
       </c>
     </row>
-    <row r="54" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:71">
       <c r="A54" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B54" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C54">
         <v>12</v>
@@ -13448,7 +13471,7 @@
       <c r="AK54" s="44">
         <v>10.53</v>
       </c>
-      <c r="AL54" s="88">
+      <c r="AL54" s="69">
         <v>6.76</v>
       </c>
       <c r="AM54" s="45">
@@ -13565,12 +13588,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:71">
       <c r="A55" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B55" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C55">
         <v>12</v>
@@ -13672,7 +13695,7 @@
       <c r="AK55" s="44">
         <v>7.31</v>
       </c>
-      <c r="AL55" s="88">
+      <c r="AL55" s="69">
         <v>6.44</v>
       </c>
       <c r="AM55" s="45">
@@ -13789,12 +13812,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:71" ht="15" thickBot="1">
       <c r="A56" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C56" s="5">
         <v>12</v>
@@ -13898,7 +13921,7 @@
       <c r="AK56" s="7">
         <v>28.23</v>
       </c>
-      <c r="AL56" s="89">
+      <c r="AL56" s="70">
         <v>6.52</v>
       </c>
       <c r="AM56" s="41">
@@ -14016,12 +14039,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:71">
       <c r="A57" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C57" s="3">
         <v>12</v>
@@ -14244,12 +14267,12 @@
         <v>1.8357660000000001E-4</v>
       </c>
     </row>
-    <row r="58" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:71">
       <c r="A58" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C58">
         <v>12</v>
@@ -14471,12 +14494,12 @@
         <v>6.1121202390098297</v>
       </c>
     </row>
-    <row r="59" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:71">
       <c r="A59" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B59" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C59">
         <v>12</v>
@@ -14698,12 +14721,12 @@
         <v>7.77850641102249</v>
       </c>
     </row>
-    <row r="60" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:71">
       <c r="A60" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B60" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C60">
         <v>12</v>
@@ -14922,12 +14945,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:71">
       <c r="A61" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B61" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C61">
         <v>12</v>
@@ -15144,12 +15167,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:71" ht="15" thickBot="1">
       <c r="A62" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C62" s="5">
         <v>12</v>
@@ -15370,12 +15393,12 @@
         <v>12.5223268</v>
       </c>
     </row>
-    <row r="63" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:71">
       <c r="A63" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C63" s="3">
         <v>12</v>
@@ -15383,7 +15406,9 @@
       <c r="D63" s="3">
         <v>10</v>
       </c>
-      <c r="E63" s="3"/>
+      <c r="E63" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="F63" s="60">
         <v>45543.405208333301</v>
       </c>
@@ -15391,7 +15416,9 @@
         <v>5497.99</v>
       </c>
       <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
+      <c r="I63" s="71">
+        <v>5355.165</v>
+      </c>
       <c r="J63" s="6">
         <v>20.399999999999999</v>
       </c>
@@ -15596,12 +15623,12 @@
         <v>7.33669385349988</v>
       </c>
     </row>
-    <row r="64" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:71">
       <c r="A64" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C64">
         <v>12</v>
@@ -15609,6 +15636,9 @@
       <c r="D64">
         <v>10</v>
       </c>
+      <c r="E64" t="s">
+        <v>91</v>
+      </c>
       <c r="F64" s="61">
         <v>45543.413275462997</v>
       </c>
@@ -15616,7 +15646,9 @@
         <v>5497.99</v>
       </c>
       <c r="H64" s="44"/>
-      <c r="I64" s="44"/>
+      <c r="I64" s="72">
+        <v>5442.6</v>
+      </c>
       <c r="J64" s="44">
         <v>20.6</v>
       </c>
@@ -15821,12 +15853,12 @@
         <v>10.188405115560199</v>
       </c>
     </row>
-    <row r="65" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:71">
       <c r="A65" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C65">
         <v>12</v>
@@ -15834,6 +15866,9 @@
       <c r="D65">
         <v>10</v>
       </c>
+      <c r="E65" t="s">
+        <v>92</v>
+      </c>
       <c r="F65" s="61">
         <v>45543.423032407401</v>
       </c>
@@ -15841,7 +15876,9 @@
         <v>5497.99</v>
       </c>
       <c r="H65" s="44"/>
-      <c r="I65" s="44"/>
+      <c r="I65" s="72">
+        <v>4749.375</v>
+      </c>
       <c r="J65" s="44">
         <v>20.2</v>
       </c>
@@ -16046,12 +16083,12 @@
         <v>3.17424264055634</v>
       </c>
     </row>
-    <row r="66" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:71">
       <c r="A66" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B66" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C66">
         <v>12</v>
@@ -16059,6 +16096,9 @@
       <c r="D66">
         <v>10</v>
       </c>
+      <c r="E66" t="s">
+        <v>93</v>
+      </c>
       <c r="F66" s="61">
         <v>45543.425671296303</v>
       </c>
@@ -16066,7 +16106,9 @@
         <v>5497.99</v>
       </c>
       <c r="H66" s="44"/>
-      <c r="I66" s="44"/>
+      <c r="I66" s="72">
+        <v>4983.66</v>
+      </c>
       <c r="J66" s="44">
         <v>20.2</v>
       </c>
@@ -16156,7 +16198,7 @@
       </c>
       <c r="AM66" s="45">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>2.2755468611111111E-2</v>
       </c>
       <c r="AN66" s="44">
         <v>233.93</v>
@@ -16207,7 +16249,9 @@
       <c r="BB66" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC66" s="11"/>
+      <c r="BC66" s="11">
+        <v>1.72E-2</v>
+      </c>
       <c r="BE66" s="22"/>
       <c r="BF66" s="11">
         <f t="shared" si="17"/>
@@ -16231,11 +16275,11 @@
       </c>
       <c r="BK66" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>32.767874800000001</v>
       </c>
       <c r="BL66" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.2755468611111111E-2</v>
       </c>
       <c r="BM66" s="48" t="str">
         <f t="shared" si="31"/>
@@ -16255,23 +16299,23 @@
       </c>
       <c r="BQ66" s="28">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>59.105113275613277</v>
       </c>
       <c r="BR66" s="49">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>2.2755468611111111E-2</v>
       </c>
       <c r="BS66" s="30">
         <f t="shared" si="21"/>
         <v>8.0490855249999989</v>
       </c>
     </row>
-    <row r="67" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:71">
       <c r="A67" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C67">
         <v>12</v>
@@ -16279,6 +16323,9 @@
       <c r="D67">
         <v>10</v>
       </c>
+      <c r="E67" t="s">
+        <v>94</v>
+      </c>
       <c r="F67" s="61">
         <v>45543.428912037001</v>
       </c>
@@ -16286,7 +16333,9 @@
         <v>5497.99</v>
       </c>
       <c r="H67" s="44"/>
-      <c r="I67" s="44"/>
+      <c r="I67" s="72">
+        <v>2729.7449999999999</v>
+      </c>
       <c r="J67" s="44">
         <v>21.1</v>
       </c>
@@ -16372,7 +16421,7 @@
       </c>
       <c r="AM67" s="45">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>2.8444202777777781E-2</v>
       </c>
       <c r="AN67" s="44">
         <v>261.68</v>
@@ -16423,7 +16472,9 @@
       <c r="BB67" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC67" s="11"/>
+      <c r="BC67" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BE67" s="22"/>
       <c r="BF67" s="11">
         <f t="shared" ref="BF67:BF74" si="82">BB67*K67*BH67/1000</f>
@@ -16447,11 +16498,11 @@
       </c>
       <c r="BK67" s="47">
         <f t="shared" ref="BK67:BK74" si="84">AM67*24*60</f>
-        <v>0</v>
+        <v>40.959652000000006</v>
       </c>
       <c r="BL67" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.8444202777777781E-2</v>
       </c>
       <c r="BM67" s="48" t="str">
         <f t="shared" si="31"/>
@@ -16471,23 +16522,23 @@
       </c>
       <c r="BQ67" s="28">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>73.881046176046183</v>
       </c>
       <c r="BR67" s="49">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>2.8444202777777781E-2</v>
       </c>
       <c r="BS67" s="30">
         <f t="shared" ref="BS67:BS74" si="86">IF(BO67&lt;&gt;"",BO67,BP67)</f>
         <v>15.001472545000004</v>
       </c>
     </row>
-    <row r="68" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:71" ht="15" thickBot="1">
       <c r="A68" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C68" s="5">
         <v>12</v>
@@ -16495,7 +16546,9 @@
       <c r="D68" s="5">
         <v>10</v>
       </c>
-      <c r="E68" s="5"/>
+      <c r="E68" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="F68" s="62">
         <v>45543.4315740741</v>
       </c>
@@ -16503,7 +16556,9 @@
         <v>5497.99</v>
       </c>
       <c r="H68" s="7"/>
-      <c r="I68" s="7"/>
+      <c r="I68" s="73">
+        <v>5515.9350000000004</v>
+      </c>
       <c r="J68" s="7">
         <v>21.5</v>
       </c>
@@ -16593,7 +16648,7 @@
       </c>
       <c r="AM68" s="41">
         <f t="shared" si="79"/>
-        <v>0</v>
+        <v>1.0622002499999998E-2</v>
       </c>
       <c r="AN68" s="7">
         <v>201.93</v>
@@ -16644,7 +16699,9 @@
       <c r="BB68" s="23">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC68" s="12"/>
+      <c r="BC68" s="12">
+        <v>8.0999999999999996E-3</v>
+      </c>
       <c r="BD68" s="5"/>
       <c r="BE68" s="23"/>
       <c r="BF68" s="12">
@@ -16669,11 +16726,11 @@
       </c>
       <c r="BK68" s="14">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>15.295683599999997</v>
       </c>
       <c r="BL68" s="14">
         <f t="shared" ref="BL68:BL80" si="89">IF(B68="Python",BC68*BH68/24/60,"")</f>
-        <v>0</v>
+        <v>1.0622002499999998E-2</v>
       </c>
       <c r="BM68" s="48" t="str">
         <f t="shared" si="31"/>
@@ -16693,23 +16750,23 @@
       </c>
       <c r="BQ68" s="29">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>27.589616883116879</v>
       </c>
       <c r="BR68" s="38">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>1.0622002499999998E-2</v>
       </c>
       <c r="BS68" s="31">
         <f t="shared" si="86"/>
         <v>11.046882599999998</v>
       </c>
     </row>
-    <row r="69" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:71">
       <c r="A69" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C69" s="3">
         <v>12</v>
@@ -16717,71 +16774,140 @@
       <c r="D69" s="3">
         <v>11</v>
       </c>
-      <c r="E69" s="3"/>
-      <c r="F69" s="60"/>
+      <c r="E69" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F69" s="60">
+        <v>45544.577546296299</v>
+      </c>
       <c r="G69" s="63">
         <v>6057.48</v>
       </c>
       <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="6"/>
-      <c r="L69" s="6"/>
-      <c r="M69" s="6"/>
-      <c r="N69" s="6"/>
-      <c r="O69" s="6"/>
-      <c r="P69" s="6"/>
-      <c r="Q69" s="6"/>
+      <c r="I69" s="6">
+        <v>5674.0649999999996</v>
+      </c>
+      <c r="J69" s="6">
+        <v>22.2</v>
+      </c>
+      <c r="K69" s="6">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="L69" s="6">
+        <v>89.7</v>
+      </c>
+      <c r="M69" s="6">
+        <v>17</v>
+      </c>
+      <c r="N69" s="6">
+        <v>355</v>
+      </c>
+      <c r="O69" s="6">
+        <v>1.72</v>
+      </c>
+      <c r="P69" s="6">
+        <v>0.21</v>
+      </c>
+      <c r="Q69" s="6">
+        <v>0</v>
+      </c>
       <c r="R69" s="6"/>
-      <c r="S69" s="6"/>
-      <c r="T69" s="6"/>
-      <c r="U69" s="6"/>
-      <c r="V69" s="6"/>
-      <c r="W69" s="6"/>
-      <c r="X69" s="6"/>
-      <c r="Y69" s="6"/>
-      <c r="Z69" s="6"/>
-      <c r="AA69" s="6"/>
-      <c r="AB69" s="6"/>
-      <c r="AC69" s="6"/>
-      <c r="AD69" s="16"/>
-      <c r="AE69" s="6"/>
-      <c r="AF69" s="6"/>
-      <c r="AG69" s="6"/>
+      <c r="S69" s="6">
+        <v>0.17</v>
+      </c>
+      <c r="T69" s="6">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="U69" s="6">
+        <v>2.37</v>
+      </c>
+      <c r="V69" s="6">
+        <v>7.2590000000000003</v>
+      </c>
+      <c r="W69" s="6">
+        <v>51.3</v>
+      </c>
+      <c r="X69" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="6">
+        <v>3.44</v>
+      </c>
+      <c r="Z69" s="6">
+        <v>151.1</v>
+      </c>
+      <c r="AA69" s="6">
+        <v>22.4</v>
+      </c>
+      <c r="AB69" s="6">
+        <v>45</v>
+      </c>
+      <c r="AC69" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="16">
+        <v>7.3</v>
+      </c>
+      <c r="AE69" s="6">
+        <v>299</v>
+      </c>
+      <c r="AF69" s="6">
+        <v>40.5</v>
+      </c>
+      <c r="AG69" s="6">
+        <v>7.3</v>
+      </c>
       <c r="AH69" s="40">
         <f>AF69/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI69" s="6"/>
-      <c r="AJ69" s="6"/>
-      <c r="AK69" s="44"/>
-      <c r="AL69" s="6"/>
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="AI69" s="6">
+        <v>34</v>
+      </c>
+      <c r="AJ69" s="6">
+        <v>27.91</v>
+      </c>
+      <c r="AK69" s="44">
+        <v>47.91</v>
+      </c>
+      <c r="AL69" s="6">
+        <f>AL51+3.09</f>
+        <v>8.379999999999999</v>
+      </c>
       <c r="AM69" s="42">
         <f>BR69</f>
-        <v>0</v>
-      </c>
-      <c r="AN69" s="6"/>
-      <c r="AO69" s="6"/>
-      <c r="AP69" s="6"/>
-      <c r="AQ69" s="6"/>
+        <v>2.7214024885993001E-2</v>
+      </c>
+      <c r="AN69" s="6">
+        <v>181.29</v>
+      </c>
+      <c r="AO69" s="6">
+        <v>73.31</v>
+      </c>
+      <c r="AP69" s="6">
+        <v>485</v>
+      </c>
+      <c r="AQ69" s="6">
+        <v>1912</v>
+      </c>
       <c r="AR69" s="40">
         <v>137.11999999999989</v>
       </c>
       <c r="AS69" s="40">
-        <f t="shared" ref="AS67:AS80" si="90">AQ69-AR69</f>
-        <v>-137.11999999999989</v>
+        <f t="shared" ref="AS69:AS80" si="90">AQ69-AR69</f>
+        <v>1774.88</v>
       </c>
       <c r="AT69" s="40">
         <f t="shared" si="36"/>
-        <v>-169.89</v>
+        <v>11.400000000000006</v>
       </c>
       <c r="AU69" s="40">
         <f t="shared" si="37"/>
-        <v>-65.31</v>
+        <v>8</v>
       </c>
       <c r="AV69" s="40">
         <f t="shared" si="65"/>
-        <v>497</v>
+        <v>12</v>
       </c>
       <c r="AW69" s="24">
         <v>15</v>
@@ -16802,39 +16928,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC69" s="8"/>
-      <c r="BD69" s="9"/>
-      <c r="BE69" s="21"/>
+      <c r="BD69" s="46">
+        <f>BM69*24*60/BH69</f>
+        <v>2.1082524120846741E-2</v>
+      </c>
+      <c r="BE69" s="22">
+        <f>BP69/BH69</f>
+        <v>5.1774073553105659E-3</v>
+      </c>
       <c r="BF69" s="8">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>1.1097035999999998E-2</v>
       </c>
       <c r="BG69" s="9">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>15.979731839999996</v>
       </c>
       <c r="BH69" s="9">
         <f t="shared" si="41"/>
-        <v>1520</v>
-      </c>
-      <c r="BI69" s="10" t="str">
+        <v>1858.8</v>
+      </c>
+      <c r="BI69" s="10">
         <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ69" s="10" t="str">
+        <v>9.7530664945125883E-2</v>
+      </c>
+      <c r="BJ69" s="10">
         <f t="shared" si="88"/>
-        <v/>
+        <v>0.10664117647058823</v>
       </c>
       <c r="BK69" s="10">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>39.188195835829923</v>
       </c>
       <c r="BL69" s="10" t="str">
         <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BM69" s="10">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>2.7214024885993001E-2</v>
       </c>
       <c r="BN69" s="35" t="str">
         <f t="shared" si="85"/>
@@ -16845,28 +16976,27 @@
         <v/>
       </c>
       <c r="BP69" s="50">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>9.6237647920512792</v>
       </c>
       <c r="BQ69" s="27">
         <f>IF(BL69&lt;&gt;"",BL69/0.000385,IF(BM69&lt;&gt;"",BM69/0.000385,BN69/0.000385))</f>
-        <v>0</v>
+        <v>70.685778924657143</v>
       </c>
       <c r="BR69" s="37">
         <f>IF(BL69&lt;&gt;"",BL69,IF(BM69&lt;&gt;"",BM69,BN69))</f>
-        <v>0</v>
+        <v>2.7214024885993001E-2</v>
       </c>
       <c r="BS69" s="32">
         <f t="shared" si="86"/>
-        <v>0</v>
+        <v>9.6237647920512792</v>
       </c>
     </row>
-    <row r="70" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:71">
       <c r="A70" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C70">
         <v>12</v>
@@ -16874,70 +17004,137 @@
       <c r="D70">
         <v>11</v>
       </c>
-      <c r="F70" s="61"/>
+      <c r="F70" s="61">
+        <v>45544.6039467593</v>
+      </c>
       <c r="G70" s="64">
         <v>6057.48</v>
       </c>
       <c r="H70" s="44"/>
-      <c r="I70" s="44"/>
-      <c r="J70" s="44"/>
-      <c r="K70" s="44"/>
-      <c r="L70" s="44"/>
-      <c r="M70" s="44"/>
-      <c r="N70" s="44"/>
-      <c r="O70" s="44"/>
-      <c r="P70" s="44"/>
-      <c r="Q70" s="44"/>
+      <c r="I70" s="44">
+        <v>6019.3950000000004</v>
+      </c>
+      <c r="J70" s="44">
+        <v>18.8</v>
+      </c>
+      <c r="K70" s="44">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="L70" s="44">
+        <v>90.8</v>
+      </c>
+      <c r="M70" s="44">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="N70" s="44">
+        <v>351</v>
+      </c>
+      <c r="O70" s="44">
+        <v>2.5</v>
+      </c>
+      <c r="P70" s="44">
+        <v>0.21</v>
+      </c>
+      <c r="Q70" s="44">
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="R70" s="44"/>
-      <c r="S70" s="44"/>
-      <c r="T70" s="44"/>
-      <c r="U70" s="44"/>
-      <c r="V70" s="44"/>
-      <c r="W70" s="44"/>
-      <c r="X70" s="44"/>
-      <c r="Y70" s="44"/>
-      <c r="Z70" s="44"/>
-      <c r="AA70" s="44"/>
-      <c r="AB70" s="44"/>
-      <c r="AC70" s="44"/>
-      <c r="AD70" s="17"/>
-      <c r="AE70" s="44"/>
-      <c r="AF70" s="44"/>
-      <c r="AG70" s="44"/>
+      <c r="S70" s="44">
+        <v>0</v>
+      </c>
+      <c r="T70" s="44">
+        <v>0.16</v>
+      </c>
+      <c r="U70" s="44">
+        <v>0</v>
+      </c>
+      <c r="V70" s="44">
+        <v>7.2969999999999997</v>
+      </c>
+      <c r="W70" s="44">
+        <v>113.3</v>
+      </c>
+      <c r="X70" s="44">
+        <v>68.3</v>
+      </c>
+      <c r="Y70" s="44">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="Z70" s="44">
+        <v>155.69999999999999</v>
+      </c>
+      <c r="AA70" s="44">
+        <v>54</v>
+      </c>
+      <c r="AB70" s="44">
+        <v>99.3</v>
+      </c>
+      <c r="AC70" s="44">
+        <v>55.7</v>
+      </c>
+      <c r="AD70" s="17">
+        <v>7.34</v>
+      </c>
+      <c r="AE70" s="44">
+        <v>300</v>
+      </c>
+      <c r="AF70" s="44">
+        <v>48.3</v>
+      </c>
+      <c r="AG70" s="44">
+        <v>7.27</v>
+      </c>
       <c r="AH70" s="45">
         <f t="shared" ref="AH70:AH74" si="91">AF70/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI70" s="44"/>
-      <c r="AJ70" s="44"/>
-      <c r="AK70" s="44"/>
-      <c r="AL70" s="44"/>
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="AI70" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ70" s="44">
+        <v>24.57</v>
+      </c>
+      <c r="AK70" s="44">
+        <v>27.96</v>
+      </c>
+      <c r="AL70" s="44">
+        <f>AL52+3.01</f>
+        <v>6.01</v>
+      </c>
       <c r="AM70" s="45">
         <f t="shared" ref="AM70:AM74" si="92">BR70</f>
-        <v>0</v>
-      </c>
-      <c r="AN70" s="44"/>
-      <c r="AO70" s="44"/>
-      <c r="AP70" s="44"/>
-      <c r="AQ70" s="44"/>
+        <v>1.7809574480595398E-2</v>
+      </c>
+      <c r="AN70" s="44">
+        <v>205.53</v>
+      </c>
+      <c r="AO70" s="44">
+        <v>79.069999999999993</v>
+      </c>
+      <c r="AP70" s="44">
+        <v>458</v>
+      </c>
+      <c r="AQ70" s="44">
+        <v>1845</v>
+      </c>
       <c r="AR70" s="45">
         <v>45.769999999999982</v>
       </c>
       <c r="AS70" s="45">
         <f t="shared" si="90"/>
-        <v>-45.769999999999982</v>
+        <v>1799.23</v>
       </c>
       <c r="AT70" s="45">
         <f t="shared" si="36"/>
-        <v>-185.31</v>
+        <v>20.22</v>
       </c>
       <c r="AU70" s="45">
         <f t="shared" si="37"/>
-        <v>-68.25</v>
+        <v>10.819999999999993</v>
       </c>
       <c r="AV70" s="45">
         <f t="shared" si="65"/>
-        <v>481</v>
+        <v>23</v>
       </c>
       <c r="AW70" s="25">
         <v>15</v>
@@ -16958,39 +17155,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC70" s="11"/>
-      <c r="BD70" s="46"/>
-      <c r="BE70" s="22"/>
+      <c r="BD70" s="46">
+        <f>BM70*24*60/BH70</f>
+        <v>1.3764820277626683E-2</v>
+      </c>
+      <c r="BE70" s="22">
+        <f>BP70/BH70</f>
+        <v>4.396909262276265E-3</v>
+      </c>
       <c r="BF70" s="11">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>9.5579081999999996E-3</v>
       </c>
       <c r="BG70" s="46">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>13.763387807999999</v>
       </c>
       <c r="BH70" s="46">
         <f t="shared" si="41"/>
-        <v>1520</v>
-      </c>
-      <c r="BI70" s="47" t="str">
+        <v>1863.1399999999999</v>
+      </c>
+      <c r="BI70" s="47">
         <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ70" s="47" t="str">
+        <v>0.1103137713752053</v>
+      </c>
+      <c r="BJ70" s="47">
         <f t="shared" si="88"/>
-        <v/>
+        <v>0.12090000000000001</v>
       </c>
       <c r="BK70" s="47">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>25.645787252057374</v>
       </c>
       <c r="BL70" s="47" t="str">
         <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BM70" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.7809574480595398E-2</v>
       </c>
       <c r="BN70" s="48" t="str">
         <f t="shared" si="85"/>
@@ -17001,28 +17203,27 @@
         <v/>
       </c>
       <c r="BP70" s="51">
-        <f t="shared" ref="BP70:BP80" si="93">IF(B70="Julia",BE70*BH70,"")</f>
-        <v>0</v>
+        <v>8.1920575229174002</v>
       </c>
       <c r="BQ70" s="28">
-        <f t="shared" ref="BQ70:BQ74" si="94">IF(BL70&lt;&gt;"",BL70/0.000385,IF(BM70&lt;&gt;"",BM70/0.000385,BN70/0.000385))</f>
-        <v>0</v>
+        <f t="shared" ref="BQ70:BQ74" si="93">IF(BL70&lt;&gt;"",BL70/0.000385,IF(BM70&lt;&gt;"",BM70/0.000385,BN70/0.000385))</f>
+        <v>46.258635014533503</v>
       </c>
       <c r="BR70" s="49">
-        <f t="shared" ref="BR70:BR74" si="95">IF(BL70&lt;&gt;"",BL70,IF(BM70&lt;&gt;"",BM70,BN70))</f>
-        <v>0</v>
+        <f t="shared" ref="BR70:BR74" si="94">IF(BL70&lt;&gt;"",BL70,IF(BM70&lt;&gt;"",BM70,BN70))</f>
+        <v>1.7809574480595398E-2</v>
       </c>
       <c r="BS70" s="30">
         <f t="shared" si="86"/>
-        <v>0</v>
+        <v>8.1920575229174002</v>
       </c>
     </row>
-    <row r="71" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:71">
       <c r="A71" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B71" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C71">
         <v>12</v>
@@ -17030,70 +17231,137 @@
       <c r="D71">
         <v>11</v>
       </c>
-      <c r="F71" s="61"/>
+      <c r="F71" s="61">
+        <v>45544.5913657407</v>
+      </c>
       <c r="G71" s="64">
         <v>6057.48</v>
       </c>
       <c r="H71" s="44"/>
-      <c r="I71" s="44"/>
-      <c r="J71" s="44"/>
-      <c r="K71" s="44"/>
-      <c r="L71" s="44"/>
-      <c r="M71" s="44"/>
-      <c r="N71" s="44"/>
-      <c r="O71" s="44"/>
-      <c r="P71" s="44"/>
-      <c r="Q71" s="44"/>
+      <c r="I71" s="44">
+        <v>5282.2049999999999</v>
+      </c>
+      <c r="J71" s="44">
+        <v>19.2</v>
+      </c>
+      <c r="K71" s="44">
+        <v>16.5</v>
+      </c>
+      <c r="L71" s="44">
+        <v>86</v>
+      </c>
+      <c r="M71" s="44">
+        <v>19</v>
+      </c>
+      <c r="N71" s="44">
+        <v>446</v>
+      </c>
+      <c r="O71" s="44">
+        <v>2.98</v>
+      </c>
+      <c r="P71" s="44">
+        <v>0.2</v>
+      </c>
+      <c r="Q71" s="44">
+        <v>2.21</v>
+      </c>
       <c r="R71" s="44"/>
-      <c r="S71" s="44"/>
-      <c r="T71" s="44"/>
-      <c r="U71" s="44"/>
-      <c r="V71" s="44"/>
-      <c r="W71" s="44"/>
-      <c r="X71" s="44"/>
-      <c r="Y71" s="44"/>
-      <c r="Z71" s="44"/>
-      <c r="AA71" s="44"/>
-      <c r="AB71" s="44"/>
-      <c r="AC71" s="44"/>
-      <c r="AD71" s="17"/>
-      <c r="AE71" s="44"/>
-      <c r="AF71" s="44"/>
-      <c r="AG71" s="44"/>
+      <c r="S71" s="44">
+        <v>1</v>
+      </c>
+      <c r="T71" s="44">
+        <v>3.23</v>
+      </c>
+      <c r="U71" s="44">
+        <v>1.39</v>
+      </c>
+      <c r="V71" s="44">
+        <v>7.266</v>
+      </c>
+      <c r="W71" s="44">
+        <v>127.3</v>
+      </c>
+      <c r="X71" s="44">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="Y71" s="44">
+        <v>1.48</v>
+      </c>
+      <c r="Z71" s="44">
+        <v>178.2</v>
+      </c>
+      <c r="AA71" s="44">
+        <v>56.4</v>
+      </c>
+      <c r="AB71" s="44">
+        <v>111.7</v>
+      </c>
+      <c r="AC71" s="44">
+        <v>16.3</v>
+      </c>
+      <c r="AD71" s="17">
+        <v>7.3070000000000004</v>
+      </c>
+      <c r="AE71" s="44">
+        <v>298</v>
+      </c>
+      <c r="AF71" s="44">
+        <v>50</v>
+      </c>
+      <c r="AG71" s="44">
+        <v>7.27</v>
+      </c>
       <c r="AH71" s="45">
         <f t="shared" si="91"/>
-        <v>0</v>
-      </c>
-      <c r="AI71" s="44"/>
-      <c r="AJ71" s="44"/>
-      <c r="AK71" s="44"/>
-      <c r="AL71" s="44"/>
+        <v>0.5</v>
+      </c>
+      <c r="AI71" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ71" s="44">
+        <v>38.049999999999997</v>
+      </c>
+      <c r="AK71" s="44">
+        <v>5.17</v>
+      </c>
+      <c r="AL71" s="44">
+        <f>AL53+3.04</f>
+        <v>9.6999999999999993</v>
+      </c>
       <c r="AM71" s="45">
         <f t="shared" si="92"/>
-        <v>0</v>
-      </c>
-      <c r="AN71" s="44"/>
-      <c r="AO71" s="44"/>
-      <c r="AP71" s="44"/>
-      <c r="AQ71" s="44"/>
+        <v>3.24883333333333E-2</v>
+      </c>
+      <c r="AN71" s="44">
+        <v>287.8</v>
+      </c>
+      <c r="AO71" s="44">
+        <v>88.58</v>
+      </c>
+      <c r="AP71" s="44">
+        <v>338</v>
+      </c>
+      <c r="AQ71" s="44">
+        <v>1970</v>
+      </c>
       <c r="AR71" s="45">
         <v>84.700000000000045</v>
       </c>
       <c r="AS71" s="45">
         <f t="shared" si="90"/>
-        <v>-84.700000000000045</v>
+        <v>1885.3</v>
       </c>
       <c r="AT71" s="45">
         <f t="shared" si="36"/>
-        <v>-249.44</v>
+        <v>38.360000000000014</v>
       </c>
       <c r="AU71" s="45">
         <f t="shared" si="37"/>
-        <v>-84.76</v>
+        <v>3.8199999999999932</v>
       </c>
       <c r="AV71" s="45">
         <f t="shared" si="65"/>
-        <v>384</v>
+        <v>46</v>
       </c>
       <c r="AW71" s="25">
         <v>15</v>
@@ -17114,39 +17382,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC71" s="11"/>
-      <c r="BD71" s="46"/>
-      <c r="BE71" s="22"/>
+      <c r="BD71" s="46">
+        <f>BM71*24*60/BH71</f>
+        <v>2.3999999999999973E-2</v>
+      </c>
+      <c r="BE71" s="22">
+        <f>BP71/BH71</f>
+        <v>5.1005554585699941E-3</v>
+      </c>
       <c r="BF71" s="11">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>9.6490350000000003E-3</v>
       </c>
       <c r="BG71" s="46">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>13.894610400000001</v>
       </c>
       <c r="BH71" s="46">
         <f t="shared" si="41"/>
-        <v>1520</v>
-      </c>
-      <c r="BI71" s="47" t="str">
+        <v>1949.3000000000002</v>
+      </c>
+      <c r="BI71" s="47">
         <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ71" s="47" t="str">
+        <v>0.14764274354896628</v>
+      </c>
+      <c r="BJ71" s="47">
         <f t="shared" si="88"/>
-        <v/>
+        <v>0.16929411764705882</v>
       </c>
       <c r="BK71" s="47">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>46.783199999999951</v>
       </c>
       <c r="BL71" s="47" t="str">
         <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BM71" s="47">
-        <f t="shared" ref="BM71:BM80" si="96">IF(B71="Julia",BD71*BH71/24/60,"")</f>
-        <v>0</v>
+        <v>3.24883333333333E-2</v>
       </c>
       <c r="BN71" s="48" t="str">
         <f t="shared" si="85"/>
@@ -17157,28 +17430,27 @@
         <v/>
       </c>
       <c r="BP71" s="51">
+        <v>9.9425127553904904</v>
+      </c>
+      <c r="BQ71" s="28">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="BQ71" s="28">
+        <v>84.385281385281303</v>
+      </c>
+      <c r="BR71" s="49">
         <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="BR71" s="49">
-        <f t="shared" si="95"/>
-        <v>0</v>
+        <v>3.24883333333333E-2</v>
       </c>
       <c r="BS71" s="30">
         <f t="shared" si="86"/>
-        <v>0</v>
+        <v>9.9425127553904904</v>
       </c>
     </row>
-    <row r="72" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:71">
       <c r="A72" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B72" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C72">
         <v>12</v>
@@ -17186,70 +17458,137 @@
       <c r="D72">
         <v>11</v>
       </c>
-      <c r="F72" s="61"/>
+      <c r="F72" s="61">
+        <v>45544.610312500001</v>
+      </c>
       <c r="G72" s="64">
         <v>6057.48</v>
       </c>
       <c r="H72" s="44"/>
-      <c r="I72" s="44"/>
-      <c r="J72" s="44"/>
-      <c r="K72" s="44"/>
-      <c r="L72" s="44"/>
-      <c r="M72" s="44"/>
-      <c r="N72" s="44"/>
-      <c r="O72" s="44"/>
-      <c r="P72" s="44"/>
-      <c r="Q72" s="44"/>
+      <c r="I72" s="44">
+        <v>5403.24</v>
+      </c>
+      <c r="J72" s="44">
+        <v>19.5</v>
+      </c>
+      <c r="K72" s="44">
+        <v>17.2</v>
+      </c>
+      <c r="L72" s="44">
+        <v>88</v>
+      </c>
+      <c r="M72" s="44">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="N72" s="44">
+        <v>437</v>
+      </c>
+      <c r="O72" s="44">
+        <v>2.12</v>
+      </c>
+      <c r="P72" s="44">
+        <v>0.2</v>
+      </c>
+      <c r="Q72" s="44">
+        <v>0.77</v>
+      </c>
       <c r="R72" s="44"/>
-      <c r="S72" s="44"/>
-      <c r="T72" s="44"/>
-      <c r="U72" s="44"/>
-      <c r="V72" s="44"/>
-      <c r="W72" s="44"/>
-      <c r="X72" s="44"/>
-      <c r="Y72" s="44"/>
-      <c r="Z72" s="44"/>
-      <c r="AA72" s="44"/>
-      <c r="AB72" s="44"/>
-      <c r="AC72" s="44"/>
-      <c r="AD72" s="17"/>
-      <c r="AE72" s="44"/>
-      <c r="AF72" s="44"/>
-      <c r="AG72" s="44"/>
+      <c r="S72" s="44">
+        <v>0.83</v>
+      </c>
+      <c r="T72" s="44">
+        <v>2.97</v>
+      </c>
+      <c r="U72" s="44">
+        <v>2.21</v>
+      </c>
+      <c r="V72" s="44">
+        <v>7.2830000000000004</v>
+      </c>
+      <c r="W72" s="44">
+        <v>125.9</v>
+      </c>
+      <c r="X72" s="44">
+        <v>102.1</v>
+      </c>
+      <c r="Y72" s="44">
+        <v>1.45</v>
+      </c>
+      <c r="Z72" s="44">
+        <v>182.7</v>
+      </c>
+      <c r="AA72" s="44">
+        <v>58</v>
+      </c>
+      <c r="AB72" s="44">
+        <v>110.4</v>
+      </c>
+      <c r="AC72" s="44">
+        <v>85.6</v>
+      </c>
+      <c r="AD72" s="17">
+        <v>7.3239999999999998</v>
+      </c>
+      <c r="AE72" s="44">
+        <v>302</v>
+      </c>
+      <c r="AF72" s="44">
+        <v>100</v>
+      </c>
+      <c r="AG72" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH72" s="45">
         <f t="shared" si="91"/>
-        <v>0</v>
-      </c>
-      <c r="AI72" s="44"/>
-      <c r="AJ72" s="44"/>
-      <c r="AK72" s="44"/>
-      <c r="AL72" s="44"/>
+        <v>1</v>
+      </c>
+      <c r="AI72" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ72" s="44">
+        <v>43.09</v>
+      </c>
+      <c r="AK72" s="44">
+        <v>17.54</v>
+      </c>
+      <c r="AL72" s="44">
+        <f>AL54+3.1</f>
+        <v>9.86</v>
+      </c>
       <c r="AM72" s="45">
         <f t="shared" si="92"/>
-        <v>0</v>
-      </c>
-      <c r="AN72" s="44"/>
-      <c r="AO72" s="44"/>
-      <c r="AP72" s="44"/>
-      <c r="AQ72" s="44"/>
+        <v>2.3211041666666668E-2</v>
+      </c>
+      <c r="AN72" s="44">
+        <v>273.05</v>
+      </c>
+      <c r="AO72" s="44">
+        <v>79.709999999999994</v>
+      </c>
+      <c r="AP72" s="44">
+        <v>362</v>
+      </c>
+      <c r="AQ72" s="44">
+        <v>1953</v>
+      </c>
       <c r="AR72" s="45">
         <v>47.420000000000073</v>
       </c>
       <c r="AS72" s="45">
         <f t="shared" si="90"/>
-        <v>-47.420000000000073</v>
+        <v>1905.58</v>
       </c>
       <c r="AT72" s="45">
         <f t="shared" si="36"/>
-        <v>-233.93</v>
+        <v>39.120000000000005</v>
       </c>
       <c r="AU72" s="45">
         <f t="shared" si="37"/>
-        <v>-70.87</v>
+        <v>8.8399999999999892</v>
       </c>
       <c r="AV72" s="45">
         <f t="shared" si="65"/>
-        <v>406</v>
+        <v>44</v>
       </c>
       <c r="AW72" s="25">
         <v>15</v>
@@ -17269,38 +17608,40 @@
       <c r="BB72" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC72" s="11"/>
+      <c r="BC72" s="11">
+        <v>1.72E-2</v>
+      </c>
       <c r="BE72" s="22"/>
       <c r="BF72" s="11">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>1.002717E-2</v>
       </c>
       <c r="BG72" s="46">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>14.4391248</v>
       </c>
       <c r="BH72" s="46">
-        <f t="shared" ref="BH72:BH80" si="97">AX72+SUM(AJ72:AL72,AN72:AO72)-(AW72*(D72+1))</f>
-        <v>1520</v>
-      </c>
-      <c r="BI72" s="47" t="str">
+        <f t="shared" ref="BH72:BH80" si="95">AX72+SUM(AJ72:AL72,AN72:AO72)-(AW72*(D72+1))</f>
+        <v>1943.25</v>
+      </c>
+      <c r="BI72" s="47">
         <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ72" s="47" t="str">
+        <v>0.14051202881770231</v>
+      </c>
+      <c r="BJ72" s="47">
         <f t="shared" si="88"/>
-        <v/>
+        <v>0.16061764705882353</v>
       </c>
       <c r="BK72" s="47">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>33.423900000000003</v>
       </c>
       <c r="BL72" s="47">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>2.3211041666666668E-2</v>
       </c>
       <c r="BM72" s="48" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" ref="BM72:BM80" si="96">IF(B72="Julia",BD72*BH72/24/60,"")</f>
         <v/>
       </c>
       <c r="BN72" s="48" t="str">
@@ -17309,31 +17650,31 @@
       </c>
       <c r="BO72" s="47">
         <f t="shared" si="47"/>
-        <v>11.4</v>
+        <v>10.833618750000001</v>
       </c>
       <c r="BP72" s="51" t="str">
+        <f t="shared" ref="BP72:BP80" si="97">IF(B72="Julia",BE72*BH72,"")</f>
+        <v/>
+      </c>
+      <c r="BQ72" s="28">
         <f t="shared" si="93"/>
-        <v/>
-      </c>
-      <c r="BQ72" s="28">
+        <v>60.288419913419922</v>
+      </c>
+      <c r="BR72" s="49">
         <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="BR72" s="49">
-        <f t="shared" si="95"/>
-        <v>0</v>
+        <v>2.3211041666666668E-2</v>
       </c>
       <c r="BS72" s="30">
         <f t="shared" si="86"/>
-        <v>11.4</v>
+        <v>10.833618750000001</v>
       </c>
     </row>
-    <row r="73" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:71">
       <c r="A73" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C73">
         <v>12</v>
@@ -17341,70 +17682,136 @@
       <c r="D73">
         <v>11</v>
       </c>
-      <c r="F73" s="61"/>
+      <c r="E73" t="s">
+        <v>97</v>
+      </c>
+      <c r="F73" s="61">
+        <v>45544.616192129601</v>
+      </c>
       <c r="G73" s="64">
         <v>6057.48</v>
       </c>
       <c r="H73" s="44"/>
-      <c r="I73" s="44"/>
-      <c r="J73" s="44"/>
-      <c r="K73" s="44"/>
-      <c r="L73" s="44"/>
-      <c r="M73" s="44"/>
-      <c r="N73" s="44"/>
+      <c r="I73" s="44">
+        <v>2556.4050000000002</v>
+      </c>
+      <c r="J73" s="44">
+        <v>20.2</v>
+      </c>
+      <c r="K73" s="44">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="L73" s="44">
+        <v>2.71</v>
+      </c>
+      <c r="M73" s="44">
+        <v>13.7</v>
+      </c>
+      <c r="N73" s="44">
+        <v>869</v>
+      </c>
       <c r="O73" s="44"/>
-      <c r="P73" s="44"/>
-      <c r="Q73" s="44"/>
+      <c r="P73" s="44">
+        <v>0.23</v>
+      </c>
+      <c r="Q73" s="44">
+        <v>6.87</v>
+      </c>
       <c r="R73" s="44"/>
-      <c r="S73" s="44"/>
-      <c r="T73" s="44"/>
+      <c r="S73" s="44">
+        <v>0.97</v>
+      </c>
+      <c r="T73" s="44">
+        <v>4.58</v>
+      </c>
       <c r="U73" s="44"/>
-      <c r="V73" s="44"/>
-      <c r="W73" s="44"/>
-      <c r="X73" s="44"/>
-      <c r="Y73" s="44"/>
-      <c r="Z73" s="44"/>
-      <c r="AA73" s="44"/>
-      <c r="AB73" s="44"/>
-      <c r="AC73" s="44"/>
-      <c r="AD73" s="17"/>
-      <c r="AE73" s="44"/>
-      <c r="AF73" s="44"/>
-      <c r="AG73" s="44"/>
+      <c r="V73" s="44">
+        <v>7.2770000000000001</v>
+      </c>
+      <c r="W73" s="44">
+        <v>5.8</v>
+      </c>
+      <c r="X73" s="44">
+        <v>95.2</v>
+      </c>
+      <c r="Y73" s="44">
+        <v>7.36</v>
+      </c>
+      <c r="Z73" s="44">
+        <v>318.8</v>
+      </c>
+      <c r="AA73" s="44">
+        <v>2.6</v>
+      </c>
+      <c r="AB73" s="44">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AC73" s="44">
+        <v>79.2</v>
+      </c>
+      <c r="AD73" s="17">
+        <v>7.3179999999999996</v>
+      </c>
+      <c r="AE73" s="44">
+        <v>299</v>
+      </c>
+      <c r="AF73" s="44">
+        <v>52.4</v>
+      </c>
+      <c r="AG73" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH73" s="45">
         <f t="shared" si="91"/>
-        <v>0</v>
-      </c>
-      <c r="AI73" s="44"/>
-      <c r="AJ73" s="44"/>
-      <c r="AK73" s="44"/>
-      <c r="AL73" s="44"/>
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="AI73" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ73" s="44">
+        <v>150</v>
+      </c>
+      <c r="AK73" s="44">
+        <v>9.64</v>
+      </c>
+      <c r="AL73" s="44">
+        <f>AL55+2.98</f>
+        <v>9.42</v>
+      </c>
       <c r="AM73" s="45">
         <f t="shared" si="92"/>
-        <v>0</v>
-      </c>
-      <c r="AN73" s="44"/>
-      <c r="AO73" s="44"/>
-      <c r="AP73" s="44"/>
-      <c r="AQ73" s="44"/>
+        <v>2.9077638888888889E-2</v>
+      </c>
+      <c r="AN73" s="44">
+        <v>310.07</v>
+      </c>
+      <c r="AO73" s="44">
+        <v>94.46</v>
+      </c>
+      <c r="AP73" s="44">
+        <v>295</v>
+      </c>
+      <c r="AQ73" s="44">
+        <v>2159</v>
+      </c>
       <c r="AR73" s="45">
         <v>133.55999999999995</v>
       </c>
       <c r="AS73" s="45">
         <f t="shared" si="90"/>
-        <v>-133.55999999999995</v>
+        <v>2025.44</v>
       </c>
       <c r="AT73" s="45">
         <f t="shared" si="36"/>
-        <v>-261.68</v>
+        <v>48.389999999999986</v>
       </c>
       <c r="AU73" s="45">
         <f t="shared" si="37"/>
-        <v>-77.819999999999993</v>
+        <v>16.64</v>
       </c>
       <c r="AV73" s="45">
         <f t="shared" ref="AV73:AV80" si="98">AP67-AP73</f>
-        <v>353</v>
+        <v>58</v>
       </c>
       <c r="AW73" s="25">
         <v>15</v>
@@ -17424,35 +17831,37 @@
       <c r="BB73" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC73" s="11"/>
+      <c r="BC73" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BE73" s="22"/>
       <c r="BF73" s="11">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>3.4355811900000006E-4</v>
       </c>
       <c r="BG73" s="46">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>0.49472369136000011</v>
       </c>
       <c r="BH73" s="46">
-        <f t="shared" si="97"/>
-        <v>1520</v>
-      </c>
-      <c r="BI73" s="47" t="str">
+        <f t="shared" si="95"/>
+        <v>2093.59</v>
+      </c>
+      <c r="BI73" s="47">
         <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ73" s="47" t="str">
+        <v>0.14810445216112036</v>
+      </c>
+      <c r="BJ73" s="47">
         <f t="shared" si="88"/>
-        <v/>
+        <v>0.18239411764705882</v>
       </c>
       <c r="BK73" s="47">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>41.871799999999993</v>
       </c>
       <c r="BL73" s="47">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>2.9077638888888889E-2</v>
       </c>
       <c r="BM73" s="48" t="str">
         <f t="shared" si="96"/>
@@ -17464,31 +17873,31 @@
       </c>
       <c r="BO73" s="47">
         <f t="shared" si="47"/>
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="BP73" s="51" t="str">
+        <f t="shared" si="97"/>
+        <v/>
+      </c>
+      <c r="BQ73" s="28">
         <f t="shared" si="93"/>
-        <v/>
-      </c>
-      <c r="BQ73" s="28">
+        <v>75.526334776334778</v>
+      </c>
+      <c r="BR73" s="49">
         <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="BR73" s="49">
-        <f t="shared" si="95"/>
-        <v>0</v>
+        <v>2.9077638888888889E-2</v>
       </c>
       <c r="BS73" s="30">
         <f t="shared" si="86"/>
-        <v>11.4</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:71" ht="15" thickBot="1">
       <c r="A74" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C74" s="5">
         <v>12</v>
@@ -17497,70 +17906,137 @@
         <v>11</v>
       </c>
       <c r="E74" s="5"/>
-      <c r="F74" s="62"/>
+      <c r="F74" s="62">
+        <v>45544.621018518519</v>
+      </c>
       <c r="G74" s="65">
         <v>6057.48</v>
       </c>
       <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
-      <c r="P74" s="7"/>
-      <c r="Q74" s="7"/>
+      <c r="I74" s="7">
+        <v>6130.83</v>
+      </c>
+      <c r="J74" s="7">
+        <v>19.8</v>
+      </c>
+      <c r="K74" s="7">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="L74" s="7">
+        <v>90.2</v>
+      </c>
+      <c r="M74" s="7">
+        <v>17.8</v>
+      </c>
+      <c r="N74" s="7">
+        <v>359</v>
+      </c>
+      <c r="O74" s="7">
+        <v>1.91</v>
+      </c>
+      <c r="P74" s="7">
+        <v>0.18</v>
+      </c>
+      <c r="Q74" s="7">
+        <v>0.4</v>
+      </c>
       <c r="R74" s="7"/>
-      <c r="S74" s="7"/>
-      <c r="T74" s="7"/>
-      <c r="U74" s="7"/>
-      <c r="V74" s="7"/>
-      <c r="W74" s="7"/>
-      <c r="X74" s="7"/>
-      <c r="Y74" s="7"/>
-      <c r="Z74" s="7"/>
-      <c r="AA74" s="7"/>
-      <c r="AB74" s="7"/>
-      <c r="AC74" s="7"/>
-      <c r="AD74" s="18"/>
-      <c r="AE74" s="7"/>
-      <c r="AF74" s="7"/>
-      <c r="AG74" s="7"/>
+      <c r="S74" s="7">
+        <v>0.09</v>
+      </c>
+      <c r="T74" s="7">
+        <v>0.13</v>
+      </c>
+      <c r="U74" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="V74" s="7">
+        <v>7.2969999999999997</v>
+      </c>
+      <c r="W74" s="7">
+        <v>117.9</v>
+      </c>
+      <c r="X74" s="7">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="Y74" s="7">
+        <v>1.92</v>
+      </c>
+      <c r="Z74" s="7">
+        <v>159.1</v>
+      </c>
+      <c r="AA74" s="7">
+        <v>56.2</v>
+      </c>
+      <c r="AB74" s="7">
+        <v>103.4</v>
+      </c>
+      <c r="AC74" s="7">
+        <v>32.9</v>
+      </c>
+      <c r="AD74" s="18">
+        <v>7.3390000000000004</v>
+      </c>
+      <c r="AE74" s="7">
+        <v>298</v>
+      </c>
+      <c r="AF74" s="7">
+        <v>49.9</v>
+      </c>
+      <c r="AG74" s="7">
+        <v>7.29</v>
+      </c>
       <c r="AH74" s="41">
         <f t="shared" si="91"/>
-        <v>0</v>
-      </c>
-      <c r="AI74" s="7"/>
-      <c r="AJ74" s="7"/>
-      <c r="AK74" s="7"/>
-      <c r="AL74" s="7"/>
+        <v>0.499</v>
+      </c>
+      <c r="AI74" s="7">
+        <v>34</v>
+      </c>
+      <c r="AJ74" s="7">
+        <v>28.27</v>
+      </c>
+      <c r="AK74" s="7">
+        <v>45.05</v>
+      </c>
+      <c r="AL74" s="7">
+        <f>AL56+3.03</f>
+        <v>9.5499999999999989</v>
+      </c>
       <c r="AM74" s="41">
         <f t="shared" si="92"/>
-        <v>0</v>
-      </c>
-      <c r="AN74" s="7"/>
-      <c r="AO74" s="7"/>
-      <c r="AP74" s="7"/>
-      <c r="AQ74" s="7"/>
+        <v>1.07172E-2</v>
+      </c>
+      <c r="AN74" s="7">
+        <v>220.19</v>
+      </c>
+      <c r="AO74" s="7">
+        <v>82.22</v>
+      </c>
+      <c r="AP74" s="7">
+        <v>438</v>
+      </c>
+      <c r="AQ74" s="7">
+        <v>1899</v>
+      </c>
       <c r="AR74" s="41">
         <v>51.660000000000082</v>
       </c>
       <c r="AS74" s="41">
         <f t="shared" si="90"/>
-        <v>-51.660000000000082</v>
+        <v>1847.34</v>
       </c>
       <c r="AT74" s="41">
         <f t="shared" ref="AT74:AT80" si="99">AN74-AN68</f>
-        <v>-201.93</v>
+        <v>18.259999999999991</v>
       </c>
       <c r="AU74" s="41">
         <f t="shared" ref="AU74:AU80" si="100">AO74-AO68</f>
-        <v>-69.75</v>
+        <v>12.469999999999999</v>
       </c>
       <c r="AV74" s="41">
         <f t="shared" si="98"/>
-        <v>460</v>
+        <v>22</v>
       </c>
       <c r="AW74" s="26">
         <v>15</v>
@@ -17580,36 +18056,38 @@
       <c r="BB74" s="23">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC74" s="12"/>
+      <c r="BC74" s="12">
+        <v>8.0999999999999996E-3</v>
+      </c>
       <c r="BD74" s="5"/>
       <c r="BE74" s="23"/>
       <c r="BF74" s="12">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>1.0231353599999996E-2</v>
       </c>
       <c r="BG74" s="13">
         <f t="shared" si="83"/>
-        <v>0</v>
+        <v>14.733149183999995</v>
       </c>
       <c r="BH74" s="13">
-        <f t="shared" si="97"/>
-        <v>1520</v>
-      </c>
-      <c r="BI74" s="14" t="str">
+        <f t="shared" si="95"/>
+        <v>1905.2799999999997</v>
+      </c>
+      <c r="BI74" s="14">
         <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ74" s="14" t="str">
+        <v>0.11556831541820627</v>
+      </c>
+      <c r="BJ74" s="14">
         <f t="shared" si="88"/>
-        <v/>
+        <v>0.1295235294117647</v>
       </c>
       <c r="BK74" s="14">
         <f t="shared" si="84"/>
-        <v>0</v>
+        <v>15.432768000000001</v>
       </c>
       <c r="BL74" s="14">
         <f t="shared" si="89"/>
-        <v>0</v>
+        <v>1.07172E-2</v>
       </c>
       <c r="BM74" s="48" t="str">
         <f t="shared" si="96"/>
@@ -17621,31 +18099,31 @@
       </c>
       <c r="BO74" s="14">
         <f t="shared" si="47"/>
-        <v>11.4</v>
+        <v>12.384319999999997</v>
       </c>
       <c r="BP74" s="52" t="str">
+        <f t="shared" si="97"/>
+        <v/>
+      </c>
+      <c r="BQ74" s="29">
         <f t="shared" si="93"/>
-        <v/>
-      </c>
-      <c r="BQ74" s="29">
+        <v>27.836883116883119</v>
+      </c>
+      <c r="BR74" s="38">
         <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="BR74" s="38">
-        <f t="shared" si="95"/>
-        <v>0</v>
+        <v>1.07172E-2</v>
       </c>
       <c r="BS74" s="31">
         <f t="shared" si="86"/>
-        <v>11.4</v>
+        <v>12.384319999999997</v>
       </c>
     </row>
-    <row r="75" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:71">
       <c r="A75" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C75" s="3">
         <v>12</v>
@@ -17654,70 +18132,137 @@
         <v>12</v>
       </c>
       <c r="E75" s="3"/>
-      <c r="F75" s="60"/>
+      <c r="F75" s="60">
+        <v>45545.392534722203</v>
+      </c>
       <c r="G75" s="63">
         <v>6478.05</v>
       </c>
       <c r="H75" s="6"/>
-      <c r="I75" s="6"/>
-      <c r="J75" s="6"/>
-      <c r="K75" s="6"/>
-      <c r="L75" s="6"/>
-      <c r="M75" s="6"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="6"/>
-      <c r="Q75" s="6"/>
+      <c r="I75" s="6">
+        <v>6054.6149999999998</v>
+      </c>
+      <c r="J75" s="6">
+        <v>20.3</v>
+      </c>
+      <c r="K75" s="6">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="L75" s="6">
+        <v>81.8</v>
+      </c>
+      <c r="M75" s="6">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="N75" s="6">
+        <v>376</v>
+      </c>
+      <c r="O75" s="6">
+        <v>1.22</v>
+      </c>
+      <c r="P75" s="6">
+        <v>0.24</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>3.54</v>
+      </c>
       <c r="R75" s="6"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="6"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="6"/>
-      <c r="AB75" s="6"/>
-      <c r="AC75" s="6"/>
-      <c r="AD75" s="16"/>
-      <c r="AE75" s="6"/>
-      <c r="AF75" s="6"/>
-      <c r="AG75" s="6"/>
+      <c r="S75" s="6">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0.36</v>
+      </c>
+      <c r="U75" s="6">
+        <v>0.96</v>
+      </c>
+      <c r="V75" s="6">
+        <v>7.1950000000000003</v>
+      </c>
+      <c r="W75" s="6">
+        <v>101.7</v>
+      </c>
+      <c r="X75" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="6">
+        <v>1.95</v>
+      </c>
+      <c r="Z75" s="6">
+        <v>152.6</v>
+      </c>
+      <c r="AA75" s="6">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="AB75" s="6">
+        <v>89.2</v>
+      </c>
+      <c r="AC75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="16">
+        <v>7.2350000000000003</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>299</v>
+      </c>
+      <c r="AF75" s="6">
+        <v>52.3</v>
+      </c>
+      <c r="AG75" s="6">
+        <v>7.21</v>
+      </c>
       <c r="AH75" s="40">
         <f>AF75/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI75" s="6"/>
-      <c r="AJ75" s="6"/>
-      <c r="AK75" s="44"/>
-      <c r="AL75" s="6"/>
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="AI75" s="6">
+        <v>34</v>
+      </c>
+      <c r="AJ75" s="6">
+        <v>27.91</v>
+      </c>
+      <c r="AK75" s="44">
+        <v>48.36</v>
+      </c>
+      <c r="AL75" s="6">
+        <f>AL51+3.79</f>
+        <v>9.08</v>
+      </c>
       <c r="AM75" s="42">
         <f>BR75</f>
         <v>0</v>
       </c>
-      <c r="AN75" s="6"/>
-      <c r="AO75" s="6"/>
-      <c r="AP75" s="6"/>
-      <c r="AQ75" s="6"/>
+      <c r="AN75" s="6">
+        <v>210.09</v>
+      </c>
+      <c r="AO75" s="6">
+        <v>83.64</v>
+      </c>
+      <c r="AP75" s="6">
+        <v>452</v>
+      </c>
+      <c r="AQ75" s="6">
+        <v>1877</v>
+      </c>
       <c r="AR75" s="40">
         <v>137.11999999999989</v>
       </c>
       <c r="AS75" s="40">
         <f t="shared" si="90"/>
-        <v>-137.11999999999989</v>
+        <v>1739.88</v>
       </c>
       <c r="AT75" s="40">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>28.800000000000011</v>
       </c>
       <c r="AU75" s="40">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>10.329999999999998</v>
       </c>
       <c r="AV75" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AW75" s="24">
         <v>15</v>
@@ -17742,23 +18287,23 @@
       <c r="BE75" s="21"/>
       <c r="BF75" s="8">
         <f t="shared" ref="BF75:BF80" si="101">BB75*K75*BH75/1000</f>
-        <v>0</v>
+        <v>9.3827184000000001E-3</v>
       </c>
       <c r="BG75" s="9">
         <f t="shared" ref="BG75:BG80" si="102">BF75*24*60</f>
-        <v>0</v>
+        <v>13.511114495999999</v>
       </c>
       <c r="BH75" s="9">
-        <f t="shared" si="97"/>
-        <v>1505</v>
-      </c>
-      <c r="BI75" s="10" t="str">
+        <f t="shared" si="95"/>
+        <v>1884.08</v>
+      </c>
+      <c r="BI75" s="10">
         <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ75" s="10" t="str">
+        <v>0.11150800390641587</v>
+      </c>
+      <c r="BJ75" s="10">
         <f t="shared" si="88"/>
-        <v/>
+        <v>0.12358235294117648</v>
       </c>
       <c r="BK75" s="10">
         <f t="shared" ref="BK75:BK80" si="103">AM75*24*60</f>
@@ -17781,7 +18326,7 @@
         <v/>
       </c>
       <c r="BP75" s="50">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="BQ75" s="27">
@@ -17797,12 +18342,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:71">
       <c r="A76" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B76" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C76">
         <v>12</v>
@@ -17810,70 +18355,137 @@
       <c r="D76">
         <v>12</v>
       </c>
-      <c r="F76" s="61"/>
+      <c r="F76" s="61">
+        <v>45545.396412037</v>
+      </c>
       <c r="G76" s="64">
         <v>6478.05</v>
       </c>
       <c r="H76" s="44"/>
-      <c r="I76" s="44"/>
-      <c r="J76" s="44"/>
-      <c r="K76" s="44"/>
-      <c r="L76" s="44"/>
-      <c r="M76" s="44"/>
-      <c r="N76" s="44"/>
-      <c r="O76" s="44"/>
-      <c r="P76" s="44"/>
-      <c r="Q76" s="44"/>
+      <c r="I76" s="44">
+        <v>6468.72</v>
+      </c>
+      <c r="J76" s="44">
+        <v>19.5</v>
+      </c>
+      <c r="K76" s="44">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="L76" s="44">
+        <v>90.4</v>
+      </c>
+      <c r="M76" s="44">
+        <v>18</v>
+      </c>
+      <c r="N76" s="44">
+        <v>359</v>
+      </c>
+      <c r="O76" s="44">
+        <v>2.39</v>
+      </c>
+      <c r="P76" s="44">
+        <v>0.22</v>
+      </c>
+      <c r="Q76" s="44">
+        <v>0.83</v>
+      </c>
       <c r="R76" s="44"/>
-      <c r="S76" s="44"/>
-      <c r="T76" s="44"/>
-      <c r="U76" s="44"/>
-      <c r="V76" s="44"/>
-      <c r="W76" s="44"/>
-      <c r="X76" s="44"/>
-      <c r="Y76" s="44"/>
-      <c r="Z76" s="44"/>
-      <c r="AA76" s="44"/>
-      <c r="AB76" s="44"/>
-      <c r="AC76" s="44"/>
-      <c r="AD76" s="17"/>
-      <c r="AE76" s="44"/>
-      <c r="AF76" s="44"/>
-      <c r="AG76" s="44"/>
+      <c r="S76" s="44">
+        <v>0.11</v>
+      </c>
+      <c r="T76" s="44">
+        <v>0.13</v>
+      </c>
+      <c r="U76" s="44">
+        <v>0.16</v>
+      </c>
+      <c r="V76" s="44">
+        <v>7.1790000000000003</v>
+      </c>
+      <c r="W76" s="44">
+        <v>125.2</v>
+      </c>
+      <c r="X76" s="44">
+        <v>40.6</v>
+      </c>
+      <c r="Y76" s="44">
+        <v>1.65</v>
+      </c>
+      <c r="Z76" s="44">
+        <v>154.1</v>
+      </c>
+      <c r="AA76" s="44">
+        <v>45.2</v>
+      </c>
+      <c r="AB76" s="44">
+        <v>109.8</v>
+      </c>
+      <c r="AC76" s="44">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="AD76" s="17">
+        <v>7.2190000000000003</v>
+      </c>
+      <c r="AE76" s="44">
+        <v>301</v>
+      </c>
+      <c r="AF76" s="44">
+        <v>50.2</v>
+      </c>
+      <c r="AG76" s="44">
+        <v>7.23</v>
+      </c>
       <c r="AH76" s="45">
         <f t="shared" ref="AH76:AH80" si="106">AF76/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI76" s="44"/>
-      <c r="AJ76" s="44"/>
-      <c r="AK76" s="44"/>
-      <c r="AL76" s="44"/>
+        <v>0.502</v>
+      </c>
+      <c r="AI76" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ76" s="44">
+        <v>24.57</v>
+      </c>
+      <c r="AK76" s="44">
+        <v>28.85</v>
+      </c>
+      <c r="AL76" s="44">
+        <f>AL52+3.7</f>
+        <v>6.7</v>
+      </c>
       <c r="AM76" s="45">
         <f t="shared" ref="AM76:AM80" si="107">BR76</f>
         <v>0</v>
       </c>
-      <c r="AN76" s="44"/>
-      <c r="AO76" s="44"/>
-      <c r="AP76" s="44"/>
-      <c r="AQ76" s="44"/>
+      <c r="AN76" s="44">
+        <v>225.39</v>
+      </c>
+      <c r="AO76" s="44">
+        <v>87.89</v>
+      </c>
+      <c r="AP76" s="44">
+        <v>435</v>
+      </c>
+      <c r="AQ76" s="44">
+        <v>1785</v>
+      </c>
       <c r="AR76" s="45">
         <v>45.769999999999982</v>
       </c>
       <c r="AS76" s="45">
         <f t="shared" si="90"/>
-        <v>-45.769999999999982</v>
+        <v>1739.23</v>
       </c>
       <c r="AT76" s="45">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>19.859999999999985</v>
       </c>
       <c r="AU76" s="45">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>8.8200000000000074</v>
       </c>
       <c r="AV76" s="45">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AW76" s="25">
         <v>15</v>
@@ -17898,23 +18510,23 @@
       <c r="BE76" s="22"/>
       <c r="BF76" s="11">
         <f t="shared" si="101"/>
-        <v>0</v>
+        <v>9.917951999999999E-3</v>
       </c>
       <c r="BG76" s="46">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>14.281850879999997</v>
       </c>
       <c r="BH76" s="46">
-        <f t="shared" si="97"/>
-        <v>1505</v>
-      </c>
-      <c r="BI76" s="47" t="str">
+        <f t="shared" si="95"/>
+        <v>1878.4</v>
+      </c>
+      <c r="BI76" s="47">
         <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ76" s="47" t="str">
+        <v>0.11999041737649062</v>
+      </c>
+      <c r="BJ76" s="47">
         <f t="shared" si="88"/>
-        <v/>
+        <v>0.13258235294117646</v>
       </c>
       <c r="BK76" s="47">
         <f t="shared" si="103"/>
@@ -17937,7 +18549,7 @@
         <v/>
       </c>
       <c r="BP76" s="51">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="BQ76" s="28">
@@ -17953,12 +18565,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:71">
       <c r="A77" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B77" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C77">
         <v>12</v>
@@ -17966,70 +18578,137 @@
       <c r="D77">
         <v>12</v>
       </c>
-      <c r="F77" s="61"/>
+      <c r="F77" s="61">
+        <v>45545.400358796302</v>
+      </c>
       <c r="G77" s="64">
         <v>6478.05</v>
       </c>
       <c r="H77" s="44"/>
-      <c r="I77" s="44"/>
-      <c r="J77" s="44"/>
-      <c r="K77" s="44"/>
-      <c r="L77" s="44"/>
-      <c r="M77" s="44"/>
-      <c r="N77" s="44"/>
-      <c r="O77" s="44"/>
-      <c r="P77" s="44"/>
-      <c r="Q77" s="44"/>
+      <c r="I77" s="44">
+        <v>5555.64</v>
+      </c>
+      <c r="J77" s="44">
+        <v>18.5</v>
+      </c>
+      <c r="K77" s="44">
+        <v>15.5</v>
+      </c>
+      <c r="L77" s="44">
+        <v>83.8</v>
+      </c>
+      <c r="M77" s="44">
+        <v>18.8</v>
+      </c>
+      <c r="N77" s="44">
+        <v>463</v>
+      </c>
+      <c r="O77" s="44">
+        <v>3.89</v>
+      </c>
+      <c r="P77" s="44">
+        <v>0.22</v>
+      </c>
+      <c r="Q77" s="44">
+        <v>3.86</v>
+      </c>
       <c r="R77" s="44"/>
-      <c r="S77" s="44"/>
-      <c r="T77" s="44"/>
-      <c r="U77" s="44"/>
-      <c r="V77" s="44"/>
-      <c r="W77" s="44"/>
-      <c r="X77" s="44"/>
-      <c r="Y77" s="44"/>
-      <c r="Z77" s="44"/>
-      <c r="AA77" s="44"/>
-      <c r="AB77" s="44"/>
-      <c r="AC77" s="44"/>
-      <c r="AD77" s="17"/>
-      <c r="AE77" s="44"/>
-      <c r="AF77" s="44"/>
-      <c r="AG77" s="44"/>
+      <c r="S77" s="44">
+        <v>1.3</v>
+      </c>
+      <c r="T77" s="44">
+        <v>4.2</v>
+      </c>
+      <c r="U77" s="44">
+        <v>1.34</v>
+      </c>
+      <c r="V77" s="44">
+        <v>7.2329999999999997</v>
+      </c>
+      <c r="W77" s="44">
+        <v>116.5</v>
+      </c>
+      <c r="X77" s="44">
+        <v>21.9</v>
+      </c>
+      <c r="Y77" s="44">
+        <v>1.24</v>
+      </c>
+      <c r="Z77" s="44">
+        <v>178.2</v>
+      </c>
+      <c r="AA77" s="44">
+        <v>47.8</v>
+      </c>
+      <c r="AB77" s="44">
+        <v>102.2</v>
+      </c>
+      <c r="AC77" s="44">
+        <v>17.7</v>
+      </c>
+      <c r="AD77" s="17">
+        <v>7.274</v>
+      </c>
+      <c r="AE77" s="44">
+        <v>300</v>
+      </c>
+      <c r="AF77" s="44">
+        <v>50.7</v>
+      </c>
+      <c r="AG77" s="44">
+        <v>7.25</v>
+      </c>
       <c r="AH77" s="45">
         <f t="shared" si="106"/>
-        <v>0</v>
-      </c>
-      <c r="AI77" s="44"/>
-      <c r="AJ77" s="44"/>
-      <c r="AK77" s="44"/>
-      <c r="AL77" s="44"/>
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="AI77" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ77" s="44">
+        <v>38.049999999999997</v>
+      </c>
+      <c r="AK77" s="44">
+        <v>5.17</v>
+      </c>
+      <c r="AL77" s="44">
+        <f>AL53+3.75</f>
+        <v>10.41</v>
+      </c>
       <c r="AM77" s="45">
         <f t="shared" si="107"/>
         <v>0</v>
       </c>
-      <c r="AN77" s="44"/>
-      <c r="AO77" s="44"/>
-      <c r="AP77" s="44"/>
-      <c r="AQ77" s="44"/>
+      <c r="AN77" s="44">
+        <v>324.02</v>
+      </c>
+      <c r="AO77" s="44">
+        <v>99.25</v>
+      </c>
+      <c r="AP77" s="44">
+        <v>295</v>
+      </c>
+      <c r="AQ77" s="44">
+        <v>1948</v>
+      </c>
       <c r="AR77" s="45">
         <v>84.700000000000045</v>
       </c>
       <c r="AS77" s="45">
         <f t="shared" si="90"/>
-        <v>-84.700000000000045</v>
+        <v>1863.3</v>
       </c>
       <c r="AT77" s="45">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>36.21999999999997</v>
       </c>
       <c r="AU77" s="45">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>10.670000000000002</v>
       </c>
       <c r="AV77" s="45">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AW77" s="25">
         <v>15</v>
@@ -18054,23 +18733,23 @@
       <c r="BE77" s="22"/>
       <c r="BF77" s="11">
         <f t="shared" si="101"/>
-        <v>0</v>
+        <v>9.2158350000000003E-3</v>
       </c>
       <c r="BG77" s="46">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>13.270802400000001</v>
       </c>
       <c r="BH77" s="46">
-        <f t="shared" si="97"/>
-        <v>1505</v>
-      </c>
-      <c r="BI77" s="47" t="str">
+        <f t="shared" si="95"/>
+        <v>1981.9</v>
+      </c>
+      <c r="BI77" s="47">
         <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ77" s="47" t="str">
+        <v>0.16348958070538372</v>
+      </c>
+      <c r="BJ77" s="47">
         <f t="shared" si="88"/>
-        <v/>
+        <v>0.19059999999999999</v>
       </c>
       <c r="BK77" s="47">
         <f t="shared" si="103"/>
@@ -18093,7 +18772,7 @@
         <v/>
       </c>
       <c r="BP77" s="51">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="BQ77" s="28">
@@ -18109,12 +18788,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:71">
       <c r="A78" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B78" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C78">
         <v>12</v>
@@ -18122,70 +18801,137 @@
       <c r="D78">
         <v>12</v>
       </c>
-      <c r="F78" s="61"/>
+      <c r="F78" s="61">
+        <v>45545.404328703698</v>
+      </c>
       <c r="G78" s="64">
         <v>6478.05</v>
       </c>
       <c r="H78" s="44"/>
-      <c r="I78" s="44"/>
-      <c r="J78" s="44"/>
-      <c r="K78" s="44"/>
-      <c r="L78" s="44"/>
-      <c r="M78" s="44"/>
-      <c r="N78" s="44"/>
-      <c r="O78" s="44"/>
-      <c r="P78" s="44"/>
-      <c r="Q78" s="44"/>
+      <c r="I78" s="44">
+        <v>5741.085</v>
+      </c>
+      <c r="J78" s="44">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="K78" s="44">
+        <v>16.3</v>
+      </c>
+      <c r="L78" s="44">
+        <v>86.2</v>
+      </c>
+      <c r="M78" s="44">
+        <v>19</v>
+      </c>
+      <c r="N78" s="44">
+        <v>451</v>
+      </c>
+      <c r="O78" s="44">
+        <v>2.31</v>
+      </c>
+      <c r="P78" s="44">
+        <v>0.21</v>
+      </c>
+      <c r="Q78" s="44">
+        <v>2.1800000000000002</v>
+      </c>
       <c r="R78" s="44"/>
-      <c r="S78" s="44"/>
-      <c r="T78" s="44"/>
-      <c r="U78" s="44"/>
-      <c r="V78" s="44"/>
-      <c r="W78" s="44"/>
-      <c r="X78" s="44"/>
-      <c r="Y78" s="44"/>
-      <c r="Z78" s="44"/>
-      <c r="AA78" s="44"/>
-      <c r="AB78" s="44"/>
-      <c r="AC78" s="44"/>
-      <c r="AD78" s="17"/>
-      <c r="AE78" s="44"/>
-      <c r="AF78" s="44"/>
-      <c r="AG78" s="44"/>
+      <c r="S78" s="44">
+        <v>1.19</v>
+      </c>
+      <c r="T78" s="44">
+        <v>3.68</v>
+      </c>
+      <c r="U78" s="44">
+        <v>1.96</v>
+      </c>
+      <c r="V78" s="44">
+        <v>7.27</v>
+      </c>
+      <c r="W78" s="44">
+        <v>112.6</v>
+      </c>
+      <c r="X78" s="44">
+        <v>20.9</v>
+      </c>
+      <c r="Y78" s="44">
+        <v>1.23</v>
+      </c>
+      <c r="Z78" s="44">
+        <v>182.1</v>
+      </c>
+      <c r="AA78" s="44">
+        <v>50.4</v>
+      </c>
+      <c r="AB78" s="44">
+        <v>98.7</v>
+      </c>
+      <c r="AC78" s="44">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="AD78" s="17">
+        <v>7.3120000000000003</v>
+      </c>
+      <c r="AE78" s="44">
+        <v>299</v>
+      </c>
+      <c r="AF78" s="44">
+        <v>49.3</v>
+      </c>
+      <c r="AG78" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH78" s="45">
         <f t="shared" si="106"/>
-        <v>0</v>
-      </c>
-      <c r="AI78" s="44"/>
-      <c r="AJ78" s="44"/>
-      <c r="AK78" s="44"/>
-      <c r="AL78" s="44"/>
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="AI78" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ78" s="44">
+        <v>43.09</v>
+      </c>
+      <c r="AK78" s="44">
+        <v>21.45</v>
+      </c>
+      <c r="AL78" s="44">
+        <f>AL54+3.82</f>
+        <v>10.58</v>
+      </c>
       <c r="AM78" s="45">
         <f t="shared" si="107"/>
         <v>0</v>
       </c>
-      <c r="AN78" s="44"/>
-      <c r="AO78" s="44"/>
-      <c r="AP78" s="44"/>
-      <c r="AQ78" s="44"/>
+      <c r="AN78" s="44">
+        <v>299.92</v>
+      </c>
+      <c r="AO78" s="44">
+        <v>91.22</v>
+      </c>
+      <c r="AP78" s="44">
+        <v>332</v>
+      </c>
+      <c r="AQ78" s="44">
+        <v>1913</v>
+      </c>
       <c r="AR78" s="45">
         <v>47.420000000000073</v>
       </c>
       <c r="AS78" s="45">
         <f t="shared" si="90"/>
-        <v>-47.420000000000073</v>
+        <v>1865.58</v>
       </c>
       <c r="AT78" s="45">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>26.870000000000005</v>
       </c>
       <c r="AU78" s="45">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>11.510000000000005</v>
       </c>
       <c r="AV78" s="45">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AW78" s="25">
         <v>15</v>
@@ -18209,23 +18955,23 @@
       <c r="BE78" s="22"/>
       <c r="BF78" s="11">
         <f t="shared" si="101"/>
-        <v>0</v>
+        <v>9.6394614000000003E-3</v>
       </c>
       <c r="BG78" s="46">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>13.880824416000001</v>
       </c>
       <c r="BH78" s="46">
-        <f t="shared" si="97"/>
-        <v>1505</v>
-      </c>
-      <c r="BI78" s="47" t="str">
+        <f t="shared" si="95"/>
+        <v>1971.2600000000002</v>
+      </c>
+      <c r="BI78" s="47">
         <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ78" s="47" t="str">
+        <v>0.15214634294816512</v>
+      </c>
+      <c r="BJ78" s="47">
         <f t="shared" si="88"/>
-        <v/>
+        <v>0.17642352941176473</v>
       </c>
       <c r="BK78" s="47">
         <f t="shared" si="103"/>
@@ -18245,10 +18991,10 @@
       </c>
       <c r="BO78" s="47">
         <f t="shared" si="47"/>
-        <v>11.2875</v>
+        <v>0</v>
       </c>
       <c r="BP78" s="51" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v/>
       </c>
       <c r="BQ78" s="28">
@@ -18261,15 +19007,15 @@
       </c>
       <c r="BS78" s="30">
         <f t="shared" si="105"/>
-        <v>11.2875</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:71" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:71">
       <c r="A79" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B79" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C79">
         <v>12</v>
@@ -18277,62 +19023,125 @@
       <c r="D79">
         <v>12</v>
       </c>
-      <c r="F79" s="61"/>
+      <c r="F79" s="61">
+        <v>45545.408437500002</v>
+      </c>
       <c r="G79" s="64">
         <v>6478.05</v>
       </c>
       <c r="H79" s="44"/>
-      <c r="I79" s="44"/>
-      <c r="J79" s="44"/>
-      <c r="K79" s="44"/>
-      <c r="L79" s="44"/>
-      <c r="M79" s="44"/>
-      <c r="N79" s="44"/>
+      <c r="I79" s="44">
+        <v>2610.5250000000001</v>
+      </c>
+      <c r="J79" s="44">
+        <v>19.3</v>
+      </c>
+      <c r="K79" s="44">
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="L79" s="44">
+        <v>2.92</v>
+      </c>
+      <c r="M79" s="44">
+        <v>13.5</v>
+      </c>
+      <c r="N79" s="44">
+        <v>882</v>
+      </c>
       <c r="O79" s="44"/>
-      <c r="P79" s="44"/>
-      <c r="Q79" s="44"/>
+      <c r="P79" s="44">
+        <v>0.24</v>
+      </c>
+      <c r="Q79" s="44">
+        <v>7.21</v>
+      </c>
       <c r="R79" s="44"/>
-      <c r="S79" s="44"/>
-      <c r="T79" s="44"/>
+      <c r="S79" s="44">
+        <v>1.36</v>
+      </c>
+      <c r="T79" s="44">
+        <v>4.67</v>
+      </c>
       <c r="U79" s="44"/>
-      <c r="V79" s="44"/>
-      <c r="W79" s="44"/>
-      <c r="X79" s="44"/>
-      <c r="Y79" s="44"/>
-      <c r="Z79" s="44"/>
-      <c r="AA79" s="44"/>
-      <c r="AB79" s="44"/>
-      <c r="AC79" s="44"/>
-      <c r="AD79" s="17"/>
-      <c r="AE79" s="44"/>
-      <c r="AF79" s="44"/>
-      <c r="AG79" s="44"/>
+      <c r="V79" s="44">
+        <v>7.2850000000000001</v>
+      </c>
+      <c r="W79" s="44">
+        <v>2.4</v>
+      </c>
+      <c r="X79" s="44">
+        <v>120</v>
+      </c>
+      <c r="Y79" s="44">
+        <v>7.15</v>
+      </c>
+      <c r="Z79" s="44">
+        <v>311.39999999999998</v>
+      </c>
+      <c r="AA79" s="44">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB79" s="44">
+        <v>2.1</v>
+      </c>
+      <c r="AC79" s="44">
+        <v>102.7</v>
+      </c>
+      <c r="AD79" s="17">
+        <v>7.327</v>
+      </c>
+      <c r="AE79" s="44">
+        <v>300</v>
+      </c>
+      <c r="AF79" s="44">
+        <v>70</v>
+      </c>
+      <c r="AG79" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH79" s="45">
         <f t="shared" si="106"/>
-        <v>0</v>
-      </c>
-      <c r="AI79" s="44"/>
-      <c r="AJ79" s="44"/>
-      <c r="AK79" s="44"/>
-      <c r="AL79" s="44"/>
+        <v>0.7</v>
+      </c>
+      <c r="AI79" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ79" s="44">
+        <v>150</v>
+      </c>
+      <c r="AK79" s="44">
+        <v>11.11</v>
+      </c>
+      <c r="AL79" s="44">
+        <f>AL55+3.67</f>
+        <v>10.11</v>
+      </c>
       <c r="AM79" s="45">
         <f t="shared" si="107"/>
         <v>0</v>
       </c>
-      <c r="AN79" s="44"/>
-      <c r="AO79" s="44"/>
-      <c r="AP79" s="44"/>
-      <c r="AQ79" s="44"/>
+      <c r="AN79" s="44">
+        <v>313.83999999999997</v>
+      </c>
+      <c r="AO79" s="44">
+        <v>94.46</v>
+      </c>
+      <c r="AP79" s="44">
+        <v>290</v>
+      </c>
+      <c r="AQ79" s="44">
+        <v>2143</v>
+      </c>
       <c r="AR79" s="45">
         <v>133.55999999999995</v>
       </c>
       <c r="AS79" s="45">
         <f t="shared" si="90"/>
-        <v>-133.55999999999995</v>
+        <v>2009.44</v>
       </c>
       <c r="AT79" s="45">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>3.7699999999999818</v>
       </c>
       <c r="AU79" s="45">
         <f t="shared" si="100"/>
@@ -18340,7 +19149,7 @@
       </c>
       <c r="AV79" s="45">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AW79" s="25">
         <v>15</v>
@@ -18364,23 +19173,23 @@
       <c r="BE79" s="22"/>
       <c r="BF79" s="11">
         <f t="shared" si="101"/>
-        <v>0</v>
+        <v>3.5270078399999991E-4</v>
       </c>
       <c r="BG79" s="46">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>0.50788912895999982</v>
       </c>
       <c r="BH79" s="46">
-        <f t="shared" si="97"/>
-        <v>1505</v>
-      </c>
-      <c r="BI79" s="47" t="str">
+        <f t="shared" si="95"/>
+        <v>2084.52</v>
+      </c>
+      <c r="BI79" s="47">
         <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ79" s="47" t="str">
+        <v>0.15055744248076294</v>
+      </c>
+      <c r="BJ79" s="47">
         <f t="shared" si="88"/>
-        <v/>
+        <v>0.18461176470588234</v>
       </c>
       <c r="BK79" s="47">
         <f t="shared" si="103"/>
@@ -18400,10 +19209,10 @@
       </c>
       <c r="BO79" s="47">
         <f t="shared" si="47"/>
-        <v>11.2875</v>
+        <v>0</v>
       </c>
       <c r="BP79" s="51" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v/>
       </c>
       <c r="BQ79" s="28">
@@ -18416,15 +19225,15 @@
       </c>
       <c r="BS79" s="30">
         <f t="shared" si="105"/>
-        <v>11.2875</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:71" ht="15" thickBot="1">
       <c r="A80" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C80" s="5">
         <v>12</v>
@@ -18433,70 +19242,137 @@
         <v>12</v>
       </c>
       <c r="E80" s="5"/>
-      <c r="F80" s="62"/>
+      <c r="F80" s="62">
+        <v>45545.448750000003</v>
+      </c>
       <c r="G80" s="65">
         <v>6478.05</v>
       </c>
       <c r="H80" s="7"/>
-      <c r="I80" s="7"/>
-      <c r="J80" s="7"/>
-      <c r="K80" s="7"/>
-      <c r="L80" s="7"/>
-      <c r="M80" s="7"/>
-      <c r="N80" s="7"/>
-      <c r="O80" s="7"/>
-      <c r="P80" s="7"/>
-      <c r="Q80" s="7"/>
+      <c r="I80" s="7">
+        <v>6376.7849999999999</v>
+      </c>
+      <c r="J80" s="7">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="K80" s="7">
+        <v>17.8</v>
+      </c>
+      <c r="L80" s="7">
+        <v>88.4</v>
+      </c>
+      <c r="M80" s="7">
+        <v>17.7</v>
+      </c>
+      <c r="N80" s="7">
+        <v>368</v>
+      </c>
+      <c r="O80" s="7">
+        <v>1.76</v>
+      </c>
+      <c r="P80" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="Q80" s="7">
+        <v>1.2</v>
+      </c>
       <c r="R80" s="7"/>
-      <c r="S80" s="7"/>
-      <c r="T80" s="7"/>
-      <c r="U80" s="7"/>
-      <c r="V80" s="7"/>
-      <c r="W80" s="7"/>
-      <c r="X80" s="7"/>
-      <c r="Y80" s="7"/>
-      <c r="Z80" s="7"/>
-      <c r="AA80" s="7"/>
-      <c r="AB80" s="7"/>
-      <c r="AC80" s="7"/>
-      <c r="AD80" s="18"/>
-      <c r="AE80" s="7"/>
-      <c r="AF80" s="7"/>
-      <c r="AG80" s="7"/>
+      <c r="S80" s="7">
+        <v>0.16</v>
+      </c>
+      <c r="T80" s="7">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="U80" s="7">
+        <v>0.36</v>
+      </c>
+      <c r="V80" s="7">
+        <v>7.25</v>
+      </c>
+      <c r="W80" s="7">
+        <v>111.1</v>
+      </c>
+      <c r="X80" s="7">
+        <v>30.8</v>
+      </c>
+      <c r="Y80" s="7">
+        <v>1.76</v>
+      </c>
+      <c r="Z80" s="7">
+        <v>161.4</v>
+      </c>
+      <c r="AA80" s="7">
+        <v>47.4</v>
+      </c>
+      <c r="AB80" s="7">
+        <v>97.4</v>
+      </c>
+      <c r="AC80" s="7">
+        <v>24.9</v>
+      </c>
+      <c r="AD80" s="18">
+        <v>7.2910000000000004</v>
+      </c>
+      <c r="AE80" s="7">
+        <v>301</v>
+      </c>
+      <c r="AF80" s="7">
+        <v>50.9</v>
+      </c>
+      <c r="AG80" s="7">
+        <v>7.3</v>
+      </c>
       <c r="AH80" s="41">
         <f t="shared" si="106"/>
-        <v>0</v>
-      </c>
-      <c r="AI80" s="7"/>
-      <c r="AJ80" s="7"/>
-      <c r="AK80" s="7"/>
-      <c r="AL80" s="7"/>
+        <v>0.50900000000000001</v>
+      </c>
+      <c r="AI80" s="7">
+        <v>34</v>
+      </c>
+      <c r="AJ80" s="7">
+        <v>28.271000000000001</v>
+      </c>
+      <c r="AK80" s="7">
+        <v>48.545000000000002</v>
+      </c>
+      <c r="AL80" s="7">
+        <f>AL56+3.73</f>
+        <v>10.25</v>
+      </c>
       <c r="AM80" s="41">
         <f t="shared" si="107"/>
         <v>0</v>
       </c>
-      <c r="AN80" s="7"/>
-      <c r="AO80" s="7"/>
-      <c r="AP80" s="7"/>
-      <c r="AQ80" s="7"/>
+      <c r="AN80" s="7">
+        <v>232.6</v>
+      </c>
+      <c r="AO80" s="7">
+        <v>95.38</v>
+      </c>
+      <c r="AP80" s="7">
+        <v>424</v>
+      </c>
+      <c r="AQ80" s="7">
+        <v>1824</v>
+      </c>
       <c r="AR80" s="41">
         <v>51.660000000000082</v>
       </c>
       <c r="AS80" s="41">
         <f t="shared" si="90"/>
-        <v>-51.660000000000082</v>
+        <v>1772.34</v>
       </c>
       <c r="AT80" s="41">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>12.409999999999997</v>
       </c>
       <c r="AU80" s="41">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>13.159999999999997</v>
       </c>
       <c r="AV80" s="41">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW80" s="26">
         <v>15</v>
@@ -18521,23 +19397,23 @@
       <c r="BE80" s="23"/>
       <c r="BF80" s="12">
         <f t="shared" si="101"/>
-        <v>0</v>
+        <v>1.025304564E-2</v>
       </c>
       <c r="BG80" s="13">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>14.7643857216</v>
       </c>
       <c r="BH80" s="13">
-        <f t="shared" si="97"/>
-        <v>1505</v>
-      </c>
-      <c r="BI80" s="14" t="str">
+        <f t="shared" si="95"/>
+        <v>1920.0459999999998</v>
+      </c>
+      <c r="BI80" s="14">
         <f t="shared" si="87"/>
-        <v/>
-      </c>
-      <c r="BJ80" s="14" t="str">
+        <v>0.12114293095061265</v>
+      </c>
+      <c r="BJ80" s="14">
         <f t="shared" si="88"/>
-        <v/>
+        <v>0.1368235294117647</v>
       </c>
       <c r="BK80" s="14">
         <f t="shared" si="103"/>
@@ -18557,10 +19433,10 @@
       </c>
       <c r="BO80" s="14">
         <f t="shared" si="47"/>
-        <v>11.2875</v>
+        <v>8.6402069999999984</v>
       </c>
       <c r="BP80" s="52" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v/>
       </c>
       <c r="BQ80" s="29">
@@ -18573,16 +19449,16 @@
       </c>
       <c r="BS80" s="31">
         <f t="shared" si="105"/>
-        <v>11.2875</v>
+        <v>8.6402069999999984</v>
       </c>
     </row>
-    <row r="83" spans="19:28" x14ac:dyDescent="0.3">
+    <row r="83" spans="19:28">
       <c r="S83" s="39"/>
     </row>
-    <row r="86" spans="19:28" x14ac:dyDescent="0.3">
+    <row r="86" spans="19:28">
       <c r="AB86" s="59"/>
     </row>
-    <row r="87" spans="19:28" x14ac:dyDescent="0.3">
+    <row r="87" spans="19:28">
       <c r="AB87" s="59"/>
     </row>
   </sheetData>
@@ -18626,15 +19502,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
@@ -18650,6 +19517,15 @@
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18876,45 +19752,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}"/>
 </file>
--- a/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
+++ b/data/mr24-045-experiment/MR24-045-MasterDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myteams.gsk.com/sites/BiopharmModelPredictiveControl/Shared Documents/General/data/MR24-045-MPC-3L/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1470" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{970C3D87-E5E3-4C81-A6EA-E66F76EC7286}"/>
+  <xr:revisionPtr revIDLastSave="1624" documentId="14_{29998BAB-B97E-4D42-B36C-5857DA37A7C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63D091B6-3F2B-4BC1-A245-7155FD4BA60A}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1575" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MasterDataTable" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="90">
   <si>
     <t>Batch Data</t>
   </si>
@@ -307,6 +307,9 @@
   <si>
     <t>MR24-045-806</t>
   </si>
+  <si>
+    <t>Antifoam totalizer reset due to schedule restart</t>
+  </si>
 </sst>
 </file>
 
@@ -318,7 +321,7 @@
     <numFmt numFmtId="166" formatCode="0.00000"/>
     <numFmt numFmtId="167" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -510,6 +513,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -990,7 +1000,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
@@ -1077,6 +1087,9 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1229,6 +1242,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1546,91 +1563,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="68" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="69" t="s">
+      <c r="A1" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="70"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="70"/>
-      <c r="Q1" s="70"/>
-      <c r="R1" s="70"/>
-      <c r="S1" s="70"/>
-      <c r="T1" s="70"/>
-      <c r="U1" s="70"/>
-      <c r="V1" s="70"/>
-      <c r="W1" s="70"/>
-      <c r="X1" s="70"/>
-      <c r="Y1" s="70"/>
-      <c r="Z1" s="70"/>
-      <c r="AA1" s="70"/>
-      <c r="AB1" s="70"/>
-      <c r="AC1" s="70"/>
-      <c r="AD1" s="71"/>
-      <c r="AE1" s="84" t="s">
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="73"/>
+      <c r="U1" s="73"/>
+      <c r="V1" s="73"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="74"/>
+      <c r="AE1" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="AF1" s="85"/>
-      <c r="AG1" s="85"/>
-      <c r="AH1" s="85"/>
-      <c r="AI1" s="85"/>
-      <c r="AJ1" s="85"/>
-      <c r="AK1" s="85"/>
-      <c r="AL1" s="85"/>
-      <c r="AM1" s="85"/>
-      <c r="AN1" s="85"/>
-      <c r="AO1" s="85"/>
-      <c r="AP1" s="85"/>
-      <c r="AQ1" s="85"/>
-      <c r="AR1" s="85"/>
-      <c r="AS1" s="85"/>
-      <c r="AT1" s="85"/>
-      <c r="AU1" s="85"/>
-      <c r="AV1" s="85"/>
-      <c r="AW1" s="86"/>
-      <c r="AX1" s="78" t="s">
+      <c r="AF1" s="88"/>
+      <c r="AG1" s="88"/>
+      <c r="AH1" s="88"/>
+      <c r="AI1" s="88"/>
+      <c r="AJ1" s="88"/>
+      <c r="AK1" s="88"/>
+      <c r="AL1" s="88"/>
+      <c r="AM1" s="88"/>
+      <c r="AN1" s="88"/>
+      <c r="AO1" s="88"/>
+      <c r="AP1" s="88"/>
+      <c r="AQ1" s="88"/>
+      <c r="AR1" s="88"/>
+      <c r="AS1" s="88"/>
+      <c r="AT1" s="88"/>
+      <c r="AU1" s="88"/>
+      <c r="AV1" s="88"/>
+      <c r="AW1" s="89"/>
+      <c r="AX1" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="AY1" s="79"/>
-      <c r="AZ1" s="79"/>
-      <c r="BA1" s="79"/>
-      <c r="BB1" s="80"/>
-      <c r="BC1" s="81" t="s">
+      <c r="AY1" s="82"/>
+      <c r="AZ1" s="82"/>
+      <c r="BA1" s="82"/>
+      <c r="BB1" s="83"/>
+      <c r="BC1" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="BD1" s="82"/>
-      <c r="BE1" s="83"/>
-      <c r="BF1" s="75" t="s">
+      <c r="BD1" s="85"/>
+      <c r="BE1" s="86"/>
+      <c r="BF1" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="BG1" s="76"/>
-      <c r="BH1" s="76"/>
-      <c r="BI1" s="76"/>
-      <c r="BJ1" s="76"/>
-      <c r="BK1" s="76"/>
-      <c r="BL1" s="76"/>
-      <c r="BM1" s="76"/>
-      <c r="BN1" s="76"/>
-      <c r="BO1" s="76"/>
-      <c r="BP1" s="77"/>
-      <c r="BQ1" s="72" t="s">
+      <c r="BG1" s="79"/>
+      <c r="BH1" s="79"/>
+      <c r="BI1" s="79"/>
+      <c r="BJ1" s="79"/>
+      <c r="BK1" s="79"/>
+      <c r="BL1" s="79"/>
+      <c r="BM1" s="79"/>
+      <c r="BN1" s="79"/>
+      <c r="BO1" s="79"/>
+      <c r="BP1" s="80"/>
+      <c r="BQ1" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="BR1" s="73"/>
-      <c r="BS1" s="74"/>
+      <c r="BR1" s="76"/>
+      <c r="BS1" s="77"/>
     </row>
     <row r="2" spans="1:71" ht="60.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
@@ -9172,7 +9189,7 @@
         <v>84.700000000000045</v>
       </c>
       <c r="AS35" s="45">
-        <f t="shared" ref="AS35:AS66" si="60">AQ35-AR35</f>
+        <f t="shared" ref="AS35:AS65" si="60">AQ35-AR35</f>
         <v>1755.3</v>
       </c>
       <c r="AT35" s="45">
@@ -12650,7 +12667,9 @@
       <c r="D51" s="3">
         <v>8</v>
       </c>
-      <c r="E51" s="3"/>
+      <c r="E51" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="F51" s="60">
         <v>45541.409976851901</v>
       </c>
@@ -12744,7 +12763,7 @@
       <c r="AK51" s="44">
         <v>33.090000000000003</v>
       </c>
-      <c r="AL51" s="6">
+      <c r="AL51" s="68">
         <v>5.29</v>
       </c>
       <c r="AM51" s="42">
@@ -12877,6 +12896,9 @@
       <c r="D52">
         <v>8</v>
       </c>
+      <c r="E52" t="s">
+        <v>89</v>
+      </c>
       <c r="F52" s="61">
         <v>45541.414027777799</v>
       </c>
@@ -12970,7 +12992,7 @@
       <c r="AK52" s="44">
         <v>26.68</v>
       </c>
-      <c r="AL52" s="44">
+      <c r="AL52" s="69">
         <v>3</v>
       </c>
       <c r="AM52" s="45">
@@ -13103,6 +13125,9 @@
       <c r="D53">
         <v>8</v>
       </c>
+      <c r="E53" t="s">
+        <v>89</v>
+      </c>
       <c r="F53" s="61">
         <v>45541.418136574102</v>
       </c>
@@ -13196,7 +13221,7 @@
       <c r="AK53" s="44">
         <v>1.24</v>
       </c>
-      <c r="AL53" s="44">
+      <c r="AL53" s="69">
         <v>6.66</v>
       </c>
       <c r="AM53" s="45">
@@ -13329,6 +13354,9 @@
       <c r="D54">
         <v>8</v>
       </c>
+      <c r="E54" t="s">
+        <v>89</v>
+      </c>
       <c r="F54" s="61">
         <v>45541.4217361111</v>
       </c>
@@ -13420,7 +13448,7 @@
       <c r="AK54" s="44">
         <v>10.53</v>
       </c>
-      <c r="AL54" s="44">
+      <c r="AL54" s="69">
         <v>6.76</v>
       </c>
       <c r="AM54" s="45">
@@ -13550,6 +13578,9 @@
       <c r="D55">
         <v>8</v>
       </c>
+      <c r="E55" t="s">
+        <v>89</v>
+      </c>
       <c r="F55" s="61">
         <v>45541.425601851901</v>
       </c>
@@ -13641,7 +13672,7 @@
       <c r="AK55" s="44">
         <v>7.31</v>
       </c>
-      <c r="AL55" s="44">
+      <c r="AL55" s="69">
         <v>6.44</v>
       </c>
       <c r="AM55" s="45">
@@ -13771,7 +13802,9 @@
       <c r="D56" s="5">
         <v>8</v>
       </c>
-      <c r="E56" s="5"/>
+      <c r="E56" s="5" t="s">
+        <v>89</v>
+      </c>
       <c r="F56" s="62">
         <v>45541.429097222201</v>
       </c>
@@ -13865,7 +13898,7 @@
       <c r="AK56" s="7">
         <v>28.23</v>
       </c>
-      <c r="AL56" s="7">
+      <c r="AL56" s="70">
         <v>6.52</v>
       </c>
       <c r="AM56" s="41">
@@ -13997,7 +14030,9 @@
         <v>9</v>
       </c>
       <c r="E57" s="3"/>
-      <c r="F57" s="60"/>
+      <c r="F57" s="60">
+        <v>45542.536215277803</v>
+      </c>
       <c r="G57" s="3">
         <v>4805.7299999999996</v>
       </c>
@@ -14094,7 +14129,7 @@
       </c>
       <c r="AM57" s="42">
         <f>BR57</f>
-        <v>0</v>
+        <v>1.55878779022903E-2</v>
       </c>
       <c r="AN57" s="6">
         <v>150.99</v>
@@ -14146,8 +14181,14 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC57" s="8"/>
-      <c r="BD57" s="9"/>
-      <c r="BE57" s="21"/>
+      <c r="BD57" s="46">
+        <f>BM57*24*60/BH57</f>
+        <v>1.2227344977136538E-2</v>
+      </c>
+      <c r="BE57" s="22">
+        <f>BP57/BH57</f>
+        <v>9.9999999999999995E-8</v>
+      </c>
       <c r="BF57" s="8">
         <f t="shared" si="17"/>
         <v>1.1345033880000001E-2</v>
@@ -14170,15 +14211,14 @@
       </c>
       <c r="BK57" s="10">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>22.446544179298034</v>
       </c>
       <c r="BL57" s="10" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM57" s="10">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.55878779022903E-2</v>
       </c>
       <c r="BN57" s="35" t="str">
         <f t="shared" si="32"/>
@@ -14189,20 +14229,19 @@
         <v/>
       </c>
       <c r="BP57" s="50">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1.8357660000000001E-4</v>
       </c>
       <c r="BQ57" s="27">
         <f>IF(BL57&lt;&gt;"",BL57/0.000385,IF(BM57&lt;&gt;"",BM57/0.000385,BN57/0.000385))</f>
-        <v>0</v>
+        <v>40.487994551403375</v>
       </c>
       <c r="BR57" s="37">
         <f>IF(BL57&lt;&gt;"",BL57,IF(BM57&lt;&gt;"",BM57,BN57))</f>
-        <v>0</v>
+        <v>1.55878779022903E-2</v>
       </c>
       <c r="BS57" s="32">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1.8357660000000001E-4</v>
       </c>
     </row>
     <row r="58" spans="1:71" x14ac:dyDescent="0.3">
@@ -14218,7 +14257,9 @@
       <c r="D58">
         <v>9</v>
       </c>
-      <c r="F58" s="61"/>
+      <c r="F58" s="61">
+        <v>45542.542280092603</v>
+      </c>
       <c r="G58">
         <v>4805.7299999999996</v>
       </c>
@@ -14315,7 +14356,7 @@
       </c>
       <c r="AM58" s="45">
         <f t="shared" ref="AM58:AM62" si="75">BR58</f>
-        <v>0</v>
+        <v>1.4239072354215201E-2</v>
       </c>
       <c r="AN58" s="44">
         <v>167.56</v>
@@ -14367,8 +14408,14 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC58" s="11"/>
-      <c r="BD58" s="46"/>
-      <c r="BE58" s="22"/>
+      <c r="BD58" s="46">
+        <f>BM58*24*60/BH58</f>
+        <v>1.1176787745194918E-2</v>
+      </c>
+      <c r="BE58" s="22">
+        <f>BP58/BH58</f>
+        <v>3.3316909083529549E-3</v>
+      </c>
       <c r="BF58" s="11">
         <f t="shared" si="17"/>
         <v>1.1502565799999998E-2</v>
@@ -14391,15 +14438,14 @@
       </c>
       <c r="BK58" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>20.504264190069886</v>
       </c>
       <c r="BL58" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM58" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.4239072354215201E-2</v>
       </c>
       <c r="BN58" s="48" t="str">
         <f t="shared" si="32"/>
@@ -14410,20 +14456,19 @@
         <v/>
       </c>
       <c r="BP58" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>6.1121202390098297</v>
       </c>
       <c r="BQ58" s="28">
         <f t="shared" ref="BQ58:BQ62" si="76">IF(BL58&lt;&gt;"",BL58/0.000385,IF(BM58&lt;&gt;"",BM58/0.000385,BN58/0.000385))</f>
-        <v>0</v>
+        <v>36.984603517442082</v>
       </c>
       <c r="BR58" s="49">
         <f t="shared" ref="BR58:BR62" si="77">IF(BL58&lt;&gt;"",BL58,IF(BM58&lt;&gt;"",BM58,BN58))</f>
-        <v>0</v>
+        <v>1.4239072354215201E-2</v>
       </c>
       <c r="BS58" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>6.1121202390098297</v>
       </c>
     </row>
     <row r="59" spans="1:71" x14ac:dyDescent="0.3">
@@ -14439,7 +14484,9 @@
       <c r="D59">
         <v>9</v>
       </c>
-      <c r="F59" s="61"/>
+      <c r="F59" s="61">
+        <v>45542.544826388897</v>
+      </c>
       <c r="G59">
         <v>4805.7299999999996</v>
       </c>
@@ -14536,7 +14583,7 @@
       </c>
       <c r="AM59" s="45">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>3.1427878333333298E-2</v>
       </c>
       <c r="AN59" s="44">
         <v>211.31</v>
@@ -14588,8 +14635,14 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC59" s="11"/>
-      <c r="BD59" s="46"/>
-      <c r="BE59" s="22"/>
+      <c r="BD59" s="46">
+        <f>BM59*24*60/BH59</f>
+        <v>2.3999999999999973E-2</v>
+      </c>
+      <c r="BE59" s="22">
+        <f>BP59/BH59</f>
+        <v>4.1250564909925723E-3</v>
+      </c>
       <c r="BF59" s="11">
         <f t="shared" si="17"/>
         <v>9.8997816750000002E-3</v>
@@ -14612,15 +14665,14 @@
       </c>
       <c r="BK59" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>45.256144799999952</v>
       </c>
       <c r="BL59" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM59" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>3.1427878333333298E-2</v>
       </c>
       <c r="BN59" s="48" t="str">
         <f t="shared" si="32"/>
@@ -14631,20 +14683,19 @@
         <v/>
       </c>
       <c r="BP59" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>7.77850641102249</v>
       </c>
       <c r="BQ59" s="28">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>81.630852813852727</v>
       </c>
       <c r="BR59" s="49">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>3.1427878333333298E-2</v>
       </c>
       <c r="BS59" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>7.77850641102249</v>
       </c>
     </row>
     <row r="60" spans="1:71" x14ac:dyDescent="0.3">
@@ -14660,13 +14711,15 @@
       <c r="D60">
         <v>9</v>
       </c>
-      <c r="F60" s="61"/>
+      <c r="F60" s="61">
+        <v>45542.547604166699</v>
+      </c>
       <c r="G60">
         <v>4805.7299999999996</v>
       </c>
       <c r="H60" s="44"/>
       <c r="I60" s="44">
-        <v>4576.09</v>
+        <v>4576.0950000000003</v>
       </c>
       <c r="J60" s="44">
         <v>19.2</v>
@@ -14757,7 +14810,7 @@
       </c>
       <c r="AM60" s="45">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>2.3587912499999995E-2</v>
       </c>
       <c r="AN60" s="44">
         <v>204.07</v>
@@ -14808,7 +14861,9 @@
       <c r="BB60" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC60" s="11"/>
+      <c r="BC60" s="11">
+        <v>1.7999999999999999E-2</v>
+      </c>
       <c r="BE60" s="22"/>
       <c r="BF60" s="11">
         <f t="shared" si="17"/>
@@ -14832,11 +14887,11 @@
       </c>
       <c r="BK60" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>33.966593999999986</v>
       </c>
       <c r="BL60" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.3587912499999995E-2</v>
       </c>
       <c r="BM60" s="48" t="str">
         <f t="shared" si="31"/>
@@ -14856,11 +14911,11 @@
       </c>
       <c r="BQ60" s="28">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>61.267305194805189</v>
       </c>
       <c r="BR60" s="49">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>2.3587912499999995E-2</v>
       </c>
       <c r="BS60" s="30">
         <f t="shared" si="21"/>
@@ -14880,7 +14935,9 @@
       <c r="D61">
         <v>9</v>
       </c>
-      <c r="F61" s="61"/>
+      <c r="F61" s="61">
+        <v>45542.550289351901</v>
+      </c>
       <c r="G61">
         <v>4805.7299999999996</v>
       </c>
@@ -14975,7 +15032,7 @@
       </c>
       <c r="AM61" s="45">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>2.752684166666667E-2</v>
       </c>
       <c r="AN61" s="44">
         <v>227.05</v>
@@ -15026,7 +15083,9 @@
       <c r="BB61" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC61" s="11"/>
+      <c r="BC61" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BE61" s="22"/>
       <c r="BF61" s="11">
         <f t="shared" si="17"/>
@@ -15050,11 +15109,11 @@
       </c>
       <c r="BK61" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>39.638652000000008</v>
       </c>
       <c r="BL61" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.752684166666667E-2</v>
       </c>
       <c r="BM61" s="48" t="str">
         <f t="shared" si="31"/>
@@ -15074,11 +15133,11 @@
       </c>
       <c r="BQ61" s="28">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>71.498290043290055</v>
       </c>
       <c r="BR61" s="49">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>2.752684166666667E-2</v>
       </c>
       <c r="BS61" s="30">
         <f t="shared" si="21"/>
@@ -15099,7 +15158,9 @@
         <v>9</v>
       </c>
       <c r="E62" s="5"/>
-      <c r="F62" s="62"/>
+      <c r="F62" s="62">
+        <v>45542.552824074097</v>
+      </c>
       <c r="G62" s="5">
         <v>4805.7299999999996</v>
       </c>
@@ -15196,7 +15257,7 @@
       </c>
       <c r="AM62" s="41">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>1.1032315277777779E-2</v>
       </c>
       <c r="AN62" s="7">
         <v>187.96</v>
@@ -15247,7 +15308,9 @@
       <c r="BB62" s="23">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC62" s="12"/>
+      <c r="BC62" s="12">
+        <v>8.5000000000000006E-3</v>
+      </c>
       <c r="BD62" s="5"/>
       <c r="BE62" s="23"/>
       <c r="BF62" s="12">
@@ -15272,11 +15335,11 @@
       </c>
       <c r="BK62" s="14">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>15.886534000000001</v>
       </c>
       <c r="BL62" s="14">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1.1032315277777779E-2</v>
       </c>
       <c r="BM62" s="48" t="str">
         <f t="shared" si="31"/>
@@ -15296,11 +15359,11 @@
       </c>
       <c r="BQ62" s="29">
         <f t="shared" si="76"/>
-        <v>0</v>
+        <v>28.655364357864364</v>
       </c>
       <c r="BR62" s="38">
         <f t="shared" si="77"/>
-        <v>0</v>
+        <v>1.1032315277777779E-2</v>
       </c>
       <c r="BS62" s="31">
         <f t="shared" si="21"/>
@@ -15321,70 +15384,137 @@
         <v>10</v>
       </c>
       <c r="E63" s="3"/>
-      <c r="F63" s="60"/>
+      <c r="F63" s="60">
+        <v>45543.405208333301</v>
+      </c>
       <c r="G63" s="63">
         <v>5497.99</v>
       </c>
       <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="6"/>
-      <c r="N63" s="6"/>
-      <c r="O63" s="6"/>
-      <c r="P63" s="6"/>
-      <c r="Q63" s="6"/>
+      <c r="I63" s="6">
+        <v>5803.62</v>
+      </c>
+      <c r="J63" s="6">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="K63" s="6">
+        <v>18.7</v>
+      </c>
+      <c r="L63" s="6">
+        <v>91.5</v>
+      </c>
+      <c r="M63" s="6">
+        <v>17.3</v>
+      </c>
+      <c r="N63" s="6">
+        <v>347</v>
+      </c>
+      <c r="O63" s="6">
+        <v>1.72</v>
+      </c>
+      <c r="P63" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>1.64</v>
+      </c>
       <c r="R63" s="6"/>
-      <c r="S63" s="6"/>
-      <c r="T63" s="6"/>
-      <c r="U63" s="6"/>
-      <c r="V63" s="6"/>
-      <c r="W63" s="6"/>
-      <c r="X63" s="6"/>
-      <c r="Y63" s="6"/>
-      <c r="Z63" s="6"/>
-      <c r="AA63" s="6"/>
-      <c r="AB63" s="6"/>
-      <c r="AC63" s="6"/>
-      <c r="AD63" s="16"/>
-      <c r="AE63" s="6"/>
-      <c r="AF63" s="6"/>
-      <c r="AG63" s="6"/>
+      <c r="S63" s="6">
+        <v>0.11</v>
+      </c>
+      <c r="T63" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="U63" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="V63" s="6">
+        <v>7.2460000000000004</v>
+      </c>
+      <c r="W63" s="6">
+        <v>95.9</v>
+      </c>
+      <c r="X63" s="6">
+        <v>11.5</v>
+      </c>
+      <c r="Y63" s="6">
+        <v>2.23</v>
+      </c>
+      <c r="Z63" s="6">
+        <v>146.4</v>
+      </c>
+      <c r="AA63" s="6">
+        <v>40.6</v>
+      </c>
+      <c r="AB63" s="6">
+        <v>84.1</v>
+      </c>
+      <c r="AC63" s="6">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="AD63" s="16">
+        <v>7.2869999999999999</v>
+      </c>
+      <c r="AE63" s="6">
+        <v>300</v>
+      </c>
+      <c r="AF63" s="6">
+        <v>47.8</v>
+      </c>
+      <c r="AG63" s="6">
+        <v>7.29</v>
+      </c>
       <c r="AH63" s="40">
         <f>AF63/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI63" s="6"/>
-      <c r="AJ63" s="6"/>
-      <c r="AK63" s="44"/>
-      <c r="AL63" s="6"/>
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="AI63" s="6">
+        <v>34</v>
+      </c>
+      <c r="AJ63" s="6">
+        <v>22.065000000000001</v>
+      </c>
+      <c r="AK63" s="44">
+        <v>44.018999999999998</v>
+      </c>
+      <c r="AL63" s="6">
+        <f>AL51+1.91</f>
+        <v>7.2</v>
+      </c>
       <c r="AM63" s="42">
         <f>BR63</f>
-        <v>0</v>
-      </c>
-      <c r="AN63" s="6"/>
-      <c r="AO63" s="6"/>
-      <c r="AP63" s="6"/>
-      <c r="AQ63" s="6"/>
+        <v>5.1207888888888803E-3</v>
+      </c>
+      <c r="AN63" s="6">
+        <v>169.89</v>
+      </c>
+      <c r="AO63" s="6">
+        <v>65.31</v>
+      </c>
+      <c r="AP63" s="6">
+        <v>497</v>
+      </c>
+      <c r="AQ63" s="6">
+        <v>1984</v>
+      </c>
       <c r="AR63" s="40">
         <v>137.11999999999989</v>
       </c>
       <c r="AS63" s="40">
         <f t="shared" si="60"/>
-        <v>-137.11999999999989</v>
+        <v>1846.88</v>
       </c>
       <c r="AT63" s="40">
         <f t="shared" si="36"/>
-        <v>-150.99</v>
+        <v>18.899999999999977</v>
       </c>
       <c r="AU63" s="40">
         <f t="shared" si="37"/>
-        <v>-65.31</v>
+        <v>0</v>
       </c>
       <c r="AV63" s="40">
         <f t="shared" si="65"/>
-        <v>518</v>
+        <v>21</v>
       </c>
       <c r="AW63" s="24">
         <v>15</v>
@@ -15405,39 +15535,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC63" s="8"/>
-      <c r="BD63" s="9"/>
-      <c r="BE63" s="21"/>
+      <c r="BD63" s="46">
+        <f>BM63*24*60/BH63</f>
+        <v>3.999999999999994E-3</v>
+      </c>
+      <c r="BE63" s="22">
+        <f>BP63/BH63</f>
+        <v>3.9797979551218672E-3</v>
+      </c>
       <c r="BF63" s="8">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.0341945239999999E-2</v>
       </c>
       <c r="BG63" s="9">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.892401145599999</v>
       </c>
       <c r="BH63" s="9">
         <f t="shared" si="41"/>
-        <v>1535</v>
-      </c>
-      <c r="BI63" s="10" t="str">
+        <v>1843.4839999999999</v>
+      </c>
+      <c r="BI63" s="10">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ63" s="10" t="str">
+        <v>9.2157024416810771E-2</v>
+      </c>
+      <c r="BJ63" s="10">
         <f t="shared" si="9"/>
-        <v/>
+        <v>9.9935294117647053E-2</v>
       </c>
       <c r="BK63" s="10">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>7.3739359999999881</v>
       </c>
       <c r="BL63" s="10" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM63" s="10">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>5.1207888888888803E-3</v>
       </c>
       <c r="BN63" s="35" t="str">
         <f t="shared" si="32"/>
@@ -15448,20 +15583,19 @@
         <v/>
       </c>
       <c r="BP63" s="50">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>7.33669385349988</v>
       </c>
       <c r="BQ63" s="27">
         <f>IF(BL63&lt;&gt;"",BL63/0.000385,IF(BM63&lt;&gt;"",BM63/0.000385,BN63/0.000385))</f>
-        <v>0</v>
+        <v>13.300750360750339</v>
       </c>
       <c r="BR63" s="37">
         <f>IF(BL63&lt;&gt;"",BL63,IF(BM63&lt;&gt;"",BM63,BN63))</f>
-        <v>0</v>
+        <v>5.1207888888888803E-3</v>
       </c>
       <c r="BS63" s="32">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>7.33669385349988</v>
       </c>
     </row>
     <row r="64" spans="1:71" x14ac:dyDescent="0.3">
@@ -15477,70 +15611,137 @@
       <c r="D64">
         <v>10</v>
       </c>
-      <c r="F64" s="61"/>
+      <c r="F64" s="61">
+        <v>45543.413275462997</v>
+      </c>
       <c r="G64" s="64">
         <v>5497.99</v>
       </c>
       <c r="H64" s="44"/>
-      <c r="I64" s="44"/>
-      <c r="J64" s="44"/>
-      <c r="K64" s="44"/>
-      <c r="L64" s="44"/>
-      <c r="M64" s="44"/>
-      <c r="N64" s="44"/>
-      <c r="O64" s="44"/>
-      <c r="P64" s="44"/>
-      <c r="Q64" s="44"/>
+      <c r="I64" s="44">
+        <v>5945.67</v>
+      </c>
+      <c r="J64" s="44">
+        <v>20.6</v>
+      </c>
+      <c r="K64" s="44">
+        <v>19.3</v>
+      </c>
+      <c r="L64" s="44">
+        <v>93.9</v>
+      </c>
+      <c r="M64" s="44">
+        <v>17.8</v>
+      </c>
+      <c r="N64" s="44">
+        <v>348</v>
+      </c>
+      <c r="O64" s="44">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="P64" s="44">
+        <v>0.21</v>
+      </c>
+      <c r="Q64" s="44">
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="R64" s="44"/>
-      <c r="S64" s="44"/>
-      <c r="T64" s="44"/>
-      <c r="U64" s="44"/>
-      <c r="V64" s="44"/>
-      <c r="W64" s="44"/>
-      <c r="X64" s="44"/>
-      <c r="Y64" s="44"/>
-      <c r="Z64" s="44"/>
-      <c r="AA64" s="44"/>
-      <c r="AB64" s="44"/>
-      <c r="AC64" s="44"/>
-      <c r="AD64" s="17"/>
-      <c r="AE64" s="44"/>
-      <c r="AF64" s="44"/>
-      <c r="AG64" s="44"/>
+      <c r="S64" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="T64" s="44">
+        <v>0.15</v>
+      </c>
+      <c r="U64" s="44">
+        <v>0.16</v>
+      </c>
+      <c r="V64" s="44">
+        <v>7.2619999999999996</v>
+      </c>
+      <c r="W64" s="44">
+        <v>105</v>
+      </c>
+      <c r="X64" s="44">
+        <v>55.7</v>
+      </c>
+      <c r="Y64" s="44">
+        <v>2.15</v>
+      </c>
+      <c r="Z64" s="44">
+        <v>154.19999999999999</v>
+      </c>
+      <c r="AA64" s="44">
+        <v>46.1</v>
+      </c>
+      <c r="AB64" s="44">
+        <v>92.1</v>
+      </c>
+      <c r="AC64" s="44">
+        <v>45.2</v>
+      </c>
+      <c r="AD64" s="17">
+        <v>7.3029999999999999</v>
+      </c>
+      <c r="AE64" s="44">
+        <v>300</v>
+      </c>
+      <c r="AF64" s="44">
+        <v>49.9</v>
+      </c>
+      <c r="AG64" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH64" s="45">
         <f t="shared" ref="AH64:AH68" si="78">AF64/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI64" s="44"/>
-      <c r="AJ64" s="44"/>
-      <c r="AK64" s="44"/>
-      <c r="AL64" s="44"/>
+        <v>0.499</v>
+      </c>
+      <c r="AI64" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ64" s="44">
+        <v>24.568000000000001</v>
+      </c>
+      <c r="AK64" s="44">
+        <v>27.469000000000001</v>
+      </c>
+      <c r="AL64" s="44">
+        <f>AL52+1.86</f>
+        <v>4.8600000000000003</v>
+      </c>
       <c r="AM64" s="45">
         <f t="shared" ref="AM64:AM68" si="79">BR64</f>
-        <v>0</v>
-      </c>
-      <c r="AN64" s="44"/>
-      <c r="AO64" s="44"/>
-      <c r="AP64" s="44"/>
-      <c r="AQ64" s="44"/>
+        <v>1.1401776999282799E-2</v>
+      </c>
+      <c r="AN64" s="44">
+        <v>185.31</v>
+      </c>
+      <c r="AO64" s="44">
+        <v>68.25</v>
+      </c>
+      <c r="AP64" s="44">
+        <v>481</v>
+      </c>
+      <c r="AQ64" s="44">
+        <v>1988</v>
+      </c>
       <c r="AR64" s="45">
         <v>45.769999999999982</v>
       </c>
       <c r="AS64" s="45">
         <f t="shared" si="60"/>
-        <v>-45.769999999999982</v>
+        <v>1942.23</v>
       </c>
       <c r="AT64" s="45">
         <f t="shared" si="36"/>
-        <v>-167.56</v>
+        <v>17.75</v>
       </c>
       <c r="AU64" s="45">
         <f t="shared" si="37"/>
-        <v>-61.42</v>
+        <v>6.8299999999999983</v>
       </c>
       <c r="AV64" s="45">
         <f t="shared" si="65"/>
-        <v>501</v>
+        <v>20</v>
       </c>
       <c r="AW64" s="25">
         <v>15</v>
@@ -15561,39 +15762,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC64" s="11"/>
-      <c r="BD64" s="46"/>
-      <c r="BE64" s="22"/>
+      <c r="BD64" s="46">
+        <f>BM64*24*60/BH64</f>
+        <v>8.8967442096820649E-3</v>
+      </c>
+      <c r="BE64" s="22">
+        <f>BP64/BH64</f>
+        <v>5.5208033108114681E-3</v>
+      </c>
       <c r="BF64" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.068519603E-2</v>
       </c>
       <c r="BG64" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>15.386682283200003</v>
       </c>
       <c r="BH64" s="46">
         <f t="shared" si="41"/>
-        <v>1535</v>
-      </c>
-      <c r="BI64" s="47" t="str">
+        <v>1845.4569999999999</v>
+      </c>
+      <c r="BI64" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ64" s="47" t="str">
+        <v>0.10041415215851685</v>
+      </c>
+      <c r="BJ64" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0.10900588235294117</v>
       </c>
       <c r="BK64" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>16.418558878967232</v>
       </c>
       <c r="BL64" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM64" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>1.1401776999282799E-2</v>
       </c>
       <c r="BN64" s="48" t="str">
         <f t="shared" si="32"/>
@@ -15604,20 +15810,19 @@
         <v/>
       </c>
       <c r="BP64" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>10.188405115560199</v>
       </c>
       <c r="BQ64" s="28">
         <f t="shared" ref="BQ64:BQ68" si="80">IF(BL64&lt;&gt;"",BL64/0.000385,IF(BM64&lt;&gt;"",BM64/0.000385,BN64/0.000385))</f>
-        <v>0</v>
+        <v>29.615005192942338</v>
       </c>
       <c r="BR64" s="49">
         <f t="shared" ref="BR64:BR68" si="81">IF(BL64&lt;&gt;"",BL64,IF(BM64&lt;&gt;"",BM64,BN64))</f>
-        <v>0</v>
+        <v>1.1401776999282799E-2</v>
       </c>
       <c r="BS64" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>10.188405115560199</v>
       </c>
     </row>
     <row r="65" spans="1:71" x14ac:dyDescent="0.3">
@@ -15633,70 +15838,137 @@
       <c r="D65">
         <v>10</v>
       </c>
-      <c r="F65" s="61"/>
+      <c r="F65" s="61">
+        <v>45543.423032407401</v>
+      </c>
       <c r="G65" s="64">
         <v>5497.99</v>
       </c>
       <c r="H65" s="44"/>
-      <c r="I65" s="44"/>
-      <c r="J65" s="44"/>
-      <c r="K65" s="44"/>
-      <c r="L65" s="44"/>
-      <c r="M65" s="44"/>
-      <c r="N65" s="44"/>
-      <c r="O65" s="44"/>
-      <c r="P65" s="44"/>
-      <c r="Q65" s="44"/>
+      <c r="I65" s="44">
+        <v>5235.63</v>
+      </c>
+      <c r="J65" s="44">
+        <v>20.2</v>
+      </c>
+      <c r="K65" s="44">
+        <v>18</v>
+      </c>
+      <c r="L65" s="44">
+        <v>89.1</v>
+      </c>
+      <c r="M65" s="44">
+        <v>19.2</v>
+      </c>
+      <c r="N65" s="44">
+        <v>438</v>
+      </c>
+      <c r="O65" s="44">
+        <v>2.36</v>
+      </c>
+      <c r="P65" s="44">
+        <v>0.22</v>
+      </c>
+      <c r="Q65" s="44">
+        <v>3.22</v>
+      </c>
       <c r="R65" s="44"/>
-      <c r="S65" s="44"/>
-      <c r="T65" s="44"/>
-      <c r="U65" s="44"/>
-      <c r="V65" s="44"/>
-      <c r="W65" s="44"/>
-      <c r="X65" s="44"/>
-      <c r="Y65" s="44"/>
-      <c r="Z65" s="44"/>
-      <c r="AA65" s="44"/>
-      <c r="AB65" s="44"/>
-      <c r="AC65" s="44"/>
-      <c r="AD65" s="17"/>
-      <c r="AE65" s="44"/>
-      <c r="AF65" s="44"/>
-      <c r="AG65" s="44"/>
+      <c r="S65" s="44">
+        <v>0.78</v>
+      </c>
+      <c r="T65" s="44">
+        <v>2.21</v>
+      </c>
+      <c r="U65" s="44">
+        <v>2.19</v>
+      </c>
+      <c r="V65" s="44">
+        <v>7.2469999999999999</v>
+      </c>
+      <c r="W65" s="44">
+        <v>118.5</v>
+      </c>
+      <c r="X65" s="44">
+        <v>46.8</v>
+      </c>
+      <c r="Y65" s="44">
+        <v>1.5</v>
+      </c>
+      <c r="Z65" s="44">
+        <v>176.3</v>
+      </c>
+      <c r="AA65" s="44">
+        <v>50.2</v>
+      </c>
+      <c r="AB65" s="44">
+        <v>104</v>
+      </c>
+      <c r="AC65" s="44">
+        <v>37.9</v>
+      </c>
+      <c r="AD65" s="17">
+        <v>7.2880000000000003</v>
+      </c>
+      <c r="AE65" s="44">
+        <v>298</v>
+      </c>
+      <c r="AF65" s="44">
+        <v>50.4</v>
+      </c>
+      <c r="AG65" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH65" s="45">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="AI65" s="44"/>
-      <c r="AJ65" s="44"/>
-      <c r="AK65" s="44"/>
-      <c r="AL65" s="44"/>
+        <v>0.504</v>
+      </c>
+      <c r="AI65" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ65" s="44">
+        <v>38.045999999999999</v>
+      </c>
+      <c r="AK65" s="44">
+        <v>5.1144999999999996</v>
+      </c>
+      <c r="AL65" s="44">
+        <f>AL53+1.87</f>
+        <v>8.5300000000000011</v>
+      </c>
       <c r="AM65" s="45">
         <f t="shared" si="79"/>
-        <v>0</v>
-      </c>
-      <c r="AN65" s="44"/>
-      <c r="AO65" s="44"/>
-      <c r="AP65" s="44"/>
-      <c r="AQ65" s="44"/>
+        <v>2.08588154275034E-2</v>
+      </c>
+      <c r="AN65" s="44">
+        <v>249.44</v>
+      </c>
+      <c r="AO65" s="44">
+        <v>84.76</v>
+      </c>
+      <c r="AP65" s="44">
+        <v>384</v>
+      </c>
+      <c r="AQ65" s="44">
+        <v>2061</v>
+      </c>
       <c r="AR65" s="45">
         <v>84.700000000000045</v>
       </c>
       <c r="AS65" s="45">
         <f t="shared" si="60"/>
-        <v>-84.700000000000045</v>
+        <v>1976.3</v>
       </c>
       <c r="AT65" s="45">
         <f t="shared" si="36"/>
-        <v>-211.31</v>
+        <v>38.129999999999995</v>
       </c>
       <c r="AU65" s="45">
         <f t="shared" si="37"/>
-        <v>-76.27</v>
+        <v>8.4900000000000091</v>
       </c>
       <c r="AV65" s="45">
         <f t="shared" si="65"/>
-        <v>430</v>
+        <v>46</v>
       </c>
       <c r="AW65" s="25">
         <v>15</v>
@@ -15717,39 +15989,44 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC65" s="11"/>
-      <c r="BD65" s="46"/>
-      <c r="BE65" s="22"/>
+      <c r="BD65" s="46">
+        <f>BM65*24*60/BH65</f>
+        <v>1.5636859162771067E-2</v>
+      </c>
+      <c r="BE65" s="22">
+        <f>BP65/BH65</f>
+        <v>1.6524849493275854E-3</v>
+      </c>
       <c r="BF65" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.0372808699999998E-2</v>
       </c>
       <c r="BG65" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.936844527999996</v>
       </c>
       <c r="BH65" s="46">
         <f t="shared" si="41"/>
-        <v>1535</v>
-      </c>
-      <c r="BI65" s="47" t="str">
+        <v>1920.8905</v>
+      </c>
+      <c r="BI65" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ65" s="47" t="str">
+        <v>0.12985643897973362</v>
+      </c>
+      <c r="BJ65" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0.14672941176470589</v>
       </c>
       <c r="BK65" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>30.036694215604896</v>
       </c>
       <c r="BL65" s="47" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="BM65" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <v>2.08588154275034E-2</v>
       </c>
       <c r="BN65" s="48" t="str">
         <f t="shared" si="32"/>
@@ -15760,20 +16037,19 @@
         <v/>
       </c>
       <c r="BP65" s="51">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>3.17424264055634</v>
       </c>
       <c r="BQ65" s="28">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>54.178741370138702</v>
       </c>
       <c r="BR65" s="49">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>2.08588154275034E-2</v>
       </c>
       <c r="BS65" s="30">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>3.17424264055634</v>
       </c>
     </row>
     <row r="66" spans="1:71" x14ac:dyDescent="0.3">
@@ -15789,70 +16065,137 @@
       <c r="D66">
         <v>10</v>
       </c>
-      <c r="F66" s="61"/>
+      <c r="F66" s="61">
+        <v>45543.425671296303</v>
+      </c>
       <c r="G66" s="64">
         <v>5497.99</v>
       </c>
       <c r="H66" s="44"/>
-      <c r="I66" s="44"/>
-      <c r="J66" s="44"/>
-      <c r="K66" s="44"/>
-      <c r="L66" s="44"/>
-      <c r="M66" s="44"/>
-      <c r="N66" s="44"/>
-      <c r="O66" s="44"/>
-      <c r="P66" s="44"/>
-      <c r="Q66" s="44"/>
+      <c r="I66" s="44">
+        <v>5350.9049999999997</v>
+      </c>
+      <c r="J66" s="44">
+        <v>20.2</v>
+      </c>
+      <c r="K66" s="44">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="L66" s="44">
+        <v>89.7</v>
+      </c>
+      <c r="M66" s="44">
+        <v>19</v>
+      </c>
+      <c r="N66" s="44">
+        <v>430</v>
+      </c>
+      <c r="O66" s="44">
+        <v>1.71</v>
+      </c>
+      <c r="P66" s="44">
+        <v>0.21</v>
+      </c>
+      <c r="Q66" s="44">
+        <v>1.31</v>
+      </c>
       <c r="R66" s="44"/>
-      <c r="S66" s="44"/>
-      <c r="T66" s="44"/>
-      <c r="U66" s="44"/>
-      <c r="V66" s="44"/>
-      <c r="W66" s="44"/>
-      <c r="X66" s="44"/>
-      <c r="Y66" s="44"/>
-      <c r="Z66" s="44"/>
-      <c r="AA66" s="44"/>
-      <c r="AB66" s="44"/>
-      <c r="AC66" s="44"/>
-      <c r="AD66" s="17"/>
-      <c r="AE66" s="44"/>
-      <c r="AF66" s="44"/>
-      <c r="AG66" s="44"/>
+      <c r="S66" s="44">
+        <v>0.6</v>
+      </c>
+      <c r="T66" s="44">
+        <v>2.08</v>
+      </c>
+      <c r="U66" s="44">
+        <v>2.54</v>
+      </c>
+      <c r="V66" s="44">
+        <v>7.2779999999999996</v>
+      </c>
+      <c r="W66" s="44">
+        <v>128.30000000000001</v>
+      </c>
+      <c r="X66" s="44">
+        <v>30</v>
+      </c>
+      <c r="Y66" s="44">
+        <v>1.48</v>
+      </c>
+      <c r="Z66" s="44">
+        <v>183.1</v>
+      </c>
+      <c r="AA66" s="44">
+        <v>58.4</v>
+      </c>
+      <c r="AB66" s="44">
+        <v>112.5</v>
+      </c>
+      <c r="AC66" s="44">
+        <v>24.3</v>
+      </c>
+      <c r="AD66" s="17">
+        <v>7.319</v>
+      </c>
+      <c r="AE66" s="44">
+        <v>301</v>
+      </c>
+      <c r="AF66" s="44">
+        <v>51.1</v>
+      </c>
+      <c r="AG66" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH66" s="45">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="AI66" s="44"/>
-      <c r="AJ66" s="44"/>
-      <c r="AK66" s="44"/>
-      <c r="AL66" s="44"/>
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="AI66" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ66" s="44">
+        <v>43.091000000000001</v>
+      </c>
+      <c r="AK66" s="44">
+        <v>13.548</v>
+      </c>
+      <c r="AL66" s="44">
+        <f>AL54+1.91</f>
+        <v>8.67</v>
+      </c>
       <c r="AM66" s="45">
         <f t="shared" si="79"/>
-        <v>0</v>
-      </c>
-      <c r="AN66" s="44"/>
-      <c r="AO66" s="44"/>
-      <c r="AP66" s="44"/>
-      <c r="AQ66" s="44"/>
+        <v>2.2755468611111111E-2</v>
+      </c>
+      <c r="AN66" s="44">
+        <v>233.93</v>
+      </c>
+      <c r="AO66" s="44">
+        <v>70.87</v>
+      </c>
+      <c r="AP66" s="44">
+        <v>406</v>
+      </c>
+      <c r="AQ66" s="44">
+        <v>2044</v>
+      </c>
       <c r="AR66" s="45">
         <v>47.420000000000073</v>
       </c>
       <c r="AS66" s="45">
-        <f t="shared" si="60"/>
-        <v>-47.420000000000073</v>
+        <f>AQ66-AR66</f>
+        <v>1996.58</v>
       </c>
       <c r="AT66" s="45">
         <f t="shared" si="36"/>
-        <v>-204.07</v>
+        <v>29.860000000000014</v>
       </c>
       <c r="AU66" s="45">
         <f t="shared" si="37"/>
-        <v>-70.87</v>
+        <v>0</v>
       </c>
       <c r="AV66" s="45">
         <f t="shared" si="65"/>
-        <v>443</v>
+        <v>37</v>
       </c>
       <c r="AW66" s="25">
         <v>15</v>
@@ -15872,35 +16215,37 @@
       <c r="BB66" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC66" s="11"/>
+      <c r="BC66" s="11">
+        <v>1.72E-2</v>
+      </c>
       <c r="BE66" s="22"/>
       <c r="BF66" s="11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.034474187E-2</v>
       </c>
       <c r="BG66" s="46">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14.8964282928</v>
       </c>
       <c r="BH66" s="46">
         <f t="shared" si="41"/>
-        <v>1535</v>
-      </c>
-      <c r="BI66" s="47" t="str">
+        <v>1905.1089999999999</v>
+      </c>
+      <c r="BI66" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ66" s="47" t="str">
+        <v>0.12279087443290647</v>
+      </c>
+      <c r="BJ66" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0.13760588235294119</v>
       </c>
       <c r="BK66" s="47">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>32.767874800000001</v>
       </c>
       <c r="BL66" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.2755468611111111E-2</v>
       </c>
       <c r="BM66" s="48" t="str">
         <f t="shared" si="31"/>
@@ -15912,7 +16257,7 @@
       </c>
       <c r="BO66" s="47">
         <f t="shared" si="47"/>
-        <v>11.512499999999999</v>
+        <v>8.0490855249999989</v>
       </c>
       <c r="BP66" s="51" t="str">
         <f t="shared" si="28"/>
@@ -15920,15 +16265,15 @@
       </c>
       <c r="BQ66" s="28">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>59.105113275613277</v>
       </c>
       <c r="BR66" s="49">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>2.2755468611111111E-2</v>
       </c>
       <c r="BS66" s="30">
         <f t="shared" si="21"/>
-        <v>11.512499999999999</v>
+        <v>8.0490855249999989</v>
       </c>
     </row>
     <row r="67" spans="1:71" x14ac:dyDescent="0.3">
@@ -15944,70 +16289,133 @@
       <c r="D67">
         <v>10</v>
       </c>
-      <c r="F67" s="61"/>
+      <c r="F67" s="61">
+        <v>45543.428912037001</v>
+      </c>
       <c r="G67" s="64">
         <v>5497.99</v>
       </c>
       <c r="H67" s="44"/>
-      <c r="I67" s="44"/>
-      <c r="J67" s="44"/>
-      <c r="K67" s="44"/>
-      <c r="L67" s="44"/>
-      <c r="M67" s="44"/>
-      <c r="N67" s="44"/>
+      <c r="I67" s="44">
+        <v>2975.5050000000001</v>
+      </c>
+      <c r="J67" s="44">
+        <v>21.1</v>
+      </c>
+      <c r="K67" s="44">
+        <v>8.32</v>
+      </c>
+      <c r="L67" s="44">
+        <v>39.5</v>
+      </c>
+      <c r="M67" s="44">
+        <v>15.6</v>
+      </c>
+      <c r="N67" s="44">
+        <v>818</v>
+      </c>
       <c r="O67" s="44"/>
-      <c r="P67" s="44"/>
-      <c r="Q67" s="44"/>
+      <c r="P67" s="44">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="Q67" s="44">
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="R67" s="44"/>
-      <c r="S67" s="44"/>
-      <c r="T67" s="44"/>
+      <c r="S67" s="44">
+        <v>0.75</v>
+      </c>
+      <c r="T67" s="44">
+        <v>3.48</v>
+      </c>
       <c r="U67" s="44"/>
-      <c r="V67" s="44"/>
-      <c r="W67" s="44"/>
-      <c r="X67" s="44"/>
-      <c r="Y67" s="44"/>
-      <c r="Z67" s="44"/>
-      <c r="AA67" s="44"/>
-      <c r="AB67" s="44"/>
-      <c r="AC67" s="44"/>
-      <c r="AD67" s="17"/>
-      <c r="AE67" s="44"/>
-      <c r="AF67" s="44"/>
-      <c r="AG67" s="44"/>
+      <c r="V67" s="44">
+        <v>7.032</v>
+      </c>
+      <c r="W67" s="44">
+        <v>66.3</v>
+      </c>
+      <c r="X67" s="44">
+        <v>86</v>
+      </c>
+      <c r="Y67" s="44">
+        <v>7.2</v>
+      </c>
+      <c r="Z67" s="44">
+        <v>327.9</v>
+      </c>
+      <c r="AA67" s="44">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="AB67" s="44">
+        <v>58.1</v>
+      </c>
+      <c r="AC67" s="44">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="AD67" s="17">
+        <v>7.069</v>
+      </c>
+      <c r="AE67" s="44">
+        <v>301</v>
+      </c>
+      <c r="AF67" s="44">
+        <v>45.2</v>
+      </c>
+      <c r="AG67" s="44">
+        <v>7.09</v>
+      </c>
       <c r="AH67" s="45">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="AI67" s="44"/>
-      <c r="AJ67" s="44"/>
-      <c r="AK67" s="44"/>
-      <c r="AL67" s="44"/>
+        <v>0.45200000000000001</v>
+      </c>
+      <c r="AI67" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ67" s="44">
+        <v>157.88999999999999</v>
+      </c>
+      <c r="AK67" s="44">
+        <v>7.3125999999999998</v>
+      </c>
+      <c r="AL67" s="44">
+        <f>AL55+1.84</f>
+        <v>8.2800000000000011</v>
+      </c>
       <c r="AM67" s="45">
         <f t="shared" si="79"/>
-        <v>0</v>
-      </c>
-      <c r="AN67" s="44"/>
-      <c r="AO67" s="44"/>
-      <c r="AP67" s="44"/>
-      <c r="AQ67" s="44"/>
+        <v>2.8444202777777781E-2</v>
+      </c>
+      <c r="AN67" s="44">
+        <v>261.68</v>
+      </c>
+      <c r="AO67" s="44">
+        <v>77.819999999999993</v>
+      </c>
+      <c r="AP67" s="44">
+        <v>353</v>
+      </c>
+      <c r="AQ67" s="44">
+        <v>2185</v>
+      </c>
       <c r="AR67" s="45">
         <v>133.55999999999995</v>
       </c>
       <c r="AS67" s="45">
-        <f t="shared" ref="AS67:AS80" si="82">AQ67-AR67</f>
-        <v>-133.55999999999995</v>
+        <f>AQ67-AR67</f>
+        <v>2051.44</v>
       </c>
       <c r="AT67" s="45">
         <f t="shared" si="36"/>
-        <v>-227.05</v>
+        <v>34.629999999999995</v>
       </c>
       <c r="AU67" s="45">
         <f t="shared" si="37"/>
-        <v>-77.819999999999993</v>
+        <v>0</v>
       </c>
       <c r="AV67" s="45">
         <f t="shared" si="65"/>
-        <v>394</v>
+        <v>41</v>
       </c>
       <c r="AW67" s="25">
         <v>15</v>
@@ -16027,47 +16435,49 @@
       <c r="BB67" s="22">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC67" s="11"/>
+      <c r="BC67" s="11">
+        <v>0.02</v>
+      </c>
       <c r="BE67" s="22"/>
       <c r="BF67" s="11">
-        <f t="shared" ref="BF67:BF74" si="83">BB67*K67*BH67/1000</f>
-        <v>0</v>
+        <f t="shared" ref="BF67:BF74" si="82">BB67*K67*BH67/1000</f>
+        <v>5.1117645696000013E-3</v>
       </c>
       <c r="BG67" s="46">
-        <f t="shared" ref="BG67:BG74" si="84">BF67*24*60</f>
-        <v>0</v>
+        <f t="shared" ref="BG67:BG74" si="83">BF67*24*60</f>
+        <v>7.3609409802240027</v>
       </c>
       <c r="BH67" s="46">
         <f t="shared" si="41"/>
-        <v>1535</v>
-      </c>
-      <c r="BI67" s="47" t="str">
+        <v>2047.9826000000003</v>
+      </c>
+      <c r="BI67" s="47">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="BJ67" s="47" t="str">
+        <v>0.12777452308432696</v>
+      </c>
+      <c r="BJ67" s="47">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0.1539294117647059</v>
       </c>
       <c r="BK67" s="47">
-        <f t="shared" ref="BK67:BK74" si="85">AM67*24*60</f>
-        <v>0</v>
+        <f t="shared" ref="BK67:BK74" si="84">AM67*24*60</f>
+        <v>40.959652000000006</v>
       </c>
       <c r="BL67" s="47">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2.8444202777777781E-2</v>
       </c>
       <c r="BM67" s="48" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BN67" s="48" t="str">
-        <f t="shared" ref="BN67:BN74" si="86">IF(B67="No MPC", BB67*K67*BH67/1000,"")</f>
+        <f t="shared" ref="BN67:BN74" si="85">IF(B67="No MPC", BB67*K67*BH67/1000,"")</f>
         <v/>
       </c>
       <c r="BO67" s="47">
         <f t="shared" si="47"/>
-        <v>11.512499999999999</v>
+        <v>15.001472545000004</v>
       </c>
       <c r="BP67" s="51" t="str">
         <f t="shared" si="28"/>
@@ -16075,15 +16485,15 @@
       </c>
       <c r="BQ67" s="28">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>73.881046176046183</v>
       </c>
       <c r="BR67" s="49">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>2.8444202777777781E-2</v>
       </c>
       <c r="BS67" s="30">
-        <f t="shared" ref="BS67:BS74" si="87">IF(BO67&lt;&gt;"",BO67,BP67)</f>
-        <v>11.512499999999999</v>
+        <f t="shared" ref="BS67:BS74" si="86">IF(BO67&lt;&gt;"",BO67,BP67)</f>
+        <v>15.001472545000004</v>
       </c>
     </row>
     <row r="68" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -16100,70 +16510,137 @@
         <v>10</v>
       </c>
       <c r="E68" s="5"/>
-      <c r="F68" s="62"/>
+      <c r="F68" s="62">
+        <v>45543.4315740741</v>
+      </c>
       <c r="G68" s="65">
         <v>5497.99</v>
       </c>
       <c r="H68" s="7"/>
-      <c r="I68" s="7"/>
-      <c r="J68" s="7"/>
-      <c r="K68" s="7"/>
-      <c r="L68" s="7"/>
-      <c r="M68" s="7"/>
-      <c r="N68" s="7"/>
-      <c r="O68" s="7"/>
-      <c r="P68" s="7"/>
-      <c r="Q68" s="7"/>
+      <c r="I68" s="7">
+        <v>5979</v>
+      </c>
+      <c r="J68" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="K68" s="7">
+        <v>19.7</v>
+      </c>
+      <c r="L68" s="7">
+        <v>92</v>
+      </c>
+      <c r="M68" s="7">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="N68" s="7">
+        <v>367</v>
+      </c>
+      <c r="O68" s="7">
+        <v>1.57</v>
+      </c>
+      <c r="P68" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="Q68" s="7">
+        <v>0.66</v>
+      </c>
       <c r="R68" s="7"/>
-      <c r="S68" s="7"/>
-      <c r="T68" s="7"/>
-      <c r="U68" s="7"/>
-      <c r="V68" s="7"/>
-      <c r="W68" s="7"/>
-      <c r="X68" s="7"/>
-      <c r="Y68" s="7"/>
-      <c r="Z68" s="7"/>
-      <c r="AA68" s="7"/>
-      <c r="AB68" s="7"/>
-      <c r="AC68" s="7"/>
-      <c r="AD68" s="18"/>
-      <c r="AE68" s="7"/>
-      <c r="AF68" s="7"/>
-      <c r="AG68" s="7"/>
+      <c r="S68" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="T68" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="U68" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="V68" s="7">
+        <v>7.2640000000000002</v>
+      </c>
+      <c r="W68" s="7">
+        <v>120.2</v>
+      </c>
+      <c r="X68" s="7">
+        <v>31.7</v>
+      </c>
+      <c r="Y68" s="7">
+        <v>1.79</v>
+      </c>
+      <c r="Z68" s="7">
+        <v>160</v>
+      </c>
+      <c r="AA68" s="7">
+        <v>53</v>
+      </c>
+      <c r="AB68" s="7">
+        <v>105.4</v>
+      </c>
+      <c r="AC68" s="7">
+        <v>25.6</v>
+      </c>
+      <c r="AD68" s="18">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="AE68" s="7">
+        <v>299</v>
+      </c>
+      <c r="AF68" s="7">
+        <v>49.3</v>
+      </c>
+      <c r="AG68" s="7">
+        <v>7.3</v>
+      </c>
       <c r="AH68" s="41">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="AI68" s="7"/>
-      <c r="AJ68" s="7"/>
-      <c r="AK68" s="7"/>
-      <c r="AL68" s="7"/>
+        <v>0.49299999999999999</v>
+      </c>
+      <c r="AI68" s="7">
+        <v>34</v>
+      </c>
+      <c r="AJ68" s="7">
+        <v>28.271000000000001</v>
+      </c>
+      <c r="AK68" s="7">
+        <v>45.024999999999999</v>
+      </c>
+      <c r="AL68" s="7">
+        <f>AL56+1.86</f>
+        <v>8.379999999999999</v>
+      </c>
       <c r="AM68" s="41">
         <f t="shared" si="79"/>
-        <v>0</v>
-      </c>
-      <c r="AN68" s="7"/>
-      <c r="AO68" s="7"/>
-      <c r="AP68" s="7"/>
-      <c r="AQ68" s="7"/>
+        <v>1.0622002499999998E-2</v>
+      </c>
+      <c r="AN68" s="7">
+        <v>201.93</v>
+      </c>
+      <c r="AO68" s="7">
+        <v>69.75</v>
+      </c>
+      <c r="AP68" s="7">
+        <v>460</v>
+      </c>
+      <c r="AQ68" s="7">
+        <v>2025</v>
+      </c>
       <c r="AR68" s="41">
         <v>51.660000000000082</v>
       </c>
       <c r="AS68" s="41">
-        <f t="shared" si="82"/>
-        <v>-51.660000000000082</v>
+        <f>AQ68-AR68</f>
+        <v>1973.34</v>
       </c>
       <c r="AT68" s="41">
         <f t="shared" si="36"/>
-        <v>-187.96</v>
+        <v>13.969999999999999</v>
       </c>
       <c r="AU68" s="41">
         <f t="shared" si="37"/>
-        <v>-56.59</v>
+        <v>13.159999999999997</v>
       </c>
       <c r="AV68" s="41">
         <f t="shared" si="65"/>
-        <v>476</v>
+        <v>16</v>
       </c>
       <c r="AW68" s="26">
         <v>15</v>
@@ -16183,48 +16660,50 @@
       <c r="BB68" s="23">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="BC68" s="12"/>
+      <c r="BC68" s="12">
+        <v>8.0999999999999996E-3</v>
+      </c>
       <c r="BD68" s="5"/>
       <c r="BE68" s="23"/>
       <c r="BF68" s="12">
+        <f t="shared" si="82"/>
+        <v>1.1160183959999999E-2</v>
+      </c>
+      <c r="BG68" s="13">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="BG68" s="13">
-        <f t="shared" si="84"/>
-        <v>0</v>
+        <v>16.070664902399997</v>
       </c>
       <c r="BH68" s="13">
         <f t="shared" si="41"/>
-        <v>1535</v>
-      </c>
-      <c r="BI68" s="14" t="str">
-        <f t="shared" ref="BI68:BI80" si="88">IF(ISBLANK(AN68),"",IFERROR(AN68/BH68,0))</f>
-        <v/>
-      </c>
-      <c r="BJ68" s="14" t="str">
-        <f t="shared" ref="BJ68:BJ80" si="89">IF(ISBLANK(AN68),"",AN68/AX68)</f>
-        <v/>
+        <v>1888.3559999999998</v>
+      </c>
+      <c r="BI68" s="14">
+        <f t="shared" ref="BI68:BI80" si="87">IF(ISBLANK(AN68),"",IFERROR(AN68/BH68,0))</f>
+        <v>0.10693428569612935</v>
+      </c>
+      <c r="BJ68" s="14">
+        <f t="shared" ref="BJ68:BJ80" si="88">IF(ISBLANK(AN68),"",AN68/AX68)</f>
+        <v>0.11878235294117648</v>
       </c>
       <c r="BK68" s="14">
-        <f t="shared" si="85"/>
-        <v>0</v>
+        <f t="shared" si="84"/>
+        <v>15.295683599999997</v>
       </c>
       <c r="BL68" s="14">
-        <f t="shared" ref="BL68:BL80" si="90">IF(B68="Python",BC68*BH68/24/60,"")</f>
-        <v>0</v>
+        <f t="shared" ref="BL68:BL80" si="89">IF(B68="Python",BC68*BH68/24/60,"")</f>
+        <v>1.0622002499999998E-2</v>
       </c>
       <c r="BM68" s="48" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="BN68" s="36" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v/>
       </c>
       <c r="BO68" s="14">
         <f t="shared" si="47"/>
-        <v>11.512499999999999</v>
+        <v>11.046882599999998</v>
       </c>
       <c r="BP68" s="52" t="str">
         <f t="shared" si="28"/>
@@ -16232,15 +16711,15 @@
       </c>
       <c r="BQ68" s="29">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>27.589616883116879</v>
       </c>
       <c r="BR68" s="38">
         <f t="shared" si="81"/>
-        <v>0</v>
+        <v>1.0622002499999998E-2</v>
       </c>
       <c r="BS68" s="31">
-        <f t="shared" si="87"/>
-        <v>11.512499999999999</v>
+        <f t="shared" si="86"/>
+        <v>11.046882599999998</v>
       </c>
     </row>
     <row r="69" spans="1:71" x14ac:dyDescent="0.3">
@@ -16257,70 +16736,137 @@
         <v>11</v>
       </c>
       <c r="E69" s="3"/>
-      <c r="F69" s="60"/>
+      <c r="F69" s="60">
+        <v>45544.577546296299</v>
+      </c>
       <c r="G69" s="63">
         <v>6057.48</v>
       </c>
       <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="6"/>
-      <c r="L69" s="6"/>
-      <c r="M69" s="6"/>
-      <c r="N69" s="6"/>
-      <c r="O69" s="6"/>
-      <c r="P69" s="6"/>
-      <c r="Q69" s="6"/>
+      <c r="I69" s="6">
+        <v>5674.0649999999996</v>
+      </c>
+      <c r="J69" s="6">
+        <v>22.2</v>
+      </c>
+      <c r="K69" s="6">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="L69" s="6">
+        <v>89.7</v>
+      </c>
+      <c r="M69" s="6">
+        <v>17</v>
+      </c>
+      <c r="N69" s="6">
+        <v>355</v>
+      </c>
+      <c r="O69" s="6">
+        <v>1.72</v>
+      </c>
+      <c r="P69" s="6">
+        <v>0.21</v>
+      </c>
+      <c r="Q69" s="6">
+        <v>0</v>
+      </c>
       <c r="R69" s="6"/>
-      <c r="S69" s="6"/>
-      <c r="T69" s="6"/>
-      <c r="U69" s="6"/>
-      <c r="V69" s="6"/>
-      <c r="W69" s="6"/>
-      <c r="X69" s="6"/>
-      <c r="Y69" s="6"/>
-      <c r="Z69" s="6"/>
-      <c r="AA69" s="6"/>
-      <c r="AB69" s="6"/>
-      <c r="AC69" s="6"/>
-      <c r="AD69" s="16"/>
-      <c r="AE69" s="6"/>
-      <c r="AF69" s="6"/>
-      <c r="AG69" s="6"/>
+      <c r="S69" s="6">
+        <v>0.17</v>
+      </c>
+      <c r="T69" s="6">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="U69" s="6">
+        <v>2.37</v>
+      </c>
+      <c r="V69" s="6">
+        <v>7.2590000000000003</v>
+      </c>
+      <c r="W69" s="6">
+        <v>51.3</v>
+      </c>
+      <c r="X69" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="6">
+        <v>3.44</v>
+      </c>
+      <c r="Z69" s="6">
+        <v>151.1</v>
+      </c>
+      <c r="AA69" s="6">
+        <v>22.4</v>
+      </c>
+      <c r="AB69" s="6">
+        <v>45</v>
+      </c>
+      <c r="AC69" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="16">
+        <v>7.3</v>
+      </c>
+      <c r="AE69" s="6">
+        <v>299</v>
+      </c>
+      <c r="AF69" s="6">
+        <v>40.5</v>
+      </c>
+      <c r="AG69" s="6">
+        <v>7.3</v>
+      </c>
       <c r="AH69" s="40">
         <f>AF69/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI69" s="6"/>
-      <c r="AJ69" s="6"/>
-      <c r="AK69" s="44"/>
-      <c r="AL69" s="6"/>
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="AI69" s="6">
+        <v>34</v>
+      </c>
+      <c r="AJ69" s="6">
+        <v>27.91</v>
+      </c>
+      <c r="AK69" s="44">
+        <v>47.91</v>
+      </c>
+      <c r="AL69" s="6">
+        <f>AL51+3.09</f>
+        <v>8.379999999999999</v>
+      </c>
       <c r="AM69" s="42">
         <f>BR69</f>
-        <v>0</v>
-      </c>
-      <c r="AN69" s="6"/>
-      <c r="AO69" s="6"/>
-      <c r="AP69" s="6"/>
-      <c r="AQ69" s="6"/>
+        <v>2.7214024885993001E-2</v>
+      </c>
+      <c r="AN69" s="6">
+        <v>181.29</v>
+      </c>
+      <c r="AO69" s="6">
+        <v>73.31</v>
+      </c>
+      <c r="AP69" s="6">
+        <v>485</v>
+      </c>
+      <c r="AQ69" s="6">
+        <v>1912</v>
+      </c>
       <c r="AR69" s="40">
         <v>137.11999999999989</v>
       </c>
       <c r="AS69" s="40">
-        <f t="shared" si="82"/>
-        <v>-137.11999999999989</v>
+        <f t="shared" ref="AS69:AS80" si="90">AQ69-AR69</f>
+        <v>1774.88</v>
       </c>
       <c r="AT69" s="40">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>11.400000000000006</v>
       </c>
       <c r="AU69" s="40">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV69" s="40">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW69" s="24">
         <v>15</v>
@@ -16341,42 +16887,47 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC69" s="8"/>
-      <c r="BD69" s="9"/>
-      <c r="BE69" s="21"/>
+      <c r="BD69" s="46">
+        <f>BM69*24*60/BH69</f>
+        <v>2.1082524120846741E-2</v>
+      </c>
+      <c r="BE69" s="22">
+        <f>BP69/BH69</f>
+        <v>5.1774073553105659E-3</v>
+      </c>
       <c r="BF69" s="8">
+        <f t="shared" si="82"/>
+        <v>1.1097035999999998E-2</v>
+      </c>
+      <c r="BG69" s="9">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="BG69" s="9">
-        <f t="shared" si="84"/>
-        <v>0</v>
+        <v>15.979731839999996</v>
       </c>
       <c r="BH69" s="9">
         <f t="shared" si="41"/>
-        <v>1520</v>
-      </c>
-      <c r="BI69" s="10" t="str">
+        <v>1858.8</v>
+      </c>
+      <c r="BI69" s="10">
+        <f t="shared" si="87"/>
+        <v>9.7530664945125883E-2</v>
+      </c>
+      <c r="BJ69" s="10">
         <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ69" s="10" t="str">
+        <v>0.10664117647058823</v>
+      </c>
+      <c r="BK69" s="10">
+        <f t="shared" si="84"/>
+        <v>39.188195835829923</v>
+      </c>
+      <c r="BL69" s="10" t="str">
         <f t="shared" si="89"/>
         <v/>
       </c>
-      <c r="BK69" s="10">
+      <c r="BM69" s="10">
+        <v>2.7214024885993001E-2</v>
+      </c>
+      <c r="BN69" s="35" t="str">
         <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-      <c r="BL69" s="10" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="BM69" s="10">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="BN69" s="35" t="str">
-        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="BO69" s="10" t="str">
@@ -16384,20 +16935,19 @@
         <v/>
       </c>
       <c r="BP69" s="50">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <v>9.6237647920512792</v>
       </c>
       <c r="BQ69" s="27">
         <f>IF(BL69&lt;&gt;"",BL69/0.000385,IF(BM69&lt;&gt;"",BM69/0.000385,BN69/0.000385))</f>
-        <v>0</v>
+        <v>70.685778924657143</v>
       </c>
       <c r="BR69" s="37">
         <f>IF(BL69&lt;&gt;"",BL69,IF(BM69&lt;&gt;"",BM69,BN69))</f>
-        <v>0</v>
+        <v>2.7214024885993001E-2</v>
       </c>
       <c r="BS69" s="32">
-        <f t="shared" si="87"/>
-        <v>0</v>
+        <f t="shared" si="86"/>
+        <v>9.6237647920512792</v>
       </c>
     </row>
     <row r="70" spans="1:71" x14ac:dyDescent="0.3">
@@ -16413,70 +16963,137 @@
       <c r="D70">
         <v>11</v>
       </c>
-      <c r="F70" s="61"/>
+      <c r="F70" s="61">
+        <v>45544.6039467593</v>
+      </c>
       <c r="G70" s="64">
         <v>6057.48</v>
       </c>
       <c r="H70" s="44"/>
-      <c r="I70" s="44"/>
-      <c r="J70" s="44"/>
-      <c r="K70" s="44"/>
-      <c r="L70" s="44"/>
-      <c r="M70" s="44"/>
-      <c r="N70" s="44"/>
-      <c r="O70" s="44"/>
-      <c r="P70" s="44"/>
-      <c r="Q70" s="44"/>
+      <c r="I70" s="44">
+        <v>6019.3950000000004</v>
+      </c>
+      <c r="J70" s="44">
+        <v>18.8</v>
+      </c>
+      <c r="K70" s="44">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="L70" s="44">
+        <v>90.8</v>
+      </c>
+      <c r="M70" s="44">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="N70" s="44">
+        <v>351</v>
+      </c>
+      <c r="O70" s="44">
+        <v>2.5</v>
+      </c>
+      <c r="P70" s="44">
+        <v>0.21</v>
+      </c>
+      <c r="Q70" s="44">
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="R70" s="44"/>
-      <c r="S70" s="44"/>
-      <c r="T70" s="44"/>
-      <c r="U70" s="44"/>
-      <c r="V70" s="44"/>
-      <c r="W70" s="44"/>
-      <c r="X70" s="44"/>
-      <c r="Y70" s="44"/>
-      <c r="Z70" s="44"/>
-      <c r="AA70" s="44"/>
-      <c r="AB70" s="44"/>
-      <c r="AC70" s="44"/>
-      <c r="AD70" s="17"/>
-      <c r="AE70" s="44"/>
-      <c r="AF70" s="44"/>
-      <c r="AG70" s="44"/>
+      <c r="S70" s="44">
+        <v>0</v>
+      </c>
+      <c r="T70" s="44">
+        <v>0.16</v>
+      </c>
+      <c r="U70" s="44">
+        <v>0</v>
+      </c>
+      <c r="V70" s="44">
+        <v>7.2969999999999997</v>
+      </c>
+      <c r="W70" s="44">
+        <v>113.3</v>
+      </c>
+      <c r="X70" s="44">
+        <v>68.3</v>
+      </c>
+      <c r="Y70" s="44">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="Z70" s="44">
+        <v>155.69999999999999</v>
+      </c>
+      <c r="AA70" s="44">
+        <v>54</v>
+      </c>
+      <c r="AB70" s="44">
+        <v>99.3</v>
+      </c>
+      <c r="AC70" s="44">
+        <v>55.7</v>
+      </c>
+      <c r="AD70" s="17">
+        <v>7.34</v>
+      </c>
+      <c r="AE70" s="44">
+        <v>300</v>
+      </c>
+      <c r="AF70" s="44">
+        <v>48.3</v>
+      </c>
+      <c r="AG70" s="44">
+        <v>7.27</v>
+      </c>
       <c r="AH70" s="45">
         <f t="shared" ref="AH70:AH74" si="91">AF70/100</f>
-        <v>0</v>
-      </c>
-      <c r="AI70" s="44"/>
-      <c r="AJ70" s="44"/>
-      <c r="AK70" s="44"/>
-      <c r="AL70" s="44"/>
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="AI70" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ70" s="44">
+        <v>24.57</v>
+      </c>
+      <c r="AK70" s="44">
+        <v>27.96</v>
+      </c>
+      <c r="AL70" s="44">
+        <f>AL52+3.01</f>
+        <v>6.01</v>
+      </c>
       <c r="AM70" s="45">
         <f t="shared" ref="AM70:AM74" si="92">BR70</f>
-        <v>0</v>
-      </c>
-      <c r="AN70" s="44"/>
-      <c r="AO70" s="44"/>
-      <c r="AP70" s="44"/>
-      <c r="AQ70" s="44"/>
+        <v>1.7809574480595398E-2</v>
+      </c>
+      <c r="AN70" s="44">
+        <v>205.53</v>
+      </c>
+      <c r="AO70" s="44">
+        <v>79.069999999999993</v>
+      </c>
+      <c r="AP70" s="44">
+        <v>458</v>
+      </c>
+      <c r="AQ70" s="44">
+        <v>1845</v>
+      </c>
       <c r="AR70" s="45">
         <v>45.769999999999982</v>
       </c>
       <c r="AS70" s="45">
-        <f t="shared" si="82"/>
-        <v>-45.769999999999982</v>
+        <f t="shared" si="90"/>
+        <v>1799.23</v>
       </c>
       <c r="AT70" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>20.22</v>
       </c>
       <c r="AU70" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>10.819999999999993</v>
       </c>
       <c r="AV70" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AW70" s="25">
         <v>15</v>
@@ -16497,42 +17114,47 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC70" s="11"/>
-      <c r="BD70" s="46"/>
-      <c r="BE70" s="22"/>
+      <c r="BD70" s="46">
+        <f>BM70*24*60/BH70</f>
+        <v>1.3764820277626683E-2</v>
+      </c>
+      <c r="BE70" s="22">
+        <f>BP70/BH70</f>
+        <v>4.396909262276265E-3</v>
+      </c>
       <c r="BF70" s="11">
+        <f t="shared" si="82"/>
+        <v>9.5579081999999996E-3</v>
+      </c>
+      <c r="BG70" s="46">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="BG70" s="46">
-        <f t="shared" si="84"/>
-        <v>0</v>
+        <v>13.763387807999999</v>
       </c>
       <c r="BH70" s="46">
         <f t="shared" si="41"/>
-        <v>1520</v>
-      </c>
-      <c r="BI70" s="47" t="str">
+        <v>1863.1399999999999</v>
+      </c>
+      <c r="BI70" s="47">
+        <f t="shared" si="87"/>
+        <v>0.1103137713752053</v>
+      </c>
+      <c r="BJ70" s="47">
         <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ70" s="47" t="str">
+        <v>0.12090000000000001</v>
+      </c>
+      <c r="BK70" s="47">
+        <f t="shared" si="84"/>
+        <v>25.645787252057374</v>
+      </c>
+      <c r="BL70" s="47" t="str">
         <f t="shared" si="89"/>
         <v/>
       </c>
-      <c r="BK70" s="47">
+      <c r="BM70" s="47">
+        <v>1.7809574480595398E-2</v>
+      </c>
+      <c r="BN70" s="48" t="str">
         <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-      <c r="BL70" s="47" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="BM70" s="47">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="BN70" s="48" t="str">
-        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="BO70" s="47" t="str">
@@ -16540,20 +17162,19 @@
         <v/>
       </c>
       <c r="BP70" s="51">
-        <f t="shared" ref="BP70:BP80" si="93">IF(B70="Julia",BE70*BH70,"")</f>
-        <v>0</v>
+        <v>8.1920575229174002</v>
       </c>
       <c r="BQ70" s="28">
-        <f t="shared" ref="BQ70:BQ74" si="94">IF(BL70&lt;&gt;"",BL70/0.000385,IF(BM70&lt;&gt;"",BM70/0.000385,BN70/0.000385))</f>
-        <v>0</v>
+        <f t="shared" ref="BQ70:BQ74" si="93">IF(BL70&lt;&gt;"",BL70/0.000385,IF(BM70&lt;&gt;"",BM70/0.000385,BN70/0.000385))</f>
+        <v>46.258635014533503</v>
       </c>
       <c r="BR70" s="49">
-        <f t="shared" ref="BR70:BR74" si="95">IF(BL70&lt;&gt;"",BL70,IF(BM70&lt;&gt;"",BM70,BN70))</f>
-        <v>0</v>
+        <f t="shared" ref="BR70:BR74" si="94">IF(BL70&lt;&gt;"",BL70,IF(BM70&lt;&gt;"",BM70,BN70))</f>
+        <v>1.7809574480595398E-2</v>
       </c>
       <c r="BS70" s="30">
-        <f t="shared" si="87"/>
-        <v>0</v>
+        <f t="shared" si="86"/>
+        <v>8.1920575229174002</v>
       </c>
     </row>
     <row r="71" spans="1:71" x14ac:dyDescent="0.3">
@@ -16569,70 +17190,137 @@
       <c r="D71">
         <v>11</v>
       </c>
-      <c r="F71" s="61"/>
+      <c r="F71" s="61">
+        <v>45544.5913657407</v>
+      </c>
       <c r="G71" s="64">
         <v>6057.48</v>
       </c>
       <c r="H71" s="44"/>
-      <c r="I71" s="44"/>
-      <c r="J71" s="44"/>
-      <c r="K71" s="44"/>
-      <c r="L71" s="44"/>
-      <c r="M71" s="44"/>
-      <c r="N71" s="44"/>
-      <c r="O71" s="44"/>
-      <c r="P71" s="44"/>
-      <c r="Q71" s="44"/>
+      <c r="I71" s="44">
+        <v>5282.2049999999999</v>
+      </c>
+      <c r="J71" s="44">
+        <v>19.2</v>
+      </c>
+      <c r="K71" s="44">
+        <v>16.5</v>
+      </c>
+      <c r="L71" s="44">
+        <v>86</v>
+      </c>
+      <c r="M71" s="44">
+        <v>19</v>
+      </c>
+      <c r="N71" s="44">
+        <v>446</v>
+      </c>
+      <c r="O71" s="44">
+        <v>2.98</v>
+      </c>
+      <c r="P71" s="44">
+        <v>0.2</v>
+      </c>
+      <c r="Q71" s="44">
+        <v>2.21</v>
+      </c>
       <c r="R71" s="44"/>
-      <c r="S71" s="44"/>
-      <c r="T71" s="44"/>
-      <c r="U71" s="44"/>
-      <c r="V71" s="44"/>
-      <c r="W71" s="44"/>
-      <c r="X71" s="44"/>
-      <c r="Y71" s="44"/>
-      <c r="Z71" s="44"/>
-      <c r="AA71" s="44"/>
-      <c r="AB71" s="44"/>
-      <c r="AC71" s="44"/>
-      <c r="AD71" s="17"/>
-      <c r="AE71" s="44"/>
-      <c r="AF71" s="44"/>
-      <c r="AG71" s="44"/>
+      <c r="S71" s="44">
+        <v>1</v>
+      </c>
+      <c r="T71" s="44">
+        <v>3.23</v>
+      </c>
+      <c r="U71" s="44">
+        <v>1.39</v>
+      </c>
+      <c r="V71" s="44">
+        <v>7.266</v>
+      </c>
+      <c r="W71" s="44">
+        <v>127.3</v>
+      </c>
+      <c r="X71" s="44">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="Y71" s="44">
+        <v>1.48</v>
+      </c>
+      <c r="Z71" s="44">
+        <v>178.2</v>
+      </c>
+      <c r="AA71" s="44">
+        <v>56.4</v>
+      </c>
+      <c r="AB71" s="44">
+        <v>111.7</v>
+      </c>
+      <c r="AC71" s="44">
+        <v>16.3</v>
+      </c>
+      <c r="AD71" s="17">
+        <v>7.3070000000000004</v>
+      </c>
+      <c r="AE71" s="44">
+        <v>298</v>
+      </c>
+      <c r="AF71" s="44">
+        <v>50</v>
+      </c>
+      <c r="AG71" s="44">
+        <v>7.27</v>
+      </c>
       <c r="AH71" s="45">
         <f t="shared" si="91"/>
-        <v>0</v>
-      </c>
-      <c r="AI71" s="44"/>
-      <c r="AJ71" s="44"/>
-      <c r="AK71" s="44"/>
-      <c r="AL71" s="44"/>
+        <v>0.5</v>
+      </c>
+      <c r="AI71" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ71" s="44">
+        <v>38.049999999999997</v>
+      </c>
+      <c r="AK71" s="44">
+        <v>5.17</v>
+      </c>
+      <c r="AL71" s="44">
+        <f>AL53+3.04</f>
+        <v>9.6999999999999993</v>
+      </c>
       <c r="AM71" s="45">
         <f t="shared" si="92"/>
-        <v>0</v>
-      </c>
-      <c r="AN71" s="44"/>
-      <c r="AO71" s="44"/>
-      <c r="AP71" s="44"/>
-      <c r="AQ71" s="44"/>
+        <v>3.24883333333333E-2</v>
+      </c>
+      <c r="AN71" s="44">
+        <v>287.8</v>
+      </c>
+      <c r="AO71" s="44">
+        <v>88.58</v>
+      </c>
+      <c r="AP71" s="44">
+        <v>338</v>
+      </c>
+      <c r="AQ71" s="44">
+        <v>1970</v>
+      </c>
       <c r="AR71" s="45">
         <v>84.700000000000045</v>
       </c>
       <c r="AS71" s="45">
-        <f t="shared" si="82"/>
-        <v>-84.700000000000045</v>
+        <f t="shared" si="90"/>
+        <v>1885.3</v>
       </c>
       <c r="AT71" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>38.360000000000014</v>
       </c>
       <c r="AU71" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>3.8199999999999932</v>
       </c>
       <c r="AV71" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AW71" s="25">
         <v>15</v>
@@ -16653,42 +17341,47 @@
         <v>2.9999999999999997E-4</v>
       </c>
       <c r="BC71" s="11"/>
-      <c r="BD71" s="46"/>
-      <c r="BE71" s="22"/>
+      <c r="BD71" s="46">
+        <f>BM71*24*60/BH71</f>
+        <v>2.3999999999999973E-2</v>
+      </c>
+      <c r="BE71" s="22">
+        <f>BP71/BH71</f>
+        <v>5.1005554585699941E-3</v>
+      </c>
       <c r="BF71" s="11">
+        <f t="shared" si="82"/>
+        <v>9.6490350000000003E-3</v>
+      </c>
+      <c r="BG71" s="46">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="BG71" s="46">
-        <f t="shared" si="84"/>
-        <v>0</v>
+        <v>13.894610400000001</v>
       </c>
       <c r="BH71" s="46">
         <f t="shared" si="41"/>
-        <v>1520</v>
-      </c>
-      <c r="BI71" s="47" t="str">
+        <v>1949.3000000000002</v>
+      </c>
+      <c r="BI71" s="47">
+        <f t="shared" si="87"/>
+        <v>0.14764274354896628</v>
+      </c>
+      <c r="BJ71" s="47">
         <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ71" s="47" t="str">
+        <v>0.16929411764705882</v>
+      </c>
+      <c r="BK71" s="47">
+        <f t="shared" si="84"/>
+        <v>46.783199999999951</v>
+      </c>
+      <c r="BL71" s="47" t="str">
         <f t="shared" si="89"/>
         <v/>
       </c>
-      <c r="BK71" s="47">
+      <c r="BM71" s="47">
+        <v>3.24883333333333E-2</v>
+      </c>
+      <c r="BN71" s="48" t="str">
         <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-      <c r="BL71" s="47" t="str">
-        <f t="shared" si="90"/>
-        <v/>
-      </c>
-      <c r="BM71" s="47">
-        <f t="shared" ref="BM71:BM80" si="96">IF(B71="Julia",BD71*BH71/24/60,"")</f>
-        <v>0</v>
-      </c>
-      <c r="BN71" s="48" t="str">
-        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="BO71" s="47" t="str">
@@ -16696,20 +17389,19 @@
         <v/>
       </c>
       <c r="BP71" s="51">
+        <v>9.9425127553904904</v>
+      </c>
+      <c r="BQ71" s="28">
         <f t="shared" si="93"/>
-        <v>0</v>
-      </c>
-      <c r="BQ71" s="28">
+        <v>84.385281385281303</v>
+      </c>
+      <c r="BR71" s="49">
         <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="BR71" s="49">
-        <f t="shared" si="95"/>
-        <v>0</v>
+        <v>3.24883333333333E-2</v>
       </c>
       <c r="BS71" s="30">
-        <f t="shared" si="87"/>
-        <v>0</v>
+        <f t="shared" si="86"/>
+        <v>9.9425127553904904</v>
       </c>
     </row>
     <row r="72" spans="1:71" x14ac:dyDescent="0.3">
@@ -16725,70 +17417,137 @@
       <c r="D72">
         <v>11</v>
       </c>
-      <c r="F72" s="61"/>
+      <c r="F72" s="61">
+        <v>45544.610312500001</v>
+      </c>
       <c r="G72" s="64">
         <v>6057.48</v>
       </c>
       <c r="H72" s="44"/>
-      <c r="I72" s="44"/>
-      <c r="J72" s="44"/>
-      <c r="K72" s="44"/>
-      <c r="L72" s="44"/>
-      <c r="M72" s="44"/>
-      <c r="N72" s="44"/>
-      <c r="O72" s="44"/>
-      <c r="P72" s="44"/>
-      <c r="Q72" s="44"/>
+      <c r="I72" s="44">
+        <v>5403.24</v>
+      </c>
+      <c r="J72" s="44">
+        <v>19.5</v>
+      </c>
+      <c r="K72" s="44">
+        <v>17.2</v>
+      </c>
+      <c r="L72" s="44">
+        <v>88</v>
+      </c>
+      <c r="M72" s="44">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="N72" s="44">
+        <v>437</v>
+      </c>
+      <c r="O72" s="44">
+        <v>2.12</v>
+      </c>
+      <c r="P72" s="44">
+        <v>0.2</v>
+      </c>
+      <c r="Q72" s="44">
+        <v>0.77</v>
+      </c>
       <c r="R72" s="44"/>
-      <c r="S72" s="44"/>
-      <c r="T72" s="44"/>
-      <c r="U72" s="44"/>
-      <c r="V72" s="44"/>
-      <c r="W72" s="44"/>
-      <c r="X72" s="44"/>
-      <c r="Y72" s="44"/>
-      <c r="Z72" s="44"/>
-      <c r="AA72" s="44"/>
-      <c r="AB72" s="44"/>
-      <c r="AC72" s="44"/>
-      <c r="AD72" s="17"/>
-      <c r="AE72" s="44"/>
-      <c r="AF72" s="44"/>
-      <c r="AG72" s="44"/>
+      <c r="S72" s="44">
+        <v>0.83</v>
+      </c>
+      <c r="T72" s="44">
+        <v>2.97</v>
+      </c>
+      <c r="U72" s="44">
+        <v>2.21</v>
+      </c>
+      <c r="V72" s="44">
+        <v>7.2830000000000004</v>
+      </c>
+      <c r="W72" s="44">
+        <v>125.9</v>
+      </c>
+      <c r="X72" s="44">
+        <v>102.1</v>
+      </c>
+      <c r="Y72" s="44">
+        <v>1.45</v>
+      </c>
+      <c r="Z72" s="44">
+        <v>182.7</v>
+      </c>
+      <c r="AA72" s="44">
+        <v>58</v>
+      </c>
+      <c r="AB72" s="44">
+        <v>110.4</v>
+      </c>
+      <c r="AC72" s="44">
+        <v>85.6</v>
+      </c>
+      <c r="AD72" s="17">
+        <v>7.3239999999999998</v>
+      </c>
+      <c r="AE72" s="44">
+        <v>302</v>
+      </c>
+      <c r="AF72" s="44">
+        <v>100</v>
+      </c>
+      <c r="AG72" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH72" s="45">
         <f t="shared" si="91"/>
-        <v>0</v>
-      </c>
-      <c r="AI72" s="44"/>
-      <c r="AJ72" s="44"/>
-      <c r="AK72" s="44"/>
-      <c r="AL72" s="44"/>
+        <v>1</v>
+      </c>
+      <c r="AI72" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ72" s="44">
+        <v>43.09</v>
+      </c>
+      <c r="AK72" s="44">
+        <v>17.54</v>
+      </c>
+      <c r="AL72" s="44">
+        <f>AL54+3.1</f>
+        <v>9.86</v>
+      </c>
       <c r="AM72" s="45">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="AN72" s="44"/>
-      <c r="AO72" s="44"/>
-      <c r="AP72" s="44"/>
-      <c r="AQ72" s="44"/>
+      <c r="AN72" s="44">
+        <v>273.05</v>
+      </c>
+      <c r="AO72" s="44">
+        <v>79.709999999999994</v>
+      </c>
+      <c r="AP72" s="44">
+        <v>362</v>
+      </c>
+      <c r="AQ72" s="44">
+        <v>1953</v>
+      </c>
       <c r="AR72" s="45">
         <v>47.420000000000073</v>
       </c>
       <c r="AS72" s="45">
-        <f t="shared" si="82"/>
-        <v>-47.420000000000073</v>
+        <f t="shared" si="90"/>
+        <v>1905.58</v>
       </c>
       <c r="AT72" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>39.120000000000005</v>
       </c>
       <c r="AU72" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>8.8399999999999892</v>
       </c>
       <c r="AV72" s="45">
         <f t="shared" si="65"/>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AW72" s="25">
         <v>15</v>
@@ -16811,60 +17570,60 @@
       <c r="BC72" s="11"/>
       <c r="BE72" s="22"/>
       <c r="BF72" s="11">
+        <f t="shared" si="82"/>
+        <v>1.002717E-2</v>
+      </c>
+      <c r="BG72" s="46">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="BG72" s="46">
+        <v>14.4391248</v>
+      </c>
+      <c r="BH72" s="46">
+        <f t="shared" ref="BH72:BH80" si="95">AX72+SUM(AJ72:AL72,AN72:AO72)-(AW72*(D72+1))</f>
+        <v>1943.25</v>
+      </c>
+      <c r="BI72" s="47">
+        <f t="shared" si="87"/>
+        <v>0.14051202881770231</v>
+      </c>
+      <c r="BJ72" s="47">
+        <f t="shared" si="88"/>
+        <v>0.16061764705882353</v>
+      </c>
+      <c r="BK72" s="47">
         <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="BH72" s="46">
-        <f t="shared" ref="BH72:BH80" si="97">AX72+SUM(AJ72:AL72,AN72:AO72)-(AW72*(D72+1))</f>
-        <v>1520</v>
-      </c>
-      <c r="BI72" s="47" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ72" s="47" t="str">
+      <c r="BL72" s="47">
         <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BK72" s="47">
+        <v>0</v>
+      </c>
+      <c r="BM72" s="48" t="str">
+        <f t="shared" ref="BM71:BM80" si="96">IF(B72="Julia",BD72*BH72/24/60,"")</f>
+        <v/>
+      </c>
+      <c r="BN72" s="48" t="str">
         <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-      <c r="BL72" s="47">
-        <f t="shared" si="90"/>
-        <v>0</v>
-      </c>
-      <c r="BM72" s="48" t="str">
-        <f t="shared" si="96"/>
-        <v/>
-      </c>
-      <c r="BN72" s="48" t="str">
-        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="BO72" s="47">
         <f t="shared" si="47"/>
-        <v>11.4</v>
+        <v>10.833618750000001</v>
       </c>
       <c r="BP72" s="51" t="str">
+        <f t="shared" ref="BP70:BP80" si="97">IF(B72="Julia",BE72*BH72,"")</f>
+        <v/>
+      </c>
+      <c r="BQ72" s="28">
         <f t="shared" si="93"/>
-        <v/>
-      </c>
-      <c r="BQ72" s="28">
+        <v>0</v>
+      </c>
+      <c r="BR72" s="49">
         <f t="shared" si="94"/>
         <v>0</v>
       </c>
-      <c r="BR72" s="49">
-        <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
       <c r="BS72" s="30">
-        <f t="shared" si="87"/>
-        <v>11.4</v>
+        <f t="shared" si="86"/>
+        <v>10.833618750000001</v>
       </c>
     </row>
     <row r="73" spans="1:71" x14ac:dyDescent="0.3">
@@ -16880,70 +17639,133 @@
       <c r="D73">
         <v>11</v>
       </c>
-      <c r="F73" s="61"/>
+      <c r="F73" s="61">
+        <v>45544.616192129601</v>
+      </c>
       <c r="G73" s="64">
         <v>6057.48</v>
       </c>
       <c r="H73" s="44"/>
-      <c r="I73" s="44"/>
-      <c r="J73" s="44"/>
-      <c r="K73" s="44"/>
-      <c r="L73" s="44"/>
-      <c r="M73" s="44"/>
-      <c r="N73" s="44"/>
+      <c r="I73" s="44">
+        <v>2556.4050000000002</v>
+      </c>
+      <c r="J73" s="44">
+        <v>20.2</v>
+      </c>
+      <c r="K73" s="44">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="L73" s="44">
+        <v>2.71</v>
+      </c>
+      <c r="M73" s="44">
+        <v>13.7</v>
+      </c>
+      <c r="N73" s="44">
+        <v>869</v>
+      </c>
       <c r="O73" s="44"/>
-      <c r="P73" s="44"/>
-      <c r="Q73" s="44"/>
+      <c r="P73" s="44">
+        <v>0.23</v>
+      </c>
+      <c r="Q73" s="44">
+        <v>6.87</v>
+      </c>
       <c r="R73" s="44"/>
-      <c r="S73" s="44"/>
-      <c r="T73" s="44"/>
+      <c r="S73" s="44">
+        <v>0.97</v>
+      </c>
+      <c r="T73" s="44">
+        <v>4.58</v>
+      </c>
       <c r="U73" s="44"/>
-      <c r="V73" s="44"/>
-      <c r="W73" s="44"/>
-      <c r="X73" s="44"/>
-      <c r="Y73" s="44"/>
-      <c r="Z73" s="44"/>
-      <c r="AA73" s="44"/>
-      <c r="AB73" s="44"/>
-      <c r="AC73" s="44"/>
-      <c r="AD73" s="17"/>
-      <c r="AE73" s="44"/>
-      <c r="AF73" s="44"/>
-      <c r="AG73" s="44"/>
+      <c r="V73" s="44">
+        <v>7.2770000000000001</v>
+      </c>
+      <c r="W73" s="44">
+        <v>5.8</v>
+      </c>
+      <c r="X73" s="44">
+        <v>95.2</v>
+      </c>
+      <c r="Y73" s="44">
+        <v>7.36</v>
+      </c>
+      <c r="Z73" s="44">
+        <v>318.8</v>
+      </c>
+      <c r="AA73" s="44">
+        <v>2.6</v>
+      </c>
+      <c r="AB73" s="44">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AC73" s="44">
+        <v>79.2</v>
+      </c>
+      <c r="AD73" s="17">
+        <v>7.3179999999999996</v>
+      </c>
+      <c r="AE73" s="44">
+        <v>299</v>
+      </c>
+      <c r="AF73" s="44">
+        <v>52.4</v>
+      </c>
+      <c r="AG73" s="44">
+        <v>7.3</v>
+      </c>
       <c r="AH73" s="45">
         <f t="shared" si="91"/>
-        <v>0</v>
-      </c>
-      <c r="AI73" s="44"/>
-      <c r="AJ73" s="44"/>
-      <c r="AK73" s="44"/>
-      <c r="AL73" s="44"/>
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="AI73" s="44">
+        <v>34</v>
+      </c>
+      <c r="AJ73" s="44">
+        <v>150</v>
+      </c>
+      <c r="AK73" s="44">
+        <v>9.64</v>
+      </c>
+      <c r="AL73" s="44">
+        <f>AL55+2.98</f>
+        <v>9.42</v>
+      </c>
       <c r="AM73" s="45">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="AN73" s="44"/>
-      <c r="AO73" s="44"/>
-      <c r="AP73" s="44"/>
-      <c r="AQ73" s="44"/>
+      <c r="AN73" s="44">
+        <v>310.07</v>
+      </c>
+      <c r="AO73" s="44">
+        <v>94.46</v>
+      </c>
+      <c r="AP73" s="44">
+        <v>295</v>
+      </c>
+      <c r="AQ73" s="44">
+        <v>2159</v>
+      </c>
       <c r="AR73" s="45">
         <v>133.55999999999995</v>
       </c>
       <c r="AS73" s="45">
-        <f t="shared" si="82"/>
-        <v>-133.55999999999995</v>
+        <f t="shared" si="90"/>
+        <v>2025.44</v>
       </c>
       <c r="AT73" s="45">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>48.389999999999986</v>
       </c>
       <c r="AU73" s="45">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>16.64</v>
       </c>
       <c r="AV73" s="45">
         <f t="shared" ref="AV73:AV80" si="98">AP67-AP73</f>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AW73" s="25">
         <v>15</v>
@@ -16966,31 +17788,31 @@
       <c r="BC73" s="11"/>
       <c r="BE73" s="22"/>
       <c r="BF73" s="11">
+        <f t="shared" si="82"/>
+        <v>3.4355811900000006E-4</v>
+      </c>
+      <c r="BG73" s="46">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="BG73" s="46">
+        <v>0.49472369136000011</v>
+      </c>
+      <c r="BH73" s="46">
+        <f t="shared" si="95"/>
+        <v>2093.59</v>
+      </c>
+      <c r="BI73" s="47">
+        <f t="shared" si="87"/>
+        <v>0.14810445216112036</v>
+      </c>
+      <c r="BJ73" s="47">
+        <f t="shared" si="88"/>
+        <v>0.18239411764705882</v>
+      </c>
+      <c r="BK73" s="47">
         <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="BH73" s="46">
-        <f t="shared" si="97"/>
-        <v>1520</v>
-      </c>
-      <c r="BI73" s="47" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ73" s="47" t="str">
+      <c r="BL73" s="47">
         <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BK73" s="47">
-        <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-      <c r="BL73" s="47">
-        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="BM73" s="48" t="str">
@@ -16998,28 +17820,28 @@
         <v/>
       </c>
       <c r="BN73" s="48" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v/>
       </c>
       <c r="BO73" s="47">
         <f t="shared" si="47"/>
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="BP73" s="51" t="str">
+        <f t="shared" si="97"/>
+        <v/>
+      </c>
+      <c r="BQ73" s="28">
         <f t="shared" si="93"/>
-        <v/>
-      </c>
-      <c r="BQ73" s="28">
+        <v>0</v>
+      </c>
+      <c r="BR73" s="49">
         <f t="shared" si="94"/>
         <v>0</v>
       </c>
-      <c r="BR73" s="49">
-        <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
       <c r="BS73" s="30">
-        <f t="shared" si="87"/>
-        <v>11.4</v>
+        <f t="shared" si="86"/>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:71" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -17036,70 +17858,137 @@
         <v>11</v>
       </c>
       <c r="E74" s="5"/>
-      <c r="F74" s="62"/>
+      <c r="F74" s="62">
+        <v>45544.621018518519</v>
+      </c>
       <c r="G74" s="65">
         <v>6057.48</v>
       </c>
       <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
-      <c r="P74" s="7"/>
-      <c r="Q74" s="7"/>
+      <c r="I74" s="7">
+        <v>6130.83</v>
+      </c>
+      <c r="J74" s="7">
+        <v>19.8</v>
+      </c>
+      <c r="K74" s="7">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="L74" s="7">
+        <v>90.2</v>
+      </c>
+      <c r="M74" s="7">
+        <v>17.8</v>
+      </c>
+      <c r="N74" s="7">
+        <v>359</v>
+      </c>
+      <c r="O74" s="7">
+        <v>1.91</v>
+      </c>
+      <c r="P74" s="7">
+        <v>0.18</v>
+      </c>
+      <c r="Q74" s="7">
+        <v>0.4</v>
+      </c>
       <c r="R74" s="7"/>
-      <c r="S74" s="7"/>
-      <c r="T74" s="7"/>
-      <c r="U74" s="7"/>
-      <c r="V74" s="7"/>
-      <c r="W74" s="7"/>
-      <c r="X74" s="7"/>
-      <c r="Y74" s="7"/>
-      <c r="Z74" s="7"/>
-      <c r="AA74" s="7"/>
-      <c r="AB74" s="7"/>
-      <c r="AC74" s="7"/>
-      <c r="AD74" s="18"/>
-      <c r="AE74" s="7"/>
-      <c r="AF74" s="7"/>
-      <c r="AG74" s="7"/>
+      <c r="S74" s="7">
+        <v>0.09</v>
+      </c>
+      <c r="T74" s="7">
+        <v>0.13</v>
+      </c>
+      <c r="U74" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="V74" s="7">
+        <v>7.2969999999999997</v>
+      </c>
+      <c r="W74" s="7">
+        <v>117.9</v>
+      </c>
+      <c r="X74" s="7">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="Y74" s="7">
+        <v>1.92</v>
+      </c>
+      <c r="Z74" s="7">
+        <v>159.1</v>
+      </c>
+      <c r="AA74" s="7">
+        <v>56.2</v>
+      </c>
+      <c r="AB74" s="7">
+        <v>103.4</v>
+      </c>
+      <c r="AC74" s="7">
+        <v>32.9</v>
+      </c>
+      <c r="AD74" s="18">
+        <v>7.3390000000000004</v>
+      </c>
+      <c r="AE74" s="7">
+        <v>298</v>
+      </c>
+      <c r="AF74" s="7">
+        <v>49.9</v>
+      </c>
+      <c r="AG74" s="7">
+        <v>7.29</v>
+      </c>
       <c r="AH74" s="41">
         <f t="shared" si="91"/>
-        <v>0</v>
-      </c>
-      <c r="AI74" s="7"/>
-      <c r="AJ74" s="7"/>
-      <c r="AK74" s="7"/>
-      <c r="AL74" s="7"/>
+        <v>0.499</v>
+      </c>
+      <c r="AI74" s="7">
+        <v>34</v>
+      </c>
+      <c r="AJ74" s="7">
+        <v>28.27</v>
+      </c>
+      <c r="AK74" s="7">
+        <v>45.05</v>
+      </c>
+      <c r="AL74" s="7">
+        <f>AL56+3.03</f>
+        <v>9.5499999999999989</v>
+      </c>
       <c r="AM74" s="41">
         <f t="shared" si="92"/>
         <v>0</v>
       </c>
-      <c r="AN74" s="7"/>
-      <c r="AO74" s="7"/>
-      <c r="AP74" s="7"/>
-      <c r="AQ74" s="7"/>
+      <c r="AN74" s="7">
+        <v>220.19</v>
+      </c>
+      <c r="AO74" s="7">
+        <v>82.22</v>
+      </c>
+      <c r="AP74" s="7">
+        <v>438</v>
+      </c>
+      <c r="AQ74" s="7">
+        <v>1899</v>
+      </c>
       <c r="AR74" s="41">
         <v>51.660000000000082</v>
       </c>
       <c r="AS74" s="41">
-        <f t="shared" si="82"/>
-        <v>-51.660000000000082</v>
+        <f t="shared" si="90"/>
+        <v>1847.34</v>
       </c>
       <c r="AT74" s="41">
         <f t="shared" ref="AT74:AT80" si="99">AN74-AN68</f>
-        <v>0</v>
+        <v>18.259999999999991</v>
       </c>
       <c r="AU74" s="41">
         <f t="shared" ref="AU74:AU80" si="100">AO74-AO68</f>
-        <v>0</v>
+        <v>12.469999999999999</v>
       </c>
       <c r="AV74" s="41">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AW74" s="26">
         <v>15</v>
@@ -17123,31 +18012,31 @@
       <c r="BD74" s="5"/>
       <c r="BE74" s="23"/>
       <c r="BF74" s="12">
+        <f t="shared" si="82"/>
+        <v>1.0231353599999996E-2</v>
+      </c>
+      <c r="BG74" s="13">
         <f t="shared" si="83"/>
-        <v>0</v>
-      </c>
-      <c r="BG74" s="13">
+        <v>14.733149183999995</v>
+      </c>
+      <c r="BH74" s="13">
+        <f t="shared" si="95"/>
+        <v>1905.2799999999997</v>
+      </c>
+      <c r="BI74" s="14">
+        <f t="shared" si="87"/>
+        <v>0.11556831541820627</v>
+      </c>
+      <c r="BJ74" s="14">
+        <f t="shared" si="88"/>
+        <v>0.1295235294117647</v>
+      </c>
+      <c r="BK74" s="14">
         <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="BH74" s="13">
-        <f t="shared" si="97"/>
-        <v>1520</v>
-      </c>
-      <c r="BI74" s="14" t="str">
-        <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ74" s="14" t="str">
+      <c r="BL74" s="14">
         <f t="shared" si="89"/>
-        <v/>
-      </c>
-      <c r="BK74" s="14">
-        <f t="shared" si="85"/>
-        <v>0</v>
-      </c>
-      <c r="BL74" s="14">
-        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="BM74" s="48" t="str">
@@ -17155,28 +18044,28 @@
         <v/>
       </c>
       <c r="BN74" s="36" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v/>
       </c>
       <c r="BO74" s="14">
         <f t="shared" si="47"/>
-        <v>11.4</v>
+        <v>12.384319999999997</v>
       </c>
       <c r="BP74" s="52" t="str">
+        <f t="shared" si="97"/>
+        <v/>
+      </c>
+      <c r="BQ74" s="29">
         <f t="shared" si="93"/>
-        <v/>
-      </c>
-      <c r="BQ74" s="29">
+        <v>0</v>
+      </c>
+      <c r="BR74" s="38">
         <f t="shared" si="94"/>
         <v>0</v>
       </c>
-      <c r="BR74" s="38">
-        <f t="shared" si="95"/>
-        <v>0</v>
-      </c>
       <c r="BS74" s="31">
-        <f t="shared" si="87"/>
-        <v>11.4</v>
+        <f t="shared" si="86"/>
+        <v>12.384319999999997</v>
       </c>
     </row>
     <row r="75" spans="1:71" x14ac:dyDescent="0.3">
@@ -17243,20 +18132,20 @@
         <v>137.11999999999989</v>
       </c>
       <c r="AS75" s="40">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>-137.11999999999989</v>
       </c>
       <c r="AT75" s="40">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>-181.29</v>
       </c>
       <c r="AU75" s="40">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>-73.31</v>
       </c>
       <c r="AV75" s="40">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="AW75" s="24">
         <v>15</v>
@@ -17288,15 +18177,15 @@
         <v>0</v>
       </c>
       <c r="BH75" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="95"/>
         <v>1505</v>
       </c>
       <c r="BI75" s="10" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ75" s="10" t="str">
         <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ75" s="10" t="str">
-        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BK75" s="10">
@@ -17304,7 +18193,7 @@
         <v>0</v>
       </c>
       <c r="BL75" s="10" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BM75" s="10">
@@ -17320,7 +18209,7 @@
         <v/>
       </c>
       <c r="BP75" s="50">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="BQ75" s="27">
@@ -17399,20 +18288,20 @@
         <v>45.769999999999982</v>
       </c>
       <c r="AS76" s="45">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>-45.769999999999982</v>
       </c>
       <c r="AT76" s="45">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>-205.53</v>
       </c>
       <c r="AU76" s="45">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>-79.069999999999993</v>
       </c>
       <c r="AV76" s="45">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>458</v>
       </c>
       <c r="AW76" s="25">
         <v>15</v>
@@ -17444,15 +18333,15 @@
         <v>0</v>
       </c>
       <c r="BH76" s="46">
-        <f t="shared" si="97"/>
+        <f t="shared" si="95"/>
         <v>1505</v>
       </c>
       <c r="BI76" s="47" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ76" s="47" t="str">
         <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ76" s="47" t="str">
-        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BK76" s="47">
@@ -17460,7 +18349,7 @@
         <v>0</v>
       </c>
       <c r="BL76" s="47" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BM76" s="47">
@@ -17476,7 +18365,7 @@
         <v/>
       </c>
       <c r="BP76" s="51">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="BQ76" s="28">
@@ -17555,20 +18444,20 @@
         <v>84.700000000000045</v>
       </c>
       <c r="AS77" s="45">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>-84.700000000000045</v>
       </c>
       <c r="AT77" s="45">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>-287.8</v>
       </c>
       <c r="AU77" s="45">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>-88.58</v>
       </c>
       <c r="AV77" s="45">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="AW77" s="25">
         <v>15</v>
@@ -17600,15 +18489,15 @@
         <v>0</v>
       </c>
       <c r="BH77" s="46">
-        <f t="shared" si="97"/>
+        <f t="shared" si="95"/>
         <v>1505</v>
       </c>
       <c r="BI77" s="47" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ77" s="47" t="str">
         <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ77" s="47" t="str">
-        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BK77" s="47">
@@ -17616,7 +18505,7 @@
         <v>0</v>
       </c>
       <c r="BL77" s="47" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BM77" s="47">
@@ -17632,7 +18521,7 @@
         <v/>
       </c>
       <c r="BP77" s="51">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="BQ77" s="28">
@@ -17711,20 +18600,20 @@
         <v>47.420000000000073</v>
       </c>
       <c r="AS78" s="45">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>-47.420000000000073</v>
       </c>
       <c r="AT78" s="45">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>-273.05</v>
       </c>
       <c r="AU78" s="45">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>-79.709999999999994</v>
       </c>
       <c r="AV78" s="45">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>362</v>
       </c>
       <c r="AW78" s="25">
         <v>15</v>
@@ -17755,15 +18644,15 @@
         <v>0</v>
       </c>
       <c r="BH78" s="46">
-        <f t="shared" si="97"/>
+        <f t="shared" si="95"/>
         <v>1505</v>
       </c>
       <c r="BI78" s="47" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ78" s="47" t="str">
         <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ78" s="47" t="str">
-        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BK78" s="47">
@@ -17771,7 +18660,7 @@
         <v>0</v>
       </c>
       <c r="BL78" s="47">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="BM78" s="48" t="str">
@@ -17787,7 +18676,7 @@
         <v>11.2875</v>
       </c>
       <c r="BP78" s="51" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v/>
       </c>
       <c r="BQ78" s="28">
@@ -17866,20 +18755,20 @@
         <v>133.55999999999995</v>
       </c>
       <c r="AS79" s="45">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>-133.55999999999995</v>
       </c>
       <c r="AT79" s="45">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>-310.07</v>
       </c>
       <c r="AU79" s="45">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>-94.46</v>
       </c>
       <c r="AV79" s="45">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="AW79" s="25">
         <v>15</v>
@@ -17910,15 +18799,15 @@
         <v>0</v>
       </c>
       <c r="BH79" s="46">
-        <f t="shared" si="97"/>
+        <f t="shared" si="95"/>
         <v>1505</v>
       </c>
       <c r="BI79" s="47" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ79" s="47" t="str">
         <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ79" s="47" t="str">
-        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BK79" s="47">
@@ -17926,7 +18815,7 @@
         <v>0</v>
       </c>
       <c r="BL79" s="47">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="BM79" s="48" t="str">
@@ -17942,7 +18831,7 @@
         <v>11.2875</v>
       </c>
       <c r="BP79" s="51" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v/>
       </c>
       <c r="BQ79" s="28">
@@ -18022,20 +18911,20 @@
         <v>51.660000000000082</v>
       </c>
       <c r="AS80" s="41">
-        <f t="shared" si="82"/>
+        <f t="shared" si="90"/>
         <v>-51.660000000000082</v>
       </c>
       <c r="AT80" s="41">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>-220.19</v>
       </c>
       <c r="AU80" s="41">
         <f t="shared" si="100"/>
-        <v>0</v>
+        <v>-82.22</v>
       </c>
       <c r="AV80" s="41">
         <f t="shared" si="98"/>
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="AW80" s="26">
         <v>15</v>
@@ -18067,15 +18956,15 @@
         <v>0</v>
       </c>
       <c r="BH80" s="13">
-        <f t="shared" si="97"/>
+        <f t="shared" si="95"/>
         <v>1505</v>
       </c>
       <c r="BI80" s="14" t="str">
+        <f t="shared" si="87"/>
+        <v/>
+      </c>
+      <c r="BJ80" s="14" t="str">
         <f t="shared" si="88"/>
-        <v/>
-      </c>
-      <c r="BJ80" s="14" t="str">
-        <f t="shared" si="89"/>
         <v/>
       </c>
       <c r="BK80" s="14">
@@ -18083,7 +18972,7 @@
         <v>0</v>
       </c>
       <c r="BL80" s="14">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="BM80" s="36" t="str">
@@ -18099,7 +18988,7 @@
         <v>11.2875</v>
       </c>
       <c r="BP80" s="52" t="str">
-        <f t="shared" si="93"/>
+        <f t="shared" si="97"/>
         <v/>
       </c>
       <c r="BQ80" s="29">
@@ -18165,6 +19054,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B75172DAFC2BB6479729CB287362C7E3" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0fc11b0946794a47057850b4f6c92dd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="34d8c884-fe7e-4d4f-a833-b92a2823f74b" xmlns:ns3="a198008e-c7f6-4ed0-9865-26ace3c97b59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb90ec7fe59ed1d44226abab88cd233b" ns2:_="" ns3:_="">
     <xsd:import namespace="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
@@ -18387,34 +19303,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="34d8c884-fe7e-4d4f-a833-b92a2823f74b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="a198008e-c7f6-4ed0-9865-26ace3c97b59">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F43DC28-AE43-4EFF-8739-4E0C557B415B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18431,29 +19345,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81736866-79EE-4C47-B374-7C3565856A36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="34d8c884-fe7e-4d4f-a833-b92a2823f74b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a198008e-c7f6-4ed0-9865-26ace3c97b59"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA2C79D-5C43-4F8C-8CB2-6CBFC4591548}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>